--- a/PV_ICE/baselines/SupportingMaterial/Manual Files/BaselineGraphs.xlsx
+++ b/PV_ICE/baselines/SupportingMaterial/Manual Files/BaselineGraphs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25028"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hmirletz\Documents\GitHub\PV_ICE\PV_ICE\baselines\SupportingMaterial\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hmirletz\Documents\GitHub\PV_ICE\PV_ICE\baselines\SupportingMaterial\Manual Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5BA104A-C648-4039-9CC4-A304B7711A21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A77E539-5F2C-4B89-87CA-73FC844C1CA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-2865" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{31D47E9D-A833-4D35-B79A-EFF0E4DE6D01}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{31D47E9D-A833-4D35-B79A-EFF0E4DE6D01}"/>
   </bookViews>
   <sheets>
     <sheet name="mass per m2" sheetId="1" r:id="rId1"/>
@@ -235,16 +235,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -955,6 +949,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -962,7 +957,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3964,6 +3958,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3971,7 +3966,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -6975,6 +6969,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -6982,7 +6977,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -7604,6 +7598,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -7611,7 +7606,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -8561,6 +8555,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -8568,7 +8563,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -9518,6 +9512,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -9525,7 +9520,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -11346,6 +11340,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -11353,7 +11348,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -13125,6 +13119,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -13132,7 +13127,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -15125,6 +15119,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -15132,7 +15127,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -16250,6 +16244,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -16257,7 +16252,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -17373,6 +17367,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -17380,7 +17375,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -18398,6 +18392,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -18405,7 +18400,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -19023,6 +19017,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -19030,7 +19025,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -20552,6 +20546,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -20559,7 +20554,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -22689,6 +22683,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -22696,7 +22691,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -23128,6 +23122,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -23135,7 +23130,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -28353,6 +28347,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -28360,7 +28355,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -38495,9 +38489,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -38535,7 +38529,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -38641,7 +38635,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -38783,7 +38777,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -38803,55 +38797,55 @@
     <col min="8" max="8" width="10.08984375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11.81640625" customWidth="1"/>
     <col min="10" max="10" width="7.6328125" customWidth="1"/>
-    <col min="11" max="11" width="2.453125" style="8" customWidth="1"/>
+    <col min="11" max="11" width="2.453125" style="6" customWidth="1"/>
     <col min="12" max="13" width="8.26953125" customWidth="1"/>
     <col min="14" max="20" width="11.81640625" customWidth="1"/>
-    <col min="21" max="21" width="2.26953125" style="8" customWidth="1"/>
+    <col min="21" max="21" width="2.26953125" style="6" customWidth="1"/>
     <col min="34" max="34" width="11.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
       <c r="I1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="J1" s="3"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="6" t="s">
+      <c r="J1" s="2"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="4"/>
-      <c r="Q1" s="4"/>
-      <c r="R1" s="4"/>
-      <c r="S1" s="4"/>
-      <c r="T1" s="4"/>
-      <c r="U1" s="7"/>
-      <c r="V1" s="10" t="s">
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+      <c r="T1" s="2"/>
+      <c r="U1" s="5"/>
+      <c r="V1" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="W1" s="10"/>
-      <c r="X1" s="10"/>
-      <c r="Y1" s="10"/>
-      <c r="Z1" s="10"/>
+      <c r="W1" s="8"/>
+      <c r="X1" s="8"/>
+      <c r="Y1" s="8"/>
+      <c r="Z1" s="8"/>
       <c r="AA1" s="2"/>
       <c r="AB1" s="2"/>
       <c r="AC1" s="2"/>
-      <c r="AD1" s="10" t="s">
+      <c r="AD1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="AE1" s="10"/>
-      <c r="AF1" s="10"/>
-      <c r="AG1" s="10"/>
-      <c r="AH1" s="10"/>
+      <c r="AE1" s="8"/>
+      <c r="AF1" s="8"/>
+      <c r="AG1" s="8"/>
+      <c r="AH1" s="8"/>
       <c r="AI1" s="1" t="s">
         <v>18</v>
       </c>
@@ -39108,47 +39102,47 @@
       <c r="H18">
         <v>532</v>
       </c>
-      <c r="I18" s="5">
+      <c r="I18" s="3">
         <f>SUM(B18:H18)</f>
         <v>13410.982838600001</v>
       </c>
-      <c r="J18" s="5">
+      <c r="J18" s="3">
         <f>AD18*1000/100</f>
         <v>125</v>
       </c>
-      <c r="K18" s="9"/>
-      <c r="L18" s="5">
+      <c r="K18" s="7"/>
+      <c r="L18" s="3">
         <f>I18/J18</f>
         <v>107.28786270880001</v>
       </c>
-      <c r="M18" s="5">
+      <c r="M18" s="3">
         <v>121.9734352</v>
       </c>
-      <c r="N18" s="5"/>
-      <c r="O18" s="5"/>
-      <c r="P18" s="5"/>
-      <c r="Q18" s="5"/>
-      <c r="R18" s="5"/>
-      <c r="S18" s="5"/>
-      <c r="T18" s="5"/>
-      <c r="U18" s="9"/>
-      <c r="V18" s="5">
+      <c r="N18" s="3"/>
+      <c r="O18" s="3"/>
+      <c r="P18" s="3"/>
+      <c r="Q18" s="3"/>
+      <c r="R18" s="3"/>
+      <c r="S18" s="3"/>
+      <c r="T18" s="3"/>
+      <c r="U18" s="7"/>
+      <c r="V18" s="3">
         <f t="shared" ref="V18:V49" si="0">B18/$I18*100</f>
         <v>59.652600381935436</v>
       </c>
-      <c r="W18" s="5">
+      <c r="W18" s="3">
         <f t="shared" ref="W18:W49" si="1">C18/$I18*100</f>
         <v>6.326318054468322</v>
       </c>
-      <c r="X18" s="5">
+      <c r="X18" s="3">
         <f t="shared" ref="X18:X49" si="2">D18/$I18*100</f>
         <v>23.049655996149905</v>
       </c>
-      <c r="Y18" s="5">
+      <c r="Y18" s="3">
         <f t="shared" ref="Y18:Y49" si="3">E18/$I18*100</f>
         <v>4.0086547456660612E-2</v>
       </c>
-      <c r="Z18" s="5">
+      <c r="Z18" s="3">
         <f t="shared" ref="Z18:Z49" si="4">F18/$I18*100</f>
         <v>0.65617860420128982</v>
       </c>
@@ -39193,47 +39187,47 @@
       <c r="H19">
         <v>532</v>
       </c>
-      <c r="I19" s="5">
+      <c r="I19" s="3">
         <f t="shared" ref="I19:I73" si="5">SUM(B19:H19)</f>
         <v>13317.14968887</v>
       </c>
-      <c r="J19" s="5">
+      <c r="J19" s="3">
         <f t="shared" ref="J19:J73" si="6">AD19*1000/100</f>
         <v>127</v>
       </c>
-      <c r="K19" s="9"/>
-      <c r="L19" s="5">
+      <c r="K19" s="7"/>
+      <c r="L19" s="3">
         <f t="shared" ref="L19:L73" si="7">I19/J19</f>
         <v>104.85944636905512</v>
       </c>
-      <c r="M19" s="5">
+      <c r="M19" s="3">
         <v>119.3832118</v>
       </c>
-      <c r="N19" s="5"/>
-      <c r="O19" s="5"/>
-      <c r="P19" s="5"/>
-      <c r="Q19" s="5"/>
-      <c r="R19" s="5"/>
-      <c r="S19" s="5"/>
-      <c r="T19" s="5"/>
-      <c r="U19" s="9"/>
-      <c r="V19" s="5">
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+      <c r="S19" s="3"/>
+      <c r="T19" s="3"/>
+      <c r="U19" s="7"/>
+      <c r="V19" s="3">
         <f t="shared" si="0"/>
         <v>60.072914902249053</v>
       </c>
-      <c r="W19" s="5">
+      <c r="W19" s="3">
         <f t="shared" si="1"/>
         <v>6.2459740540062931</v>
       </c>
-      <c r="X19" s="5">
+      <c r="X19" s="3">
         <f t="shared" si="2"/>
         <v>22.658125924062034</v>
       </c>
-      <c r="Y19" s="5">
+      <c r="Y19" s="3">
         <f t="shared" si="3"/>
         <v>4.0368998814311365E-2</v>
       </c>
-      <c r="Z19" s="5">
+      <c r="Z19" s="3">
         <f t="shared" si="4"/>
         <v>0.63505652895590559</v>
       </c>
@@ -39278,47 +39272,47 @@
       <c r="H20">
         <v>532</v>
       </c>
-      <c r="I20" s="5">
+      <c r="I20" s="3">
         <f t="shared" si="5"/>
         <v>12979.668857139999</v>
       </c>
-      <c r="J20" s="5">
+      <c r="J20" s="3">
         <f t="shared" si="6"/>
         <v>128.80000000000001</v>
       </c>
-      <c r="K20" s="9"/>
-      <c r="L20" s="5">
+      <c r="K20" s="7"/>
+      <c r="L20" s="3">
         <f t="shared" si="7"/>
         <v>100.77382653059004</v>
       </c>
-      <c r="M20" s="5">
+      <c r="M20" s="3">
         <v>116.8479943</v>
       </c>
-      <c r="N20" s="5"/>
-      <c r="O20" s="5"/>
-      <c r="P20" s="5"/>
-      <c r="Q20" s="5"/>
-      <c r="R20" s="5"/>
-      <c r="S20" s="5"/>
-      <c r="T20" s="5"/>
-      <c r="U20" s="9"/>
-      <c r="V20" s="5">
+      <c r="N20" s="3"/>
+      <c r="O20" s="3"/>
+      <c r="P20" s="3"/>
+      <c r="Q20" s="3"/>
+      <c r="R20" s="3"/>
+      <c r="S20" s="3"/>
+      <c r="T20" s="3"/>
+      <c r="U20" s="7"/>
+      <c r="V20" s="3">
         <f t="shared" si="0"/>
         <v>61.634854386899654</v>
       </c>
-      <c r="W20" s="5">
+      <c r="W20" s="3">
         <f t="shared" si="1"/>
         <v>6.2802064441851559</v>
       </c>
-      <c r="X20" s="5">
+      <c r="X20" s="3">
         <f t="shared" si="2"/>
         <v>20.801763355578633</v>
       </c>
-      <c r="Y20" s="5">
+      <c r="Y20" s="3">
         <f t="shared" si="3"/>
         <v>4.1418622147996562E-2</v>
       </c>
-      <c r="Z20" s="5">
+      <c r="Z20" s="3">
         <f t="shared" si="4"/>
         <v>0.62515352304511262</v>
       </c>
@@ -39363,47 +39357,47 @@
       <c r="H21">
         <v>532</v>
       </c>
-      <c r="I21" s="5">
+      <c r="I21" s="3">
         <f t="shared" si="5"/>
         <v>12799.977242410001</v>
       </c>
-      <c r="J21" s="5">
+      <c r="J21" s="3">
         <f t="shared" si="6"/>
         <v>130.6</v>
       </c>
-      <c r="K21" s="9"/>
-      <c r="L21" s="5">
+      <c r="K21" s="7"/>
+      <c r="L21" s="3">
         <f t="shared" si="7"/>
         <v>98.009014107274126</v>
       </c>
-      <c r="M21" s="5">
+      <c r="M21" s="3">
         <v>114.36661460000001</v>
       </c>
-      <c r="N21" s="5"/>
-      <c r="O21" s="5"/>
-      <c r="P21" s="5"/>
-      <c r="Q21" s="5"/>
-      <c r="R21" s="5"/>
-      <c r="S21" s="5"/>
-      <c r="T21" s="5"/>
-      <c r="U21" s="9"/>
-      <c r="V21" s="5">
+      <c r="N21" s="3"/>
+      <c r="O21" s="3"/>
+      <c r="P21" s="3"/>
+      <c r="Q21" s="3"/>
+      <c r="R21" s="3"/>
+      <c r="S21" s="3"/>
+      <c r="T21" s="3"/>
+      <c r="U21" s="7"/>
+      <c r="V21" s="3">
         <f t="shared" si="0"/>
         <v>62.500111121242483</v>
       </c>
-      <c r="W21" s="5">
+      <c r="W21" s="3">
         <f t="shared" si="1"/>
         <v>6.2384039485186955</v>
       </c>
-      <c r="X21" s="5">
+      <c r="X21" s="3">
         <f t="shared" si="2"/>
         <v>19.846696778358446</v>
       </c>
-      <c r="Y21" s="5">
+      <c r="Y21" s="3">
         <f t="shared" si="3"/>
         <v>4.2000074673474955E-2</v>
       </c>
-      <c r="Z21" s="5">
+      <c r="Z21" s="3">
         <f t="shared" si="4"/>
         <v>0.60714393657287336</v>
       </c>
@@ -39448,47 +39442,47 @@
       <c r="H22">
         <v>532</v>
       </c>
-      <c r="I22" s="5">
+      <c r="I22" s="3">
         <f t="shared" si="5"/>
         <v>12724.239199690001</v>
       </c>
-      <c r="J22" s="5">
+      <c r="J22" s="3">
         <f t="shared" si="6"/>
         <v>132.4</v>
       </c>
-      <c r="K22" s="9"/>
-      <c r="L22" s="5">
+      <c r="K22" s="7"/>
+      <c r="L22" s="3">
         <f t="shared" si="7"/>
         <v>96.104525677416916</v>
       </c>
-      <c r="M22" s="5">
+      <c r="M22" s="3">
         <v>111.9379294</v>
       </c>
-      <c r="N22" s="5"/>
-      <c r="O22" s="5"/>
-      <c r="P22" s="5"/>
-      <c r="Q22" s="5"/>
-      <c r="R22" s="5"/>
-      <c r="S22" s="5"/>
-      <c r="T22" s="5"/>
-      <c r="U22" s="9"/>
-      <c r="V22" s="5">
+      <c r="N22" s="3"/>
+      <c r="O22" s="3"/>
+      <c r="P22" s="3"/>
+      <c r="Q22" s="3"/>
+      <c r="R22" s="3"/>
+      <c r="S22" s="3"/>
+      <c r="T22" s="3"/>
+      <c r="U22" s="7"/>
+      <c r="V22" s="3">
         <f t="shared" si="0"/>
         <v>62.872128340646903</v>
       </c>
-      <c r="W22" s="5">
+      <c r="W22" s="3">
         <f t="shared" si="1"/>
         <v>6.144796235982807</v>
       </c>
-      <c r="X22" s="5">
+      <c r="X22" s="3">
         <f t="shared" si="2"/>
         <v>19.52728862610925</v>
       </c>
-      <c r="Y22" s="5">
+      <c r="Y22" s="3">
         <f t="shared" si="3"/>
         <v>4.2250070244914728E-2</v>
       </c>
-      <c r="Z22" s="5">
+      <c r="Z22" s="3">
         <f t="shared" si="4"/>
         <v>0.5838126203396885</v>
       </c>
@@ -39533,49 +39527,49 @@
       <c r="H23">
         <v>532</v>
       </c>
-      <c r="I23" s="5">
+      <c r="I23" s="3">
         <f t="shared" si="5"/>
         <v>12627.92969253</v>
       </c>
-      <c r="J23" s="5">
+      <c r="J23" s="3">
         <f t="shared" si="6"/>
         <v>134.19999999999999</v>
       </c>
-      <c r="K23" s="9"/>
-      <c r="L23" s="5">
+      <c r="K23" s="7"/>
+      <c r="L23" s="3">
         <f t="shared" si="7"/>
         <v>94.097836755067078</v>
       </c>
-      <c r="M23" s="5">
+      <c r="M23" s="3">
         <v>109.5608196</v>
       </c>
-      <c r="N23" s="5">
+      <c r="N23" s="3">
         <v>110</v>
       </c>
-      <c r="O23" s="5"/>
-      <c r="P23" s="5"/>
-      <c r="Q23" s="5"/>
-      <c r="R23" s="5"/>
-      <c r="S23" s="5"/>
-      <c r="T23" s="5"/>
-      <c r="U23" s="9"/>
-      <c r="V23" s="5">
+      <c r="O23" s="3"/>
+      <c r="P23" s="3"/>
+      <c r="Q23" s="3"/>
+      <c r="R23" s="3"/>
+      <c r="S23" s="3"/>
+      <c r="T23" s="3"/>
+      <c r="U23" s="7"/>
+      <c r="V23" s="3">
         <f t="shared" si="0"/>
         <v>63.351635579127176</v>
       </c>
-      <c r="W23" s="5">
+      <c r="W23" s="3">
         <f t="shared" si="1"/>
         <v>6.0599233265661612</v>
       </c>
-      <c r="X23" s="5">
+      <c r="X23" s="3">
         <f t="shared" si="2"/>
         <v>19.274436295284413</v>
       </c>
-      <c r="Y23" s="5">
+      <c r="Y23" s="3">
         <f t="shared" si="3"/>
         <v>4.2572299109173463E-2</v>
       </c>
-      <c r="Z23" s="5">
+      <c r="Z23" s="3">
         <f t="shared" si="4"/>
         <v>0.3591132714084222</v>
       </c>
@@ -39620,49 +39614,49 @@
       <c r="H24">
         <v>532</v>
       </c>
-      <c r="I24" s="5">
+      <c r="I24" s="3">
         <f t="shared" si="5"/>
         <v>12562.671303610001</v>
       </c>
-      <c r="J24" s="5">
+      <c r="J24" s="3">
         <f t="shared" si="6"/>
         <v>136</v>
       </c>
-      <c r="K24" s="9"/>
-      <c r="L24" s="5">
+      <c r="K24" s="7"/>
+      <c r="L24" s="3">
         <f t="shared" si="7"/>
         <v>92.372583114779417</v>
       </c>
-      <c r="M24" s="5">
+      <c r="M24" s="3">
         <v>107.23419010000001</v>
       </c>
-      <c r="N24" s="5"/>
-      <c r="O24" s="5"/>
-      <c r="P24" s="5"/>
-      <c r="Q24" s="5"/>
-      <c r="R24" s="5">
+      <c r="N24" s="3"/>
+      <c r="O24" s="3"/>
+      <c r="P24" s="3"/>
+      <c r="Q24" s="3"/>
+      <c r="R24" s="3">
         <v>74.400000000000006</v>
       </c>
-      <c r="S24" s="5"/>
-      <c r="T24" s="5"/>
-      <c r="U24" s="9"/>
-      <c r="V24" s="5">
+      <c r="S24" s="3"/>
+      <c r="T24" s="3"/>
+      <c r="U24" s="7"/>
+      <c r="V24" s="3">
         <f t="shared" si="0"/>
         <v>63.680723682558863</v>
       </c>
-      <c r="W24" s="5">
+      <c r="W24" s="3">
         <f t="shared" si="1"/>
         <v>5.9589805767255939</v>
       </c>
-      <c r="X24" s="5">
+      <c r="X24" s="3">
         <f t="shared" si="2"/>
         <v>19.004985622078006</v>
       </c>
-      <c r="Y24" s="5">
+      <c r="Y24" s="3">
         <f t="shared" si="3"/>
         <v>4.2793446314679559E-2</v>
       </c>
-      <c r="Z24" s="5">
+      <c r="Z24" s="3">
         <f t="shared" si="4"/>
         <v>0.34351201800208858</v>
       </c>
@@ -39707,49 +39701,49 @@
       <c r="H25">
         <v>532</v>
       </c>
-      <c r="I25" s="5">
+      <c r="I25" s="3">
         <f t="shared" si="5"/>
         <v>12501.194776599999</v>
       </c>
-      <c r="J25" s="5">
+      <c r="J25" s="3">
         <f t="shared" si="6"/>
         <v>137.2222222</v>
       </c>
-      <c r="K25" s="9"/>
-      <c r="L25" s="5">
+      <c r="K25" s="7"/>
+      <c r="L25" s="3">
         <f t="shared" si="7"/>
         <v>91.101824297668301</v>
       </c>
-      <c r="M25" s="5">
+      <c r="M25" s="3">
         <v>104.9569687</v>
       </c>
-      <c r="N25" s="5"/>
-      <c r="O25" s="5"/>
-      <c r="P25" s="5"/>
-      <c r="Q25" s="5"/>
-      <c r="R25" s="5">
+      <c r="N25" s="3"/>
+      <c r="O25" s="3"/>
+      <c r="P25" s="3"/>
+      <c r="Q25" s="3"/>
+      <c r="R25" s="3">
         <v>74.400000000000006</v>
       </c>
-      <c r="S25" s="5"/>
-      <c r="T25" s="5"/>
-      <c r="U25" s="9"/>
-      <c r="V25" s="5">
+      <c r="S25" s="3"/>
+      <c r="T25" s="3"/>
+      <c r="U25" s="7"/>
+      <c r="V25" s="3">
         <f t="shared" si="0"/>
         <v>63.993883328452483</v>
       </c>
-      <c r="W25" s="5">
+      <c r="W25" s="3">
         <f t="shared" si="1"/>
         <v>5.8552117751986357</v>
       </c>
-      <c r="X25" s="5">
+      <c r="X25" s="3">
         <f t="shared" si="2"/>
         <v>18.757305920784546</v>
       </c>
-      <c r="Y25" s="5">
+      <c r="Y25" s="3">
         <f t="shared" si="3"/>
         <v>4.3003889596720073E-2</v>
       </c>
-      <c r="Z25" s="5">
+      <c r="Z25" s="3">
         <f t="shared" si="4"/>
         <v>0.32764868264167674</v>
       </c>
@@ -39794,51 +39788,51 @@
       <c r="H26">
         <v>532</v>
       </c>
-      <c r="I26" s="5">
+      <c r="I26" s="3">
         <f t="shared" si="5"/>
         <v>12455.36948159</v>
       </c>
-      <c r="J26" s="5">
+      <c r="J26" s="3">
         <f t="shared" si="6"/>
         <v>138.44444439999998</v>
       </c>
-      <c r="K26" s="9"/>
-      <c r="L26" s="5">
+      <c r="K26" s="7"/>
+      <c r="L26" s="3">
         <f t="shared" si="7"/>
         <v>89.966553266690724</v>
       </c>
-      <c r="M26" s="5">
+      <c r="M26" s="3">
         <v>102.7281064</v>
       </c>
-      <c r="N26" s="5"/>
-      <c r="O26" s="5"/>
-      <c r="P26" s="5"/>
-      <c r="Q26" s="5"/>
-      <c r="R26" s="5">
+      <c r="N26" s="3"/>
+      <c r="O26" s="3"/>
+      <c r="P26" s="3"/>
+      <c r="Q26" s="3"/>
+      <c r="R26" s="3">
         <v>74.400000000000006</v>
       </c>
-      <c r="S26" s="5">
+      <c r="S26" s="3">
         <v>102.7</v>
       </c>
-      <c r="T26" s="5"/>
-      <c r="U26" s="9"/>
-      <c r="V26" s="5">
+      <c r="T26" s="3"/>
+      <c r="U26" s="7"/>
+      <c r="V26" s="3">
         <f t="shared" si="0"/>
         <v>64.229327053080354</v>
       </c>
-      <c r="W26" s="5">
+      <c r="W26" s="3">
         <f t="shared" si="1"/>
         <v>5.7431914433154425</v>
       </c>
-      <c r="X26" s="5">
+      <c r="X26" s="3">
         <f t="shared" si="2"/>
         <v>18.609580843234109</v>
       </c>
-      <c r="Y26" s="5">
+      <c r="Y26" s="3">
         <f t="shared" si="3"/>
         <v>4.316210777967E-2</v>
       </c>
-      <c r="Z26" s="5">
+      <c r="Z26" s="3">
         <f t="shared" si="4"/>
         <v>0.31123696769733511</v>
       </c>
@@ -39883,51 +39877,51 @@
       <c r="H27">
         <v>532</v>
       </c>
-      <c r="I27" s="5">
+      <c r="I27" s="3">
         <f t="shared" si="5"/>
         <v>12374.66669057</v>
       </c>
-      <c r="J27" s="5">
+      <c r="J27" s="3">
         <f t="shared" si="6"/>
         <v>139.66666670000001</v>
       </c>
-      <c r="K27" s="9"/>
-      <c r="L27" s="5">
+      <c r="K27" s="7"/>
+      <c r="L27" s="3">
         <f t="shared" si="7"/>
         <v>88.601432130906574</v>
       </c>
-      <c r="M27" s="5">
+      <c r="M27" s="3">
         <v>100.5465761</v>
       </c>
-      <c r="N27" s="5"/>
-      <c r="O27" s="5"/>
-      <c r="P27" s="5"/>
-      <c r="Q27" s="5"/>
-      <c r="R27" s="5">
+      <c r="N27" s="3"/>
+      <c r="O27" s="3"/>
+      <c r="P27" s="3"/>
+      <c r="Q27" s="3"/>
+      <c r="R27" s="3">
         <v>74.400000000000006</v>
       </c>
-      <c r="S27" s="5">
+      <c r="S27" s="3">
         <v>102.7</v>
       </c>
-      <c r="T27" s="5"/>
-      <c r="U27" s="9"/>
-      <c r="V27" s="5">
+      <c r="T27" s="3"/>
+      <c r="U27" s="7"/>
+      <c r="V27" s="3">
         <f t="shared" si="0"/>
         <v>64.648205887406448</v>
       </c>
-      <c r="W27" s="5">
+      <c r="W27" s="3">
         <f t="shared" si="1"/>
         <v>5.6462126816913614</v>
       </c>
-      <c r="X27" s="5">
+      <c r="X27" s="3">
         <f t="shared" si="2"/>
         <v>18.230949716966343</v>
       </c>
-      <c r="Y27" s="5">
+      <c r="Y27" s="3">
         <f t="shared" si="3"/>
         <v>4.3443594356337135E-2</v>
       </c>
-      <c r="Z27" s="5">
+      <c r="Z27" s="3">
         <f t="shared" si="4"/>
         <v>0.2955346554737423</v>
       </c>
@@ -39972,55 +39966,55 @@
       <c r="H28">
         <v>532</v>
       </c>
-      <c r="I28" s="5">
+      <c r="I28" s="3">
         <f t="shared" si="5"/>
         <v>12113.835995859999</v>
       </c>
-      <c r="J28" s="5">
+      <c r="J28" s="3">
         <f t="shared" si="6"/>
         <v>140.88888890000001</v>
       </c>
-      <c r="K28" s="9"/>
-      <c r="L28" s="5">
+      <c r="K28" s="7"/>
+      <c r="L28" s="3">
         <f t="shared" si="7"/>
         <v>85.981485768250664</v>
       </c>
-      <c r="M28" s="5">
+      <c r="M28" s="3">
         <v>98.411372709999995</v>
       </c>
-      <c r="N28" s="5">
+      <c r="N28" s="3">
         <v>98</v>
       </c>
-      <c r="O28" s="5"/>
-      <c r="P28" s="5"/>
-      <c r="Q28" s="5">
+      <c r="O28" s="3"/>
+      <c r="P28" s="3"/>
+      <c r="Q28" s="3">
         <v>101.6</v>
       </c>
-      <c r="R28" s="5">
+      <c r="R28" s="3">
         <v>74.400000000000006</v>
       </c>
-      <c r="S28" s="5">
+      <c r="S28" s="3">
         <v>102.7</v>
       </c>
-      <c r="T28" s="5"/>
-      <c r="U28" s="9"/>
-      <c r="V28" s="5">
+      <c r="T28" s="3"/>
+      <c r="U28" s="7"/>
+      <c r="V28" s="3">
         <f t="shared" si="0"/>
         <v>66.040187457829745</v>
       </c>
-      <c r="W28" s="5">
+      <c r="W28" s="3">
         <f t="shared" si="1"/>
         <v>4.8064873934151713</v>
       </c>
-      <c r="X28" s="5">
+      <c r="X28" s="3">
         <f t="shared" si="2"/>
         <v>17.449739733329881</v>
       </c>
-      <c r="Y28" s="5">
+      <c r="Y28" s="3">
         <f t="shared" si="3"/>
         <v>4.4379005971661591E-2</v>
       </c>
-      <c r="Z28" s="5">
+      <c r="Z28" s="3">
         <f t="shared" si="4"/>
         <v>0.28378411984237417</v>
       </c>
@@ -40065,53 +40059,53 @@
       <c r="H29">
         <v>532</v>
       </c>
-      <c r="I29" s="5">
+      <c r="I29" s="3">
         <f t="shared" si="5"/>
         <v>11964.83833814</v>
       </c>
-      <c r="J29" s="5">
+      <c r="J29" s="3">
         <f t="shared" si="6"/>
         <v>142.11111109999999</v>
       </c>
-      <c r="K29" s="9"/>
-      <c r="L29" s="5">
+      <c r="K29" s="7"/>
+      <c r="L29" s="3">
         <f t="shared" si="7"/>
         <v>84.193545779264554</v>
       </c>
-      <c r="M29" s="5">
+      <c r="M29" s="3">
         <v>96.321512409999997</v>
       </c>
-      <c r="N29" s="5"/>
-      <c r="O29" s="5"/>
-      <c r="P29" s="5"/>
-      <c r="Q29" s="5">
+      <c r="N29" s="3"/>
+      <c r="O29" s="3"/>
+      <c r="P29" s="3"/>
+      <c r="Q29" s="3">
         <v>101.6</v>
       </c>
-      <c r="R29" s="5">
+      <c r="R29" s="3">
         <v>74.400000000000006</v>
       </c>
-      <c r="S29" s="5">
+      <c r="S29" s="3">
         <v>102.7</v>
       </c>
-      <c r="T29" s="5"/>
-      <c r="U29" s="9"/>
-      <c r="V29" s="5">
+      <c r="T29" s="3"/>
+      <c r="U29" s="7"/>
+      <c r="V29" s="3">
         <f t="shared" si="0"/>
         <v>66.862583295409934</v>
       </c>
-      <c r="W29" s="5">
+      <c r="W29" s="3">
         <f t="shared" si="1"/>
         <v>3.8930739123752436</v>
       </c>
-      <c r="X29" s="5">
+      <c r="X29" s="3">
         <f t="shared" si="2"/>
         <v>17.413352542829998</v>
       </c>
-      <c r="Y29" s="5">
+      <c r="Y29" s="3">
         <f t="shared" si="3"/>
         <v>4.4931655974515483E-2</v>
       </c>
-      <c r="Z29" s="5">
+      <c r="Z29" s="3">
         <f t="shared" si="4"/>
         <v>0.26897862077594109</v>
       </c>
@@ -40156,55 +40150,55 @@
       <c r="H30">
         <v>532</v>
       </c>
-      <c r="I30" s="5">
+      <c r="I30" s="3">
         <f t="shared" si="5"/>
         <v>11910.556731430001</v>
       </c>
-      <c r="J30" s="5">
+      <c r="J30" s="3">
         <f t="shared" si="6"/>
         <v>143.33333329999999</v>
       </c>
-      <c r="K30" s="9"/>
-      <c r="L30" s="5">
+      <c r="K30" s="7"/>
+      <c r="L30" s="3">
         <f t="shared" si="7"/>
         <v>83.096907447906261</v>
       </c>
-      <c r="M30" s="5">
+      <c r="M30" s="3">
         <v>94.276032310000005</v>
       </c>
-      <c r="N30" s="5"/>
-      <c r="O30" s="5">
+      <c r="N30" s="3"/>
+      <c r="O30" s="3">
         <v>102.3</v>
       </c>
-      <c r="P30" s="5"/>
-      <c r="Q30" s="5">
+      <c r="P30" s="3"/>
+      <c r="Q30" s="3">
         <v>101.6</v>
       </c>
-      <c r="R30" s="5">
+      <c r="R30" s="3">
         <v>74.400000000000006</v>
       </c>
-      <c r="S30" s="5">
+      <c r="S30" s="3">
         <v>102.7</v>
       </c>
-      <c r="T30" s="5"/>
-      <c r="U30" s="9"/>
-      <c r="V30" s="5">
+      <c r="T30" s="3"/>
+      <c r="U30" s="7"/>
+      <c r="V30" s="3">
         <f t="shared" si="0"/>
         <v>67.16730527708512</v>
       </c>
-      <c r="W30" s="5">
+      <c r="W30" s="3">
         <f t="shared" si="1"/>
         <v>3.715275532270367</v>
       </c>
-      <c r="X30" s="5">
+      <c r="X30" s="3">
         <f t="shared" si="2"/>
         <v>17.250932986012582</v>
       </c>
-      <c r="Y30" s="5">
+      <c r="Y30" s="3">
         <f t="shared" si="3"/>
         <v>4.513642914620121E-2</v>
       </c>
-      <c r="Z30" s="5">
+      <c r="Z30" s="3">
         <f t="shared" si="4"/>
         <v>0.2517814415078104</v>
       </c>
@@ -40249,55 +40243,55 @@
       <c r="H31">
         <v>532</v>
       </c>
-      <c r="I31" s="5">
+      <c r="I31" s="3">
         <f t="shared" si="5"/>
         <v>11857.71451071</v>
       </c>
-      <c r="J31" s="5">
+      <c r="J31" s="3">
         <f t="shared" si="6"/>
         <v>144.55555560000002</v>
       </c>
-      <c r="K31" s="9"/>
-      <c r="L31" s="5">
+      <c r="K31" s="7"/>
+      <c r="L31" s="3">
         <f t="shared" si="7"/>
         <v>82.02877060997578</v>
       </c>
-      <c r="M31" s="5">
+      <c r="M31" s="3">
         <v>92.273989950000001</v>
       </c>
-      <c r="N31" s="5"/>
-      <c r="O31" s="5">
+      <c r="N31" s="3"/>
+      <c r="O31" s="3">
         <v>102.3</v>
       </c>
-      <c r="P31" s="5"/>
-      <c r="Q31" s="5">
+      <c r="P31" s="3"/>
+      <c r="Q31" s="3">
         <v>101.6</v>
       </c>
-      <c r="R31" s="5">
+      <c r="R31" s="3">
         <v>74.400000000000006</v>
       </c>
-      <c r="S31" s="5">
+      <c r="S31" s="3">
         <v>102.7</v>
       </c>
-      <c r="T31" s="5"/>
-      <c r="U31" s="9"/>
-      <c r="V31" s="5">
+      <c r="T31" s="3"/>
+      <c r="U31" s="7"/>
+      <c r="V31" s="3">
         <f t="shared" si="0"/>
         <v>67.466626834153615</v>
       </c>
-      <c r="W31" s="5">
+      <c r="W31" s="3">
         <f t="shared" si="1"/>
         <v>3.5354199126767352</v>
       </c>
-      <c r="X31" s="5">
+      <c r="X31" s="3">
         <f t="shared" si="2"/>
         <v>17.097090869989334</v>
       </c>
-      <c r="Y31" s="5">
+      <c r="Y31" s="3">
         <f t="shared" si="3"/>
         <v>4.5337573232551227E-2</v>
       </c>
-      <c r="Z31" s="5">
+      <c r="Z31" s="3">
         <f t="shared" si="4"/>
         <v>0.23439833776480232</v>
       </c>
@@ -40342,55 +40336,55 @@
       <c r="H32">
         <v>532</v>
       </c>
-      <c r="I32" s="5">
+      <c r="I32" s="3">
         <f t="shared" si="5"/>
         <v>11829.49639</v>
       </c>
-      <c r="J32" s="5">
+      <c r="J32" s="3">
         <f t="shared" si="6"/>
         <v>145.7777778</v>
       </c>
-      <c r="K32" s="9"/>
-      <c r="L32" s="5">
+      <c r="K32" s="7"/>
+      <c r="L32" s="3">
         <f t="shared" si="7"/>
         <v>81.147459980008009</v>
       </c>
-      <c r="M32" s="5">
+      <c r="M32" s="3">
         <v>90.314462890000001</v>
       </c>
-      <c r="N32" s="5"/>
-      <c r="O32" s="5">
+      <c r="N32" s="3"/>
+      <c r="O32" s="3">
         <v>102.3</v>
       </c>
-      <c r="P32" s="5"/>
-      <c r="Q32" s="5">
+      <c r="P32" s="3"/>
+      <c r="Q32" s="3">
         <v>101.6</v>
       </c>
-      <c r="R32" s="5">
+      <c r="R32" s="3">
         <v>74.400000000000006</v>
       </c>
-      <c r="S32" s="5">
+      <c r="S32" s="3">
         <v>102.7</v>
       </c>
-      <c r="T32" s="5"/>
-      <c r="U32" s="9"/>
-      <c r="V32" s="5">
+      <c r="T32" s="3"/>
+      <c r="U32" s="7"/>
+      <c r="V32" s="3">
         <f t="shared" si="0"/>
         <v>67.627561954055423</v>
       </c>
-      <c r="W32" s="5">
+      <c r="W32" s="3">
         <f t="shared" si="1"/>
         <v>3.5438533152973899</v>
       </c>
-      <c r="X32" s="5">
+      <c r="X32" s="3">
         <f t="shared" si="2"/>
         <v>16.917883264175035</v>
       </c>
-      <c r="Y32" s="5">
+      <c r="Y32" s="3">
         <f t="shared" si="3"/>
         <v>4.5445721633125248E-2</v>
       </c>
-      <c r="Z32" s="5">
+      <c r="Z32" s="3">
         <f t="shared" si="4"/>
         <v>0.21640819825297736</v>
       </c>
@@ -40438,57 +40432,57 @@
       <c r="H33">
         <v>532</v>
       </c>
-      <c r="I33" s="5">
+      <c r="I33" s="3">
         <f t="shared" si="5"/>
         <v>11802.07407517</v>
       </c>
-      <c r="J33" s="5">
+      <c r="J33" s="3">
         <f t="shared" si="6"/>
         <v>147</v>
       </c>
-      <c r="K33" s="9"/>
-      <c r="L33" s="5">
+      <c r="K33" s="7"/>
+      <c r="L33" s="3">
         <f t="shared" si="7"/>
         <v>80.286218198435378</v>
       </c>
-      <c r="M33" s="5">
+      <c r="M33" s="3">
         <v>88.396548280000005</v>
       </c>
-      <c r="N33" s="5">
+      <c r="N33" s="3">
         <v>95</v>
       </c>
-      <c r="O33" s="5">
+      <c r="O33" s="3">
         <v>102.3</v>
       </c>
-      <c r="P33" s="5"/>
-      <c r="Q33" s="5">
+      <c r="P33" s="3"/>
+      <c r="Q33" s="3">
         <v>101.6</v>
       </c>
-      <c r="R33" s="5">
+      <c r="R33" s="3">
         <v>74.400000000000006</v>
       </c>
-      <c r="S33" s="5">
+      <c r="S33" s="3">
         <v>102.7</v>
       </c>
-      <c r="T33" s="5"/>
-      <c r="U33" s="9"/>
-      <c r="V33" s="5">
+      <c r="T33" s="3"/>
+      <c r="U33" s="7"/>
+      <c r="V33" s="3">
         <f t="shared" si="0"/>
         <v>67.784695715738138</v>
       </c>
-      <c r="W33" s="5">
+      <c r="W33" s="3">
         <f t="shared" si="1"/>
         <v>3.5520875172439679</v>
       </c>
-      <c r="X33" s="5">
+      <c r="X33" s="3">
         <f t="shared" si="2"/>
         <v>16.837300345205438</v>
       </c>
-      <c r="Y33" s="5">
+      <c r="Y33" s="3">
         <f t="shared" si="3"/>
         <v>4.5551315520976028E-2</v>
       </c>
-      <c r="Z33" s="5">
+      <c r="Z33" s="3">
         <f t="shared" si="4"/>
         <v>0.10445126925559001</v>
       </c>
@@ -40539,55 +40533,55 @@
       <c r="H34">
         <v>532</v>
       </c>
-      <c r="I34" s="5">
+      <c r="I34" s="3">
         <f t="shared" si="5"/>
         <v>11779.461976809998</v>
       </c>
-      <c r="J34" s="5">
+      <c r="J34" s="3">
         <f t="shared" si="6"/>
         <v>151</v>
       </c>
-      <c r="K34" s="9"/>
-      <c r="L34" s="5">
+      <c r="K34" s="7"/>
+      <c r="L34" s="3">
         <f t="shared" si="7"/>
         <v>78.009681965629127</v>
       </c>
-      <c r="M34" s="5">
+      <c r="M34" s="3">
         <v>86.519362419999993</v>
       </c>
-      <c r="N34" s="5"/>
-      <c r="O34" s="5">
+      <c r="N34" s="3"/>
+      <c r="O34" s="3">
         <v>102.3</v>
       </c>
-      <c r="P34" s="5"/>
-      <c r="Q34" s="5">
+      <c r="P34" s="3"/>
+      <c r="Q34" s="3">
         <v>101.6</v>
       </c>
-      <c r="R34" s="5">
+      <c r="R34" s="3">
         <v>74.400000000000006</v>
       </c>
-      <c r="S34" s="5">
+      <c r="S34" s="3">
         <v>102.7</v>
       </c>
-      <c r="T34" s="5"/>
-      <c r="U34" s="9"/>
-      <c r="V34" s="5">
+      <c r="T34" s="3"/>
+      <c r="U34" s="7"/>
+      <c r="V34" s="3">
         <f t="shared" si="0"/>
         <v>67.914816616832312</v>
       </c>
-      <c r="W34" s="5">
+      <c r="W34" s="3">
         <f t="shared" si="1"/>
         <v>3.5589061777635553</v>
       </c>
-      <c r="X34" s="5">
+      <c r="X34" s="3">
         <f t="shared" si="2"/>
         <v>16.695101472984032</v>
       </c>
-      <c r="Y34" s="5">
+      <c r="Y34" s="3">
         <f t="shared" si="3"/>
         <v>4.5638756766511315E-2</v>
       </c>
-      <c r="Z34" s="5">
+      <c r="Z34" s="3">
         <f t="shared" si="4"/>
         <v>8.7209813404245107E-2</v>
       </c>
@@ -40635,59 +40629,59 @@
       <c r="H35">
         <v>532</v>
       </c>
-      <c r="I35" s="5">
+      <c r="I35" s="3">
         <f t="shared" si="5"/>
         <v>11853.800475448999</v>
       </c>
-      <c r="J35" s="5">
+      <c r="J35" s="3">
         <f t="shared" si="6"/>
         <v>154</v>
       </c>
-      <c r="K35" s="9"/>
-      <c r="L35" s="5">
+      <c r="K35" s="7"/>
+      <c r="L35" s="3">
         <f t="shared" si="7"/>
         <v>76.972730360058435</v>
       </c>
-      <c r="M35" s="5">
+      <c r="M35" s="3">
         <v>84.682040420000007</v>
       </c>
-      <c r="N35" s="5">
+      <c r="N35" s="3">
         <v>78</v>
       </c>
-      <c r="O35" s="5">
+      <c r="O35" s="3">
         <v>102.3</v>
       </c>
-      <c r="P35" s="5">
+      <c r="P35" s="3">
         <v>102</v>
       </c>
-      <c r="Q35" s="5">
+      <c r="Q35" s="3">
         <v>101.6</v>
       </c>
-      <c r="R35" s="5">
+      <c r="R35" s="3">
         <v>74.400000000000006</v>
       </c>
-      <c r="S35" s="5">
+      <c r="S35" s="3">
         <v>102.7</v>
       </c>
-      <c r="T35" s="5"/>
-      <c r="U35" s="9"/>
-      <c r="V35" s="5">
+      <c r="T35" s="3"/>
+      <c r="U35" s="7"/>
+      <c r="V35" s="3">
         <f t="shared" si="0"/>
         <v>68.163792842092235</v>
       </c>
-      <c r="W35" s="5">
+      <c r="W35" s="3">
         <f t="shared" si="1"/>
         <v>3.53658728159182</v>
       </c>
-      <c r="X35" s="5">
+      <c r="X35" s="3">
         <f t="shared" si="2"/>
         <v>16.559973335687904</v>
       </c>
-      <c r="Y35" s="5">
+      <c r="Y35" s="3">
         <f t="shared" si="3"/>
         <v>4.5352543356322758E-2</v>
       </c>
-      <c r="Z35" s="5">
+      <c r="Z35" s="3">
         <f t="shared" si="4"/>
         <v>6.9330317023821073E-2</v>
       </c>
@@ -40735,57 +40729,57 @@
       <c r="H36">
         <v>532</v>
       </c>
-      <c r="I36" s="5">
+      <c r="I36" s="3">
         <f t="shared" si="5"/>
         <v>11587.806922214</v>
       </c>
-      <c r="J36" s="5">
+      <c r="J36" s="3">
         <f t="shared" si="6"/>
         <v>160</v>
       </c>
-      <c r="K36" s="9"/>
-      <c r="L36" s="5">
+      <c r="K36" s="7"/>
+      <c r="L36" s="3">
         <f t="shared" si="7"/>
         <v>72.423793263837496</v>
       </c>
-      <c r="M36" s="5">
+      <c r="M36" s="3">
         <v>82.883735720000004</v>
       </c>
-      <c r="N36" s="5"/>
-      <c r="O36" s="5">
+      <c r="N36" s="3"/>
+      <c r="O36" s="3">
         <v>102.3</v>
       </c>
-      <c r="P36" s="5">
+      <c r="P36" s="3">
         <v>102</v>
       </c>
-      <c r="Q36" s="5">
+      <c r="Q36" s="3">
         <v>101.6</v>
       </c>
-      <c r="R36" s="5">
+      <c r="R36" s="3">
         <v>74.400000000000006</v>
       </c>
-      <c r="S36" s="5">
+      <c r="S36" s="3">
         <v>102.7</v>
       </c>
-      <c r="T36" s="5"/>
-      <c r="U36" s="9"/>
-      <c r="V36" s="5">
+      <c r="T36" s="3"/>
+      <c r="U36" s="7"/>
+      <c r="V36" s="3">
         <f t="shared" si="0"/>
         <v>70.418846765190381</v>
       </c>
-      <c r="W36" s="5">
+      <c r="W36" s="3">
         <f t="shared" si="1"/>
         <v>3.6177682525616559</v>
       </c>
-      <c r="X36" s="5">
+      <c r="X36" s="3">
         <f t="shared" si="2"/>
         <v>13.975535999788487</v>
       </c>
-      <c r="Y36" s="5">
+      <c r="Y36" s="3">
         <f t="shared" si="3"/>
         <v>4.6393593162948957E-2</v>
       </c>
-      <c r="Z36" s="5">
+      <c r="Z36" s="3">
         <f t="shared" si="4"/>
         <v>4.9645237037664186E-2</v>
       </c>
@@ -40833,57 +40827,57 @@
       <c r="H37">
         <v>532</v>
       </c>
-      <c r="I37" s="5">
+      <c r="I37" s="3">
         <f t="shared" si="5"/>
         <v>11695.467606342001</v>
       </c>
-      <c r="J37" s="5">
+      <c r="J37" s="3">
         <f t="shared" si="6"/>
         <v>163</v>
       </c>
-      <c r="K37" s="9"/>
-      <c r="L37" s="5">
+      <c r="K37" s="7"/>
+      <c r="L37" s="3">
         <f t="shared" si="7"/>
         <v>71.751335008233141</v>
       </c>
-      <c r="M37" s="5">
+      <c r="M37" s="3">
         <v>81.123619750000003</v>
       </c>
-      <c r="N37" s="5"/>
-      <c r="O37" s="5">
+      <c r="N37" s="3"/>
+      <c r="O37" s="3">
         <v>102.3</v>
       </c>
-      <c r="P37" s="5">
+      <c r="P37" s="3">
         <v>102</v>
       </c>
-      <c r="Q37" s="5">
+      <c r="Q37" s="3">
         <v>101.6</v>
       </c>
-      <c r="R37" s="5">
+      <c r="R37" s="3">
         <v>74.400000000000006</v>
       </c>
-      <c r="S37" s="5">
+      <c r="S37" s="3">
         <v>102.7</v>
       </c>
-      <c r="T37" s="5"/>
-      <c r="U37" s="9"/>
-      <c r="V37" s="5">
+      <c r="T37" s="3"/>
+      <c r="U37" s="7"/>
+      <c r="V37" s="3">
         <f t="shared" si="0"/>
         <v>70.905245340538485</v>
       </c>
-      <c r="W37" s="5">
+      <c r="W37" s="3">
         <f t="shared" si="1"/>
         <v>3.5844654879183557</v>
       </c>
-      <c r="X37" s="5">
+      <c r="X37" s="3">
         <f t="shared" si="2"/>
         <v>13.618435616343538</v>
       </c>
-      <c r="Y37" s="5">
+      <c r="Y37" s="3">
         <f t="shared" si="3"/>
         <v>4.5966524648273173E-2</v>
       </c>
-      <c r="Z37" s="5">
+      <c r="Z37" s="3">
         <f t="shared" si="4"/>
         <v>4.5674790626612519E-2</v>
       </c>
@@ -40931,59 +40925,59 @@
       <c r="H38">
         <v>532</v>
       </c>
-      <c r="I38" s="5">
+      <c r="I38" s="3">
         <f t="shared" si="5"/>
         <v>11532.713136597</v>
       </c>
-      <c r="J38" s="5">
+      <c r="J38" s="3">
         <f t="shared" si="6"/>
         <v>170</v>
       </c>
-      <c r="K38" s="9"/>
-      <c r="L38" s="5">
+      <c r="K38" s="7"/>
+      <c r="L38" s="3">
         <f t="shared" si="7"/>
         <v>67.83948903880588</v>
       </c>
-      <c r="M38" s="5">
+      <c r="M38" s="3">
         <v>79.40088154</v>
       </c>
-      <c r="N38" s="5">
+      <c r="N38" s="3">
         <v>65</v>
       </c>
-      <c r="O38" s="5">
+      <c r="O38" s="3">
         <v>102.3</v>
       </c>
-      <c r="P38" s="5">
+      <c r="P38" s="3">
         <v>102</v>
       </c>
-      <c r="Q38" s="5">
+      <c r="Q38" s="3">
         <v>101.6</v>
       </c>
-      <c r="R38" s="5">
+      <c r="R38" s="3">
         <v>74.400000000000006</v>
       </c>
-      <c r="S38" s="5">
+      <c r="S38" s="3">
         <v>102.7</v>
       </c>
-      <c r="T38" s="5"/>
-      <c r="U38" s="9"/>
-      <c r="V38" s="5">
+      <c r="T38" s="3"/>
+      <c r="U38" s="7"/>
+      <c r="V38" s="3">
         <f t="shared" si="0"/>
         <v>71.324608551107843</v>
       </c>
-      <c r="W38" s="5">
+      <c r="W38" s="3">
         <f t="shared" si="1"/>
         <v>3.6350509635905226</v>
       </c>
-      <c r="X38" s="5">
+      <c r="X38" s="3">
         <f t="shared" si="2"/>
         <v>12.965226883647318</v>
       </c>
-      <c r="Y38" s="5">
+      <c r="Y38" s="3">
         <f t="shared" si="3"/>
         <v>5.0189057262096555E-2</v>
       </c>
-      <c r="Z38" s="5">
+      <c r="Z38" s="3">
         <f t="shared" si="4"/>
         <v>3.919331508087566E-2</v>
       </c>
@@ -41034,57 +41028,57 @@
       <c r="H39">
         <v>532</v>
       </c>
-      <c r="I39" s="5">
+      <c r="I39" s="3">
         <f t="shared" si="5"/>
         <v>11385.743893008999</v>
       </c>
-      <c r="J39" s="5">
+      <c r="J39" s="3">
         <f t="shared" si="6"/>
         <v>175</v>
       </c>
-      <c r="K39" s="9"/>
-      <c r="L39" s="5">
+      <c r="K39" s="7"/>
+      <c r="L39" s="3">
         <f t="shared" si="7"/>
         <v>65.06139367433714</v>
       </c>
-      <c r="M39" s="5">
+      <c r="M39" s="3">
         <v>77.714727339999996</v>
       </c>
-      <c r="N39" s="5"/>
-      <c r="O39" s="5">
+      <c r="N39" s="3"/>
+      <c r="O39" s="3">
         <v>102.3</v>
       </c>
-      <c r="P39" s="5">
+      <c r="P39" s="3">
         <v>102</v>
       </c>
-      <c r="Q39" s="5">
+      <c r="Q39" s="3">
         <v>101.6</v>
       </c>
-      <c r="R39" s="5">
+      <c r="R39" s="3">
         <v>74.400000000000006</v>
       </c>
-      <c r="S39" s="5">
+      <c r="S39" s="3">
         <v>102.7</v>
       </c>
-      <c r="T39" s="5"/>
-      <c r="U39" s="9"/>
-      <c r="V39" s="5">
+      <c r="T39" s="3"/>
+      <c r="U39" s="7"/>
+      <c r="V39" s="3">
         <f t="shared" si="0"/>
         <v>71.658800484785772</v>
       </c>
-      <c r="W39" s="5">
+      <c r="W39" s="3">
         <f t="shared" si="1"/>
         <v>3.6819728595635004</v>
       </c>
-      <c r="X39" s="5">
+      <c r="X39" s="3">
         <f t="shared" si="2"/>
         <v>12.406095985237382</v>
       </c>
-      <c r="Y39" s="5">
+      <c r="Y39" s="3">
         <f t="shared" si="3"/>
         <v>5.4456872192664374E-2</v>
       </c>
-      <c r="Z39" s="5">
+      <c r="Z39" s="3">
         <f t="shared" si="4"/>
         <v>3.6007809832410746E-2</v>
       </c>
@@ -41132,57 +41126,57 @@
       <c r="H40">
         <v>532</v>
       </c>
-      <c r="I40" s="5">
+      <c r="I40" s="3">
         <f t="shared" si="5"/>
         <v>11480.063846300998</v>
       </c>
-      <c r="J40" s="5">
+      <c r="J40" s="3">
         <f t="shared" si="6"/>
         <v>177</v>
       </c>
-      <c r="K40" s="9"/>
-      <c r="L40" s="5">
+      <c r="K40" s="7"/>
+      <c r="L40" s="3">
         <f t="shared" si="7"/>
         <v>64.859117775711852</v>
       </c>
-      <c r="M40" s="5">
+      <c r="M40" s="3">
         <v>76.064380240000006</v>
       </c>
-      <c r="N40" s="5"/>
-      <c r="O40" s="5">
+      <c r="N40" s="3"/>
+      <c r="O40" s="3">
         <v>102.3</v>
       </c>
-      <c r="P40" s="5">
+      <c r="P40" s="3">
         <v>102</v>
       </c>
-      <c r="Q40" s="5">
+      <c r="Q40" s="3">
         <v>101.6</v>
       </c>
-      <c r="R40" s="5">
+      <c r="R40" s="3">
         <v>74.400000000000006</v>
       </c>
-      <c r="S40" s="5">
+      <c r="S40" s="3">
         <v>102.7</v>
       </c>
-      <c r="T40" s="5"/>
-      <c r="U40" s="9"/>
-      <c r="V40" s="5">
+      <c r="T40" s="3"/>
+      <c r="U40" s="7"/>
+      <c r="V40" s="3">
         <f t="shared" si="0"/>
         <v>72.209964256174828</v>
       </c>
-      <c r="W40" s="5">
+      <c r="W40" s="3">
         <f t="shared" si="1"/>
         <v>3.6517218511382872</v>
       </c>
-      <c r="X40" s="5">
+      <c r="X40" s="3">
         <f t="shared" si="2"/>
         <v>12.019278938458111</v>
       </c>
-      <c r="Y40" s="5">
+      <c r="Y40" s="3">
         <f t="shared" si="3"/>
         <v>6.2750870521692745E-2</v>
       </c>
-      <c r="Z40" s="5">
+      <c r="Z40" s="3">
         <f t="shared" si="4"/>
         <v>3.5532122082355268E-2</v>
       </c>
@@ -41230,57 +41224,57 @@
       <c r="H41">
         <v>532</v>
       </c>
-      <c r="I41" s="5">
+      <c r="I41" s="3">
         <f t="shared" si="5"/>
         <v>11515.394229122998</v>
       </c>
-      <c r="J41" s="5">
+      <c r="J41" s="3">
         <f t="shared" si="6"/>
         <v>184</v>
       </c>
-      <c r="K41" s="9"/>
-      <c r="L41" s="5">
+      <c r="K41" s="7"/>
+      <c r="L41" s="3">
         <f t="shared" si="7"/>
         <v>62.583664288711944</v>
       </c>
-      <c r="M41" s="5">
+      <c r="M41" s="3">
         <v>74.449079859999998</v>
       </c>
-      <c r="N41" s="5"/>
-      <c r="O41" s="5">
+      <c r="N41" s="3"/>
+      <c r="O41" s="3">
         <v>102.3</v>
       </c>
-      <c r="P41" s="5">
+      <c r="P41" s="3">
         <v>102</v>
       </c>
-      <c r="Q41" s="5">
+      <c r="Q41" s="3">
         <v>101.6</v>
       </c>
-      <c r="R41" s="5">
+      <c r="R41" s="3">
         <v>74.400000000000006</v>
       </c>
-      <c r="S41" s="5">
+      <c r="S41" s="3">
         <v>102.7</v>
       </c>
-      <c r="T41" s="5"/>
-      <c r="U41" s="9"/>
-      <c r="V41" s="5">
+      <c r="T41" s="3"/>
+      <c r="U41" s="7"/>
+      <c r="V41" s="3">
         <f t="shared" si="0"/>
         <v>72.512932113796495</v>
       </c>
-      <c r="W41" s="5">
+      <c r="W41" s="3">
         <f t="shared" si="1"/>
         <v>3.5678761849153848</v>
       </c>
-      <c r="X41" s="5">
+      <c r="X41" s="3">
         <f t="shared" si="2"/>
         <v>11.824750763254618</v>
       </c>
-      <c r="Y41" s="5">
+      <c r="Y41" s="3">
         <f t="shared" si="3"/>
         <v>6.4736993381838775E-2</v>
       </c>
-      <c r="Z41" s="5">
+      <c r="Z41" s="3">
         <f t="shared" si="4"/>
         <v>3.7452767462295221E-2</v>
       </c>
@@ -41328,57 +41322,57 @@
       <c r="H42">
         <v>532</v>
       </c>
-      <c r="I42" s="5">
+      <c r="I42" s="3">
         <f t="shared" si="5"/>
         <v>11749.006155509998</v>
       </c>
-      <c r="J42" s="5">
+      <c r="J42" s="3">
         <f t="shared" si="6"/>
         <v>192</v>
       </c>
-      <c r="K42" s="9"/>
-      <c r="L42" s="5">
+      <c r="K42" s="7"/>
+      <c r="L42" s="3">
         <f t="shared" si="7"/>
         <v>61.192740393281241</v>
       </c>
-      <c r="M42" s="5">
+      <c r="M42" s="3">
         <v>72.868081930000002</v>
       </c>
-      <c r="N42" s="5"/>
-      <c r="O42" s="5">
+      <c r="N42" s="3"/>
+      <c r="O42" s="3">
         <v>102.3</v>
       </c>
-      <c r="P42" s="5">
+      <c r="P42" s="3">
         <v>102</v>
       </c>
-      <c r="Q42" s="5">
+      <c r="Q42" s="3">
         <v>101.6</v>
       </c>
-      <c r="R42" s="5">
+      <c r="R42" s="3">
         <v>74.400000000000006</v>
       </c>
-      <c r="S42" s="5">
+      <c r="S42" s="3">
         <v>102.7</v>
       </c>
-      <c r="T42" s="5"/>
-      <c r="U42" s="9"/>
-      <c r="V42" s="5">
+      <c r="T42" s="3"/>
+      <c r="U42" s="7"/>
+      <c r="V42" s="3">
         <f t="shared" si="0"/>
         <v>73.26151579181267</v>
       </c>
-      <c r="W42" s="5">
+      <c r="W42" s="3">
         <f t="shared" si="1"/>
         <v>3.4227632650563029</v>
       </c>
-      <c r="X42" s="5">
+      <c r="X42" s="3">
         <f t="shared" si="2"/>
         <v>11.436261426843004</v>
       </c>
-      <c r="Y42" s="5">
+      <c r="Y42" s="3">
         <f t="shared" si="3"/>
         <v>7.0313351535063545E-2</v>
       </c>
-      <c r="Z42" s="5">
+      <c r="Z42" s="3">
         <f t="shared" si="4"/>
         <v>3.5299239400389731E-2</v>
       </c>
@@ -41426,61 +41420,61 @@
       <c r="H43">
         <v>532</v>
       </c>
-      <c r="I43" s="5">
+      <c r="I43" s="3">
         <f t="shared" si="5"/>
         <v>12092.466287744999</v>
       </c>
-      <c r="J43" s="5">
+      <c r="J43" s="3">
         <f t="shared" si="6"/>
         <v>202.52588490000002</v>
       </c>
-      <c r="K43" s="9"/>
-      <c r="L43" s="5">
+      <c r="K43" s="7"/>
+      <c r="L43" s="3">
         <f t="shared" si="7"/>
         <v>59.708250595798276</v>
       </c>
-      <c r="M43" s="5">
+      <c r="M43" s="3">
         <v>71.320658019999996</v>
       </c>
-      <c r="N43" s="5">
+      <c r="N43" s="3">
         <v>65</v>
       </c>
-      <c r="O43" s="5">
+      <c r="O43" s="3">
         <v>102.3</v>
       </c>
-      <c r="P43" s="5">
+      <c r="P43" s="3">
         <v>102</v>
       </c>
-      <c r="Q43" s="5">
+      <c r="Q43" s="3">
         <v>101.6</v>
       </c>
-      <c r="R43" s="5">
+      <c r="R43" s="3">
         <v>74.400000000000006</v>
       </c>
-      <c r="S43" s="5">
+      <c r="S43" s="3">
         <v>102.7</v>
       </c>
-      <c r="T43" s="5">
+      <c r="T43" s="3">
         <v>76</v>
       </c>
-      <c r="U43" s="9"/>
-      <c r="V43" s="5">
+      <c r="U43" s="7"/>
+      <c r="V43" s="3">
         <f t="shared" si="0"/>
         <v>74.223899297500125</v>
       </c>
-      <c r="W43" s="5">
+      <c r="W43" s="3">
         <f t="shared" si="1"/>
         <v>3.1428988450864019</v>
       </c>
-      <c r="X43" s="5">
+      <c r="X43" s="3">
         <f t="shared" si="2"/>
         <v>11.111439362553419</v>
       </c>
-      <c r="Y43" s="5">
+      <c r="Y43" s="3">
         <f t="shared" si="3"/>
         <v>6.8019871251043598E-2</v>
       </c>
-      <c r="Z43" s="5">
+      <c r="Z43" s="3">
         <f t="shared" si="4"/>
         <v>2.9728968098453872E-2</v>
       </c>
@@ -41531,59 +41525,59 @@
       <c r="H44">
         <v>520</v>
       </c>
-      <c r="I44" s="5">
+      <c r="I44" s="3">
         <f t="shared" si="5"/>
         <v>12047.313171469001</v>
       </c>
-      <c r="J44" s="5">
+      <c r="J44" s="3">
         <f t="shared" si="6"/>
         <v>208.94864799999999</v>
       </c>
-      <c r="K44" s="9"/>
-      <c r="L44" s="5">
+      <c r="K44" s="7"/>
+      <c r="L44" s="3">
         <f t="shared" si="7"/>
         <v>57.656813225558658</v>
       </c>
-      <c r="M44" s="5">
+      <c r="M44" s="3">
         <v>69.806095139999996</v>
       </c>
-      <c r="N44" s="5"/>
-      <c r="O44" s="5">
+      <c r="N44" s="3"/>
+      <c r="O44" s="3">
         <v>102.3</v>
       </c>
-      <c r="P44" s="5">
+      <c r="P44" s="3">
         <v>102</v>
       </c>
-      <c r="Q44" s="5">
+      <c r="Q44" s="3">
         <v>101.6</v>
       </c>
-      <c r="R44" s="5">
+      <c r="R44" s="3">
         <v>74.400000000000006</v>
       </c>
-      <c r="S44" s="5">
+      <c r="S44" s="3">
         <v>102.7</v>
       </c>
-      <c r="T44" s="5">
+      <c r="T44" s="3">
         <v>76</v>
       </c>
-      <c r="U44" s="9"/>
-      <c r="V44" s="5">
+      <c r="U44" s="7"/>
+      <c r="V44" s="3">
         <f t="shared" si="0"/>
         <v>74.9295703657655</v>
       </c>
-      <c r="W44" s="5">
+      <c r="W44" s="3">
         <f t="shared" si="1"/>
         <v>3.0494794679202579</v>
       </c>
-      <c r="X44" s="5">
+      <c r="X44" s="3">
         <f t="shared" si="2"/>
         <v>10.559835648772097</v>
       </c>
-      <c r="Y44" s="5">
+      <c r="Y44" s="3">
         <f t="shared" si="3"/>
         <v>6.8646675671929766E-2</v>
       </c>
-      <c r="Z44" s="5">
+      <c r="Z44" s="3">
         <f t="shared" si="4"/>
         <v>2.7734639429088385E-2</v>
       </c>
@@ -41631,59 +41625,59 @@
       <c r="H45">
         <v>510</v>
       </c>
-      <c r="I45" s="5">
+      <c r="I45" s="3">
         <f t="shared" si="5"/>
         <v>12072.594883022</v>
       </c>
-      <c r="J45" s="5">
+      <c r="J45" s="3">
         <f t="shared" si="6"/>
         <v>213.6288232</v>
       </c>
-      <c r="K45" s="9"/>
-      <c r="L45" s="5">
+      <c r="K45" s="7"/>
+      <c r="L45" s="3">
         <f t="shared" si="7"/>
         <v>56.512013230160413</v>
       </c>
-      <c r="M45" s="5">
+      <c r="M45" s="3">
         <v>68.323695470000004</v>
       </c>
-      <c r="N45" s="5"/>
-      <c r="O45" s="5">
+      <c r="N45" s="3"/>
+      <c r="O45" s="3">
         <v>102.3</v>
       </c>
-      <c r="P45" s="5">
+      <c r="P45" s="3">
         <v>102</v>
       </c>
-      <c r="Q45" s="5">
+      <c r="Q45" s="3">
         <v>101.6</v>
       </c>
-      <c r="R45" s="5">
+      <c r="R45" s="3">
         <v>74.400000000000006</v>
       </c>
-      <c r="S45" s="5">
+      <c r="S45" s="3">
         <v>102.7</v>
       </c>
-      <c r="T45" s="5">
+      <c r="T45" s="3">
         <v>76</v>
       </c>
-      <c r="U45" s="9"/>
-      <c r="V45" s="5">
+      <c r="U45" s="7"/>
+      <c r="V45" s="3">
         <f t="shared" si="0"/>
         <v>75.431173564903631</v>
       </c>
-      <c r="W45" s="5">
+      <c r="W45" s="3">
         <f t="shared" si="1"/>
         <v>2.9381148248321756</v>
       </c>
-      <c r="X45" s="5">
+      <c r="X45" s="3">
         <f t="shared" si="2"/>
         <v>10.360119809527786</v>
       </c>
-      <c r="Y45" s="5">
+      <c r="Y45" s="3">
         <f t="shared" si="3"/>
         <v>6.8874008285438534E-2</v>
       </c>
-      <c r="Z45" s="5">
+      <c r="Z45" s="3">
         <f t="shared" si="4"/>
         <v>2.5625261610912303E-2</v>
       </c>
@@ -41731,59 +41725,59 @@
       <c r="H46">
         <v>500</v>
       </c>
-      <c r="I46" s="5">
+      <c r="I46" s="3">
         <f t="shared" si="5"/>
         <v>12101.860575282</v>
       </c>
-      <c r="J46" s="5">
+      <c r="J46" s="3">
         <f t="shared" si="6"/>
         <v>217.3311205</v>
       </c>
-      <c r="K46" s="9"/>
-      <c r="L46" s="5">
+      <c r="K46" s="7"/>
+      <c r="L46" s="3">
         <f t="shared" si="7"/>
         <v>55.683974515200646</v>
       </c>
-      <c r="M46" s="5">
+      <c r="M46" s="3">
         <v>66.87277598</v>
       </c>
-      <c r="N46" s="5"/>
-      <c r="O46" s="5">
+      <c r="N46" s="3"/>
+      <c r="O46" s="3">
         <v>102.3</v>
       </c>
-      <c r="P46" s="5">
+      <c r="P46" s="3">
         <v>102</v>
       </c>
-      <c r="Q46" s="5">
+      <c r="Q46" s="3">
         <v>101.6</v>
       </c>
-      <c r="R46" s="5">
+      <c r="R46" s="3">
         <v>74.400000000000006</v>
       </c>
-      <c r="S46" s="5">
+      <c r="S46" s="3">
         <v>102.7</v>
       </c>
-      <c r="T46" s="5">
+      <c r="T46" s="3">
         <v>76</v>
       </c>
-      <c r="U46" s="9"/>
-      <c r="V46" s="5">
+      <c r="U46" s="7"/>
+      <c r="V46" s="3">
         <f t="shared" si="0"/>
         <v>75.885438795728334</v>
       </c>
-      <c r="W46" s="5">
+      <c r="W46" s="3">
         <f t="shared" si="1"/>
         <v>2.879689707480201</v>
       </c>
-      <c r="X46" s="5">
+      <c r="X46" s="3">
         <f t="shared" si="2"/>
         <v>10.157893576387982</v>
       </c>
-      <c r="Y46" s="5">
+      <c r="Y46" s="3">
         <f t="shared" si="3"/>
         <v>6.929975723839947E-2</v>
       </c>
-      <c r="Z46" s="5">
+      <c r="Z46" s="3">
         <f t="shared" si="4"/>
         <v>2.395386943988528E-2</v>
       </c>
@@ -41831,59 +41825,59 @@
       <c r="H47">
         <v>490</v>
       </c>
-      <c r="I47" s="5">
+      <c r="I47" s="3">
         <f t="shared" si="5"/>
         <v>11968.629252107001</v>
       </c>
-      <c r="J47" s="5">
+      <c r="J47" s="3">
         <f t="shared" si="6"/>
         <v>220.40369699999999</v>
       </c>
-      <c r="K47" s="9"/>
-      <c r="L47" s="5">
+      <c r="K47" s="7"/>
+      <c r="L47" s="3">
         <f t="shared" si="7"/>
         <v>54.303214578596659</v>
       </c>
-      <c r="M47" s="5">
+      <c r="M47" s="3">
         <v>65.452668169999995</v>
       </c>
-      <c r="N47" s="5"/>
-      <c r="O47" s="5">
+      <c r="N47" s="3"/>
+      <c r="O47" s="3">
         <v>102.3</v>
       </c>
-      <c r="P47" s="5">
+      <c r="P47" s="3">
         <v>102</v>
       </c>
-      <c r="Q47" s="5">
+      <c r="Q47" s="3">
         <v>101.6</v>
       </c>
-      <c r="R47" s="5">
+      <c r="R47" s="3">
         <v>74.400000000000006</v>
       </c>
-      <c r="S47" s="5">
+      <c r="S47" s="3">
         <v>102.7</v>
       </c>
-      <c r="T47" s="5">
+      <c r="T47" s="3">
         <v>76</v>
       </c>
-      <c r="U47" s="9"/>
-      <c r="V47" s="5">
+      <c r="U47" s="7"/>
+      <c r="V47" s="3">
         <f t="shared" si="0"/>
         <v>76.105833075215784</v>
       </c>
-      <c r="W47" s="5">
+      <c r="W47" s="3">
         <f t="shared" si="1"/>
         <v>2.8598543700377621</v>
       </c>
-      <c r="X47" s="5">
+      <c r="X47" s="3">
         <f t="shared" si="2"/>
         <v>10.151538446109917</v>
       </c>
-      <c r="Y47" s="5">
+      <c r="Y47" s="3">
         <f t="shared" si="3"/>
         <v>7.0670081108168512E-2</v>
       </c>
-      <c r="Z47" s="5">
+      <c r="Z47" s="3">
         <f t="shared" si="4"/>
         <v>2.2499614202068571E-2</v>
       </c>
@@ -41931,61 +41925,61 @@
       <c r="H48">
         <v>480</v>
       </c>
-      <c r="I48" s="5">
+      <c r="I48" s="3">
         <f t="shared" si="5"/>
         <v>11835.472545881999</v>
       </c>
-      <c r="J48" s="5">
+      <c r="J48" s="3">
         <f t="shared" si="6"/>
         <v>223.03538889999999</v>
       </c>
-      <c r="K48" s="9"/>
-      <c r="L48" s="5">
+      <c r="K48" s="7"/>
+      <c r="L48" s="3">
         <f t="shared" si="7"/>
         <v>53.065446717913204</v>
       </c>
-      <c r="M48" s="5">
+      <c r="M48" s="3">
         <v>64.062717710000001</v>
       </c>
-      <c r="N48" s="5">
+      <c r="N48" s="3">
         <v>65</v>
       </c>
-      <c r="O48" s="5">
+      <c r="O48" s="3">
         <v>102.3</v>
       </c>
-      <c r="P48" s="5">
+      <c r="P48" s="3">
         <v>102</v>
       </c>
-      <c r="Q48" s="5">
+      <c r="Q48" s="3">
         <v>101.6</v>
       </c>
-      <c r="R48" s="5">
+      <c r="R48" s="3">
         <v>74.400000000000006</v>
       </c>
-      <c r="S48" s="5">
+      <c r="S48" s="3">
         <v>102.7</v>
       </c>
-      <c r="T48" s="5">
+      <c r="T48" s="3">
         <v>76</v>
       </c>
-      <c r="U48" s="9"/>
-      <c r="V48" s="5">
+      <c r="U48" s="7"/>
+      <c r="V48" s="3">
         <f t="shared" si="0"/>
         <v>76.330708089414642</v>
       </c>
-      <c r="W48" s="5">
+      <c r="W48" s="3">
         <f t="shared" si="1"/>
         <v>2.8390188748053902</v>
       </c>
-      <c r="X48" s="5">
+      <c r="X48" s="3">
         <f t="shared" si="2"/>
         <v>10.144976276572667</v>
       </c>
-      <c r="Y48" s="5">
+      <c r="Y48" s="3">
         <f t="shared" si="3"/>
         <v>6.9244496163792704E-2</v>
       </c>
-      <c r="Z48" s="5">
+      <c r="Z48" s="3">
         <f t="shared" si="4"/>
         <v>2.1485842995637612E-2</v>
       </c>
@@ -42036,59 +42030,59 @@
       <c r="H49">
         <v>470</v>
       </c>
-      <c r="I49" s="5">
+      <c r="I49" s="3">
         <f t="shared" si="5"/>
         <v>11959.069885074001</v>
       </c>
-      <c r="J49" s="5">
+      <c r="J49" s="3">
         <f t="shared" si="6"/>
         <v>225.34045020000002</v>
       </c>
-      <c r="K49" s="9"/>
-      <c r="L49" s="5">
+      <c r="K49" s="7"/>
+      <c r="L49" s="3">
         <f t="shared" si="7"/>
         <v>53.071119164179251</v>
       </c>
-      <c r="M49" s="5">
+      <c r="M49" s="3">
         <v>62.70228419</v>
       </c>
-      <c r="N49" s="5"/>
-      <c r="O49" s="5">
+      <c r="N49" s="3"/>
+      <c r="O49" s="3">
         <v>102.3</v>
       </c>
-      <c r="P49" s="5">
+      <c r="P49" s="3">
         <v>102</v>
       </c>
-      <c r="Q49" s="5">
+      <c r="Q49" s="3">
         <v>101.6</v>
       </c>
-      <c r="R49" s="5">
+      <c r="R49" s="3">
         <v>74.400000000000006</v>
       </c>
-      <c r="S49" s="5">
+      <c r="S49" s="3">
         <v>102.7</v>
       </c>
-      <c r="T49" s="5">
+      <c r="T49" s="3">
         <v>76</v>
       </c>
-      <c r="U49" s="9"/>
-      <c r="V49" s="5">
+      <c r="U49" s="7"/>
+      <c r="V49" s="3">
         <f t="shared" si="0"/>
         <v>76.9726109259461</v>
       </c>
-      <c r="W49" s="5">
+      <c r="W49" s="3">
         <f t="shared" si="1"/>
         <v>2.7572146945268865</v>
       </c>
-      <c r="X49" s="5">
+      <c r="X49" s="3">
         <f t="shared" si="2"/>
         <v>9.9604441018167797</v>
       </c>
-      <c r="Y49" s="5">
+      <c r="Y49" s="3">
         <f t="shared" si="3"/>
         <v>6.6331133969712686E-2</v>
       </c>
-      <c r="Z49" s="5">
+      <c r="Z49" s="3">
         <f t="shared" si="4"/>
         <v>2.0079004722574553E-2</v>
       </c>
@@ -42136,59 +42130,59 @@
       <c r="H50">
         <v>460</v>
       </c>
-      <c r="I50" s="5">
+      <c r="I50" s="3">
         <f t="shared" si="5"/>
         <v>12080.381868788998</v>
       </c>
-      <c r="J50" s="5">
+      <c r="J50" s="3">
         <f t="shared" si="6"/>
         <v>227.39342440000001</v>
       </c>
-      <c r="K50" s="9"/>
-      <c r="L50" s="5">
+      <c r="K50" s="7"/>
+      <c r="L50" s="3">
         <f t="shared" si="7"/>
         <v>53.125467021151898</v>
       </c>
-      <c r="M50" s="5">
+      <c r="M50" s="3">
         <v>61.370740789999999</v>
       </c>
-      <c r="N50" s="5"/>
-      <c r="O50" s="5">
+      <c r="N50" s="3"/>
+      <c r="O50" s="3">
         <v>102.3</v>
       </c>
-      <c r="P50" s="5">
+      <c r="P50" s="3">
         <v>102</v>
       </c>
-      <c r="Q50" s="5">
+      <c r="Q50" s="3">
         <v>101.6</v>
       </c>
-      <c r="R50" s="5">
+      <c r="R50" s="3">
         <v>74.400000000000006</v>
       </c>
-      <c r="S50" s="5">
+      <c r="S50" s="3">
         <v>102.7</v>
       </c>
-      <c r="T50" s="5">
+      <c r="T50" s="3">
         <v>76</v>
       </c>
-      <c r="U50" s="9"/>
-      <c r="V50" s="5">
+      <c r="U50" s="7"/>
+      <c r="V50" s="3">
         <f t="shared" ref="V50:V73" si="8">B50/$I50*100</f>
         <v>77.595781067305666</v>
       </c>
-      <c r="W50" s="5">
+      <c r="W50" s="3">
         <f t="shared" ref="W50:W73" si="9">C50/$I50*100</f>
         <v>2.6775905638852597</v>
       </c>
-      <c r="X50" s="5">
+      <c r="X50" s="3">
         <f t="shared" ref="X50:X73" si="10">D50/$I50*100</f>
         <v>9.7815373043207821</v>
       </c>
-      <c r="Y50" s="5">
+      <c r="Y50" s="3">
         <f t="shared" ref="Y50:Y73" si="11">E50/$I50*100</f>
         <v>6.3489383724000259E-2</v>
       </c>
-      <c r="Z50" s="5">
+      <c r="Z50" s="3">
         <f t="shared" ref="Z50:Z73" si="12">F50/$I50*100</f>
         <v>1.8765006881584983E-2</v>
       </c>
@@ -42236,59 +42230,59 @@
       <c r="H51">
         <v>450</v>
       </c>
-      <c r="I51" s="5">
+      <c r="I51" s="3">
         <f t="shared" si="5"/>
         <v>12202.605561795001</v>
       </c>
-      <c r="J51" s="5">
+      <c r="J51" s="3">
         <f t="shared" si="6"/>
         <v>229.24571610000004</v>
       </c>
-      <c r="K51" s="9"/>
-      <c r="L51" s="5">
+      <c r="K51" s="7"/>
+      <c r="L51" s="3">
         <f t="shared" si="7"/>
         <v>53.229372262171573</v>
       </c>
-      <c r="M51" s="5">
+      <c r="M51" s="3">
         <v>60.067473990000003</v>
       </c>
-      <c r="N51" s="5"/>
-      <c r="O51" s="5">
+      <c r="N51" s="3"/>
+      <c r="O51" s="3">
         <v>102.3</v>
       </c>
-      <c r="P51" s="5">
+      <c r="P51" s="3">
         <v>102</v>
       </c>
-      <c r="Q51" s="5">
+      <c r="Q51" s="3">
         <v>101.6</v>
       </c>
-      <c r="R51" s="5">
+      <c r="R51" s="3">
         <v>74.400000000000006</v>
       </c>
-      <c r="S51" s="5">
+      <c r="S51" s="3">
         <v>102.7</v>
       </c>
-      <c r="T51" s="5">
+      <c r="T51" s="3">
         <v>76</v>
       </c>
-      <c r="U51" s="9"/>
-      <c r="V51" s="5">
+      <c r="U51" s="7"/>
+      <c r="V51" s="3">
         <f t="shared" si="8"/>
         <v>78.180638976555244</v>
       </c>
-      <c r="W51" s="5">
+      <c r="W51" s="3">
         <f t="shared" si="9"/>
         <v>2.6257367057996426</v>
       </c>
-      <c r="X51" s="5">
+      <c r="X51" s="3">
         <f t="shared" si="10"/>
         <v>9.6054702503026892</v>
       </c>
-      <c r="Y51" s="5">
+      <c r="Y51" s="3">
         <f t="shared" si="11"/>
         <v>6.0601702067244391E-2</v>
       </c>
-      <c r="Z51" s="5">
+      <c r="Z51" s="3">
         <f t="shared" si="12"/>
         <v>1.7452295882345401E-2</v>
       </c>
@@ -42336,59 +42330,59 @@
       <c r="H52">
         <v>450</v>
       </c>
-      <c r="I52" s="5">
+      <c r="I52" s="3">
         <f t="shared" si="5"/>
         <v>12385.221646146001</v>
       </c>
-      <c r="J52" s="5">
+      <c r="J52" s="3">
         <f t="shared" si="6"/>
         <v>230.93431240000001</v>
       </c>
-      <c r="K52" s="9"/>
-      <c r="L52" s="5">
+      <c r="K52" s="7"/>
+      <c r="L52" s="3">
         <f t="shared" si="7"/>
         <v>53.630928714887673</v>
       </c>
-      <c r="M52" s="5">
+      <c r="M52" s="3">
         <v>58.791883319999997</v>
       </c>
-      <c r="N52" s="5"/>
-      <c r="O52" s="5">
+      <c r="N52" s="3"/>
+      <c r="O52" s="3">
         <v>102.3</v>
       </c>
-      <c r="P52" s="5">
+      <c r="P52" s="3">
         <v>102</v>
       </c>
-      <c r="Q52" s="5">
+      <c r="Q52" s="3">
         <v>101.6</v>
       </c>
-      <c r="R52" s="5">
+      <c r="R52" s="3">
         <v>74.400000000000006</v>
       </c>
-      <c r="S52" s="5">
+      <c r="S52" s="3">
         <v>102.7</v>
       </c>
-      <c r="T52" s="5">
+      <c r="T52" s="3">
         <v>76</v>
       </c>
-      <c r="U52" s="9"/>
-      <c r="V52" s="5">
+      <c r="U52" s="7"/>
+      <c r="V52" s="3">
         <f t="shared" si="8"/>
         <v>78.608268880109733</v>
       </c>
-      <c r="W52" s="5">
+      <c r="W52" s="3">
         <f t="shared" si="9"/>
         <v>2.5623556103152434</v>
       </c>
-      <c r="X52" s="5">
+      <c r="X52" s="3">
         <f t="shared" si="10"/>
         <v>9.3868989043225639</v>
       </c>
-      <c r="Y52" s="5">
+      <c r="Y52" s="3">
         <f t="shared" si="11"/>
         <v>5.748959151825634E-2</v>
       </c>
-      <c r="Z52" s="5">
+      <c r="Z52" s="3">
         <f t="shared" si="12"/>
         <v>1.6089953574792152E-2</v>
       </c>
@@ -42436,61 +42430,61 @@
       <c r="H53">
         <v>450</v>
       </c>
-      <c r="I53" s="5">
+      <c r="I53" s="3">
         <f t="shared" si="5"/>
         <v>12565.504791508998</v>
       </c>
-      <c r="J53" s="5">
+      <c r="J53" s="3">
         <f t="shared" si="6"/>
         <v>232.48673840000001</v>
       </c>
-      <c r="K53" s="9"/>
-      <c r="L53" s="5">
+      <c r="K53" s="7"/>
+      <c r="L53" s="3">
         <f t="shared" si="7"/>
         <v>54.048264765492526</v>
       </c>
-      <c r="M53" s="5">
+      <c r="M53" s="3">
         <v>57.54338104</v>
       </c>
-      <c r="N53" s="5">
+      <c r="N53" s="3">
         <v>60</v>
       </c>
-      <c r="O53" s="5">
+      <c r="O53" s="3">
         <v>102.3</v>
       </c>
-      <c r="P53" s="5">
+      <c r="P53" s="3">
         <v>102</v>
       </c>
-      <c r="Q53" s="5">
+      <c r="Q53" s="3">
         <v>101.6</v>
       </c>
-      <c r="R53" s="5">
+      <c r="R53" s="3">
         <v>74.400000000000006</v>
       </c>
-      <c r="S53" s="5">
+      <c r="S53" s="3">
         <v>102.7</v>
       </c>
-      <c r="T53" s="5">
+      <c r="T53" s="3">
         <v>76</v>
       </c>
-      <c r="U53" s="9"/>
-      <c r="V53" s="5">
+      <c r="U53" s="7"/>
+      <c r="V53" s="3">
         <f t="shared" si="8"/>
         <v>79.019573807409259</v>
       </c>
-      <c r="W53" s="5">
+      <c r="W53" s="3">
         <f t="shared" si="9"/>
         <v>2.5012807301811204</v>
       </c>
-      <c r="X53" s="5">
+      <c r="X53" s="3">
         <f t="shared" si="10"/>
         <v>9.1763828284810867</v>
       </c>
-      <c r="Y53" s="5">
+      <c r="Y53" s="3">
         <f t="shared" si="11"/>
         <v>5.4478034218137669E-2</v>
       </c>
-      <c r="Z53" s="5">
+      <c r="Z53" s="3">
         <f t="shared" si="12"/>
         <v>1.4773073106099025E-2</v>
       </c>
@@ -42541,55 +42535,55 @@
       <c r="H54">
         <v>450</v>
       </c>
-      <c r="I54" s="5">
+      <c r="I54" s="3">
         <f t="shared" si="5"/>
         <v>12746.920713208998</v>
       </c>
-      <c r="J54" s="5">
+      <c r="J54" s="3">
         <f t="shared" si="6"/>
         <v>233.92404590000001</v>
       </c>
-      <c r="K54" s="9"/>
-      <c r="L54" s="5">
+      <c r="K54" s="7"/>
+      <c r="L54" s="3">
         <f t="shared" si="7"/>
         <v>54.491707614608238</v>
       </c>
-      <c r="M54" s="5">
+      <c r="M54" s="3">
         <v>56.321391920000003</v>
       </c>
-      <c r="N54" s="5"/>
-      <c r="O54" s="5"/>
-      <c r="P54" s="5">
+      <c r="N54" s="3"/>
+      <c r="O54" s="3"/>
+      <c r="P54" s="3">
         <v>102</v>
       </c>
-      <c r="Q54" s="5">
+      <c r="Q54" s="3">
         <v>101.6</v>
       </c>
-      <c r="R54" s="5"/>
-      <c r="S54" s="5">
+      <c r="R54" s="3"/>
+      <c r="S54" s="3">
         <v>102.7</v>
       </c>
-      <c r="T54" s="5">
+      <c r="T54" s="3">
         <v>76</v>
       </c>
-      <c r="U54" s="9"/>
-      <c r="V54" s="5">
+      <c r="U54" s="7"/>
+      <c r="V54" s="3">
         <f t="shared" si="8"/>
         <v>79.393880511964468</v>
       </c>
-      <c r="W54" s="5">
+      <c r="W54" s="3">
         <f t="shared" si="9"/>
         <v>2.4656821601966037</v>
       </c>
-      <c r="X54" s="5">
+      <c r="X54" s="3">
         <f t="shared" si="10"/>
         <v>8.9710247496481053</v>
       </c>
-      <c r="Y54" s="5">
+      <c r="Y54" s="3">
         <f t="shared" si="11"/>
         <v>5.3702695372588399E-2</v>
       </c>
-      <c r="Z54" s="5">
+      <c r="Z54" s="3">
         <f t="shared" si="12"/>
         <v>1.456282070599527E-2</v>
       </c>
@@ -42637,55 +42631,55 @@
       <c r="H55">
         <v>450</v>
       </c>
-      <c r="I55" s="5">
+      <c r="I55" s="3">
         <f t="shared" si="5"/>
         <v>12746.920713208998</v>
       </c>
-      <c r="J55" s="5">
+      <c r="J55" s="3">
         <f t="shared" si="6"/>
         <v>235.2627057</v>
       </c>
-      <c r="K55" s="9"/>
-      <c r="L55" s="5">
+      <c r="K55" s="7"/>
+      <c r="L55" s="3">
         <f t="shared" si="7"/>
         <v>54.181646322913124</v>
       </c>
-      <c r="M55" s="5">
+      <c r="M55" s="3">
         <v>55.125352909999997</v>
       </c>
-      <c r="N55" s="5"/>
-      <c r="O55" s="5"/>
-      <c r="P55" s="5">
+      <c r="N55" s="3"/>
+      <c r="O55" s="3"/>
+      <c r="P55" s="3">
         <v>102</v>
       </c>
-      <c r="Q55" s="5">
+      <c r="Q55" s="3">
         <v>101.6</v>
       </c>
-      <c r="R55" s="5"/>
-      <c r="S55" s="5">
+      <c r="R55" s="3"/>
+      <c r="S55" s="3">
         <v>102.7</v>
       </c>
-      <c r="T55" s="5">
+      <c r="T55" s="3">
         <v>76</v>
       </c>
-      <c r="U55" s="9"/>
-      <c r="V55" s="5">
+      <c r="U55" s="7"/>
+      <c r="V55" s="3">
         <f t="shared" si="8"/>
         <v>79.393880511964468</v>
       </c>
-      <c r="W55" s="5">
+      <c r="W55" s="3">
         <f t="shared" si="9"/>
         <v>2.4656821601966037</v>
       </c>
-      <c r="X55" s="5">
+      <c r="X55" s="3">
         <f t="shared" si="10"/>
         <v>8.9710247496481053</v>
       </c>
-      <c r="Y55" s="5">
+      <c r="Y55" s="3">
         <f t="shared" si="11"/>
         <v>5.3702695372588399E-2</v>
       </c>
-      <c r="Z55" s="5">
+      <c r="Z55" s="3">
         <f t="shared" si="12"/>
         <v>1.456282070599527E-2</v>
       </c>
@@ -42733,55 +42727,55 @@
       <c r="H56">
         <v>450</v>
       </c>
-      <c r="I56" s="5">
+      <c r="I56" s="3">
         <f t="shared" si="5"/>
         <v>12746.920713208998</v>
       </c>
-      <c r="J56" s="5">
+      <c r="J56" s="3">
         <f t="shared" si="6"/>
         <v>236.51585300000002</v>
       </c>
-      <c r="K56" s="9"/>
-      <c r="L56" s="5">
+      <c r="K56" s="7"/>
+      <c r="L56" s="3">
         <f t="shared" si="7"/>
         <v>53.894572188397859</v>
       </c>
-      <c r="M56" s="5">
+      <c r="M56" s="3">
         <v>53.95471294</v>
       </c>
-      <c r="N56" s="5"/>
-      <c r="O56" s="5"/>
-      <c r="P56" s="5">
+      <c r="N56" s="3"/>
+      <c r="O56" s="3"/>
+      <c r="P56" s="3">
         <v>102</v>
       </c>
-      <c r="Q56" s="5">
+      <c r="Q56" s="3">
         <v>101.6</v>
       </c>
-      <c r="R56" s="5"/>
-      <c r="S56" s="5">
+      <c r="R56" s="3"/>
+      <c r="S56" s="3">
         <v>102.7</v>
       </c>
-      <c r="T56" s="5">
+      <c r="T56" s="3">
         <v>76</v>
       </c>
-      <c r="U56" s="9"/>
-      <c r="V56" s="5">
+      <c r="U56" s="7"/>
+      <c r="V56" s="3">
         <f t="shared" si="8"/>
         <v>79.393880511964468</v>
       </c>
-      <c r="W56" s="5">
+      <c r="W56" s="3">
         <f t="shared" si="9"/>
         <v>2.4656821601966037</v>
       </c>
-      <c r="X56" s="5">
+      <c r="X56" s="3">
         <f t="shared" si="10"/>
         <v>8.9710247496481053</v>
       </c>
-      <c r="Y56" s="5">
+      <c r="Y56" s="3">
         <f t="shared" si="11"/>
         <v>5.3702695372588399E-2</v>
       </c>
-      <c r="Z56" s="5">
+      <c r="Z56" s="3">
         <f t="shared" si="12"/>
         <v>1.456282070599527E-2</v>
       </c>
@@ -42829,55 +42823,55 @@
       <c r="H57">
         <v>450</v>
       </c>
-      <c r="I57" s="5">
+      <c r="I57" s="3">
         <f t="shared" si="5"/>
         <v>12746.920713208998</v>
       </c>
-      <c r="J57" s="5">
+      <c r="J57" s="3">
         <f t="shared" si="6"/>
         <v>237.69413579999997</v>
       </c>
-      <c r="K57" s="9"/>
-      <c r="L57" s="5">
+      <c r="K57" s="7"/>
+      <c r="L57" s="3">
         <f t="shared" si="7"/>
         <v>53.627409318732546</v>
       </c>
-      <c r="M57" s="5">
+      <c r="M57" s="3">
         <v>52.808932630000001</v>
       </c>
-      <c r="N57" s="5"/>
-      <c r="O57" s="5"/>
-      <c r="P57" s="5">
+      <c r="N57" s="3"/>
+      <c r="O57" s="3"/>
+      <c r="P57" s="3">
         <v>102</v>
       </c>
-      <c r="Q57" s="5">
+      <c r="Q57" s="3">
         <v>101.6</v>
       </c>
-      <c r="R57" s="5"/>
-      <c r="S57" s="5">
+      <c r="R57" s="3"/>
+      <c r="S57" s="3">
         <v>102.7</v>
       </c>
-      <c r="T57" s="5">
+      <c r="T57" s="3">
         <v>76</v>
       </c>
-      <c r="U57" s="9"/>
-      <c r="V57" s="5">
+      <c r="U57" s="7"/>
+      <c r="V57" s="3">
         <f t="shared" si="8"/>
         <v>79.393880511964468</v>
       </c>
-      <c r="W57" s="5">
+      <c r="W57" s="3">
         <f t="shared" si="9"/>
         <v>2.4656821601966037</v>
       </c>
-      <c r="X57" s="5">
+      <c r="X57" s="3">
         <f t="shared" si="10"/>
         <v>8.9710247496481053</v>
       </c>
-      <c r="Y57" s="5">
+      <c r="Y57" s="3">
         <f t="shared" si="11"/>
         <v>5.3702695372588399E-2</v>
       </c>
-      <c r="Z57" s="5">
+      <c r="Z57" s="3">
         <f t="shared" si="12"/>
         <v>1.456282070599527E-2</v>
       </c>
@@ -42925,55 +42919,55 @@
       <c r="H58">
         <v>450</v>
       </c>
-      <c r="I58" s="5">
+      <c r="I58" s="3">
         <f t="shared" si="5"/>
         <v>12746.920713208998</v>
       </c>
-      <c r="J58" s="5">
+      <c r="J58" s="3">
         <f t="shared" si="6"/>
         <v>238.80630870000002</v>
       </c>
-      <c r="K58" s="9"/>
-      <c r="L58" s="5">
+      <c r="K58" s="7"/>
+      <c r="L58" s="3">
         <f t="shared" si="7"/>
         <v>53.377654814062275</v>
       </c>
-      <c r="M58" s="5">
+      <c r="M58" s="3">
         <v>51.687484079999997</v>
       </c>
-      <c r="N58" s="5"/>
-      <c r="O58" s="5"/>
-      <c r="P58" s="5">
+      <c r="N58" s="3"/>
+      <c r="O58" s="3"/>
+      <c r="P58" s="3">
         <v>102</v>
       </c>
-      <c r="Q58" s="5">
+      <c r="Q58" s="3">
         <v>101.6</v>
       </c>
-      <c r="R58" s="5"/>
-      <c r="S58" s="5">
+      <c r="R58" s="3"/>
+      <c r="S58" s="3">
         <v>102.7</v>
       </c>
-      <c r="T58" s="5">
+      <c r="T58" s="3">
         <v>76</v>
       </c>
-      <c r="U58" s="9"/>
-      <c r="V58" s="5">
+      <c r="U58" s="7"/>
+      <c r="V58" s="3">
         <f t="shared" si="8"/>
         <v>79.393880511964468</v>
       </c>
-      <c r="W58" s="5">
+      <c r="W58" s="3">
         <f t="shared" si="9"/>
         <v>2.4656821601966037</v>
       </c>
-      <c r="X58" s="5">
+      <c r="X58" s="3">
         <f t="shared" si="10"/>
         <v>8.9710247496481053</v>
       </c>
-      <c r="Y58" s="5">
+      <c r="Y58" s="3">
         <f t="shared" si="11"/>
         <v>5.3702695372588399E-2</v>
       </c>
-      <c r="Z58" s="5">
+      <c r="Z58" s="3">
         <f t="shared" si="12"/>
         <v>1.456282070599527E-2</v>
       </c>
@@ -43024,55 +43018,55 @@
       <c r="H59">
         <v>450</v>
       </c>
-      <c r="I59" s="5">
+      <c r="I59" s="3">
         <f t="shared" si="5"/>
         <v>12746.920713208998</v>
       </c>
-      <c r="J59" s="5">
+      <c r="J59" s="3">
         <f t="shared" si="6"/>
         <v>239.85965880000001</v>
       </c>
-      <c r="K59" s="9"/>
-      <c r="L59" s="5">
+      <c r="K59" s="7"/>
+      <c r="L59" s="3">
         <f t="shared" si="7"/>
         <v>53.14324541684455</v>
       </c>
-      <c r="M59" s="5">
+      <c r="M59" s="3">
         <v>50.589850570000003</v>
       </c>
-      <c r="N59" s="5"/>
-      <c r="O59" s="5"/>
-      <c r="P59" s="5">
+      <c r="N59" s="3"/>
+      <c r="O59" s="3"/>
+      <c r="P59" s="3">
         <v>102</v>
       </c>
-      <c r="Q59" s="5">
+      <c r="Q59" s="3">
         <v>101.6</v>
       </c>
-      <c r="R59" s="5"/>
-      <c r="S59" s="5">
+      <c r="R59" s="3"/>
+      <c r="S59" s="3">
         <v>102.7</v>
       </c>
-      <c r="T59" s="5">
+      <c r="T59" s="3">
         <v>76</v>
       </c>
-      <c r="U59" s="9"/>
-      <c r="V59" s="5">
+      <c r="U59" s="7"/>
+      <c r="V59" s="3">
         <f t="shared" si="8"/>
         <v>79.393880511964468</v>
       </c>
-      <c r="W59" s="5">
+      <c r="W59" s="3">
         <f t="shared" si="9"/>
         <v>2.4656821601966037</v>
       </c>
-      <c r="X59" s="5">
+      <c r="X59" s="3">
         <f t="shared" si="10"/>
         <v>8.9710247496481053</v>
       </c>
-      <c r="Y59" s="5">
+      <c r="Y59" s="3">
         <f t="shared" si="11"/>
         <v>5.3702695372588399E-2</v>
       </c>
-      <c r="Z59" s="5">
+      <c r="Z59" s="3">
         <f t="shared" si="12"/>
         <v>1.456282070599527E-2</v>
       </c>
@@ -43120,55 +43114,55 @@
       <c r="H60">
         <v>450</v>
       </c>
-      <c r="I60" s="5">
+      <c r="I60" s="3">
         <f t="shared" si="5"/>
         <v>12746.920713208998</v>
       </c>
-      <c r="J60" s="5">
+      <c r="J60" s="3">
         <f t="shared" si="6"/>
         <v>240.86031829999999</v>
       </c>
-      <c r="K60" s="9"/>
-      <c r="L60" s="5">
+      <c r="K60" s="7"/>
+      <c r="L60" s="3">
         <f t="shared" si="7"/>
         <v>52.922460632690274</v>
       </c>
-      <c r="M60" s="5">
+      <c r="M60" s="3">
         <v>49.515526360000003</v>
       </c>
-      <c r="N60" s="5"/>
-      <c r="O60" s="5"/>
-      <c r="P60" s="5">
+      <c r="N60" s="3"/>
+      <c r="O60" s="3"/>
+      <c r="P60" s="3">
         <v>102</v>
       </c>
-      <c r="Q60" s="5">
+      <c r="Q60" s="3">
         <v>101.6</v>
       </c>
-      <c r="R60" s="5"/>
-      <c r="S60" s="5">
+      <c r="R60" s="3"/>
+      <c r="S60" s="3">
         <v>102.7</v>
       </c>
-      <c r="T60" s="5">
+      <c r="T60" s="3">
         <v>76</v>
       </c>
-      <c r="U60" s="9"/>
-      <c r="V60" s="5">
+      <c r="U60" s="7"/>
+      <c r="V60" s="3">
         <f t="shared" si="8"/>
         <v>79.393880511964468</v>
       </c>
-      <c r="W60" s="5">
+      <c r="W60" s="3">
         <f t="shared" si="9"/>
         <v>2.4656821601966037</v>
       </c>
-      <c r="X60" s="5">
+      <c r="X60" s="3">
         <f t="shared" si="10"/>
         <v>8.9710247496481053</v>
       </c>
-      <c r="Y60" s="5">
+      <c r="Y60" s="3">
         <f t="shared" si="11"/>
         <v>5.3702695372588399E-2</v>
       </c>
-      <c r="Z60" s="5">
+      <c r="Z60" s="3">
         <f t="shared" si="12"/>
         <v>1.456282070599527E-2</v>
       </c>
@@ -43216,55 +43210,55 @@
       <c r="H61">
         <v>450</v>
       </c>
-      <c r="I61" s="5">
+      <c r="I61" s="3">
         <f t="shared" si="5"/>
         <v>12746.920713208998</v>
       </c>
-      <c r="J61" s="5">
+      <c r="J61" s="3">
         <f t="shared" si="6"/>
         <v>241.81349740000002</v>
       </c>
-      <c r="K61" s="9"/>
-      <c r="L61" s="5">
+      <c r="K61" s="7"/>
+      <c r="L61" s="3">
         <f t="shared" si="7"/>
         <v>52.71385117152272</v>
       </c>
-      <c r="M61" s="5">
+      <c r="M61" s="3">
         <v>48.464016460000003</v>
       </c>
-      <c r="N61" s="5"/>
-      <c r="O61" s="5"/>
-      <c r="P61" s="5">
+      <c r="N61" s="3"/>
+      <c r="O61" s="3"/>
+      <c r="P61" s="3">
         <v>102</v>
       </c>
-      <c r="Q61" s="5">
+      <c r="Q61" s="3">
         <v>101.6</v>
       </c>
-      <c r="R61" s="5"/>
-      <c r="S61" s="5">
+      <c r="R61" s="3"/>
+      <c r="S61" s="3">
         <v>102.7</v>
       </c>
-      <c r="T61" s="5">
+      <c r="T61" s="3">
         <v>76</v>
       </c>
-      <c r="U61" s="9"/>
-      <c r="V61" s="5">
+      <c r="U61" s="7"/>
+      <c r="V61" s="3">
         <f t="shared" si="8"/>
         <v>79.393880511964468</v>
       </c>
-      <c r="W61" s="5">
+      <c r="W61" s="3">
         <f t="shared" si="9"/>
         <v>2.4656821601966037</v>
       </c>
-      <c r="X61" s="5">
+      <c r="X61" s="3">
         <f t="shared" si="10"/>
         <v>8.9710247496481053</v>
       </c>
-      <c r="Y61" s="5">
+      <c r="Y61" s="3">
         <f t="shared" si="11"/>
         <v>5.3702695372588399E-2</v>
       </c>
-      <c r="Z61" s="5">
+      <c r="Z61" s="3">
         <f t="shared" si="12"/>
         <v>1.456282070599527E-2</v>
       </c>
@@ -43312,55 +43306,55 @@
       <c r="H62">
         <v>450</v>
       </c>
-      <c r="I62" s="5">
+      <c r="I62" s="3">
         <f t="shared" si="5"/>
         <v>12746.920713208998</v>
       </c>
-      <c r="J62" s="5">
+      <c r="J62" s="3">
         <f t="shared" si="6"/>
         <v>242.72366120000004</v>
       </c>
-      <c r="K62" s="9"/>
-      <c r="L62" s="5">
+      <c r="K62" s="7"/>
+      <c r="L62" s="3">
         <f t="shared" si="7"/>
         <v>52.516185073138622</v>
       </c>
-      <c r="M62" s="5">
+      <c r="M62" s="3">
         <v>47.43483638</v>
       </c>
-      <c r="N62" s="5"/>
-      <c r="O62" s="5"/>
-      <c r="P62" s="5">
+      <c r="N62" s="3"/>
+      <c r="O62" s="3"/>
+      <c r="P62" s="3">
         <v>102</v>
       </c>
-      <c r="Q62" s="5">
+      <c r="Q62" s="3">
         <v>101.6</v>
       </c>
-      <c r="R62" s="5"/>
-      <c r="S62" s="5">
+      <c r="R62" s="3"/>
+      <c r="S62" s="3">
         <v>102.7</v>
       </c>
-      <c r="T62" s="5">
+      <c r="T62" s="3">
         <v>76</v>
       </c>
-      <c r="U62" s="9"/>
-      <c r="V62" s="5">
+      <c r="U62" s="7"/>
+      <c r="V62" s="3">
         <f t="shared" si="8"/>
         <v>79.393880511964468</v>
       </c>
-      <c r="W62" s="5">
+      <c r="W62" s="3">
         <f t="shared" si="9"/>
         <v>2.4656821601966037</v>
       </c>
-      <c r="X62" s="5">
+      <c r="X62" s="3">
         <f t="shared" si="10"/>
         <v>8.9710247496481053</v>
       </c>
-      <c r="Y62" s="5">
+      <c r="Y62" s="3">
         <f t="shared" si="11"/>
         <v>5.3702695372588399E-2</v>
       </c>
-      <c r="Z62" s="5">
+      <c r="Z62" s="3">
         <f t="shared" si="12"/>
         <v>1.456282070599527E-2</v>
       </c>
@@ -43408,55 +43402,55 @@
       <c r="H63">
         <v>450</v>
       </c>
-      <c r="I63" s="5">
+      <c r="I63" s="3">
         <f t="shared" si="5"/>
         <v>12746.920713208998</v>
       </c>
-      <c r="J63" s="5">
+      <c r="J63" s="3">
         <f t="shared" si="6"/>
         <v>243.59466650000002</v>
       </c>
-      <c r="K63" s="9"/>
-      <c r="L63" s="5">
+      <c r="K63" s="7"/>
+      <c r="L63" s="3">
         <f t="shared" si="7"/>
         <v>52.32840643171059</v>
       </c>
-      <c r="M63" s="5">
+      <c r="M63" s="3">
         <v>46.427511940000002</v>
       </c>
-      <c r="N63" s="5"/>
-      <c r="O63" s="5"/>
-      <c r="P63" s="5">
+      <c r="N63" s="3"/>
+      <c r="O63" s="3"/>
+      <c r="P63" s="3">
         <v>102</v>
       </c>
-      <c r="Q63" s="5">
+      <c r="Q63" s="3">
         <v>101.6</v>
       </c>
-      <c r="R63" s="5"/>
-      <c r="S63" s="5">
+      <c r="R63" s="3"/>
+      <c r="S63" s="3">
         <v>102.7</v>
       </c>
-      <c r="T63" s="5">
+      <c r="T63" s="3">
         <v>76</v>
       </c>
-      <c r="U63" s="9"/>
-      <c r="V63" s="5">
+      <c r="U63" s="7"/>
+      <c r="V63" s="3">
         <f t="shared" si="8"/>
         <v>79.393880511964468</v>
       </c>
-      <c r="W63" s="5">
+      <c r="W63" s="3">
         <f t="shared" si="9"/>
         <v>2.4656821601966037</v>
       </c>
-      <c r="X63" s="5">
+      <c r="X63" s="3">
         <f t="shared" si="10"/>
         <v>8.9710247496481053</v>
       </c>
-      <c r="Y63" s="5">
+      <c r="Y63" s="3">
         <f t="shared" si="11"/>
         <v>5.3702695372588399E-2</v>
       </c>
-      <c r="Z63" s="5">
+      <c r="Z63" s="3">
         <f t="shared" si="12"/>
         <v>1.456282070599527E-2</v>
       </c>
@@ -43507,55 +43501,55 @@
       <c r="H64">
         <v>450</v>
       </c>
-      <c r="I64" s="5">
+      <c r="I64" s="3">
         <f t="shared" si="5"/>
         <v>12746.920713208998</v>
       </c>
-      <c r="J64" s="5">
+      <c r="J64" s="3">
         <f t="shared" si="6"/>
         <v>244.42986730000001</v>
       </c>
-      <c r="K64" s="9"/>
-      <c r="L64" s="5">
+      <c r="K64" s="7"/>
+      <c r="L64" s="3">
         <f t="shared" si="7"/>
         <v>52.149603704379203</v>
       </c>
-      <c r="M64" s="5">
+      <c r="M64" s="3">
         <v>45.441578999999997</v>
       </c>
-      <c r="N64" s="5"/>
-      <c r="O64" s="5"/>
-      <c r="P64" s="5">
+      <c r="N64" s="3"/>
+      <c r="O64" s="3"/>
+      <c r="P64" s="3">
         <v>102</v>
       </c>
-      <c r="Q64" s="5">
+      <c r="Q64" s="3">
         <v>101.6</v>
       </c>
-      <c r="R64" s="5"/>
-      <c r="S64" s="5">
+      <c r="R64" s="3"/>
+      <c r="S64" s="3">
         <v>102.7</v>
       </c>
-      <c r="T64" s="5">
+      <c r="T64" s="3">
         <v>76</v>
       </c>
-      <c r="U64" s="9"/>
-      <c r="V64" s="5">
+      <c r="U64" s="7"/>
+      <c r="V64" s="3">
         <f t="shared" si="8"/>
         <v>79.393880511964468</v>
       </c>
-      <c r="W64" s="5">
+      <c r="W64" s="3">
         <f t="shared" si="9"/>
         <v>2.4656821601966037</v>
       </c>
-      <c r="X64" s="5">
+      <c r="X64" s="3">
         <f t="shared" si="10"/>
         <v>8.9710247496481053</v>
       </c>
-      <c r="Y64" s="5">
+      <c r="Y64" s="3">
         <f t="shared" si="11"/>
         <v>5.3702695372588399E-2</v>
       </c>
-      <c r="Z64" s="5">
+      <c r="Z64" s="3">
         <f t="shared" si="12"/>
         <v>1.456282070599527E-2</v>
       </c>
@@ -43603,55 +43597,55 @@
       <c r="H65">
         <v>450</v>
       </c>
-      <c r="I65" s="5">
+      <c r="I65" s="3">
         <f t="shared" si="5"/>
         <v>12746.920713208998</v>
       </c>
-      <c r="J65" s="5">
+      <c r="J65" s="3">
         <f t="shared" si="6"/>
         <v>245.23219999999998</v>
       </c>
-      <c r="K65" s="9"/>
-      <c r="L65" s="5">
+      <c r="K65" s="7"/>
+      <c r="L65" s="3">
         <f t="shared" si="7"/>
         <v>51.978984461294232</v>
       </c>
-      <c r="M65" s="5">
+      <c r="M65" s="3">
         <v>44.476583300000001</v>
       </c>
-      <c r="N65" s="5"/>
-      <c r="O65" s="5"/>
-      <c r="P65" s="5">
+      <c r="N65" s="3"/>
+      <c r="O65" s="3"/>
+      <c r="P65" s="3">
         <v>102</v>
       </c>
-      <c r="Q65" s="5">
+      <c r="Q65" s="3">
         <v>101.6</v>
       </c>
-      <c r="R65" s="5"/>
-      <c r="S65" s="5">
+      <c r="R65" s="3"/>
+      <c r="S65" s="3">
         <v>102.7</v>
       </c>
-      <c r="T65" s="5">
+      <c r="T65" s="3">
         <v>76</v>
       </c>
-      <c r="U65" s="9"/>
-      <c r="V65" s="5">
+      <c r="U65" s="7"/>
+      <c r="V65" s="3">
         <f t="shared" si="8"/>
         <v>79.393880511964468</v>
       </c>
-      <c r="W65" s="5">
+      <c r="W65" s="3">
         <f t="shared" si="9"/>
         <v>2.4656821601966037</v>
       </c>
-      <c r="X65" s="5">
+      <c r="X65" s="3">
         <f t="shared" si="10"/>
         <v>8.9710247496481053</v>
       </c>
-      <c r="Y65" s="5">
+      <c r="Y65" s="3">
         <f t="shared" si="11"/>
         <v>5.3702695372588399E-2</v>
       </c>
-      <c r="Z65" s="5">
+      <c r="Z65" s="3">
         <f t="shared" si="12"/>
         <v>1.456282070599527E-2</v>
       </c>
@@ -43699,55 +43693,55 @@
       <c r="H66">
         <v>450</v>
       </c>
-      <c r="I66" s="5">
+      <c r="I66" s="3">
         <f t="shared" si="5"/>
         <v>12746.920713208998</v>
       </c>
-      <c r="J66" s="5">
+      <c r="J66" s="3">
         <f t="shared" si="6"/>
         <v>246.00424960000001</v>
       </c>
-      <c r="K66" s="9"/>
-      <c r="L66" s="5">
+      <c r="K66" s="7"/>
+      <c r="L66" s="3">
         <f t="shared" si="7"/>
         <v>51.815855758326691</v>
       </c>
-      <c r="M66" s="5">
+      <c r="M66" s="3">
         <v>43.532080209999997</v>
       </c>
-      <c r="N66" s="5"/>
-      <c r="O66" s="5"/>
-      <c r="P66" s="5">
+      <c r="N66" s="3"/>
+      <c r="O66" s="3"/>
+      <c r="P66" s="3">
         <v>102</v>
       </c>
-      <c r="Q66" s="5">
+      <c r="Q66" s="3">
         <v>101.6</v>
       </c>
-      <c r="R66" s="5"/>
-      <c r="S66" s="5">
+      <c r="R66" s="3"/>
+      <c r="S66" s="3">
         <v>102.7</v>
       </c>
-      <c r="T66" s="5">
+      <c r="T66" s="3">
         <v>76</v>
       </c>
-      <c r="U66" s="9"/>
-      <c r="V66" s="5">
+      <c r="U66" s="7"/>
+      <c r="V66" s="3">
         <f t="shared" si="8"/>
         <v>79.393880511964468</v>
       </c>
-      <c r="W66" s="5">
+      <c r="W66" s="3">
         <f t="shared" si="9"/>
         <v>2.4656821601966037</v>
       </c>
-      <c r="X66" s="5">
+      <c r="X66" s="3">
         <f t="shared" si="10"/>
         <v>8.9710247496481053</v>
       </c>
-      <c r="Y66" s="5">
+      <c r="Y66" s="3">
         <f t="shared" si="11"/>
         <v>5.3702695372588399E-2</v>
       </c>
-      <c r="Z66" s="5">
+      <c r="Z66" s="3">
         <f t="shared" si="12"/>
         <v>1.456282070599527E-2</v>
       </c>
@@ -43795,55 +43789,55 @@
       <c r="H67">
         <v>450</v>
       </c>
-      <c r="I67" s="5">
+      <c r="I67" s="3">
         <f t="shared" si="5"/>
         <v>12746.920713208998</v>
       </c>
-      <c r="J67" s="5">
+      <c r="J67" s="3">
         <f t="shared" si="6"/>
         <v>246.74830409999998</v>
       </c>
-      <c r="K67" s="9"/>
-      <c r="L67" s="5">
+      <c r="K67" s="7"/>
+      <c r="L67" s="3">
         <f t="shared" si="7"/>
         <v>51.659608197521948</v>
       </c>
-      <c r="M67" s="5">
+      <c r="M67" s="3">
         <v>42.60763455</v>
       </c>
-      <c r="N67" s="5"/>
-      <c r="O67" s="5"/>
-      <c r="P67" s="5">
+      <c r="N67" s="3"/>
+      <c r="O67" s="3"/>
+      <c r="P67" s="3">
         <v>102</v>
       </c>
-      <c r="Q67" s="5">
+      <c r="Q67" s="3">
         <v>101.6</v>
       </c>
-      <c r="R67" s="5"/>
-      <c r="S67" s="5">
+      <c r="R67" s="3"/>
+      <c r="S67" s="3">
         <v>102.7</v>
       </c>
-      <c r="T67" s="5">
+      <c r="T67" s="3">
         <v>76</v>
       </c>
-      <c r="U67" s="9"/>
-      <c r="V67" s="5">
+      <c r="U67" s="7"/>
+      <c r="V67" s="3">
         <f t="shared" si="8"/>
         <v>79.393880511964468</v>
       </c>
-      <c r="W67" s="5">
+      <c r="W67" s="3">
         <f t="shared" si="9"/>
         <v>2.4656821601966037</v>
       </c>
-      <c r="X67" s="5">
+      <c r="X67" s="3">
         <f t="shared" si="10"/>
         <v>8.9710247496481053</v>
       </c>
-      <c r="Y67" s="5">
+      <c r="Y67" s="3">
         <f t="shared" si="11"/>
         <v>5.3702695372588399E-2</v>
       </c>
-      <c r="Z67" s="5">
+      <c r="Z67" s="3">
         <f t="shared" si="12"/>
         <v>1.456282070599527E-2</v>
       </c>
@@ -43891,55 +43885,55 @@
       <c r="H68">
         <v>450</v>
       </c>
-      <c r="I68" s="5">
+      <c r="I68" s="3">
         <f t="shared" si="5"/>
         <v>12746.920713208998</v>
       </c>
-      <c r="J68" s="5">
+      <c r="J68" s="3">
         <f t="shared" si="6"/>
         <v>247.46639890000003</v>
       </c>
-      <c r="K68" s="9"/>
-      <c r="L68" s="5">
+      <c r="K68" s="7"/>
+      <c r="L68" s="3">
         <f t="shared" si="7"/>
         <v>51.509703013700729</v>
       </c>
-      <c r="M68" s="5">
+      <c r="M68" s="3">
         <v>41.702820389999999</v>
       </c>
-      <c r="N68" s="5"/>
-      <c r="O68" s="5"/>
-      <c r="P68" s="5">
+      <c r="N68" s="3"/>
+      <c r="O68" s="3"/>
+      <c r="P68" s="3">
         <v>102</v>
       </c>
-      <c r="Q68" s="5">
+      <c r="Q68" s="3">
         <v>101.6</v>
       </c>
-      <c r="R68" s="5"/>
-      <c r="S68" s="5">
+      <c r="R68" s="3"/>
+      <c r="S68" s="3">
         <v>102.7</v>
       </c>
-      <c r="T68" s="5">
+      <c r="T68" s="3">
         <v>76</v>
       </c>
-      <c r="U68" s="9"/>
-      <c r="V68" s="5">
+      <c r="U68" s="7"/>
+      <c r="V68" s="3">
         <f t="shared" si="8"/>
         <v>79.393880511964468</v>
       </c>
-      <c r="W68" s="5">
+      <c r="W68" s="3">
         <f t="shared" si="9"/>
         <v>2.4656821601966037</v>
       </c>
-      <c r="X68" s="5">
+      <c r="X68" s="3">
         <f t="shared" si="10"/>
         <v>8.9710247496481053</v>
       </c>
-      <c r="Y68" s="5">
+      <c r="Y68" s="3">
         <f t="shared" si="11"/>
         <v>5.3702695372588399E-2</v>
       </c>
-      <c r="Z68" s="5">
+      <c r="Z68" s="3">
         <f t="shared" si="12"/>
         <v>1.456282070599527E-2</v>
       </c>
@@ -43990,55 +43984,55 @@
       <c r="H69">
         <v>450</v>
       </c>
-      <c r="I69" s="5">
+      <c r="I69" s="3">
         <f t="shared" si="5"/>
         <v>12746.920713208998</v>
       </c>
-      <c r="J69" s="5">
+      <c r="J69" s="3">
         <f t="shared" si="6"/>
         <v>248.16035240000002</v>
       </c>
-      <c r="K69" s="9"/>
-      <c r="L69" s="5">
+      <c r="K69" s="7"/>
+      <c r="L69" s="3">
         <f t="shared" si="7"/>
         <v>51.365661718044031</v>
       </c>
-      <c r="M69" s="5">
+      <c r="M69" s="3">
         <v>40.817220829999997</v>
       </c>
-      <c r="N69" s="5"/>
-      <c r="O69" s="5"/>
-      <c r="P69" s="5">
+      <c r="N69" s="3"/>
+      <c r="O69" s="3"/>
+      <c r="P69" s="3">
         <v>102</v>
       </c>
-      <c r="Q69" s="5">
+      <c r="Q69" s="3">
         <v>101.6</v>
       </c>
-      <c r="R69" s="5"/>
-      <c r="S69" s="5">
+      <c r="R69" s="3"/>
+      <c r="S69" s="3">
         <v>102.7</v>
       </c>
-      <c r="T69" s="5">
+      <c r="T69" s="3">
         <v>76</v>
       </c>
-      <c r="U69" s="9"/>
-      <c r="V69" s="5">
+      <c r="U69" s="7"/>
+      <c r="V69" s="3">
         <f t="shared" si="8"/>
         <v>79.393880511964468</v>
       </c>
-      <c r="W69" s="5">
+      <c r="W69" s="3">
         <f t="shared" si="9"/>
         <v>2.4656821601966037</v>
       </c>
-      <c r="X69" s="5">
+      <c r="X69" s="3">
         <f t="shared" si="10"/>
         <v>8.9710247496481053</v>
       </c>
-      <c r="Y69" s="5">
+      <c r="Y69" s="3">
         <f t="shared" si="11"/>
         <v>5.3702695372588399E-2</v>
       </c>
-      <c r="Z69" s="5">
+      <c r="Z69" s="3">
         <f t="shared" si="12"/>
         <v>1.456282070599527E-2</v>
       </c>
@@ -44086,55 +44080,55 @@
       <c r="H70">
         <v>450</v>
       </c>
-      <c r="I70" s="5">
+      <c r="I70" s="3">
         <f t="shared" si="5"/>
         <v>12746.920713208998</v>
       </c>
-      <c r="J70" s="5">
+      <c r="J70" s="3">
         <f t="shared" si="6"/>
         <v>248.83179619999999</v>
       </c>
-      <c r="K70" s="9"/>
-      <c r="L70" s="5">
+      <c r="K70" s="7"/>
+      <c r="L70" s="3">
         <f t="shared" si="7"/>
         <v>51.227057425424789</v>
       </c>
-      <c r="M70" s="5">
+      <c r="M70" s="3">
         <v>39.950427830000002</v>
       </c>
-      <c r="N70" s="5"/>
-      <c r="O70" s="5"/>
-      <c r="P70" s="5">
+      <c r="N70" s="3"/>
+      <c r="O70" s="3"/>
+      <c r="P70" s="3">
         <v>102</v>
       </c>
-      <c r="Q70" s="5">
+      <c r="Q70" s="3">
         <v>101.6</v>
       </c>
-      <c r="R70" s="5"/>
-      <c r="S70" s="5">
+      <c r="R70" s="3"/>
+      <c r="S70" s="3">
         <v>102.7</v>
       </c>
-      <c r="T70" s="5">
+      <c r="T70" s="3">
         <v>76</v>
       </c>
-      <c r="U70" s="9"/>
-      <c r="V70" s="5">
+      <c r="U70" s="7"/>
+      <c r="V70" s="3">
         <f t="shared" si="8"/>
         <v>79.393880511964468</v>
       </c>
-      <c r="W70" s="5">
+      <c r="W70" s="3">
         <f t="shared" si="9"/>
         <v>2.4656821601966037</v>
       </c>
-      <c r="X70" s="5">
+      <c r="X70" s="3">
         <f t="shared" si="10"/>
         <v>8.9710247496481053</v>
       </c>
-      <c r="Y70" s="5">
+      <c r="Y70" s="3">
         <f t="shared" si="11"/>
         <v>5.3702695372588399E-2</v>
       </c>
-      <c r="Z70" s="5">
+      <c r="Z70" s="3">
         <f t="shared" si="12"/>
         <v>1.456282070599527E-2</v>
       </c>
@@ -44182,55 +44176,55 @@
       <c r="H71">
         <v>450</v>
       </c>
-      <c r="I71" s="5">
+      <c r="I71" s="3">
         <f t="shared" si="5"/>
         <v>12746.920713208998</v>
       </c>
-      <c r="J71" s="5">
+      <c r="J71" s="3">
         <f t="shared" si="6"/>
         <v>249.4822001</v>
       </c>
-      <c r="K71" s="9"/>
-      <c r="L71" s="5">
+      <c r="K71" s="7"/>
+      <c r="L71" s="3">
         <f t="shared" si="7"/>
         <v>51.093507705558338</v>
       </c>
-      <c r="M71" s="5">
+      <c r="M71" s="3">
         <v>39.102042009999998</v>
       </c>
-      <c r="N71" s="5"/>
-      <c r="O71" s="5"/>
-      <c r="P71" s="5">
+      <c r="N71" s="3"/>
+      <c r="O71" s="3"/>
+      <c r="P71" s="3">
         <v>102</v>
       </c>
-      <c r="Q71" s="5">
+      <c r="Q71" s="3">
         <v>101.6</v>
       </c>
-      <c r="R71" s="5"/>
-      <c r="S71" s="5">
+      <c r="R71" s="3"/>
+      <c r="S71" s="3">
         <v>102.7</v>
       </c>
-      <c r="T71" s="5">
+      <c r="T71" s="3">
         <v>76</v>
       </c>
-      <c r="U71" s="9"/>
-      <c r="V71" s="5">
+      <c r="U71" s="7"/>
+      <c r="V71" s="3">
         <f t="shared" si="8"/>
         <v>79.393880511964468</v>
       </c>
-      <c r="W71" s="5">
+      <c r="W71" s="3">
         <f t="shared" si="9"/>
         <v>2.4656821601966037</v>
       </c>
-      <c r="X71" s="5">
+      <c r="X71" s="3">
         <f t="shared" si="10"/>
         <v>8.9710247496481053</v>
       </c>
-      <c r="Y71" s="5">
+      <c r="Y71" s="3">
         <f t="shared" si="11"/>
         <v>5.3702695372588399E-2</v>
       </c>
-      <c r="Z71" s="5">
+      <c r="Z71" s="3">
         <f t="shared" si="12"/>
         <v>1.456282070599527E-2</v>
       </c>
@@ -44278,55 +44272,55 @@
       <c r="H72">
         <v>450</v>
       </c>
-      <c r="I72" s="5">
+      <c r="I72" s="3">
         <f t="shared" si="5"/>
         <v>12746.920713208998</v>
       </c>
-      <c r="J72" s="5">
+      <c r="J72" s="3">
         <f t="shared" si="6"/>
         <v>250.11289269999997</v>
       </c>
-      <c r="K72" s="9"/>
-      <c r="L72" s="5">
+      <c r="K72" s="7"/>
+      <c r="L72" s="3">
         <f t="shared" si="7"/>
         <v>50.964668696620926</v>
       </c>
-      <c r="M72" s="5">
+      <c r="M72" s="3">
         <v>38.271672479999999</v>
       </c>
-      <c r="N72" s="5"/>
-      <c r="O72" s="5"/>
-      <c r="P72" s="5">
+      <c r="N72" s="3"/>
+      <c r="O72" s="3"/>
+      <c r="P72" s="3">
         <v>102</v>
       </c>
-      <c r="Q72" s="5">
+      <c r="Q72" s="3">
         <v>101.6</v>
       </c>
-      <c r="R72" s="5"/>
-      <c r="S72" s="5">
+      <c r="R72" s="3"/>
+      <c r="S72" s="3">
         <v>102.7</v>
       </c>
-      <c r="T72" s="5">
+      <c r="T72" s="3">
         <v>76</v>
       </c>
-      <c r="U72" s="9"/>
-      <c r="V72" s="5">
+      <c r="U72" s="7"/>
+      <c r="V72" s="3">
         <f t="shared" si="8"/>
         <v>79.393880511964468</v>
       </c>
-      <c r="W72" s="5">
+      <c r="W72" s="3">
         <f t="shared" si="9"/>
         <v>2.4656821601966037</v>
       </c>
-      <c r="X72" s="5">
+      <c r="X72" s="3">
         <f t="shared" si="10"/>
         <v>8.9710247496481053</v>
       </c>
-      <c r="Y72" s="5">
+      <c r="Y72" s="3">
         <f t="shared" si="11"/>
         <v>5.3702695372588399E-2</v>
       </c>
-      <c r="Z72" s="5">
+      <c r="Z72" s="3">
         <f t="shared" si="12"/>
         <v>1.456282070599527E-2</v>
       </c>
@@ -44374,57 +44368,57 @@
       <c r="H73">
         <v>450</v>
       </c>
-      <c r="I73" s="5">
+      <c r="I73" s="3">
         <f t="shared" si="5"/>
         <v>12746.920713208998</v>
       </c>
-      <c r="J73" s="5">
+      <c r="J73" s="3">
         <f t="shared" si="6"/>
         <v>250.72507910000002</v>
       </c>
-      <c r="K73" s="9"/>
-      <c r="L73" s="5">
+      <c r="K73" s="7"/>
+      <c r="L73" s="3">
         <f t="shared" si="7"/>
         <v>50.840230099698061</v>
       </c>
-      <c r="M73" s="5">
+      <c r="M73" s="3">
         <v>37.458936649999998</v>
       </c>
-      <c r="N73" s="5">
+      <c r="N73" s="3">
         <v>42</v>
       </c>
-      <c r="O73" s="5"/>
-      <c r="P73" s="5">
+      <c r="O73" s="3"/>
+      <c r="P73" s="3">
         <v>102</v>
       </c>
-      <c r="Q73" s="5">
+      <c r="Q73" s="3">
         <v>101.6</v>
       </c>
-      <c r="R73" s="5"/>
-      <c r="S73" s="5">
+      <c r="R73" s="3"/>
+      <c r="S73" s="3">
         <v>102.7</v>
       </c>
-      <c r="T73" s="5">
+      <c r="T73" s="3">
         <v>76</v>
       </c>
-      <c r="U73" s="9"/>
-      <c r="V73" s="5">
+      <c r="U73" s="7"/>
+      <c r="V73" s="3">
         <f t="shared" si="8"/>
         <v>79.393880511964468</v>
       </c>
-      <c r="W73" s="5">
+      <c r="W73" s="3">
         <f t="shared" si="9"/>
         <v>2.4656821601966037</v>
       </c>
-      <c r="X73" s="5">
+      <c r="X73" s="3">
         <f t="shared" si="10"/>
         <v>8.9710247496481053</v>
       </c>
-      <c r="Y73" s="5">
+      <c r="Y73" s="3">
         <f t="shared" si="11"/>
         <v>5.3702695372588399E-2</v>
       </c>
-      <c r="Z73" s="5">
+      <c r="Z73" s="3">
         <f t="shared" si="12"/>
         <v>1.456282070599527E-2</v>
       </c>
@@ -47461,19 +47455,19 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10" t="s">
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
@@ -51093,4 +51087,10 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{95965d95-ecc0-4720-b759-1f33c42ed7da}" enabled="1" method="Standard" siteId="{a0f29d7e-28cd-4f54-8442-7885aee7c080}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>
--- a/PV_ICE/baselines/SupportingMaterial/Manual Files/BaselineGraphs.xlsx
+++ b/PV_ICE/baselines/SupportingMaterial/Manual Files/BaselineGraphs.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hmirletz\Documents\GitHub\PV_ICE\PV_ICE\baselines\SupportingMaterial\Manual Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A77E539-5F2C-4B89-87CA-73FC844C1CA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9E66EDF-F298-4FCC-BF88-1F35DD76603C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{31D47E9D-A833-4D35-B79A-EFF0E4DE6D01}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{31D47E9D-A833-4D35-B79A-EFF0E4DE6D01}"/>
   </bookViews>
   <sheets>
     <sheet name="mass per m2" sheetId="1" r:id="rId1"/>
-    <sheet name="VirginMatEff" sheetId="5" r:id="rId2"/>
-    <sheet name="MFG Eff" sheetId="3" r:id="rId3"/>
-    <sheet name="SF-all on one" sheetId="2" r:id="rId4"/>
-    <sheet name="ModuleLifetime" sheetId="6" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="7" r:id="rId2"/>
+    <sheet name="VirginMatEff" sheetId="5" r:id="rId3"/>
+    <sheet name="MFG Eff" sheetId="3" r:id="rId4"/>
+    <sheet name="SF-all on one" sheetId="2" r:id="rId5"/>
+    <sheet name="ModuleLifetime" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="55">
   <si>
     <t>Year</t>
   </si>
@@ -186,11 +187,35 @@
   <si>
     <t>[years]</t>
   </si>
+  <si>
+    <t>%Glass</t>
+  </si>
+  <si>
+    <t>%Silicon</t>
+  </si>
+  <si>
+    <t>%Aluminium</t>
+  </si>
+  <si>
+    <t>%Copper</t>
+  </si>
+  <si>
+    <t>%Silver</t>
+  </si>
+  <si>
+    <t>%Encapsulant</t>
+  </si>
+  <si>
+    <t>%Backsheet</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="167" formatCode="0.0"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -235,7 +260,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
@@ -255,6 +280,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -623,121 +649,121 @@
                   <c:v>8000</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>8080</c:v>
+                  <c:v>8045</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>8160</c:v>
+                  <c:v>8090</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>8292.7000000000007</c:v>
+                  <c:v>8180</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>8225.6625000000004</c:v>
+                  <c:v>8090</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>8158.8874999999998</c:v>
+                  <c:v>8135</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>8289.75</c:v>
+                  <c:v>8208.375</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>8350.15</c:v>
+                  <c:v>8253.5499999999993</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>8607.5</c:v>
+                  <c:v>8450</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>8975.5</c:v>
+                  <c:v>8764.1</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>9027</c:v>
+                  <c:v>9076.6</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>9106.5</c:v>
+                  <c:v>9484.2124999999996</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>9183.5499999999993</c:v>
+                  <c:v>9654.375</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>9108.8250000000007</c:v>
+                  <c:v>10055.525</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>9034.1</c:v>
+                  <c:v>10349.549999999999</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>9205.2083330000005</c:v>
+                  <c:v>10512.3125</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>9373.8666670000002</c:v>
+                  <c:v>10676.825000000001</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>9540.0750000000007</c:v>
+                  <c:v>10711.731249999901</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>9735.8083330000009</c:v>
+                  <c:v>10747.25</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>9929.2083330000005</c:v>
+                  <c:v>10775.4888888888</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>10120.275</c:v>
+                  <c:v>10804.155555555501</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>10120.275</c:v>
+                  <c:v>10833.25</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>10120.275</c:v>
+                  <c:v>10822.166666666601</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>10120.275</c:v>
+                  <c:v>10811.083333333299</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>10120.275</c:v>
+                  <c:v>10800</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>10120.275</c:v>
+                  <c:v>10800</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>10120.275</c:v>
+                  <c:v>10800</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>10120.275</c:v>
+                  <c:v>10800</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>10120.275</c:v>
+                  <c:v>10800</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>10120.275</c:v>
+                  <c:v>10800</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>10120.275</c:v>
+                  <c:v>10800</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>10120.275</c:v>
+                  <c:v>10800</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>10120.275</c:v>
+                  <c:v>10800</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>10120.275</c:v>
+                  <c:v>10800</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>10120.275</c:v>
+                  <c:v>10800</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>10120.275</c:v>
+                  <c:v>10800</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>10120.275</c:v>
+                  <c:v>10800</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>10120.275</c:v>
+                  <c:v>10800</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>10120.275</c:v>
+                  <c:v>10800</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>10120.275</c:v>
+                  <c:v>10800</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7270,121 +7296,121 @@
                   <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>8.08</c:v>
+                  <c:v>8.0449999999999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>8.16</c:v>
+                  <c:v>8.09</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>8.2927</c:v>
+                  <c:v>8.18</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>8.2256625000000003</c:v>
+                  <c:v>8.09</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8.1588875000000005</c:v>
+                  <c:v>8.1349999999999998</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>8.2897499999999997</c:v>
+                  <c:v>8.2083750000000002</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>8.3501499999999993</c:v>
+                  <c:v>8.2535499999999988</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>8.6074999999999999</c:v>
+                  <c:v>8.4499999999999993</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>8.9755000000000003</c:v>
+                  <c:v>8.7641000000000009</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>9.0269999999999992</c:v>
+                  <c:v>9.0766000000000009</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>9.1065000000000005</c:v>
+                  <c:v>9.4842124999999999</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>9.1835499999999985</c:v>
+                  <c:v>9.6543749999999999</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>9.1088250000000013</c:v>
+                  <c:v>10.055524999999999</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>9.0341000000000005</c:v>
+                  <c:v>10.349549999999999</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>9.2052083329999999</c:v>
+                  <c:v>10.5123125</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>9.3738666669999997</c:v>
+                  <c:v>10.676825000000001</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>9.5400749999999999</c:v>
+                  <c:v>10.7117312499999</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>9.7358083330000014</c:v>
+                  <c:v>10.747249999999999</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>9.9292083330000001</c:v>
+                  <c:v>10.7754888888888</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>10.120274999999999</c:v>
+                  <c:v>10.8041555555555</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>10.120274999999999</c:v>
+                  <c:v>10.83325</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>10.120274999999999</c:v>
+                  <c:v>10.8221666666666</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>10.120274999999999</c:v>
+                  <c:v>10.811083333333299</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>10.120274999999999</c:v>
+                  <c:v>10.8</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>10.120274999999999</c:v>
+                  <c:v>10.8</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>10.120274999999999</c:v>
+                  <c:v>10.8</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>10.120274999999999</c:v>
+                  <c:v>10.8</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>10.120274999999999</c:v>
+                  <c:v>10.8</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>10.120274999999999</c:v>
+                  <c:v>10.8</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>10.120274999999999</c:v>
+                  <c:v>10.8</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>10.120274999999999</c:v>
+                  <c:v>10.8</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>10.120274999999999</c:v>
+                  <c:v>10.8</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>10.120274999999999</c:v>
+                  <c:v>10.8</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>10.120274999999999</c:v>
+                  <c:v>10.8</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>10.120274999999999</c:v>
+                  <c:v>10.8</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>10.120274999999999</c:v>
+                  <c:v>10.8</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>10.120274999999999</c:v>
+                  <c:v>10.8</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>10.120274999999999</c:v>
+                  <c:v>10.8</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>10.120274999999999</c:v>
+                  <c:v>10.8</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9761,121 +9787,121 @@
                   <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>8.08</c:v>
+                  <c:v>8.0449999999999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>8.16</c:v>
+                  <c:v>8.09</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>8.2927</c:v>
+                  <c:v>8.18</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>8.2256625000000003</c:v>
+                  <c:v>8.09</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8.1588875000000005</c:v>
+                  <c:v>8.1349999999999998</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>8.2897499999999997</c:v>
+                  <c:v>8.2083750000000002</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>8.3501499999999993</c:v>
+                  <c:v>8.2535499999999988</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>8.6074999999999999</c:v>
+                  <c:v>8.4499999999999993</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>8.9755000000000003</c:v>
+                  <c:v>8.7641000000000009</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>9.0269999999999992</c:v>
+                  <c:v>9.0766000000000009</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>9.1065000000000005</c:v>
+                  <c:v>9.4842124999999999</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>9.1835499999999985</c:v>
+                  <c:v>9.6543749999999999</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>9.1088250000000013</c:v>
+                  <c:v>10.055524999999999</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>9.0341000000000005</c:v>
+                  <c:v>10.349549999999999</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>9.2052083329999999</c:v>
+                  <c:v>10.5123125</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>9.3738666669999997</c:v>
+                  <c:v>10.676825000000001</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>9.5400749999999999</c:v>
+                  <c:v>10.7117312499999</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>9.7358083330000014</c:v>
+                  <c:v>10.747249999999999</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>9.9292083330000001</c:v>
+                  <c:v>10.7754888888888</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>10.120274999999999</c:v>
+                  <c:v>10.8041555555555</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>10.120274999999999</c:v>
+                  <c:v>10.83325</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>10.120274999999999</c:v>
+                  <c:v>10.8221666666666</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>10.120274999999999</c:v>
+                  <c:v>10.811083333333299</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>10.120274999999999</c:v>
+                  <c:v>10.8</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>10.120274999999999</c:v>
+                  <c:v>10.8</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>10.120274999999999</c:v>
+                  <c:v>10.8</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>10.120274999999999</c:v>
+                  <c:v>10.8</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>10.120274999999999</c:v>
+                  <c:v>10.8</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>10.120274999999999</c:v>
+                  <c:v>10.8</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>10.120274999999999</c:v>
+                  <c:v>10.8</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>10.120274999999999</c:v>
+                  <c:v>10.8</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>10.120274999999999</c:v>
+                  <c:v>10.8</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>10.120274999999999</c:v>
+                  <c:v>10.8</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>10.120274999999999</c:v>
+                  <c:v>10.8</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>10.120274999999999</c:v>
+                  <c:v>10.8</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>10.120274999999999</c:v>
+                  <c:v>10.8</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>10.120274999999999</c:v>
+                  <c:v>10.8</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>10.120274999999999</c:v>
+                  <c:v>10.8</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>10.120274999999999</c:v>
+                  <c:v>10.8</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15448,31 +15474,31 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="56"/>
                 <c:pt idx="0">
-                  <c:v>848.42142860000001</c:v>
+                  <c:v>848.42142857142801</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>831.7857143</c:v>
+                  <c:v>831.78571428571399</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>815.15</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>798.51428569999996</c:v>
+                  <c:v>798.51428571428505</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>781.87857140000006</c:v>
+                  <c:v>781.87857142857104</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>765.24285710000004</c:v>
+                  <c:v>765.24285714285702</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>748.60714289999999</c:v>
+                  <c:v>748.60714285714198</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>731.97142859999997</c:v>
+                  <c:v>731.97142857142796</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>715.33571429999995</c:v>
+                  <c:v>715.33571428571395</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>698.7</c:v>
@@ -15511,28 +15537,28 @@
                   <c:v>419.22</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>419.22</c:v>
+                  <c:v>419.219999999999</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>419.22</c:v>
+                  <c:v>419.219999999999</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>410.85500830000001</c:v>
+                  <c:v>410.8550082557</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>402.1406667</c:v>
+                  <c:v>402.14066674430001</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>380.05398330000003</c:v>
+                  <c:v>400.587999999999</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>367.38034160000001</c:v>
+                  <c:v>388.94299999999998</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>354.70670000000001</c:v>
+                  <c:v>372.64</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>348.49603339999999</c:v>
+                  <c:v>337.70499999999998</c:v>
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>342.2853667</c:v>
@@ -16961,169 +16987,169 @@
                   <c:v>88</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>84.571428569999995</c:v>
+                  <c:v>84.571428571428498</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>81.142857140000004</c:v>
+                  <c:v>81.142857142857096</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>77.714285709999999</c:v>
+                  <c:v>77.714285714285694</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>74.285714290000001</c:v>
+                  <c:v>74.285714285714207</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>45.34857143</c:v>
+                  <c:v>45.348571428571397</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>43.154285710000003</c:v>
+                  <c:v>43.154285714285699</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>40.96</c:v>
+                  <c:v>40.959999999999901</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>38.765714289999998</c:v>
+                  <c:v>38.765714285714203</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>36.571428570000002</c:v>
+                  <c:v>36.571428571428498</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>34.377142859999999</c:v>
+                  <c:v>34.3771428571428</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>32.182857140000003</c:v>
+                  <c:v>32.182857142857102</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>29.98857143</c:v>
+                  <c:v>29.988571428571401</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>27.79428571</c:v>
+                  <c:v>27.794285714285699</c:v>
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>25.6</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>12.327416169999999</c:v>
+                  <c:v>12.327416173570001</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>10.272846810000001</c:v>
+                  <c:v>10.2728468113083</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>8.2182774490000003</c:v>
+                  <c:v>8.2182774490466795</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>5.7527942139999997</c:v>
+                  <c:v>5.7527942143326696</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>5.3418803419999996</c:v>
+                  <c:v>5.3418803418803398</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>4.5200525970000003</c:v>
+                  <c:v>4.5200525969756704</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>4.0997570090000002</c:v>
+                  <c:v>4.0997570089490099</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>4.079110301</c:v>
+                  <c:v>4.0797067542614096</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>4.3128338230000001</c:v>
+                  <c:v>4.3143250717191401</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>4.1473098100000003</c:v>
+                  <c:v>4.1223937921719198</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>3.5949654450000001</c:v>
+                  <c:v>3.3920347419549</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>3.3412788689999999</c:v>
+                  <c:v>6.0640035275966397</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>3.0936340219999998</c:v>
+                  <c:v>4.0231442787078002</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>2.8988638820000001</c:v>
+                  <c:v>3.2833258827952898</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>2.692895407</c:v>
+                  <c:v>3.2833258827952898</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>2.542951049</c:v>
+                  <c:v>3.2833258827952898</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>2.4012622069999998</c:v>
+                  <c:v>3.2833258827952898</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>2.2668844890000002</c:v>
+                  <c:v>3.2833258827952898</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>2.1296348279999999</c:v>
+                  <c:v>3.2833258827952898</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>1.9927764130000001</c:v>
+                  <c:v>3.2833258827952898</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>1.856311209</c:v>
+                  <c:v>3.2833258827952898</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>1.856311209</c:v>
+                  <c:v>3.2833258827952898</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>1.856311209</c:v>
+                  <c:v>3.2833258827952898</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>1.856311209</c:v>
+                  <c:v>3.2833258827952898</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>1.856311209</c:v>
+                  <c:v>3.2833258827952898</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>1.856311209</c:v>
+                  <c:v>3.2833258827952898</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>1.856311209</c:v>
+                  <c:v>3.2833258827952898</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>1.856311209</c:v>
+                  <c:v>3.2833258827952898</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>1.856311209</c:v>
+                  <c:v>3.2833258827952898</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>1.856311209</c:v>
+                  <c:v>3.2833258827952898</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>1.856311209</c:v>
+                  <c:v>3.2833258827952898</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>1.856311209</c:v>
+                  <c:v>3.2833258827952898</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>1.856311209</c:v>
+                  <c:v>3.2833258827952898</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>1.856311209</c:v>
+                  <c:v>3.2833258827952898</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>1.856311209</c:v>
+                  <c:v>3.2833258827952898</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>1.856311209</c:v>
+                  <c:v>3.2833258827952898</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>1.856311209</c:v>
+                  <c:v>3.2833258827952898</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>1.856311209</c:v>
+                  <c:v>3.2833258827952898</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>1.856311209</c:v>
+                  <c:v>3.2833258827952898</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>1.856311209</c:v>
+                  <c:v>3.2833258827952898</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>1.856311209</c:v>
+                  <c:v>3.2833258827952898</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -20866,121 +20892,121 @@
                   <c:v>8000</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>8080</c:v>
+                  <c:v>8045</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>8160</c:v>
+                  <c:v>8090</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>8292.7000000000007</c:v>
+                  <c:v>8180</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>8225.6625000000004</c:v>
+                  <c:v>8090</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>8158.8874999999998</c:v>
+                  <c:v>8135</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>8289.75</c:v>
+                  <c:v>8208.375</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>8350.15</c:v>
+                  <c:v>8253.5499999999993</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>8607.5</c:v>
+                  <c:v>8450</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>8975.5</c:v>
+                  <c:v>8764.1</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>9027</c:v>
+                  <c:v>9076.6</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>9106.5</c:v>
+                  <c:v>9484.2124999999996</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>9183.5499999999993</c:v>
+                  <c:v>9654.375</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>9108.8250000000007</c:v>
+                  <c:v>10055.525</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>9034.1</c:v>
+                  <c:v>10349.549999999999</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>9205.2083330000005</c:v>
+                  <c:v>10512.3125</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>9373.8666670000002</c:v>
+                  <c:v>10676.825000000001</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>9540.0750000000007</c:v>
+                  <c:v>10711.731249999901</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>9735.8083330000009</c:v>
+                  <c:v>10747.25</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>9929.2083330000005</c:v>
+                  <c:v>10775.4888888888</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>10120.275</c:v>
+                  <c:v>10804.155555555501</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>10120.275</c:v>
+                  <c:v>10833.25</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>10120.275</c:v>
+                  <c:v>10822.166666666601</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>10120.275</c:v>
+                  <c:v>10811.083333333299</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>10120.275</c:v>
+                  <c:v>10800</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>10120.275</c:v>
+                  <c:v>10800</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>10120.275</c:v>
+                  <c:v>10800</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>10120.275</c:v>
+                  <c:v>10800</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>10120.275</c:v>
+                  <c:v>10800</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>10120.275</c:v>
+                  <c:v>10800</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>10120.275</c:v>
+                  <c:v>10800</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>10120.275</c:v>
+                  <c:v>10800</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>10120.275</c:v>
+                  <c:v>10800</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>10120.275</c:v>
+                  <c:v>10800</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>10120.275</c:v>
+                  <c:v>10800</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>10120.275</c:v>
+                  <c:v>10800</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>10120.275</c:v>
+                  <c:v>10800</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>10120.275</c:v>
+                  <c:v>10800</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>10120.275</c:v>
+                  <c:v>10800</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>10120.275</c:v>
+                  <c:v>10800</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -21198,31 +21224,31 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="56"/>
                 <c:pt idx="0">
-                  <c:v>848.42142860000001</c:v>
+                  <c:v>848.42142857142801</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>831.7857143</c:v>
+                  <c:v>831.78571428571399</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>815.15</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>798.51428569999996</c:v>
+                  <c:v>798.51428571428505</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>781.87857140000006</c:v>
+                  <c:v>781.87857142857104</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>765.24285710000004</c:v>
+                  <c:v>765.24285714285702</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>748.60714289999999</c:v>
+                  <c:v>748.60714285714198</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>731.97142859999997</c:v>
+                  <c:v>731.97142857142796</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>715.33571429999995</c:v>
+                  <c:v>715.33571428571395</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>698.7</c:v>
@@ -21261,28 +21287,28 @@
                   <c:v>419.22</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>419.22</c:v>
+                  <c:v>419.219999999999</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>419.22</c:v>
+                  <c:v>419.219999999999</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>410.85500830000001</c:v>
+                  <c:v>410.8550082557</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>402.1406667</c:v>
+                  <c:v>402.14066674430001</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>380.05398330000003</c:v>
+                  <c:v>400.587999999999</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>367.38034160000001</c:v>
+                  <c:v>388.94299999999998</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>354.70670000000001</c:v>
+                  <c:v>372.64</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>348.49603339999999</c:v>
+                  <c:v>337.70499999999998</c:v>
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>342.2853667</c:v>
@@ -22350,169 +22376,169 @@
                   <c:v>88</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>84.571428569999995</c:v>
+                  <c:v>84.571428571428498</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>81.142857140000004</c:v>
+                  <c:v>81.142857142857096</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>77.714285709999999</c:v>
+                  <c:v>77.714285714285694</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>74.285714290000001</c:v>
+                  <c:v>74.285714285714207</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>45.34857143</c:v>
+                  <c:v>45.348571428571397</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>43.154285710000003</c:v>
+                  <c:v>43.154285714285699</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>40.96</c:v>
+                  <c:v>40.959999999999901</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>38.765714289999998</c:v>
+                  <c:v>38.765714285714203</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>36.571428570000002</c:v>
+                  <c:v>36.571428571428498</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>34.377142859999999</c:v>
+                  <c:v>34.3771428571428</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>32.182857140000003</c:v>
+                  <c:v>32.182857142857102</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>29.98857143</c:v>
+                  <c:v>29.988571428571401</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>27.79428571</c:v>
+                  <c:v>27.794285714285699</c:v>
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>25.6</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>12.327416169999999</c:v>
+                  <c:v>12.327416173570001</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>10.272846810000001</c:v>
+                  <c:v>10.2728468113083</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>8.2182774490000003</c:v>
+                  <c:v>8.2182774490466795</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>5.7527942139999997</c:v>
+                  <c:v>5.7527942143326696</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>5.3418803419999996</c:v>
+                  <c:v>5.3418803418803398</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>4.5200525970000003</c:v>
+                  <c:v>4.5200525969756704</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>4.0997570090000002</c:v>
+                  <c:v>4.0997570089490099</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>4.079110301</c:v>
+                  <c:v>4.0797067542614096</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>4.3128338230000001</c:v>
+                  <c:v>4.3143250717191401</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>4.1473098100000003</c:v>
+                  <c:v>4.1223937921719198</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>3.5949654450000001</c:v>
+                  <c:v>3.3920347419549</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>3.3412788689999999</c:v>
+                  <c:v>6.0640035275966397</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>3.0936340219999998</c:v>
+                  <c:v>4.0231442787078002</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>2.8988638820000001</c:v>
+                  <c:v>3.2833258827952898</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>2.692895407</c:v>
+                  <c:v>3.2833258827952898</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>2.542951049</c:v>
+                  <c:v>3.2833258827952898</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>2.4012622069999998</c:v>
+                  <c:v>3.2833258827952898</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>2.2668844890000002</c:v>
+                  <c:v>3.2833258827952898</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>2.1296348279999999</c:v>
+                  <c:v>3.2833258827952898</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>1.9927764130000001</c:v>
+                  <c:v>3.2833258827952898</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>1.856311209</c:v>
+                  <c:v>3.2833258827952898</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>1.856311209</c:v>
+                  <c:v>3.2833258827952898</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>1.856311209</c:v>
+                  <c:v>3.2833258827952898</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>1.856311209</c:v>
+                  <c:v>3.2833258827952898</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>1.856311209</c:v>
+                  <c:v>3.2833258827952898</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>1.856311209</c:v>
+                  <c:v>3.2833258827952898</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>1.856311209</c:v>
+                  <c:v>3.2833258827952898</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>1.856311209</c:v>
+                  <c:v>3.2833258827952898</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>1.856311209</c:v>
+                  <c:v>3.2833258827952898</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>1.856311209</c:v>
+                  <c:v>3.2833258827952898</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>1.856311209</c:v>
+                  <c:v>3.2833258827952898</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>1.856311209</c:v>
+                  <c:v>3.2833258827952898</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>1.856311209</c:v>
+                  <c:v>3.2833258827952898</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>1.856311209</c:v>
+                  <c:v>3.2833258827952898</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>1.856311209</c:v>
+                  <c:v>3.2833258827952898</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>1.856311209</c:v>
+                  <c:v>3.2833258827952898</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>1.856311209</c:v>
+                  <c:v>3.2833258827952898</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>1.856311209</c:v>
+                  <c:v>3.2833258827952898</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>1.856311209</c:v>
+                  <c:v>3.2833258827952898</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>1.856311209</c:v>
+                  <c:v>3.2833258827952898</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>1.856311209</c:v>
+                  <c:v>3.2833258827952898</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -23450,172 +23476,172 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="71"/>
                 <c:pt idx="15" formatCode="0.00">
-                  <c:v>107.28786270880001</c:v>
+                  <c:v>107.28786270857142</c:v>
                 </c:pt>
                 <c:pt idx="16" formatCode="0.00">
-                  <c:v>104.85944636905512</c:v>
+                  <c:v>104.85944636895388</c:v>
                 </c:pt>
                 <c:pt idx="17" formatCode="0.00">
-                  <c:v>100.77382653059004</c:v>
+                  <c:v>100.77382653061223</c:v>
                 </c:pt>
                 <c:pt idx="18" formatCode="0.00">
-                  <c:v>98.009014107274126</c:v>
+                  <c:v>98.009014107416334</c:v>
                 </c:pt>
                 <c:pt idx="19" formatCode="0.00">
-                  <c:v>96.104525677416916</c:v>
+                  <c:v>96.104525677600336</c:v>
                 </c:pt>
                 <c:pt idx="20" formatCode="0.00">
-                  <c:v>94.097836755067078</c:v>
+                  <c:v>94.097836755375781</c:v>
                 </c:pt>
                 <c:pt idx="21" formatCode="0.00">
-                  <c:v>92.372583114779417</c:v>
+                  <c:v>92.372583114495797</c:v>
                 </c:pt>
                 <c:pt idx="22" formatCode="0.00">
-                  <c:v>91.101824297668301</c:v>
+                  <c:v>91.101824297460084</c:v>
                 </c:pt>
                 <c:pt idx="23" formatCode="0.00">
-                  <c:v>89.966553266690724</c:v>
+                  <c:v>89.966553266556559</c:v>
                 </c:pt>
                 <c:pt idx="24" formatCode="0.00">
-                  <c:v>88.601432130906574</c:v>
+                  <c:v>88.60143213091682</c:v>
                 </c:pt>
                 <c:pt idx="25" formatCode="0.00">
-                  <c:v>85.981485768250664</c:v>
+                  <c:v>85.981485768230385</c:v>
                 </c:pt>
                 <c:pt idx="26" formatCode="0.00">
-                  <c:v>84.193545779264554</c:v>
+                  <c:v>84.193545779284662</c:v>
                 </c:pt>
                 <c:pt idx="27" formatCode="0.00">
-                  <c:v>83.096907447906261</c:v>
+                  <c:v>83.096907447896299</c:v>
                 </c:pt>
                 <c:pt idx="28" formatCode="0.00">
-                  <c:v>82.02877060997578</c:v>
+                  <c:v>82.028770610005424</c:v>
                 </c:pt>
                 <c:pt idx="29" formatCode="0.00">
                   <c:v>81.147459980008009</c:v>
                 </c:pt>
                 <c:pt idx="30" formatCode="0.00">
-                  <c:v>80.286218198435378</c:v>
+                  <c:v>80.286218198459665</c:v>
                 </c:pt>
                 <c:pt idx="31" formatCode="0.00">
-                  <c:v>78.009681965629127</c:v>
+                  <c:v>78.009681965637796</c:v>
                 </c:pt>
                 <c:pt idx="32" formatCode="0.00">
-                  <c:v>76.972730360058435</c:v>
+                  <c:v>76.745457632786014</c:v>
                 </c:pt>
                 <c:pt idx="33" formatCode="0.00">
-                  <c:v>72.423793263837496</c:v>
+                  <c:v>71.986293263839585</c:v>
                 </c:pt>
                 <c:pt idx="34" formatCode="0.00">
-                  <c:v>71.751335008233141</c:v>
+                  <c:v>71.059923965287609</c:v>
                 </c:pt>
                 <c:pt idx="35" formatCode="0.00">
-                  <c:v>67.83948903880588</c:v>
+                  <c:v>67.041474332923386</c:v>
                 </c:pt>
                 <c:pt idx="36" formatCode="0.00">
-                  <c:v>65.06139367433714</c:v>
+                  <c:v>64.924893674336843</c:v>
                 </c:pt>
                 <c:pt idx="37" formatCode="0.00">
-                  <c:v>64.859117775711852</c:v>
+                  <c:v>64.399375382792428</c:v>
                 </c:pt>
                 <c:pt idx="38" formatCode="0.00">
-                  <c:v>62.583664288711944</c:v>
+                  <c:v>62.058672393083782</c:v>
                 </c:pt>
                 <c:pt idx="39" formatCode="0.00">
-                  <c:v>61.192740393281241</c:v>
+                  <c:v>60.372298122585782</c:v>
                 </c:pt>
                 <c:pt idx="40" formatCode="0.00">
-                  <c:v>59.708250595798276</c:v>
+                  <c:v>58.764820998651295</c:v>
                 </c:pt>
                 <c:pt idx="41" formatCode="0.00">
-                  <c:v>57.656813225558658</c:v>
+                  <c:v>58.010418686832558</c:v>
                 </c:pt>
                 <c:pt idx="42" formatCode="0.00">
-                  <c:v>56.512013230160413</c:v>
+                  <c:v>58.368388715061307</c:v>
                 </c:pt>
                 <c:pt idx="43" formatCode="0.00">
-                  <c:v>55.683974515200646</c:v>
+                  <c:v>57.802485787500444</c:v>
                 </c:pt>
                 <c:pt idx="44" formatCode="0.00">
-                  <c:v>54.303214578596659</c:v>
+                  <c:v>58.60119343906829</c:v>
                 </c:pt>
                 <c:pt idx="45" formatCode="0.00">
-                  <c:v>53.065446717913204</c:v>
+                  <c:v>58.966709209597525</c:v>
                 </c:pt>
                 <c:pt idx="46" formatCode="0.00">
-                  <c:v>53.071119164179251</c:v>
+                  <c:v>58.875608458111593</c:v>
                 </c:pt>
                 <c:pt idx="47" formatCode="0.00">
-                  <c:v>53.125467021151898</c:v>
+                  <c:v>58.859910652644167</c:v>
                 </c:pt>
                 <c:pt idx="48" formatCode="0.00">
-                  <c:v>53.229372262171573</c:v>
+                  <c:v>58.345323657063062</c:v>
                 </c:pt>
                 <c:pt idx="49" formatCode="0.00">
-                  <c:v>53.630928714887673</c:v>
+                  <c:v>58.016297896041003</c:v>
                 </c:pt>
                 <c:pt idx="50" formatCode="0.00">
-                  <c:v>54.048264765492526</c:v>
+                  <c:v>57.69452681207899</c:v>
                 </c:pt>
                 <c:pt idx="51" formatCode="0.00">
-                  <c:v>54.491707614608238</c:v>
+                  <c:v>57.421323369126519</c:v>
                 </c:pt>
                 <c:pt idx="52" formatCode="0.00">
-                  <c:v>54.181646322913124</c:v>
+                  <c:v>57.218260275592819</c:v>
                 </c:pt>
                 <c:pt idx="53" formatCode="0.00">
-                  <c:v>53.894572188397859</c:v>
+                  <c:v>56.868236204654721</c:v>
                 </c:pt>
                 <c:pt idx="54" formatCode="0.00">
-                  <c:v>53.627409318732546</c:v>
+                  <c:v>56.539703918164967</c:v>
                 </c:pt>
                 <c:pt idx="55" formatCode="0.00">
-                  <c:v>53.377654814062275</c:v>
+                  <c:v>56.229974831828194</c:v>
                 </c:pt>
                 <c:pt idx="56" formatCode="0.00">
-                  <c:v>53.14324541684455</c:v>
+                  <c:v>55.983039395046426</c:v>
                 </c:pt>
                 <c:pt idx="57" formatCode="0.00">
-                  <c:v>52.922460632690274</c:v>
+                  <c:v>55.750456624231717</c:v>
                 </c:pt>
                 <c:pt idx="58" formatCode="0.00">
-                  <c:v>52.71385117152272</c:v>
+                  <c:v>55.530699784183319</c:v>
                 </c:pt>
                 <c:pt idx="59" formatCode="0.00">
-                  <c:v>52.516185073138622</c:v>
+                  <c:v>55.322471082941924</c:v>
                 </c:pt>
                 <c:pt idx="60" formatCode="0.00">
-                  <c:v>52.32840643171059</c:v>
+                  <c:v>55.124658190670168</c:v>
                 </c:pt>
                 <c:pt idx="61" formatCode="0.00">
-                  <c:v>52.149603704379203</c:v>
+                  <c:v>54.936300854763807</c:v>
                 </c:pt>
                 <c:pt idx="62" formatCode="0.00">
-                  <c:v>51.978984461294232</c:v>
+                  <c:v>54.756564300621193</c:v>
                 </c:pt>
                 <c:pt idx="63" formatCode="0.00">
-                  <c:v>51.815855758326691</c:v>
+                  <c:v>54.584718555539922</c:v>
                 </c:pt>
                 <c:pt idx="64" formatCode="0.00">
-                  <c:v>51.659608197521948</c:v>
+                  <c:v>54.420121657414846</c:v>
                 </c:pt>
                 <c:pt idx="65" formatCode="0.00">
-                  <c:v>51.509703013700729</c:v>
+                  <c:v>54.262206051291081</c:v>
                 </c:pt>
                 <c:pt idx="66" formatCode="0.00">
-                  <c:v>51.365661718044031</c:v>
+                  <c:v>54.110467679537329</c:v>
                 </c:pt>
                 <c:pt idx="67" formatCode="0.00">
-                  <c:v>51.227057425424789</c:v>
+                  <c:v>53.964456845739697</c:v>
                 </c:pt>
                 <c:pt idx="68" formatCode="0.00">
-                  <c:v>51.093507705558338</c:v>
+                  <c:v>53.823770683842042</c:v>
                 </c:pt>
                 <c:pt idx="69" formatCode="0.00">
-                  <c:v>50.964668696620926</c:v>
+                  <c:v>53.688046957216272</c:v>
                 </c:pt>
                 <c:pt idx="70" formatCode="0.00">
-                  <c:v>50.840230099698061</c:v>
+                  <c:v>53.556958785631082</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -38061,16 +38087,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>552450</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>103187</xdr:rowOff>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>146467</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>51138</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>34</xdr:col>
-      <xdr:colOff>133350</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>134937</xdr:rowOff>
+      <xdr:col>38</xdr:col>
+      <xdr:colOff>341547</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>82888</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -38097,16 +38123,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>569912</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>7937</xdr:rowOff>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>444995</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>174494</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>34</xdr:col>
-      <xdr:colOff>39687</xdr:colOff>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>528950</xdr:colOff>
       <xdr:row>48</xdr:row>
-      <xdr:rowOff>36512</xdr:rowOff>
+      <xdr:rowOff>15692</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -38133,16 +38159,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>572523</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>53764</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>93670</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>74583</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>207102</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>156147</xdr:rowOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>738003</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>176966</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -38926,6 +38952,12 @@
       <c r="Z2" t="s">
         <v>6</v>
       </c>
+      <c r="AA2" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>42</v>
+      </c>
       <c r="AD2" t="s">
         <v>19</v>
       </c>
@@ -39085,7 +39117,7 @@
         <v>8000</v>
       </c>
       <c r="C18">
-        <v>848.42142860000001</v>
+        <v>848.42142857142801</v>
       </c>
       <c r="D18">
         <v>3091.18541</v>
@@ -39104,7 +39136,7 @@
       </c>
       <c r="I18" s="3">
         <f>SUM(B18:H18)</f>
-        <v>13410.982838600001</v>
+        <v>13410.982838571428</v>
       </c>
       <c r="J18" s="3">
         <f>AD18*1000/100</f>
@@ -39113,7 +39145,7 @@
       <c r="K18" s="7"/>
       <c r="L18" s="3">
         <f>I18/J18</f>
-        <v>107.28786270880001</v>
+        <v>107.28786270857142</v>
       </c>
       <c r="M18" s="3">
         <v>121.9734352</v>
@@ -39128,23 +39160,31 @@
       <c r="U18" s="7"/>
       <c r="V18" s="3">
         <f t="shared" ref="V18:V49" si="0">B18/$I18*100</f>
-        <v>59.652600381935436</v>
+        <v>59.652600382062523</v>
       </c>
       <c r="W18" s="3">
         <f t="shared" ref="W18:W49" si="1">C18/$I18*100</f>
-        <v>6.326318054468322</v>
+        <v>6.3263180542687509</v>
       </c>
       <c r="X18" s="3">
         <f t="shared" ref="X18:X49" si="2">D18/$I18*100</f>
-        <v>23.049655996149905</v>
+        <v>23.049655996199014</v>
       </c>
       <c r="Y18" s="3">
         <f t="shared" ref="Y18:Y49" si="3">E18/$I18*100</f>
-        <v>4.0086547456660612E-2</v>
+        <v>4.0086547456746023E-2</v>
       </c>
       <c r="Z18" s="3">
-        <f t="shared" ref="Z18:Z49" si="4">F18/$I18*100</f>
-        <v>0.65617860420128982</v>
+        <f>F18/$I18*100</f>
+        <v>0.65617860420268781</v>
+      </c>
+      <c r="AA18" s="3">
+        <f>G18/$I18*100</f>
+        <v>6.3082624904031128</v>
+      </c>
+      <c r="AB18" s="3">
+        <f t="shared" ref="AA18:AB18" si="4">H18/$I18*100</f>
+        <v>3.9668979254071584</v>
       </c>
       <c r="AD18">
         <v>12.5</v>
@@ -39170,7 +39210,7 @@
         <v>8000</v>
       </c>
       <c r="C19">
-        <v>831.7857143</v>
+        <v>831.78571428571399</v>
       </c>
       <c r="D19">
         <v>3017.4165459999999</v>
@@ -39179,7 +39219,7 @@
         <v>5.3760000000000003</v>
       </c>
       <c r="F19">
-        <v>84.571428569999995</v>
+        <v>84.571428571428498</v>
       </c>
       <c r="G19">
         <v>846</v>
@@ -39189,7 +39229,7 @@
       </c>
       <c r="I19" s="3">
         <f t="shared" ref="I19:I73" si="5">SUM(B19:H19)</f>
-        <v>13317.14968887</v>
+        <v>13317.149688857144</v>
       </c>
       <c r="J19" s="3">
         <f t="shared" ref="J19:J73" si="6">AD19*1000/100</f>
@@ -39198,7 +39238,7 @@
       <c r="K19" s="7"/>
       <c r="L19" s="3">
         <f t="shared" ref="L19:L73" si="7">I19/J19</f>
-        <v>104.85944636905512</v>
+        <v>104.85944636895388</v>
       </c>
       <c r="M19" s="3">
         <v>119.3832118</v>
@@ -39213,23 +39253,31 @@
       <c r="U19" s="7"/>
       <c r="V19" s="3">
         <f t="shared" si="0"/>
-        <v>60.072914902249053</v>
+        <v>60.072914902307048</v>
       </c>
       <c r="W19" s="3">
         <f t="shared" si="1"/>
-        <v>6.2459740540062931</v>
+        <v>6.2459740539050479</v>
       </c>
       <c r="X19" s="3">
         <f t="shared" si="2"/>
-        <v>22.658125924062034</v>
+        <v>22.658125924083908</v>
       </c>
       <c r="Y19" s="3">
         <f t="shared" si="3"/>
-        <v>4.0368998814311365E-2</v>
+        <v>4.036899881435034E-2</v>
       </c>
       <c r="Z19" s="3">
-        <f t="shared" si="4"/>
-        <v>0.63505652895590559</v>
+        <f t="shared" ref="Z18:Z49" si="8">F19/$I19*100</f>
+        <v>0.6350565289672454</v>
+      </c>
+      <c r="AA19" s="3">
+        <f t="shared" ref="AA19:AA73" si="9">G19/$I19*100</f>
+        <v>6.3527107509189706</v>
+      </c>
+      <c r="AB19" s="3">
+        <f t="shared" ref="AB19:AB73" si="10">H19/$I19*100</f>
+        <v>3.9948488410034191</v>
       </c>
       <c r="AD19">
         <v>12.7</v>
@@ -39264,7 +39312,7 @@
         <v>5.3760000000000003</v>
       </c>
       <c r="F20">
-        <v>81.142857140000004</v>
+        <v>81.142857142857096</v>
       </c>
       <c r="G20">
         <v>846</v>
@@ -39274,7 +39322,7 @@
       </c>
       <c r="I20" s="3">
         <f t="shared" si="5"/>
-        <v>12979.668857139999</v>
+        <v>12979.668857142857</v>
       </c>
       <c r="J20" s="3">
         <f t="shared" si="6"/>
@@ -39283,7 +39331,7 @@
       <c r="K20" s="7"/>
       <c r="L20" s="3">
         <f t="shared" si="7"/>
-        <v>100.77382653059004</v>
+        <v>100.77382653061223</v>
       </c>
       <c r="M20" s="3">
         <v>116.8479943</v>
@@ -39298,23 +39346,31 @@
       <c r="U20" s="7"/>
       <c r="V20" s="3">
         <f t="shared" si="0"/>
-        <v>61.634854386899654</v>
+        <v>61.634854386886076</v>
       </c>
       <c r="W20" s="3">
         <f t="shared" si="1"/>
-        <v>6.2802064441851559</v>
+        <v>6.2802064441837722</v>
       </c>
       <c r="X20" s="3">
         <f t="shared" si="2"/>
-        <v>20.801763355578633</v>
+        <v>20.801763355574053</v>
       </c>
       <c r="Y20" s="3">
         <f t="shared" si="3"/>
-        <v>4.1418622147996562E-2</v>
+        <v>4.1418622147987444E-2</v>
       </c>
       <c r="Z20" s="3">
-        <f t="shared" si="4"/>
-        <v>0.62515352304511262</v>
+        <f t="shared" si="8"/>
+        <v>0.62515352306698702</v>
+      </c>
+      <c r="AA20" s="3">
+        <f t="shared" si="9"/>
+        <v>6.5178858514132019</v>
+      </c>
+      <c r="AB20" s="3">
+        <f t="shared" si="10"/>
+        <v>4.0987178167279241</v>
       </c>
       <c r="AD20">
         <v>12.88</v>
@@ -39340,7 +39396,7 @@
         <v>8000</v>
       </c>
       <c r="C21">
-        <v>798.51428569999996</v>
+        <v>798.51428571428505</v>
       </c>
       <c r="D21">
         <v>2540.3726710000001</v>
@@ -39349,7 +39405,7 @@
         <v>5.3760000000000003</v>
       </c>
       <c r="F21">
-        <v>77.714285709999999</v>
+        <v>77.714285714285694</v>
       </c>
       <c r="G21">
         <v>846</v>
@@ -39359,7 +39415,7 @@
       </c>
       <c r="I21" s="3">
         <f t="shared" si="5"/>
-        <v>12799.977242410001</v>
+        <v>12799.977242428573</v>
       </c>
       <c r="J21" s="3">
         <f t="shared" si="6"/>
@@ -39368,7 +39424,7 @@
       <c r="K21" s="7"/>
       <c r="L21" s="3">
         <f t="shared" si="7"/>
-        <v>98.009014107274126</v>
+        <v>98.009014107416334</v>
       </c>
       <c r="M21" s="3">
         <v>114.36661460000001</v>
@@ -39383,23 +39439,31 @@
       <c r="U21" s="7"/>
       <c r="V21" s="3">
         <f t="shared" si="0"/>
-        <v>62.500111121242483</v>
+        <v>62.500111121151804</v>
       </c>
       <c r="W21" s="3">
         <f t="shared" si="1"/>
-        <v>6.2384039485186955</v>
+        <v>6.2384039486212473</v>
       </c>
       <c r="X21" s="3">
         <f t="shared" si="2"/>
-        <v>19.846696778358446</v>
+        <v>19.846696778329651</v>
       </c>
       <c r="Y21" s="3">
         <f t="shared" si="3"/>
-        <v>4.2000074673474955E-2</v>
+        <v>4.2000074673414017E-2</v>
       </c>
       <c r="Z21" s="3">
-        <f t="shared" si="4"/>
-        <v>0.60714393657287336</v>
+        <f t="shared" si="8"/>
+        <v>0.60714393660547439</v>
+      </c>
+      <c r="AA21" s="3">
+        <f t="shared" si="9"/>
+        <v>6.6093867510618036</v>
+      </c>
+      <c r="AB21" s="3">
+        <f t="shared" si="10"/>
+        <v>4.1562573895565951</v>
       </c>
       <c r="AD21">
         <v>13.06</v>
@@ -39425,7 +39489,7 @@
         <v>8000</v>
       </c>
       <c r="C22">
-        <v>781.87857140000006</v>
+        <v>781.87857142857104</v>
       </c>
       <c r="D22">
         <v>2484.6989140000001</v>
@@ -39434,7 +39498,7 @@
         <v>5.3760000000000003</v>
       </c>
       <c r="F22">
-        <v>74.285714290000001</v>
+        <v>74.285714285714207</v>
       </c>
       <c r="G22">
         <v>846</v>
@@ -39444,7 +39508,7 @@
       </c>
       <c r="I22" s="3">
         <f t="shared" si="5"/>
-        <v>12724.239199690001</v>
+        <v>12724.239199714286</v>
       </c>
       <c r="J22" s="3">
         <f t="shared" si="6"/>
@@ -39453,7 +39517,7 @@
       <c r="K22" s="7"/>
       <c r="L22" s="3">
         <f t="shared" si="7"/>
-        <v>96.104525677416916</v>
+        <v>96.104525677600336</v>
       </c>
       <c r="M22" s="3">
         <v>111.9379294</v>
@@ -39468,23 +39532,31 @@
       <c r="U22" s="7"/>
       <c r="V22" s="3">
         <f t="shared" si="0"/>
-        <v>62.872128340646903</v>
+        <v>62.872128340526913</v>
       </c>
       <c r="W22" s="3">
         <f t="shared" si="1"/>
-        <v>6.144796235982807</v>
+        <v>6.1447962361956199</v>
       </c>
       <c r="X22" s="3">
         <f t="shared" si="2"/>
-        <v>19.52728862610925</v>
+        <v>19.527288626071979</v>
       </c>
       <c r="Y22" s="3">
         <f t="shared" si="3"/>
-        <v>4.2250070244914728E-2</v>
+        <v>4.2250070244834084E-2</v>
       </c>
       <c r="Z22" s="3">
-        <f t="shared" si="4"/>
-        <v>0.5838126203396885</v>
+        <f t="shared" si="8"/>
+        <v>0.58381262030489212</v>
+      </c>
+      <c r="AA22" s="3">
+        <f t="shared" si="9"/>
+        <v>6.6487275720107206</v>
+      </c>
+      <c r="AB22" s="3">
+        <f t="shared" si="10"/>
+        <v>4.1809965346450397</v>
       </c>
       <c r="AD22">
         <v>13.24</v>
@@ -39510,7 +39582,7 @@
         <v>8000</v>
       </c>
       <c r="C23">
-        <v>765.24285710000004</v>
+        <v>765.24285714285702</v>
       </c>
       <c r="D23">
         <v>2433.9622639999998</v>
@@ -39519,7 +39591,7 @@
         <v>5.3760000000000003</v>
       </c>
       <c r="F23">
-        <v>45.34857143</v>
+        <v>45.348571428571397</v>
       </c>
       <c r="G23">
         <v>846</v>
@@ -39529,7 +39601,7 @@
       </c>
       <c r="I23" s="3">
         <f t="shared" si="5"/>
-        <v>12627.92969253</v>
+        <v>12627.929692571428</v>
       </c>
       <c r="J23" s="3">
         <f t="shared" si="6"/>
@@ -39538,7 +39610,7 @@
       <c r="K23" s="7"/>
       <c r="L23" s="3">
         <f t="shared" si="7"/>
-        <v>94.097836755067078</v>
+        <v>94.097836755375781</v>
       </c>
       <c r="M23" s="3">
         <v>109.5608196</v>
@@ -39555,23 +39627,31 @@
       <c r="U23" s="7"/>
       <c r="V23" s="3">
         <f t="shared" si="0"/>
-        <v>63.351635579127176</v>
+        <v>63.351635578919343</v>
       </c>
       <c r="W23" s="3">
         <f t="shared" si="1"/>
-        <v>6.0599233265661612</v>
+        <v>6.0599233268856629</v>
       </c>
       <c r="X23" s="3">
         <f t="shared" si="2"/>
-        <v>19.274436295284413</v>
+        <v>19.274436295221182</v>
       </c>
       <c r="Y23" s="3">
         <f t="shared" si="3"/>
-        <v>4.2572299109173463E-2</v>
+        <v>4.2572299109033797E-2</v>
       </c>
       <c r="Z23" s="3">
-        <f t="shared" si="4"/>
-        <v>0.3591132714084222</v>
+        <f t="shared" si="8"/>
+        <v>0.35911327139593108</v>
+      </c>
+      <c r="AA23" s="3">
+        <f t="shared" si="9"/>
+        <v>6.6994354624707197</v>
+      </c>
+      <c r="AB23" s="3">
+        <f t="shared" si="10"/>
+        <v>4.2128837659981357</v>
       </c>
       <c r="AD23">
         <v>13.42</v>
@@ -39597,7 +39677,7 @@
         <v>8000</v>
       </c>
       <c r="C24">
-        <v>748.60714289999999</v>
+        <v>748.60714285714198</v>
       </c>
       <c r="D24">
         <v>2387.5338750000001</v>
@@ -39606,7 +39686,7 @@
         <v>5.3760000000000003</v>
       </c>
       <c r="F24">
-        <v>43.154285710000003</v>
+        <v>43.154285714285699</v>
       </c>
       <c r="G24">
         <v>846</v>
@@ -39616,7 +39696,7 @@
       </c>
       <c r="I24" s="3">
         <f t="shared" si="5"/>
-        <v>12562.671303610001</v>
+        <v>12562.671303571427</v>
       </c>
       <c r="J24" s="3">
         <f t="shared" si="6"/>
@@ -39625,7 +39705,7 @@
       <c r="K24" s="7"/>
       <c r="L24" s="3">
         <f t="shared" si="7"/>
-        <v>92.372583114779417</v>
+        <v>92.372583114495797</v>
       </c>
       <c r="M24" s="3">
         <v>107.23419010000001</v>
@@ -39642,23 +39722,31 @@
       <c r="U24" s="7"/>
       <c r="V24" s="3">
         <f t="shared" si="0"/>
-        <v>63.680723682558863</v>
+        <v>63.68072368275439</v>
       </c>
       <c r="W24" s="3">
         <f t="shared" si="1"/>
-        <v>5.9589805767255939</v>
+        <v>5.9589805764027375</v>
       </c>
       <c r="X24" s="3">
         <f t="shared" si="2"/>
-        <v>19.004985622078006</v>
+        <v>19.00498562213636</v>
       </c>
       <c r="Y24" s="3">
         <f t="shared" si="3"/>
-        <v>4.2793446314679559E-2</v>
+        <v>4.2793446314810954E-2</v>
       </c>
       <c r="Z24" s="3">
-        <f t="shared" si="4"/>
-        <v>0.34351201800208858</v>
+        <f t="shared" si="8"/>
+        <v>0.34351201803725789</v>
+      </c>
+      <c r="AA24" s="3">
+        <f t="shared" si="9"/>
+        <v>6.7342365294512776</v>
+      </c>
+      <c r="AB24" s="3">
+        <f t="shared" si="10"/>
+        <v>4.2347681249031668</v>
       </c>
       <c r="AD24">
         <v>13.6</v>
@@ -39684,7 +39772,7 @@
         <v>8000</v>
       </c>
       <c r="C25">
-        <v>731.97142859999997</v>
+        <v>731.97142857142796</v>
       </c>
       <c r="D25">
         <v>2344.8873480000002</v>
@@ -39693,7 +39781,7 @@
         <v>5.3760000000000003</v>
       </c>
       <c r="F25">
-        <v>40.96</v>
+        <v>40.959999999999901</v>
       </c>
       <c r="G25">
         <v>846</v>
@@ -39703,7 +39791,7 @@
       </c>
       <c r="I25" s="3">
         <f t="shared" si="5"/>
-        <v>12501.194776599999</v>
+        <v>12501.194776571427</v>
       </c>
       <c r="J25" s="3">
         <f t="shared" si="6"/>
@@ -39712,7 +39800,7 @@
       <c r="K25" s="7"/>
       <c r="L25" s="3">
         <f t="shared" si="7"/>
-        <v>91.101824297668301</v>
+        <v>91.101824297460084</v>
       </c>
       <c r="M25" s="3">
         <v>104.9569687</v>
@@ -39729,23 +39817,31 @@
       <c r="U25" s="7"/>
       <c r="V25" s="3">
         <f t="shared" si="0"/>
-        <v>63.993883328452483</v>
+        <v>63.993883328598756</v>
       </c>
       <c r="W25" s="3">
         <f t="shared" si="1"/>
-        <v>5.8552117751986357</v>
+        <v>5.8552117749834647</v>
       </c>
       <c r="X25" s="3">
         <f t="shared" si="2"/>
-        <v>18.757305920784546</v>
+        <v>18.75730592082742</v>
       </c>
       <c r="Y25" s="3">
         <f t="shared" si="3"/>
-        <v>4.3003889596720073E-2</v>
+        <v>4.3003889596818362E-2</v>
       </c>
       <c r="Z25" s="3">
-        <f t="shared" si="4"/>
-        <v>0.32764868264167674</v>
+        <f t="shared" si="8"/>
+        <v>0.3276486826424248</v>
+      </c>
+      <c r="AA25" s="3">
+        <f t="shared" si="9"/>
+        <v>6.7673531619993179</v>
+      </c>
+      <c r="AB25" s="3">
+        <f t="shared" si="10"/>
+        <v>4.2555932413518169</v>
       </c>
       <c r="AD25">
         <v>13.722222220000001</v>
@@ -39771,7 +39867,7 @@
         <v>8000</v>
       </c>
       <c r="C26">
-        <v>715.33571429999995</v>
+        <v>715.33571428571395</v>
       </c>
       <c r="D26">
         <v>2317.892053</v>
@@ -39780,7 +39876,7 @@
         <v>5.3760000000000003</v>
       </c>
       <c r="F26">
-        <v>38.765714289999998</v>
+        <v>38.765714285714203</v>
       </c>
       <c r="G26">
         <v>846</v>
@@ -39790,7 +39886,7 @@
       </c>
       <c r="I26" s="3">
         <f t="shared" si="5"/>
-        <v>12455.36948159</v>
+        <v>12455.369481571426</v>
       </c>
       <c r="J26" s="3">
         <f t="shared" si="6"/>
@@ -39799,7 +39895,7 @@
       <c r="K26" s="7"/>
       <c r="L26" s="3">
         <f t="shared" si="7"/>
-        <v>89.966553266690724</v>
+        <v>89.966553266556559</v>
       </c>
       <c r="M26" s="3">
         <v>102.7281064</v>
@@ -39818,23 +39914,31 @@
       <c r="U26" s="7"/>
       <c r="V26" s="3">
         <f t="shared" si="0"/>
-        <v>64.229327053080354</v>
+        <v>64.229327053176135</v>
       </c>
       <c r="W26" s="3">
         <f t="shared" si="1"/>
-        <v>5.7431914433154425</v>
+        <v>5.7431914432093096</v>
       </c>
       <c r="X26" s="3">
         <f t="shared" si="2"/>
-        <v>18.609580843234109</v>
+        <v>18.60958084326186</v>
       </c>
       <c r="Y26" s="3">
         <f t="shared" si="3"/>
-        <v>4.316210777967E-2</v>
+        <v>4.3162107779734366E-2</v>
       </c>
       <c r="Z26" s="3">
-        <f t="shared" si="4"/>
-        <v>0.31123696769733511</v>
+        <f t="shared" si="8"/>
+        <v>0.31123696766338999</v>
+      </c>
+      <c r="AA26" s="3">
+        <f t="shared" si="9"/>
+        <v>6.7922513358733756</v>
+      </c>
+      <c r="AB26" s="3">
+        <f t="shared" si="10"/>
+        <v>4.2712502490362132</v>
       </c>
       <c r="AD26">
         <v>13.84444444</v>
@@ -39869,7 +39973,7 @@
         <v>5.3760000000000003</v>
       </c>
       <c r="F27">
-        <v>36.571428570000002</v>
+        <v>36.571428571428498</v>
       </c>
       <c r="G27">
         <v>846</v>
@@ -39879,7 +39983,7 @@
       </c>
       <c r="I27" s="3">
         <f t="shared" si="5"/>
-        <v>12374.66669057</v>
+        <v>12374.66669057143</v>
       </c>
       <c r="J27" s="3">
         <f t="shared" si="6"/>
@@ -39888,7 +39992,7 @@
       <c r="K27" s="7"/>
       <c r="L27" s="3">
         <f t="shared" si="7"/>
-        <v>88.601432130906574</v>
+        <v>88.60143213091682</v>
       </c>
       <c r="M27" s="3">
         <v>100.5465761</v>
@@ -39907,23 +40011,31 @@
       <c r="U27" s="7"/>
       <c r="V27" s="3">
         <f t="shared" si="0"/>
-        <v>64.648205887406448</v>
+        <v>64.648205887398973</v>
       </c>
       <c r="W27" s="3">
         <f t="shared" si="1"/>
-        <v>5.6462126816913614</v>
+        <v>5.6462126816907094</v>
       </c>
       <c r="X27" s="3">
         <f t="shared" si="2"/>
-        <v>18.230949716966343</v>
+        <v>18.230949716964236</v>
       </c>
       <c r="Y27" s="3">
         <f t="shared" si="3"/>
-        <v>4.3443594356337135E-2</v>
+        <v>4.3443594356332119E-2</v>
       </c>
       <c r="Z27" s="3">
-        <f t="shared" si="4"/>
-        <v>0.2955346554737423</v>
+        <f t="shared" si="8"/>
+        <v>0.29553465548525193</v>
+      </c>
+      <c r="AA27" s="3">
+        <f t="shared" si="9"/>
+        <v>6.8365477725924428</v>
+      </c>
+      <c r="AB27" s="3">
+        <f t="shared" si="10"/>
+        <v>4.2991056915120316</v>
       </c>
       <c r="AD27">
         <v>13.96666667</v>
@@ -39958,7 +40070,7 @@
         <v>5.3760000000000003</v>
       </c>
       <c r="F28">
-        <v>34.377142859999999</v>
+        <v>34.3771428571428</v>
       </c>
       <c r="G28">
         <v>846</v>
@@ -39968,7 +40080,7 @@
       </c>
       <c r="I28" s="3">
         <f t="shared" si="5"/>
-        <v>12113.835995859999</v>
+        <v>12113.835995857144</v>
       </c>
       <c r="J28" s="3">
         <f t="shared" si="6"/>
@@ -39977,7 +40089,7 @@
       <c r="K28" s="7"/>
       <c r="L28" s="3">
         <f t="shared" si="7"/>
-        <v>85.981485768250664</v>
+        <v>85.981485768230385</v>
       </c>
       <c r="M28" s="3">
         <v>98.411372709999995</v>
@@ -40000,23 +40112,31 @@
       <c r="U28" s="7"/>
       <c r="V28" s="3">
         <f t="shared" si="0"/>
-        <v>66.040187457829745</v>
+        <v>66.040187457845306</v>
       </c>
       <c r="W28" s="3">
         <f t="shared" si="1"/>
-        <v>4.8064873934151713</v>
+        <v>4.8064873934163037</v>
       </c>
       <c r="X28" s="3">
         <f t="shared" si="2"/>
-        <v>17.449739733329881</v>
+        <v>17.449739733333995</v>
       </c>
       <c r="Y28" s="3">
         <f t="shared" si="3"/>
-        <v>4.4379005971661591E-2</v>
+        <v>4.4379005971672048E-2</v>
       </c>
       <c r="Z28" s="3">
-        <f t="shared" si="4"/>
-        <v>0.28378411984237417</v>
+        <f t="shared" si="8"/>
+        <v>0.28378411981885482</v>
+      </c>
+      <c r="AA28" s="3">
+        <f t="shared" si="9"/>
+        <v>6.983749823667142</v>
+      </c>
+      <c r="AB28" s="3">
+        <f t="shared" si="10"/>
+        <v>4.391672465946713</v>
       </c>
       <c r="AD28">
         <v>14.08888889</v>
@@ -40051,7 +40171,7 @@
         <v>5.3760000000000003</v>
       </c>
       <c r="F29">
-        <v>32.182857140000003</v>
+        <v>32.182857142857102</v>
       </c>
       <c r="G29">
         <v>846</v>
@@ -40061,7 +40181,7 @@
       </c>
       <c r="I29" s="3">
         <f t="shared" si="5"/>
-        <v>11964.83833814</v>
+        <v>11964.838338142858</v>
       </c>
       <c r="J29" s="3">
         <f t="shared" si="6"/>
@@ -40070,7 +40190,7 @@
       <c r="K29" s="7"/>
       <c r="L29" s="3">
         <f t="shared" si="7"/>
-        <v>84.193545779264554</v>
+        <v>84.193545779284662</v>
       </c>
       <c r="M29" s="3">
         <v>96.321512409999997</v>
@@ -40091,23 +40211,31 @@
       <c r="U29" s="7"/>
       <c r="V29" s="3">
         <f t="shared" si="0"/>
-        <v>66.862583295409934</v>
+        <v>66.862583295393975</v>
       </c>
       <c r="W29" s="3">
         <f t="shared" si="1"/>
-        <v>3.8930739123752436</v>
+        <v>3.8930739123743141</v>
       </c>
       <c r="X29" s="3">
         <f t="shared" si="2"/>
-        <v>17.413352542829998</v>
+        <v>17.413352542825837</v>
       </c>
       <c r="Y29" s="3">
         <f t="shared" si="3"/>
-        <v>4.4931655974515483E-2</v>
+        <v>4.4931655974504749E-2</v>
       </c>
       <c r="Z29" s="3">
-        <f t="shared" si="4"/>
-        <v>0.26897862077594109</v>
+        <f t="shared" si="8"/>
+        <v>0.26897862079975599</v>
+      </c>
+      <c r="AA29" s="3">
+        <f t="shared" si="9"/>
+        <v>7.0707181834879131</v>
+      </c>
+      <c r="AB29" s="3">
+        <f t="shared" si="10"/>
+        <v>4.4463617891436993</v>
       </c>
       <c r="AD29">
         <v>14.211111109999999</v>
@@ -40142,7 +40270,7 @@
         <v>5.3760000000000003</v>
       </c>
       <c r="F30">
-        <v>29.98857143</v>
+        <v>29.988571428571401</v>
       </c>
       <c r="G30">
         <v>846</v>
@@ -40152,7 +40280,7 @@
       </c>
       <c r="I30" s="3">
         <f t="shared" si="5"/>
-        <v>11910.556731430001</v>
+        <v>11910.556731428573</v>
       </c>
       <c r="J30" s="3">
         <f t="shared" si="6"/>
@@ -40161,7 +40289,7 @@
       <c r="K30" s="7"/>
       <c r="L30" s="3">
         <f t="shared" si="7"/>
-        <v>83.096907447906261</v>
+        <v>83.096907447896299</v>
       </c>
       <c r="M30" s="3">
         <v>94.276032310000005</v>
@@ -40184,23 +40312,31 @@
       <c r="U30" s="7"/>
       <c r="V30" s="3">
         <f t="shared" si="0"/>
-        <v>67.16730527708512</v>
+        <v>67.167305277093163</v>
       </c>
       <c r="W30" s="3">
         <f t="shared" si="1"/>
-        <v>3.715275532270367</v>
+        <v>3.7152755322708129</v>
       </c>
       <c r="X30" s="3">
         <f t="shared" si="2"/>
-        <v>17.250932986012582</v>
+        <v>17.25093298601465</v>
       </c>
       <c r="Y30" s="3">
         <f t="shared" si="3"/>
-        <v>4.513642914620121E-2</v>
+        <v>4.5136429146206615E-2</v>
       </c>
       <c r="Z30" s="3">
-        <f t="shared" si="4"/>
-        <v>0.2517814415078104</v>
+        <f t="shared" si="8"/>
+        <v>0.25178144149584619</v>
+      </c>
+      <c r="AA30" s="3">
+        <f t="shared" si="9"/>
+        <v>7.1029425330526035</v>
+      </c>
+      <c r="AB30" s="3">
+        <f t="shared" si="10"/>
+        <v>4.4666258009266961</v>
       </c>
       <c r="AD30">
         <v>14.33333333</v>
@@ -40235,7 +40371,7 @@
         <v>5.3760000000000003</v>
       </c>
       <c r="F31">
-        <v>27.79428571</v>
+        <v>27.794285714285699</v>
       </c>
       <c r="G31">
         <v>846</v>
@@ -40245,7 +40381,7 @@
       </c>
       <c r="I31" s="3">
         <f t="shared" si="5"/>
-        <v>11857.71451071</v>
+        <v>11857.714510714286</v>
       </c>
       <c r="J31" s="3">
         <f t="shared" si="6"/>
@@ -40254,7 +40390,7 @@
       <c r="K31" s="7"/>
       <c r="L31" s="3">
         <f t="shared" si="7"/>
-        <v>82.02877060997578</v>
+        <v>82.028770610005424</v>
       </c>
       <c r="M31" s="3">
         <v>92.273989950000001</v>
@@ -40277,23 +40413,31 @@
       <c r="U31" s="7"/>
       <c r="V31" s="3">
         <f t="shared" si="0"/>
-        <v>67.466626834153615</v>
+        <v>67.466626834129229</v>
       </c>
       <c r="W31" s="3">
         <f t="shared" si="1"/>
-        <v>3.5354199126767352</v>
+        <v>3.5354199126754575</v>
       </c>
       <c r="X31" s="3">
         <f t="shared" si="2"/>
-        <v>17.097090869989334</v>
+        <v>17.097090869983155</v>
       </c>
       <c r="Y31" s="3">
         <f t="shared" si="3"/>
-        <v>4.5337573232551227E-2</v>
+        <v>4.5337573232534845E-2</v>
       </c>
       <c r="Z31" s="3">
-        <f t="shared" si="4"/>
-        <v>0.23439833776480232</v>
+        <f t="shared" si="8"/>
+        <v>0.23439833780086028</v>
+      </c>
+      <c r="AA31" s="3">
+        <f t="shared" si="9"/>
+        <v>7.1345957877091664</v>
+      </c>
+      <c r="AB31" s="3">
+        <f t="shared" si="10"/>
+        <v>4.486530684469594</v>
       </c>
       <c r="AD31">
         <v>14.455555560000001</v>
@@ -40385,8 +40529,16 @@
         <v>4.5445721633125248E-2</v>
       </c>
       <c r="Z32" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0.21640819825297736</v>
+      </c>
+      <c r="AA32" s="3">
+        <f t="shared" si="9"/>
+        <v>7.151614676641362</v>
+      </c>
+      <c r="AB32" s="3">
+        <f t="shared" si="10"/>
+        <v>4.4972328699446855</v>
       </c>
       <c r="AD32">
         <v>14.57777778</v>
@@ -40424,7 +40576,7 @@
         <v>5.3760000000000003</v>
       </c>
       <c r="F33">
-        <v>12.327416169999999</v>
+        <v>12.327416173570001</v>
       </c>
       <c r="G33">
         <v>846</v>
@@ -40434,7 +40586,7 @@
       </c>
       <c r="I33" s="3">
         <f t="shared" si="5"/>
-        <v>11802.07407517</v>
+        <v>11802.07407517357</v>
       </c>
       <c r="J33" s="3">
         <f t="shared" si="6"/>
@@ -40443,7 +40595,7 @@
       <c r="K33" s="7"/>
       <c r="L33" s="3">
         <f t="shared" si="7"/>
-        <v>80.286218198435378</v>
+        <v>80.286218198459665</v>
       </c>
       <c r="M33" s="3">
         <v>88.396548280000005</v>
@@ -40468,23 +40620,31 @@
       <c r="U33" s="7"/>
       <c r="V33" s="3">
         <f t="shared" si="0"/>
-        <v>67.784695715738138</v>
+        <v>67.784695715717618</v>
       </c>
       <c r="W33" s="3">
         <f t="shared" si="1"/>
-        <v>3.5520875172439679</v>
+        <v>3.5520875172428932</v>
       </c>
       <c r="X33" s="3">
         <f t="shared" si="2"/>
-        <v>16.837300345205438</v>
+        <v>16.837300345200347</v>
       </c>
       <c r="Y33" s="3">
         <f t="shared" si="3"/>
-        <v>4.5551315520976028E-2</v>
+        <v>4.5551315520962248E-2</v>
       </c>
       <c r="Z33" s="3">
-        <f t="shared" si="4"/>
-        <v>0.10445126925559001</v>
+        <f t="shared" si="8"/>
+        <v>0.10445126928580732</v>
+      </c>
+      <c r="AA33" s="3">
+        <f t="shared" si="9"/>
+        <v>7.168231571937139</v>
+      </c>
+      <c r="AB33" s="3">
+        <f t="shared" si="10"/>
+        <v>4.5076822650952222</v>
       </c>
       <c r="AD33">
         <v>14.7</v>
@@ -40525,7 +40685,7 @@
         <v>5.3760000000000003</v>
       </c>
       <c r="F34">
-        <v>10.272846810000001</v>
+        <v>10.2728468113083</v>
       </c>
       <c r="G34">
         <v>846</v>
@@ -40535,7 +40695,7 @@
       </c>
       <c r="I34" s="3">
         <f t="shared" si="5"/>
-        <v>11779.461976809998</v>
+        <v>11779.461976811308</v>
       </c>
       <c r="J34" s="3">
         <f t="shared" si="6"/>
@@ -40544,7 +40704,7 @@
       <c r="K34" s="7"/>
       <c r="L34" s="3">
         <f t="shared" si="7"/>
-        <v>78.009681965629127</v>
+        <v>78.009681965637796</v>
       </c>
       <c r="M34" s="3">
         <v>86.519362419999993</v>
@@ -40567,23 +40727,31 @@
       <c r="U34" s="7"/>
       <c r="V34" s="3">
         <f t="shared" si="0"/>
-        <v>67.914816616832312</v>
+        <v>67.914816616824751</v>
       </c>
       <c r="W34" s="3">
         <f t="shared" si="1"/>
-        <v>3.5589061777635553</v>
+        <v>3.5589061777631597</v>
       </c>
       <c r="X34" s="3">
         <f t="shared" si="2"/>
-        <v>16.695101472984032</v>
+        <v>16.695101472982177</v>
       </c>
       <c r="Y34" s="3">
         <f t="shared" si="3"/>
-        <v>4.5638756766511315E-2</v>
+        <v>4.5638756766506243E-2</v>
       </c>
       <c r="Z34" s="3">
-        <f t="shared" si="4"/>
-        <v>8.7209813404245107E-2</v>
+        <f t="shared" si="8"/>
+        <v>8.7209813415342022E-2</v>
+      </c>
+      <c r="AA34" s="3">
+        <f t="shared" si="9"/>
+        <v>7.1819918572292183</v>
+      </c>
+      <c r="AB34" s="3">
+        <f t="shared" si="10"/>
+        <v>4.5163353050188464</v>
       </c>
       <c r="AD34">
         <v>15.1</v>
@@ -40609,7 +40777,7 @@
         <v>2012</v>
       </c>
       <c r="B35">
-        <v>8080</v>
+        <v>8045</v>
       </c>
       <c r="C35">
         <v>419.22</v>
@@ -40621,7 +40789,7 @@
         <v>5.3760000000000003</v>
       </c>
       <c r="F35">
-        <v>8.2182774490000003</v>
+        <v>8.2182774490466795</v>
       </c>
       <c r="G35">
         <v>846</v>
@@ -40631,7 +40799,7 @@
       </c>
       <c r="I35" s="3">
         <f t="shared" si="5"/>
-        <v>11853.800475448999</v>
+        <v>11818.800475449047</v>
       </c>
       <c r="J35" s="3">
         <f t="shared" si="6"/>
@@ -40640,7 +40808,7 @@
       <c r="K35" s="7"/>
       <c r="L35" s="3">
         <f t="shared" si="7"/>
-        <v>76.972730360058435</v>
+        <v>76.745457632786014</v>
       </c>
       <c r="M35" s="3">
         <v>84.682040420000007</v>
@@ -40667,23 +40835,31 @@
       <c r="U35" s="7"/>
       <c r="V35" s="3">
         <f t="shared" si="0"/>
-        <v>68.163792842092235</v>
+        <v>68.069513625445438</v>
       </c>
       <c r="W35" s="3">
         <f t="shared" si="1"/>
-        <v>3.53658728159182</v>
+        <v>3.5470604725990356</v>
       </c>
       <c r="X35" s="3">
         <f t="shared" si="2"/>
-        <v>16.559973335687904</v>
+        <v>16.609013766478849</v>
       </c>
       <c r="Y35" s="3">
         <f t="shared" si="3"/>
-        <v>4.5352543356322758E-2</v>
+        <v>4.5486849627146643E-2</v>
       </c>
       <c r="Z35" s="3">
-        <f t="shared" si="4"/>
-        <v>6.9330317023821073E-2</v>
+        <f t="shared" si="8"/>
+        <v>6.953563067688924E-2</v>
+      </c>
+      <c r="AA35" s="3">
+        <f t="shared" si="9"/>
+        <v>7.1580868274862457</v>
+      </c>
+      <c r="AB35" s="3">
+        <f t="shared" si="10"/>
+        <v>4.501302827686386</v>
       </c>
       <c r="AD35">
         <v>15.4</v>
@@ -40709,7 +40885,7 @@
         <v>2013</v>
       </c>
       <c r="B36">
-        <v>8160</v>
+        <v>8090</v>
       </c>
       <c r="C36">
         <v>419.22</v>
@@ -40721,7 +40897,7 @@
         <v>5.3760000000000003</v>
       </c>
       <c r="F36">
-        <v>5.7527942139999997</v>
+        <v>5.7527942143326696</v>
       </c>
       <c r="G36">
         <v>846</v>
@@ -40731,7 +40907,7 @@
       </c>
       <c r="I36" s="3">
         <f t="shared" si="5"/>
-        <v>11587.806922214</v>
+        <v>11517.806922214333</v>
       </c>
       <c r="J36" s="3">
         <f t="shared" si="6"/>
@@ -40740,7 +40916,7 @@
       <c r="K36" s="7"/>
       <c r="L36" s="3">
         <f t="shared" si="7"/>
-        <v>72.423793263837496</v>
+        <v>71.986293263839585</v>
       </c>
       <c r="M36" s="3">
         <v>82.883735720000004</v>
@@ -40765,23 +40941,31 @@
       <c r="U36" s="7"/>
       <c r="V36" s="3">
         <f t="shared" si="0"/>
-        <v>70.418846765190381</v>
+        <v>70.239065949237784</v>
       </c>
       <c r="W36" s="3">
         <f t="shared" si="1"/>
-        <v>3.6177682525616559</v>
+        <v>3.6397554050975853</v>
       </c>
       <c r="X36" s="3">
         <f t="shared" si="2"/>
-        <v>13.975535999788487</v>
+        <v>14.060472961016213</v>
       </c>
       <c r="Y36" s="3">
         <f t="shared" si="3"/>
-        <v>4.6393593162948957E-2</v>
+        <v>4.6675552353906344E-2</v>
       </c>
       <c r="Z36" s="3">
-        <f t="shared" si="4"/>
-        <v>4.9645237037664186E-2</v>
+        <f t="shared" si="8"/>
+        <v>4.9946958246341898E-2</v>
+      </c>
+      <c r="AA36" s="3">
+        <f t="shared" si="9"/>
+        <v>7.3451483056928515</v>
+      </c>
+      <c r="AB36" s="3">
+        <f t="shared" si="10"/>
+        <v>4.6189348683553151</v>
       </c>
       <c r="AD36">
         <v>16</v>
@@ -40807,7 +40991,7 @@
         <v>2014</v>
       </c>
       <c r="B37">
-        <v>8292.7000000000007</v>
+        <v>8180</v>
       </c>
       <c r="C37">
         <v>419.22</v>
@@ -40819,7 +41003,7 @@
         <v>5.3760000000000003</v>
       </c>
       <c r="F37">
-        <v>5.3418803419999996</v>
+        <v>5.3418803418803398</v>
       </c>
       <c r="G37">
         <v>848.09</v>
@@ -40829,7 +41013,7 @@
       </c>
       <c r="I37" s="3">
         <f t="shared" si="5"/>
-        <v>11695.467606342001</v>
+        <v>11582.76760634188</v>
       </c>
       <c r="J37" s="3">
         <f t="shared" si="6"/>
@@ -40838,7 +41022,7 @@
       <c r="K37" s="7"/>
       <c r="L37" s="3">
         <f t="shared" si="7"/>
-        <v>71.751335008233141</v>
+        <v>71.059923965287609</v>
       </c>
       <c r="M37" s="3">
         <v>81.123619750000003</v>
@@ -40863,23 +41047,31 @@
       <c r="U37" s="7"/>
       <c r="V37" s="3">
         <f t="shared" si="0"/>
-        <v>70.905245340538485</v>
+        <v>70.622154203639781</v>
       </c>
       <c r="W37" s="3">
         <f t="shared" si="1"/>
-        <v>3.5844654879183557</v>
+        <v>3.6193422353606204</v>
       </c>
       <c r="X37" s="3">
         <f t="shared" si="2"/>
-        <v>13.618435616343538</v>
+        <v>13.750942608292785</v>
       </c>
       <c r="Y37" s="3">
         <f t="shared" si="3"/>
-        <v>4.5966524648273173E-2</v>
+        <v>4.6413777628211188E-2</v>
       </c>
       <c r="Z37" s="3">
-        <f t="shared" si="4"/>
-        <v>4.5674790626612519E-2</v>
+        <f t="shared" si="8"/>
+        <v>4.6119205041768384E-2</v>
+      </c>
+      <c r="AA37" s="3">
+        <f t="shared" si="9"/>
+        <v>7.3219978922450943</v>
+      </c>
+      <c r="AB37" s="3">
+        <f t="shared" si="10"/>
+        <v>4.5930300777917319</v>
       </c>
       <c r="AD37">
         <v>16.3</v>
@@ -40905,7 +41097,7 @@
         <v>2015</v>
       </c>
       <c r="B38">
-        <v>8225.6625000000004</v>
+        <v>8090</v>
       </c>
       <c r="C38">
         <v>419.22</v>
@@ -40917,7 +41109,7 @@
         <v>5.7881600000000004</v>
       </c>
       <c r="F38">
-        <v>4.5200525970000003</v>
+        <v>4.5200525969756704</v>
       </c>
       <c r="G38">
         <v>850.28</v>
@@ -40927,7 +41119,7 @@
       </c>
       <c r="I38" s="3">
         <f t="shared" si="5"/>
-        <v>11532.713136597</v>
+        <v>11397.050636596976</v>
       </c>
       <c r="J38" s="3">
         <f t="shared" si="6"/>
@@ -40936,7 +41128,7 @@
       <c r="K38" s="7"/>
       <c r="L38" s="3">
         <f t="shared" si="7"/>
-        <v>67.83948903880588</v>
+        <v>67.041474332923386</v>
       </c>
       <c r="M38" s="3">
         <v>79.40088154</v>
@@ -40963,23 +41155,31 @@
       <c r="U38" s="7"/>
       <c r="V38" s="3">
         <f t="shared" si="0"/>
-        <v>71.324608551107843</v>
+        <v>70.983276796386846</v>
       </c>
       <c r="W38" s="3">
         <f t="shared" si="1"/>
-        <v>3.6350509635905226</v>
+        <v>3.6783200616293317</v>
       </c>
       <c r="X38" s="3">
         <f t="shared" si="2"/>
-        <v>12.965226883647318</v>
+        <v>13.119555854201781</v>
       </c>
       <c r="Y38" s="3">
         <f t="shared" si="3"/>
-        <v>5.0189057262096555E-2</v>
+        <v>5.0786472610849759E-2</v>
       </c>
       <c r="Z38" s="3">
-        <f t="shared" si="4"/>
-        <v>3.919331508087566E-2</v>
+        <f t="shared" si="8"/>
+        <v>3.9659844823900024E-2</v>
+      </c>
+      <c r="AA38" s="3">
+        <f t="shared" si="9"/>
+        <v>7.4605266494971332</v>
+      </c>
+      <c r="AB38" s="3">
+        <f t="shared" si="10"/>
+        <v>4.667874320850161</v>
       </c>
       <c r="AD38">
         <v>17</v>
@@ -41008,10 +41208,10 @@
         <v>2016</v>
       </c>
       <c r="B39">
-        <v>8158.8874999999998</v>
+        <v>8135</v>
       </c>
       <c r="C39">
-        <v>419.22</v>
+        <v>419.219999999999</v>
       </c>
       <c r="D39">
         <v>1412.526316</v>
@@ -41020,7 +41220,7 @@
         <v>6.2003199999999996</v>
       </c>
       <c r="F39">
-        <v>4.0997570090000002</v>
+        <v>4.0997570089490099</v>
       </c>
       <c r="G39">
         <v>852.81</v>
@@ -41030,7 +41230,7 @@
       </c>
       <c r="I39" s="3">
         <f t="shared" si="5"/>
-        <v>11385.743893008999</v>
+        <v>11361.856393008948</v>
       </c>
       <c r="J39" s="3">
         <f t="shared" si="6"/>
@@ -41039,7 +41239,7 @@
       <c r="K39" s="7"/>
       <c r="L39" s="3">
         <f t="shared" si="7"/>
-        <v>65.06139367433714</v>
+        <v>64.924893674336843</v>
       </c>
       <c r="M39" s="3">
         <v>77.714727339999996</v>
@@ -41064,23 +41264,31 @@
       <c r="U39" s="7"/>
       <c r="V39" s="3">
         <f t="shared" si="0"/>
-        <v>71.658800484785772</v>
+        <v>71.599215115987022</v>
       </c>
       <c r="W39" s="3">
         <f t="shared" si="1"/>
-        <v>3.6819728595635004</v>
+        <v>3.6897139472555636</v>
       </c>
       <c r="X39" s="3">
         <f t="shared" si="2"/>
-        <v>12.406095985237382</v>
+        <v>12.432178925172298</v>
       </c>
       <c r="Y39" s="3">
         <f t="shared" si="3"/>
-        <v>5.4456872192664374E-2</v>
+        <v>5.4571363917388642E-2</v>
       </c>
       <c r="Z39" s="3">
-        <f t="shared" si="4"/>
-        <v>3.6007809832410746E-2</v>
+        <f t="shared" si="8"/>
+        <v>3.608351370707015E-2</v>
+      </c>
+      <c r="AA39" s="3">
+        <f t="shared" si="9"/>
+        <v>7.5059037053552409</v>
+      </c>
+      <c r="AB39" s="3">
+        <f t="shared" si="10"/>
+        <v>4.6823334286054203</v>
       </c>
       <c r="AD39">
         <v>17.5</v>
@@ -41106,10 +41314,10 @@
         <v>2017</v>
       </c>
       <c r="B40">
-        <v>8289.75</v>
+        <v>8208.375</v>
       </c>
       <c r="C40">
-        <v>419.22</v>
+        <v>419.219999999999</v>
       </c>
       <c r="D40">
         <v>1379.8208959999999</v>
@@ -41118,7 +41326,7 @@
         <v>7.2038399999999996</v>
       </c>
       <c r="F40">
-        <v>4.079110301</v>
+        <v>4.0797067542614096</v>
       </c>
       <c r="G40">
         <v>847.99</v>
@@ -41128,7 +41336,7 @@
       </c>
       <c r="I40" s="3">
         <f t="shared" si="5"/>
-        <v>11480.063846300998</v>
+        <v>11398.689442754259</v>
       </c>
       <c r="J40" s="3">
         <f t="shared" si="6"/>
@@ -41137,7 +41345,7 @@
       <c r="K40" s="7"/>
       <c r="L40" s="3">
         <f t="shared" si="7"/>
-        <v>64.859117775711852</v>
+        <v>64.399375382792428</v>
       </c>
       <c r="M40" s="3">
         <v>76.064380240000006</v>
@@ -41162,23 +41370,31 @@
       <c r="U40" s="7"/>
       <c r="V40" s="3">
         <f t="shared" si="0"/>
-        <v>72.209964256174828</v>
+        <v>72.011568007213071</v>
       </c>
       <c r="W40" s="3">
         <f t="shared" si="1"/>
-        <v>3.6517218511382872</v>
+        <v>3.6777912242050093</v>
       </c>
       <c r="X40" s="3">
         <f t="shared" si="2"/>
-        <v>12.019278938458111</v>
+        <v>12.10508368466081</v>
       </c>
       <c r="Y40" s="3">
         <f t="shared" si="3"/>
-        <v>6.2750870521692745E-2</v>
+        <v>6.3198844359947229E-2</v>
       </c>
       <c r="Z40" s="3">
-        <f t="shared" si="4"/>
-        <v>3.5532122082355268E-2</v>
+        <f t="shared" si="8"/>
+        <v>3.5791015929947399E-2</v>
+      </c>
+      <c r="AA40" s="3">
+        <f t="shared" si="9"/>
+        <v>7.439364009860248</v>
+      </c>
+      <c r="AB40" s="3">
+        <f t="shared" si="10"/>
+        <v>4.6672032137709785</v>
       </c>
       <c r="AD40">
         <v>17.7</v>
@@ -41204,10 +41420,10 @@
         <v>2018</v>
       </c>
       <c r="B41">
-        <v>8350.15</v>
+        <v>8253.5499999999993</v>
       </c>
       <c r="C41">
-        <v>410.85500830000001</v>
+        <v>410.8550082557</v>
       </c>
       <c r="D41">
         <v>1361.666667</v>
@@ -41216,7 +41432,7 @@
         <v>7.45472</v>
       </c>
       <c r="F41">
-        <v>4.3128338230000001</v>
+        <v>4.3143250717191401</v>
       </c>
       <c r="G41">
         <v>848.95500000000004</v>
@@ -41226,7 +41442,7 @@
       </c>
       <c r="I41" s="3">
         <f t="shared" si="5"/>
-        <v>11515.394229122998</v>
+        <v>11418.795720327416</v>
       </c>
       <c r="J41" s="3">
         <f t="shared" si="6"/>
@@ -41235,7 +41451,7 @@
       <c r="K41" s="7"/>
       <c r="L41" s="3">
         <f t="shared" si="7"/>
-        <v>62.583664288711944</v>
+        <v>62.058672393083782</v>
       </c>
       <c r="M41" s="3">
         <v>74.449079859999998</v>
@@ -41260,23 +41476,31 @@
       <c r="U41" s="7"/>
       <c r="V41" s="3">
         <f t="shared" si="0"/>
-        <v>72.512932113796495</v>
+        <v>72.28038929978635</v>
       </c>
       <c r="W41" s="3">
         <f t="shared" si="1"/>
-        <v>3.5678761849153848</v>
+        <v>3.5980590100609957</v>
       </c>
       <c r="X41" s="3">
         <f t="shared" si="2"/>
-        <v>11.824750763254618</v>
+        <v>11.924783491625124</v>
       </c>
       <c r="Y41" s="3">
         <f t="shared" si="3"/>
-        <v>6.4736993381838775E-2</v>
+        <v>6.5284642816836796E-2</v>
       </c>
       <c r="Z41" s="3">
-        <f t="shared" si="4"/>
-        <v>3.7452767462295221E-2</v>
+        <f t="shared" si="8"/>
+        <v>3.7782662702678015E-2</v>
+      </c>
+      <c r="AA41" s="3">
+        <f t="shared" si="9"/>
+        <v>7.4347157160252406</v>
+      </c>
+      <c r="AB41" s="3">
+        <f t="shared" si="10"/>
+        <v>4.6589851769827941</v>
       </c>
       <c r="AD41">
         <v>18.399999999999999</v>
@@ -41302,10 +41526,10 @@
         <v>2019</v>
       </c>
       <c r="B42">
-        <v>8607.5</v>
+        <v>8450</v>
       </c>
       <c r="C42">
-        <v>402.1406667</v>
+        <v>402.14066674430001</v>
       </c>
       <c r="D42">
         <v>1343.6470589999999</v>
@@ -41314,7 +41538,7 @@
         <v>8.26112</v>
       </c>
       <c r="F42">
-        <v>4.1473098100000003</v>
+        <v>4.1223937921719198</v>
       </c>
       <c r="G42">
         <v>851.31</v>
@@ -41324,7 +41548,7 @@
       </c>
       <c r="I42" s="3">
         <f t="shared" si="5"/>
-        <v>11749.006155509998</v>
+        <v>11591.48123953647</v>
       </c>
       <c r="J42" s="3">
         <f t="shared" si="6"/>
@@ -41333,7 +41557,7 @@
       <c r="K42" s="7"/>
       <c r="L42" s="3">
         <f t="shared" si="7"/>
-        <v>61.192740393281241</v>
+        <v>60.372298122585782</v>
       </c>
       <c r="M42" s="3">
         <v>72.868081930000002</v>
@@ -41358,23 +41582,31 @@
       <c r="U42" s="7"/>
       <c r="V42" s="3">
         <f t="shared" si="0"/>
-        <v>73.26151579181267</v>
+        <v>72.898362386841129</v>
       </c>
       <c r="W42" s="3">
         <f t="shared" si="1"/>
-        <v>3.4227632650563029</v>
+        <v>3.4692776396227094</v>
       </c>
       <c r="X42" s="3">
         <f t="shared" si="2"/>
-        <v>11.436261426843004</v>
+        <v>11.591676949940272</v>
       </c>
       <c r="Y42" s="3">
         <f t="shared" si="3"/>
-        <v>7.0313351535063545E-2</v>
+        <v>7.1268889879429712E-2</v>
       </c>
       <c r="Z42" s="3">
-        <f t="shared" si="4"/>
-        <v>3.5299239400389731E-2</v>
+        <f t="shared" si="8"/>
+        <v>3.5563994859528145E-2</v>
+      </c>
+      <c r="AA42" s="3">
+        <f t="shared" si="9"/>
+        <v>7.3442727672830443</v>
+      </c>
+      <c r="AB42" s="3">
+        <f t="shared" si="10"/>
+        <v>4.5895773715739034</v>
       </c>
       <c r="AD42">
         <v>19.2</v>
@@ -41400,10 +41632,10 @@
         <v>2020</v>
       </c>
       <c r="B43">
-        <v>8975.5</v>
+        <v>8764.1</v>
       </c>
       <c r="C43">
-        <v>380.05398330000003</v>
+        <v>400.587999999999</v>
       </c>
       <c r="D43">
         <v>1343.6470589999999</v>
@@ -41412,7 +41644,7 @@
         <v>8.2252799999999997</v>
       </c>
       <c r="F43">
-        <v>3.5949654450000001</v>
+        <v>3.3920347419549</v>
       </c>
       <c r="G43">
         <v>849.44500000000005</v>
@@ -41422,7 +41654,7 @@
       </c>
       <c r="I43" s="3">
         <f t="shared" si="5"/>
-        <v>12092.466287744999</v>
+        <v>11901.397373741956</v>
       </c>
       <c r="J43" s="3">
         <f t="shared" si="6"/>
@@ -41431,7 +41663,7 @@
       <c r="K43" s="7"/>
       <c r="L43" s="3">
         <f t="shared" si="7"/>
-        <v>59.708250595798276</v>
+        <v>58.764820998651295</v>
       </c>
       <c r="M43" s="3">
         <v>71.320658019999996</v>
@@ -41460,23 +41692,31 @@
       <c r="U43" s="7"/>
       <c r="V43" s="3">
         <f t="shared" si="0"/>
-        <v>74.223899297500125</v>
+        <v>73.639251969993268</v>
       </c>
       <c r="W43" s="3">
         <f t="shared" si="1"/>
-        <v>3.1428988450864019</v>
+        <v>3.3658904700032619</v>
       </c>
       <c r="X43" s="3">
         <f t="shared" si="2"/>
-        <v>11.111439362553419</v>
+        <v>11.289826033071439</v>
       </c>
       <c r="Y43" s="3">
         <f t="shared" si="3"/>
-        <v>6.8019871251043598E-2</v>
+        <v>6.9111884442640562E-2</v>
       </c>
       <c r="Z43" s="3">
-        <f t="shared" si="4"/>
-        <v>2.9728968098453872E-2</v>
+        <f t="shared" si="8"/>
+        <v>2.8501146843804604E-2</v>
+      </c>
+      <c r="AA43" s="3">
+        <f t="shared" si="9"/>
+        <v>7.1373551636392714</v>
+      </c>
+      <c r="AB43" s="3">
+        <f t="shared" si="10"/>
+        <v>4.4700633320063003</v>
       </c>
       <c r="AD43">
         <v>20.252588490000001</v>
@@ -41505,10 +41745,10 @@
         <v>2021</v>
       </c>
       <c r="B44">
-        <v>9027</v>
+        <v>9076.6</v>
       </c>
       <c r="C44">
-        <v>367.38034160000001</v>
+        <v>388.94299999999998</v>
       </c>
       <c r="D44">
         <v>1272.176471</v>
@@ -41517,7 +41757,7 @@
         <v>8.2700800000000001</v>
       </c>
       <c r="F44">
-        <v>3.3412788689999999</v>
+        <v>6.0640035275966397</v>
       </c>
       <c r="G44">
         <v>849.14499999999998</v>
@@ -41527,7 +41767,7 @@
       </c>
       <c r="I44" s="3">
         <f t="shared" si="5"/>
-        <v>12047.313171469001</v>
+        <v>12121.198554527598</v>
       </c>
       <c r="J44" s="3">
         <f t="shared" si="6"/>
@@ -41536,7 +41776,7 @@
       <c r="K44" s="7"/>
       <c r="L44" s="3">
         <f t="shared" si="7"/>
-        <v>57.656813225558658</v>
+        <v>58.010418686832558</v>
       </c>
       <c r="M44" s="3">
         <v>69.806095139999996</v>
@@ -41563,23 +41803,31 @@
       <c r="U44" s="7"/>
       <c r="V44" s="3">
         <f t="shared" si="0"/>
-        <v>74.9295703657655</v>
+        <v>74.882033811826659</v>
       </c>
       <c r="W44" s="3">
         <f t="shared" si="1"/>
-        <v>3.0494794679202579</v>
+        <v>3.2087833414354816</v>
       </c>
       <c r="X44" s="3">
         <f t="shared" si="2"/>
-        <v>10.559835648772097</v>
+        <v>10.49546763281761</v>
       </c>
       <c r="Y44" s="3">
         <f t="shared" si="3"/>
-        <v>6.8646675671929766E-2</v>
+        <v>6.8228236364554065E-2</v>
       </c>
       <c r="Z44" s="3">
-        <f t="shared" si="4"/>
-        <v>2.7734639429088385E-2</v>
+        <f t="shared" si="8"/>
+        <v>5.0028085096680219E-2</v>
+      </c>
+      <c r="AA44" s="3">
+        <f t="shared" si="9"/>
+        <v>7.0054540908648111</v>
+      </c>
+      <c r="AB44" s="3">
+        <f t="shared" si="10"/>
+        <v>4.2900048015941934</v>
       </c>
       <c r="AD44">
         <v>20.894864800000001</v>
@@ -41605,10 +41853,10 @@
         <v>2022</v>
       </c>
       <c r="B45">
-        <v>9106.5</v>
+        <v>9484.2124999999996</v>
       </c>
       <c r="C45">
-        <v>354.70670000000001</v>
+        <v>372.64</v>
       </c>
       <c r="D45">
         <v>1250.7352940000001</v>
@@ -41617,7 +41865,7 @@
         <v>8.3148800000000005</v>
       </c>
       <c r="F45">
-        <v>3.0936340219999998</v>
+        <v>4.0231442787078002</v>
       </c>
       <c r="G45">
         <v>839.24437499999999</v>
@@ -41627,7 +41875,7 @@
       </c>
       <c r="I45" s="3">
         <f t="shared" si="5"/>
-        <v>12072.594883022</v>
+        <v>12469.170193278707</v>
       </c>
       <c r="J45" s="3">
         <f t="shared" si="6"/>
@@ -41636,7 +41884,7 @@
       <c r="K45" s="7"/>
       <c r="L45" s="3">
         <f t="shared" si="7"/>
-        <v>56.512013230160413</v>
+        <v>58.368388715061307</v>
       </c>
       <c r="M45" s="3">
         <v>68.323695470000004</v>
@@ -41663,23 +41911,31 @@
       <c r="U45" s="7"/>
       <c r="V45" s="3">
         <f t="shared" si="0"/>
-        <v>75.431173564903631</v>
+        <v>76.061296405371877</v>
       </c>
       <c r="W45" s="3">
         <f t="shared" si="1"/>
-        <v>2.9381148248321756</v>
+        <v>2.9884907674198335</v>
       </c>
       <c r="X45" s="3">
         <f t="shared" si="2"/>
-        <v>10.360119809527786</v>
+        <v>10.030621722319481</v>
       </c>
       <c r="Y45" s="3">
         <f t="shared" si="3"/>
-        <v>6.8874008285438534E-2</v>
+        <v>6.6683507171006406E-2</v>
       </c>
       <c r="Z45" s="3">
-        <f t="shared" si="4"/>
-        <v>2.5625261610912303E-2</v>
+        <f t="shared" si="8"/>
+        <v>3.2264731464459497E-2</v>
+      </c>
+      <c r="AA45" s="3">
+        <f t="shared" si="9"/>
+        <v>6.7305551371203549</v>
+      </c>
+      <c r="AB45" s="3">
+        <f t="shared" si="10"/>
+        <v>4.0900877291329838</v>
       </c>
       <c r="AD45">
         <v>21.362882320000001</v>
@@ -41705,10 +41961,10 @@
         <v>2023</v>
       </c>
       <c r="B46">
-        <v>9183.5499999999993</v>
+        <v>9654.375</v>
       </c>
       <c r="C46">
-        <v>348.49603339999999</v>
+        <v>337.70499999999998</v>
       </c>
       <c r="D46">
         <v>1229.294118</v>
@@ -41717,7 +41973,7 @@
         <v>8.3865599999999993</v>
       </c>
       <c r="F46">
-        <v>2.8988638820000001</v>
+        <v>3.2833258827952898</v>
       </c>
       <c r="G46">
         <v>829.23500000000001</v>
@@ -41727,7 +41983,7 @@
       </c>
       <c r="I46" s="3">
         <f t="shared" si="5"/>
-        <v>12101.860575282</v>
+        <v>12562.279003882797</v>
       </c>
       <c r="J46" s="3">
         <f t="shared" si="6"/>
@@ -41736,7 +41992,7 @@
       <c r="K46" s="7"/>
       <c r="L46" s="3">
         <f t="shared" si="7"/>
-        <v>55.683974515200646</v>
+        <v>57.802485787500444</v>
       </c>
       <c r="M46" s="3">
         <v>66.87277598</v>
@@ -41763,23 +42019,31 @@
       <c r="U46" s="7"/>
       <c r="V46" s="3">
         <f t="shared" si="0"/>
-        <v>75.885438795728334</v>
+        <v>76.852098230074247</v>
       </c>
       <c r="W46" s="3">
         <f t="shared" si="1"/>
-        <v>2.879689707480201</v>
+        <v>2.6882462958800772</v>
       </c>
       <c r="X46" s="3">
         <f t="shared" si="2"/>
-        <v>10.157893576387982</v>
+        <v>9.785597960529655</v>
       </c>
       <c r="Y46" s="3">
         <f t="shared" si="3"/>
-        <v>6.929975723839947E-2</v>
+        <v>6.6759860988661768E-2</v>
       </c>
       <c r="Z46" s="3">
-        <f t="shared" si="4"/>
-        <v>2.395386943988528E-2</v>
+        <f t="shared" si="8"/>
+        <v>2.6136387209521991E-2</v>
+      </c>
+      <c r="AA46" s="3">
+        <f t="shared" si="9"/>
+        <v>6.6009917447598241</v>
+      </c>
+      <c r="AB46" s="3">
+        <f t="shared" si="10"/>
+        <v>3.9801695205579981</v>
       </c>
       <c r="AD46">
         <v>21.733112049999999</v>
@@ -41805,7 +42069,7 @@
         <v>2024</v>
       </c>
       <c r="B47">
-        <v>9108.8250000000007</v>
+        <v>10055.525</v>
       </c>
       <c r="C47">
         <v>342.2853667</v>
@@ -41817,7 +42081,7 @@
         <v>8.45824</v>
       </c>
       <c r="F47">
-        <v>2.692895407</v>
+        <v>3.2833258827952898</v>
       </c>
       <c r="G47">
         <v>801.36775</v>
@@ -41827,7 +42091,7 @@
       </c>
       <c r="I47" s="3">
         <f t="shared" si="5"/>
-        <v>11968.629252107001</v>
+        <v>12915.919682582795</v>
       </c>
       <c r="J47" s="3">
         <f t="shared" si="6"/>
@@ -41836,7 +42100,7 @@
       <c r="K47" s="7"/>
       <c r="L47" s="3">
         <f t="shared" si="7"/>
-        <v>54.303214578596659</v>
+        <v>58.60119343906829</v>
       </c>
       <c r="M47" s="3">
         <v>65.452668169999995</v>
@@ -41863,23 +42127,31 @@
       <c r="U47" s="7"/>
       <c r="V47" s="3">
         <f t="shared" si="0"/>
-        <v>76.105833075215784</v>
+        <v>77.853728167417628</v>
       </c>
       <c r="W47" s="3">
         <f t="shared" si="1"/>
-        <v>2.8598543700377621</v>
+        <v>2.6501044843254498</v>
       </c>
       <c r="X47" s="3">
         <f t="shared" si="2"/>
-        <v>10.151538446109917</v>
+        <v>9.4069956291106074</v>
       </c>
       <c r="Y47" s="3">
         <f t="shared" si="3"/>
-        <v>7.0670081108168512E-2</v>
+        <v>6.5486935563760076E-2</v>
       </c>
       <c r="Z47" s="3">
-        <f t="shared" si="4"/>
-        <v>2.2499614202068571E-2</v>
+        <f t="shared" si="8"/>
+        <v>2.5420767266173674E-2</v>
+      </c>
+      <c r="AA47" s="3">
+        <f t="shared" si="9"/>
+        <v>6.2044962317367913</v>
+      </c>
+      <c r="AB47" s="3">
+        <f t="shared" si="10"/>
+        <v>3.7937677845795861</v>
       </c>
       <c r="AD47">
         <v>22.040369699999999</v>
@@ -41905,7 +42177,7 @@
         <v>2025</v>
       </c>
       <c r="B48">
-        <v>9034.1</v>
+        <v>10349.549999999999</v>
       </c>
       <c r="C48">
         <v>336.01129950000001</v>
@@ -41917,7 +42189,7 @@
         <v>8.1954133329999994</v>
       </c>
       <c r="F48">
-        <v>2.542951049</v>
+        <v>3.2833258827952898</v>
       </c>
       <c r="G48">
         <v>773.91700000000003</v>
@@ -41927,7 +42199,7 @@
       </c>
       <c r="I48" s="3">
         <f t="shared" si="5"/>
-        <v>11835.472545881999</v>
+        <v>13151.662920715795</v>
       </c>
       <c r="J48" s="3">
         <f t="shared" si="6"/>
@@ -41936,7 +42208,7 @@
       <c r="K48" s="7"/>
       <c r="L48" s="3">
         <f t="shared" si="7"/>
-        <v>53.065446717913204</v>
+        <v>58.966709209597525</v>
       </c>
       <c r="M48" s="3">
         <v>64.062717710000001</v>
@@ -41965,23 +42237,31 @@
       <c r="U48" s="7"/>
       <c r="V48" s="3">
         <f t="shared" si="0"/>
-        <v>76.330708089414642</v>
+        <v>78.693850826255158</v>
       </c>
       <c r="W48" s="3">
         <f t="shared" si="1"/>
-        <v>2.8390188748053902</v>
+        <v>2.5548959209616982</v>
       </c>
       <c r="X48" s="3">
         <f t="shared" si="2"/>
-        <v>10.144976276572667</v>
+        <v>9.129688688330905</v>
       </c>
       <c r="Y48" s="3">
         <f t="shared" si="3"/>
-        <v>6.9244496163792704E-2</v>
+        <v>6.2314654674512852E-2</v>
       </c>
       <c r="Z48" s="3">
-        <f t="shared" si="4"/>
-        <v>2.1485842995637612E-2</v>
+        <f t="shared" si="8"/>
+        <v>2.4965100630913912E-2</v>
+      </c>
+      <c r="AA48" s="3">
+        <f t="shared" si="9"/>
+        <v>5.8845562319040843</v>
+      </c>
+      <c r="AB48" s="3">
+        <f t="shared" si="10"/>
+        <v>3.6497285772427279</v>
       </c>
       <c r="AD48">
         <v>22.303538889999999</v>
@@ -42010,7 +42290,7 @@
         <v>2026</v>
       </c>
       <c r="B49">
-        <v>9205.2083330000005</v>
+        <v>10512.3125</v>
       </c>
       <c r="C49">
         <v>329.73723219999999</v>
@@ -42022,7 +42302,7 @@
         <v>7.9325866669999998</v>
       </c>
       <c r="F49">
-        <v>2.4012622069999998</v>
+        <v>3.2833258827952898</v>
       </c>
       <c r="G49">
         <v>752.61400000000003</v>
@@ -42032,7 +42312,7 @@
       </c>
       <c r="I49" s="3">
         <f t="shared" si="5"/>
-        <v>11959.069885074001</v>
+        <v>13267.056115749796</v>
       </c>
       <c r="J49" s="3">
         <f t="shared" si="6"/>
@@ -42041,7 +42321,7 @@
       <c r="K49" s="7"/>
       <c r="L49" s="3">
         <f t="shared" si="7"/>
-        <v>53.071119164179251</v>
+        <v>58.875608458111593</v>
       </c>
       <c r="M49" s="3">
         <v>62.70228419</v>
@@ -42068,23 +42348,31 @@
       <c r="U49" s="7"/>
       <c r="V49" s="3">
         <f t="shared" si="0"/>
-        <v>76.9726109259461</v>
+        <v>79.236210416872041</v>
       </c>
       <c r="W49" s="3">
         <f t="shared" si="1"/>
-        <v>2.7572146945268865</v>
+        <v>2.4853835645464497</v>
       </c>
       <c r="X49" s="3">
         <f t="shared" si="2"/>
-        <v>9.9604441018167797</v>
+        <v>8.9784535514695829</v>
       </c>
       <c r="Y49" s="3">
         <f t="shared" si="3"/>
-        <v>6.6331133969712686E-2</v>
+        <v>5.9791611626508034E-2</v>
       </c>
       <c r="Z49" s="3">
-        <f t="shared" si="4"/>
-        <v>2.0079004722574553E-2</v>
+        <f t="shared" si="8"/>
+        <v>2.4747961071013611E-2</v>
+      </c>
+      <c r="AA49" s="3">
+        <f t="shared" si="9"/>
+        <v>5.6728033215035927</v>
+      </c>
+      <c r="AB49" s="3">
+        <f t="shared" si="10"/>
+        <v>3.5426095729108003</v>
       </c>
       <c r="AD49">
         <v>22.534045020000001</v>
@@ -42110,7 +42398,7 @@
         <v>2027</v>
       </c>
       <c r="B50">
-        <v>9373.8666670000002</v>
+        <v>10676.825000000001</v>
       </c>
       <c r="C50">
         <v>323.463165</v>
@@ -42122,7 +42410,7 @@
         <v>7.6697600000000001</v>
       </c>
       <c r="F50">
-        <v>2.2668844890000002</v>
+        <v>3.2833258827952898</v>
       </c>
       <c r="G50">
         <v>731.46833330000004</v>
@@ -42132,7 +42420,7 @@
       </c>
       <c r="I50" s="3">
         <f t="shared" si="5"/>
-        <v>12080.381868788998</v>
+        <v>13384.356643182797</v>
       </c>
       <c r="J50" s="3">
         <f t="shared" si="6"/>
@@ -42141,7 +42429,7 @@
       <c r="K50" s="7"/>
       <c r="L50" s="3">
         <f t="shared" si="7"/>
-        <v>53.125467021151898</v>
+        <v>58.859910652644167</v>
       </c>
       <c r="M50" s="3">
         <v>61.370740789999999</v>
@@ -42167,24 +42455,32 @@
       </c>
       <c r="U50" s="7"/>
       <c r="V50" s="3">
-        <f t="shared" ref="V50:V73" si="8">B50/$I50*100</f>
-        <v>77.595781067305666</v>
+        <f t="shared" ref="V50:V73" si="11">B50/$I50*100</f>
+        <v>79.770924256102717</v>
       </c>
       <c r="W50" s="3">
-        <f t="shared" ref="W50:W73" si="9">C50/$I50*100</f>
-        <v>2.6775905638852597</v>
+        <f t="shared" ref="W50:W73" si="12">C50/$I50*100</f>
+        <v>2.4167255373066672</v>
       </c>
       <c r="X50" s="3">
-        <f t="shared" ref="X50:X73" si="10">D50/$I50*100</f>
-        <v>9.7815373043207821</v>
+        <f t="shared" ref="X50:X73" si="13">D50/$I50*100</f>
+        <v>8.8285682345580749</v>
       </c>
       <c r="Y50" s="3">
-        <f t="shared" ref="Y50:Y73" si="11">E50/$I50*100</f>
-        <v>6.3489383724000259E-2</v>
+        <f t="shared" ref="Y50:Y73" si="14">E50/$I50*100</f>
+        <v>5.7303912354326907E-2</v>
       </c>
       <c r="Z50" s="3">
-        <f t="shared" ref="Z50:Z73" si="12">F50/$I50*100</f>
-        <v>1.8765006881584983E-2</v>
+        <f t="shared" ref="Z50:Z73" si="15">F50/$I50*100</f>
+        <v>2.4531069892460039E-2</v>
+      </c>
+      <c r="AA50" s="3">
+        <f t="shared" si="9"/>
+        <v>5.4650989419993303</v>
+      </c>
+      <c r="AB50" s="3">
+        <f t="shared" si="10"/>
+        <v>3.4368480477864201</v>
       </c>
       <c r="AD50">
         <v>22.739342440000001</v>
@@ -42210,7 +42506,7 @@
         <v>2028</v>
       </c>
       <c r="B51">
-        <v>9540.0750000000007</v>
+        <v>10711.731249999901</v>
       </c>
       <c r="C51">
         <v>320.40829330000003</v>
@@ -42222,7 +42518,7 @@
         <v>7.3949866670000004</v>
       </c>
       <c r="F51">
-        <v>2.1296348279999999</v>
+        <v>3.2833258827952898</v>
       </c>
       <c r="G51">
         <v>710.48</v>
@@ -42232,7 +42528,7 @@
       </c>
       <c r="I51" s="3">
         <f t="shared" si="5"/>
-        <v>12202.605561795001</v>
+        <v>13375.415502849695</v>
       </c>
       <c r="J51" s="3">
         <f t="shared" si="6"/>
@@ -42241,7 +42537,7 @@
       <c r="K51" s="7"/>
       <c r="L51" s="3">
         <f t="shared" si="7"/>
-        <v>53.229372262171573</v>
+        <v>58.345323657063062</v>
       </c>
       <c r="M51" s="3">
         <v>60.067473990000003</v>
@@ -42267,24 +42563,32 @@
       </c>
       <c r="U51" s="7"/>
       <c r="V51" s="3">
-        <f t="shared" si="8"/>
-        <v>78.180638976555244</v>
+        <f t="shared" si="11"/>
+        <v>80.085222382196022</v>
       </c>
       <c r="W51" s="3">
+        <f t="shared" si="12"/>
+        <v>2.3955016068976365</v>
+      </c>
+      <c r="X51" s="3">
+        <f t="shared" si="13"/>
+        <v>8.7632241910561568</v>
+      </c>
+      <c r="Y51" s="3">
+        <f t="shared" si="14"/>
+        <v>5.5287902386467642E-2</v>
+      </c>
+      <c r="Z51" s="3">
+        <f t="shared" si="15"/>
+        <v>2.4547468316746958E-2</v>
+      </c>
+      <c r="AA51" s="3">
         <f t="shared" si="9"/>
-        <v>2.6257367057996426</v>
-      </c>
-      <c r="X51" s="3">
+        <v>5.3118349844805106</v>
+      </c>
+      <c r="AB51" s="3">
         <f t="shared" si="10"/>
-        <v>9.6054702503026892</v>
-      </c>
-      <c r="Y51" s="3">
-        <f t="shared" si="11"/>
-        <v>6.0601702067244391E-2</v>
-      </c>
-      <c r="Z51" s="3">
-        <f t="shared" si="12"/>
-        <v>1.7452295882345401E-2</v>
+        <v>3.3643814646664647</v>
       </c>
       <c r="AD51">
         <v>22.924571610000001</v>
@@ -42310,7 +42614,7 @@
         <v>2029</v>
       </c>
       <c r="B52">
-        <v>9735.8083330000009</v>
+        <v>10747.25</v>
       </c>
       <c r="C52">
         <v>317.35342170000001</v>
@@ -42322,7 +42626,7 @@
         <v>7.1202133329999997</v>
       </c>
       <c r="F52">
-        <v>1.9927764130000001</v>
+        <v>3.2833258827952898</v>
       </c>
       <c r="G52">
         <v>710.35866669999996</v>
@@ -42332,7 +42636,7 @@
       </c>
       <c r="I52" s="3">
         <f t="shared" si="5"/>
-        <v>12385.221646146001</v>
+        <v>13397.953862615796</v>
       </c>
       <c r="J52" s="3">
         <f t="shared" si="6"/>
@@ -42341,7 +42645,7 @@
       <c r="K52" s="7"/>
       <c r="L52" s="3">
         <f t="shared" si="7"/>
-        <v>53.630928714887673</v>
+        <v>58.016297896041003</v>
       </c>
       <c r="M52" s="3">
         <v>58.791883319999997</v>
@@ -42367,24 +42671,32 @@
       </c>
       <c r="U52" s="7"/>
       <c r="V52" s="3">
-        <f t="shared" si="8"/>
-        <v>78.608268880109733</v>
+        <f t="shared" si="11"/>
+        <v>80.215606877016995</v>
       </c>
       <c r="W52" s="3">
+        <f t="shared" si="12"/>
+        <v>2.36867080566316</v>
+      </c>
+      <c r="X52" s="3">
+        <f t="shared" si="13"/>
+        <v>8.6773566092353906</v>
+      </c>
+      <c r="Y52" s="3">
+        <f t="shared" si="14"/>
+        <v>5.3144035320702776E-2</v>
+      </c>
+      <c r="Z52" s="3">
+        <f t="shared" si="15"/>
+        <v>2.4506173975988442E-2</v>
+      </c>
+      <c r="AA52" s="3">
         <f t="shared" si="9"/>
-        <v>2.5623556103152434</v>
-      </c>
-      <c r="X52" s="3">
+        <v>5.3019936774234475</v>
+      </c>
+      <c r="AB52" s="3">
         <f t="shared" si="10"/>
-        <v>9.3868989043225639</v>
-      </c>
-      <c r="Y52" s="3">
-        <f t="shared" si="11"/>
-        <v>5.748959151825634E-2</v>
-      </c>
-      <c r="Z52" s="3">
-        <f t="shared" si="12"/>
-        <v>1.6089953574792152E-2</v>
+        <v>3.3587218213643162</v>
       </c>
       <c r="AD52">
         <v>23.093431240000001</v>
@@ -42410,7 +42722,7 @@
         <v>2030</v>
       </c>
       <c r="B53">
-        <v>9929.2083330000005</v>
+        <v>10775.4888888888</v>
       </c>
       <c r="C53">
         <v>314.29854999999998</v>
@@ -42422,7 +42734,7 @@
         <v>6.84544</v>
       </c>
       <c r="F53">
-        <v>1.856311209</v>
+        <v>3.2833258827952898</v>
       </c>
       <c r="G53">
         <v>710.23733330000005</v>
@@ -42432,7 +42744,7 @@
       </c>
       <c r="I53" s="3">
         <f t="shared" si="5"/>
-        <v>12565.504791508998</v>
+        <v>13413.212362071594</v>
       </c>
       <c r="J53" s="3">
         <f t="shared" si="6"/>
@@ -42441,7 +42753,7 @@
       <c r="K53" s="7"/>
       <c r="L53" s="3">
         <f t="shared" si="7"/>
-        <v>54.048264765492526</v>
+        <v>57.69452681207899</v>
       </c>
       <c r="M53" s="3">
         <v>57.54338104</v>
@@ -42469,24 +42781,32 @@
       </c>
       <c r="U53" s="7"/>
       <c r="V53" s="3">
-        <f t="shared" si="8"/>
-        <v>79.019573807409259</v>
+        <f t="shared" si="11"/>
+        <v>80.334886215315152</v>
       </c>
       <c r="W53" s="3">
+        <f t="shared" si="12"/>
+        <v>2.3432011774356072</v>
+      </c>
+      <c r="X53" s="3">
+        <f t="shared" si="13"/>
+        <v>8.5964405309834131</v>
+      </c>
+      <c r="Y53" s="3">
+        <f t="shared" si="14"/>
+        <v>5.1035052716803191E-2</v>
+      </c>
+      <c r="Z53" s="3">
+        <f t="shared" si="15"/>
+        <v>2.4478296430164019E-2</v>
+      </c>
+      <c r="AA53" s="3">
         <f t="shared" si="9"/>
-        <v>2.5012807301811204</v>
-      </c>
-      <c r="X53" s="3">
+        <v>5.2950576948168742</v>
+      </c>
+      <c r="AB53" s="3">
         <f t="shared" si="10"/>
-        <v>9.1763828284810867</v>
-      </c>
-      <c r="Y53" s="3">
-        <f t="shared" si="11"/>
-        <v>5.4478034218137669E-2</v>
-      </c>
-      <c r="Z53" s="3">
-        <f t="shared" si="12"/>
-        <v>1.4773073106099025E-2</v>
+        <v>3.3549010323020045</v>
       </c>
       <c r="AD53">
         <v>23.248673839999999</v>
@@ -42515,7 +42835,7 @@
         <v>2031</v>
       </c>
       <c r="B54">
-        <v>10120.275</v>
+        <v>10804.155555555501</v>
       </c>
       <c r="C54">
         <v>314.29854999999998</v>
@@ -42527,7 +42847,7 @@
         <v>6.84544</v>
       </c>
       <c r="F54">
-        <v>1.856311209</v>
+        <v>3.2833258827952898</v>
       </c>
       <c r="G54">
         <v>710.11599999999999</v>
@@ -42537,7 +42857,7 @@
       </c>
       <c r="I54" s="3">
         <f t="shared" si="5"/>
-        <v>12746.920713208998</v>
+        <v>13432.228283438295</v>
       </c>
       <c r="J54" s="3">
         <f t="shared" si="6"/>
@@ -42546,7 +42866,7 @@
       <c r="K54" s="7"/>
       <c r="L54" s="3">
         <f t="shared" si="7"/>
-        <v>54.491707614608238</v>
+        <v>57.421323369126519</v>
       </c>
       <c r="M54" s="3">
         <v>56.321391920000003</v>
@@ -42568,24 +42888,32 @@
       </c>
       <c r="U54" s="7"/>
       <c r="V54" s="3">
-        <f t="shared" si="8"/>
-        <v>79.393880511964468</v>
+        <f t="shared" si="11"/>
+        <v>80.434573680353822</v>
       </c>
       <c r="W54" s="3">
+        <f t="shared" si="12"/>
+        <v>2.3398839222195522</v>
+      </c>
+      <c r="X54" s="3">
+        <f t="shared" si="13"/>
+        <v>8.5133262171396531</v>
+      </c>
+      <c r="Y54" s="3">
+        <f t="shared" si="14"/>
+        <v>5.0962802712639338E-2</v>
+      </c>
+      <c r="Z54" s="3">
+        <f t="shared" si="15"/>
+        <v>2.4443642659375989E-2</v>
+      </c>
+      <c r="AA54" s="3">
         <f t="shared" si="9"/>
-        <v>2.4656821601966037</v>
-      </c>
-      <c r="X54" s="3">
+        <v>5.2866582149706369</v>
+      </c>
+      <c r="AB54" s="3">
         <f t="shared" si="10"/>
-        <v>8.9710247496481053</v>
-      </c>
-      <c r="Y54" s="3">
-        <f t="shared" si="11"/>
-        <v>5.3702695372588399E-2</v>
-      </c>
-      <c r="Z54" s="3">
-        <f t="shared" si="12"/>
-        <v>1.456282070599527E-2</v>
+        <v>3.3501515199443284</v>
       </c>
       <c r="AD54">
         <v>23.392404590000002</v>
@@ -42611,7 +42939,7 @@
         <v>2032</v>
       </c>
       <c r="B55">
-        <v>10120.275</v>
+        <v>10833.25</v>
       </c>
       <c r="C55">
         <v>314.29854999999998</v>
@@ -42623,7 +42951,7 @@
         <v>6.84544</v>
       </c>
       <c r="F55">
-        <v>1.856311209</v>
+        <v>3.2833258827952898</v>
       </c>
       <c r="G55">
         <v>710.11599999999999</v>
@@ -42633,7 +42961,7 @@
       </c>
       <c r="I55" s="3">
         <f t="shared" si="5"/>
-        <v>12746.920713208998</v>
+        <v>13461.322727882794</v>
       </c>
       <c r="J55" s="3">
         <f t="shared" si="6"/>
@@ -42642,7 +42970,7 @@
       <c r="K55" s="7"/>
       <c r="L55" s="3">
         <f t="shared" si="7"/>
-        <v>54.181646322913124</v>
+        <v>57.218260275592819</v>
       </c>
       <c r="M55" s="3">
         <v>55.125352909999997</v>
@@ -42664,24 +42992,32 @@
       </c>
       <c r="U55" s="7"/>
       <c r="V55" s="3">
-        <f t="shared" si="8"/>
-        <v>79.393880511964468</v>
+        <f t="shared" si="11"/>
+        <v>80.476861145010687</v>
       </c>
       <c r="W55" s="3">
+        <f t="shared" si="12"/>
+        <v>2.334826646336805</v>
+      </c>
+      <c r="X55" s="3">
+        <f t="shared" si="13"/>
+        <v>8.4949260567936413</v>
+      </c>
+      <c r="Y55" s="3">
+        <f t="shared" si="14"/>
+        <v>5.0852654961022953E-2</v>
+      </c>
+      <c r="Z55" s="3">
+        <f t="shared" si="15"/>
+        <v>2.4390811729032021E-2</v>
+      </c>
+      <c r="AA55" s="3">
         <f t="shared" si="9"/>
-        <v>2.4656821601966037</v>
-      </c>
-      <c r="X55" s="3">
+        <v>5.2752319690628759</v>
+      </c>
+      <c r="AB55" s="3">
         <f t="shared" si="10"/>
-        <v>8.9710247496481053</v>
-      </c>
-      <c r="Y55" s="3">
-        <f t="shared" si="11"/>
-        <v>5.3702695372588399E-2</v>
-      </c>
-      <c r="Z55" s="3">
-        <f t="shared" si="12"/>
-        <v>1.456282070599527E-2</v>
+        <v>3.3429107161059521</v>
       </c>
       <c r="AD55">
         <v>23.526270570000001</v>
@@ -42707,7 +43043,7 @@
         <v>2033</v>
       </c>
       <c r="B56">
-        <v>10120.275</v>
+        <v>10822.166666666601</v>
       </c>
       <c r="C56">
         <v>314.29854999999998</v>
@@ -42719,7 +43055,7 @@
         <v>6.84544</v>
       </c>
       <c r="F56">
-        <v>1.856311209</v>
+        <v>3.2833258827952898</v>
       </c>
       <c r="G56">
         <v>710.11599999999999</v>
@@ -42729,7 +43065,7 @@
       </c>
       <c r="I56" s="3">
         <f t="shared" si="5"/>
-        <v>12746.920713208998</v>
+        <v>13450.239394549395</v>
       </c>
       <c r="J56" s="3">
         <f t="shared" si="6"/>
@@ -42738,7 +43074,7 @@
       <c r="K56" s="7"/>
       <c r="L56" s="3">
         <f t="shared" si="7"/>
-        <v>53.894572188397859</v>
+        <v>56.868236204654721</v>
       </c>
       <c r="M56" s="3">
         <v>53.95471294</v>
@@ -42760,24 +43096,32 @@
       </c>
       <c r="U56" s="7"/>
       <c r="V56" s="3">
-        <f t="shared" si="8"/>
-        <v>79.393880511964468</v>
+        <f t="shared" si="11"/>
+        <v>80.460773590782324</v>
       </c>
       <c r="W56" s="3">
+        <f t="shared" si="12"/>
+        <v>2.3367506018321653</v>
+      </c>
+      <c r="X56" s="3">
+        <f t="shared" si="13"/>
+        <v>8.5019260881215732</v>
+      </c>
+      <c r="Y56" s="3">
+        <f t="shared" si="14"/>
+        <v>5.0894558819332698E-2</v>
+      </c>
+      <c r="Z56" s="3">
+        <f t="shared" si="15"/>
+        <v>2.4410910367333925E-2</v>
+      </c>
+      <c r="AA56" s="3">
         <f t="shared" si="9"/>
-        <v>2.4656821601966037</v>
-      </c>
-      <c r="X56" s="3">
+        <v>5.279578892014138</v>
+      </c>
+      <c r="AB56" s="3">
         <f t="shared" si="10"/>
-        <v>8.9710247496481053</v>
-      </c>
-      <c r="Y56" s="3">
-        <f t="shared" si="11"/>
-        <v>5.3702695372588399E-2</v>
-      </c>
-      <c r="Z56" s="3">
-        <f t="shared" si="12"/>
-        <v>1.456282070599527E-2</v>
+        <v>3.3456653580631359</v>
       </c>
       <c r="AD56">
         <v>23.651585300000001</v>
@@ -42803,7 +43147,7 @@
         <v>2034</v>
       </c>
       <c r="B57">
-        <v>10120.275</v>
+        <v>10811.083333333299</v>
       </c>
       <c r="C57">
         <v>314.29854999999998</v>
@@ -42815,7 +43159,7 @@
         <v>6.84544</v>
       </c>
       <c r="F57">
-        <v>1.856311209</v>
+        <v>3.2833258827952898</v>
       </c>
       <c r="G57">
         <v>710.11599999999999</v>
@@ -42825,7 +43169,7 @@
       </c>
       <c r="I57" s="3">
         <f t="shared" si="5"/>
-        <v>12746.920713208998</v>
+        <v>13439.156061216094</v>
       </c>
       <c r="J57" s="3">
         <f t="shared" si="6"/>
@@ -42834,7 +43178,7 @@
       <c r="K57" s="7"/>
       <c r="L57" s="3">
         <f t="shared" si="7"/>
-        <v>53.627409318732546</v>
+        <v>56.539703918164967</v>
       </c>
       <c r="M57" s="3">
         <v>52.808932630000001</v>
@@ -42856,24 +43200,32 @@
       </c>
       <c r="U57" s="7"/>
       <c r="V57" s="3">
-        <f t="shared" si="8"/>
-        <v>79.393880511964468</v>
+        <f t="shared" si="11"/>
+        <v>80.444659501595353</v>
       </c>
       <c r="W57" s="3">
+        <f t="shared" si="12"/>
+        <v>2.3386777307172624</v>
+      </c>
+      <c r="X57" s="3">
+        <f t="shared" si="13"/>
+        <v>8.5089376653650035</v>
+      </c>
+      <c r="Y57" s="3">
+        <f t="shared" si="14"/>
+        <v>5.0936531794248417E-2</v>
+      </c>
+      <c r="Z57" s="3">
+        <f t="shared" si="15"/>
+        <v>2.4431042156513101E-2</v>
+      </c>
+      <c r="AA57" s="3">
         <f t="shared" si="9"/>
-        <v>2.4656821601966037</v>
-      </c>
-      <c r="X57" s="3">
+        <v>5.2839329848197512</v>
+      </c>
+      <c r="AB57" s="3">
         <f t="shared" si="10"/>
-        <v>8.9710247496481053</v>
-      </c>
-      <c r="Y57" s="3">
-        <f t="shared" si="11"/>
-        <v>5.3702695372588399E-2</v>
-      </c>
-      <c r="Z57" s="3">
-        <f t="shared" si="12"/>
-        <v>1.456282070599527E-2</v>
+        <v>3.3484245435518813</v>
       </c>
       <c r="AD57">
         <v>23.769413579999998</v>
@@ -42899,7 +43251,7 @@
         <v>2035</v>
       </c>
       <c r="B58">
-        <v>10120.275</v>
+        <v>10800</v>
       </c>
       <c r="C58">
         <v>314.29854999999998</v>
@@ -42911,7 +43263,7 @@
         <v>6.84544</v>
       </c>
       <c r="F58">
-        <v>1.856311209</v>
+        <v>3.2833258827952898</v>
       </c>
       <c r="G58">
         <v>710.11599999999999</v>
@@ -42921,7 +43273,7 @@
       </c>
       <c r="I58" s="3">
         <f t="shared" si="5"/>
-        <v>12746.920713208998</v>
+        <v>13428.072727882794</v>
       </c>
       <c r="J58" s="3">
         <f t="shared" si="6"/>
@@ -42930,7 +43282,7 @@
       <c r="K58" s="7"/>
       <c r="L58" s="3">
         <f t="shared" si="7"/>
-        <v>53.377654814062275</v>
+        <v>56.229974831828194</v>
       </c>
       <c r="M58" s="3">
         <v>51.687484079999997</v>
@@ -42952,24 +43304,32 @@
       </c>
       <c r="U58" s="7"/>
       <c r="V58" s="3">
-        <f t="shared" si="8"/>
-        <v>79.393880511964468</v>
+        <f t="shared" si="11"/>
+        <v>80.428518811744894</v>
       </c>
       <c r="W58" s="3">
+        <f t="shared" si="12"/>
+        <v>2.3406080408499208</v>
+      </c>
+      <c r="X58" s="3">
+        <f t="shared" si="13"/>
+        <v>8.5159608171134806</v>
+      </c>
+      <c r="Y58" s="3">
+        <f t="shared" si="14"/>
+        <v>5.0978574056913986E-2</v>
+      </c>
+      <c r="Z58" s="3">
+        <f t="shared" si="15"/>
+        <v>2.4451207178656471E-2</v>
+      </c>
+      <c r="AA58" s="3">
         <f t="shared" si="9"/>
-        <v>2.4656821601966037</v>
-      </c>
-      <c r="X58" s="3">
+        <v>5.2882942652334304</v>
+      </c>
+      <c r="AB58" s="3">
         <f t="shared" si="10"/>
-        <v>8.9710247496481053</v>
-      </c>
-      <c r="Y58" s="3">
-        <f t="shared" si="11"/>
-        <v>5.3702695372588399E-2</v>
-      </c>
-      <c r="Z58" s="3">
-        <f t="shared" si="12"/>
-        <v>1.456282070599527E-2</v>
+        <v>3.3511882838227045</v>
       </c>
       <c r="AD58">
         <v>23.880630870000001</v>
@@ -42998,7 +43358,7 @@
         <v>2036</v>
       </c>
       <c r="B59">
-        <v>10120.275</v>
+        <v>10800</v>
       </c>
       <c r="C59">
         <v>314.29854999999998</v>
@@ -43010,7 +43370,7 @@
         <v>6.84544</v>
       </c>
       <c r="F59">
-        <v>1.856311209</v>
+        <v>3.2833258827952898</v>
       </c>
       <c r="G59">
         <v>710.11599999999999</v>
@@ -43020,7 +43380,7 @@
       </c>
       <c r="I59" s="3">
         <f t="shared" si="5"/>
-        <v>12746.920713208998</v>
+        <v>13428.072727882794</v>
       </c>
       <c r="J59" s="3">
         <f t="shared" si="6"/>
@@ -43029,7 +43389,7 @@
       <c r="K59" s="7"/>
       <c r="L59" s="3">
         <f t="shared" si="7"/>
-        <v>53.14324541684455</v>
+        <v>55.983039395046426</v>
       </c>
       <c r="M59" s="3">
         <v>50.589850570000003</v>
@@ -43051,24 +43411,32 @@
       </c>
       <c r="U59" s="7"/>
       <c r="V59" s="3">
-        <f t="shared" si="8"/>
-        <v>79.393880511964468</v>
+        <f t="shared" si="11"/>
+        <v>80.428518811744894</v>
       </c>
       <c r="W59" s="3">
+        <f t="shared" si="12"/>
+        <v>2.3406080408499208</v>
+      </c>
+      <c r="X59" s="3">
+        <f t="shared" si="13"/>
+        <v>8.5159608171134806</v>
+      </c>
+      <c r="Y59" s="3">
+        <f t="shared" si="14"/>
+        <v>5.0978574056913986E-2</v>
+      </c>
+      <c r="Z59" s="3">
+        <f t="shared" si="15"/>
+        <v>2.4451207178656471E-2</v>
+      </c>
+      <c r="AA59" s="3">
         <f t="shared" si="9"/>
-        <v>2.4656821601966037</v>
-      </c>
-      <c r="X59" s="3">
+        <v>5.2882942652334304</v>
+      </c>
+      <c r="AB59" s="3">
         <f t="shared" si="10"/>
-        <v>8.9710247496481053</v>
-      </c>
-      <c r="Y59" s="3">
-        <f t="shared" si="11"/>
-        <v>5.3702695372588399E-2</v>
-      </c>
-      <c r="Z59" s="3">
-        <f t="shared" si="12"/>
-        <v>1.456282070599527E-2</v>
+        <v>3.3511882838227045</v>
       </c>
       <c r="AD59">
         <v>23.985965879999998</v>
@@ -43094,7 +43462,7 @@
         <v>2037</v>
       </c>
       <c r="B60">
-        <v>10120.275</v>
+        <v>10800</v>
       </c>
       <c r="C60">
         <v>314.29854999999998</v>
@@ -43106,7 +43474,7 @@
         <v>6.84544</v>
       </c>
       <c r="F60">
-        <v>1.856311209</v>
+        <v>3.2833258827952898</v>
       </c>
       <c r="G60">
         <v>710.11599999999999</v>
@@ -43116,7 +43484,7 @@
       </c>
       <c r="I60" s="3">
         <f t="shared" si="5"/>
-        <v>12746.920713208998</v>
+        <v>13428.072727882794</v>
       </c>
       <c r="J60" s="3">
         <f t="shared" si="6"/>
@@ -43125,7 +43493,7 @@
       <c r="K60" s="7"/>
       <c r="L60" s="3">
         <f t="shared" si="7"/>
-        <v>52.922460632690274</v>
+        <v>55.750456624231717</v>
       </c>
       <c r="M60" s="3">
         <v>49.515526360000003</v>
@@ -43147,24 +43515,32 @@
       </c>
       <c r="U60" s="7"/>
       <c r="V60" s="3">
-        <f t="shared" si="8"/>
-        <v>79.393880511964468</v>
+        <f t="shared" si="11"/>
+        <v>80.428518811744894</v>
       </c>
       <c r="W60" s="3">
+        <f t="shared" si="12"/>
+        <v>2.3406080408499208</v>
+      </c>
+      <c r="X60" s="3">
+        <f t="shared" si="13"/>
+        <v>8.5159608171134806</v>
+      </c>
+      <c r="Y60" s="3">
+        <f t="shared" si="14"/>
+        <v>5.0978574056913986E-2</v>
+      </c>
+      <c r="Z60" s="3">
+        <f t="shared" si="15"/>
+        <v>2.4451207178656471E-2</v>
+      </c>
+      <c r="AA60" s="3">
         <f t="shared" si="9"/>
-        <v>2.4656821601966037</v>
-      </c>
-      <c r="X60" s="3">
+        <v>5.2882942652334304</v>
+      </c>
+      <c r="AB60" s="3">
         <f t="shared" si="10"/>
-        <v>8.9710247496481053</v>
-      </c>
-      <c r="Y60" s="3">
-        <f t="shared" si="11"/>
-        <v>5.3702695372588399E-2</v>
-      </c>
-      <c r="Z60" s="3">
-        <f t="shared" si="12"/>
-        <v>1.456282070599527E-2</v>
+        <v>3.3511882838227045</v>
       </c>
       <c r="AD60">
         <v>24.08603183</v>
@@ -43190,7 +43566,7 @@
         <v>2038</v>
       </c>
       <c r="B61">
-        <v>10120.275</v>
+        <v>10800</v>
       </c>
       <c r="C61">
         <v>314.29854999999998</v>
@@ -43202,7 +43578,7 @@
         <v>6.84544</v>
       </c>
       <c r="F61">
-        <v>1.856311209</v>
+        <v>3.2833258827952898</v>
       </c>
       <c r="G61">
         <v>710.11599999999999</v>
@@ -43212,7 +43588,7 @@
       </c>
       <c r="I61" s="3">
         <f t="shared" si="5"/>
-        <v>12746.920713208998</v>
+        <v>13428.072727882794</v>
       </c>
       <c r="J61" s="3">
         <f t="shared" si="6"/>
@@ -43221,7 +43597,7 @@
       <c r="K61" s="7"/>
       <c r="L61" s="3">
         <f t="shared" si="7"/>
-        <v>52.71385117152272</v>
+        <v>55.530699784183319</v>
       </c>
       <c r="M61" s="3">
         <v>48.464016460000003</v>
@@ -43243,24 +43619,32 @@
       </c>
       <c r="U61" s="7"/>
       <c r="V61" s="3">
-        <f t="shared" si="8"/>
-        <v>79.393880511964468</v>
+        <f t="shared" si="11"/>
+        <v>80.428518811744894</v>
       </c>
       <c r="W61" s="3">
+        <f t="shared" si="12"/>
+        <v>2.3406080408499208</v>
+      </c>
+      <c r="X61" s="3">
+        <f t="shared" si="13"/>
+        <v>8.5159608171134806</v>
+      </c>
+      <c r="Y61" s="3">
+        <f t="shared" si="14"/>
+        <v>5.0978574056913986E-2</v>
+      </c>
+      <c r="Z61" s="3">
+        <f t="shared" si="15"/>
+        <v>2.4451207178656471E-2</v>
+      </c>
+      <c r="AA61" s="3">
         <f t="shared" si="9"/>
-        <v>2.4656821601966037</v>
-      </c>
-      <c r="X61" s="3">
+        <v>5.2882942652334304</v>
+      </c>
+      <c r="AB61" s="3">
         <f t="shared" si="10"/>
-        <v>8.9710247496481053</v>
-      </c>
-      <c r="Y61" s="3">
-        <f t="shared" si="11"/>
-        <v>5.3702695372588399E-2</v>
-      </c>
-      <c r="Z61" s="3">
-        <f t="shared" si="12"/>
-        <v>1.456282070599527E-2</v>
+        <v>3.3511882838227045</v>
       </c>
       <c r="AD61">
         <v>24.181349740000002</v>
@@ -43286,7 +43670,7 @@
         <v>2039</v>
       </c>
       <c r="B62">
-        <v>10120.275</v>
+        <v>10800</v>
       </c>
       <c r="C62">
         <v>314.29854999999998</v>
@@ -43298,7 +43682,7 @@
         <v>6.84544</v>
       </c>
       <c r="F62">
-        <v>1.856311209</v>
+        <v>3.2833258827952898</v>
       </c>
       <c r="G62">
         <v>710.11599999999999</v>
@@ -43308,7 +43692,7 @@
       </c>
       <c r="I62" s="3">
         <f t="shared" si="5"/>
-        <v>12746.920713208998</v>
+        <v>13428.072727882794</v>
       </c>
       <c r="J62" s="3">
         <f t="shared" si="6"/>
@@ -43317,7 +43701,7 @@
       <c r="K62" s="7"/>
       <c r="L62" s="3">
         <f t="shared" si="7"/>
-        <v>52.516185073138622</v>
+        <v>55.322471082941924</v>
       </c>
       <c r="M62" s="3">
         <v>47.43483638</v>
@@ -43339,24 +43723,32 @@
       </c>
       <c r="U62" s="7"/>
       <c r="V62" s="3">
-        <f t="shared" si="8"/>
-        <v>79.393880511964468</v>
+        <f t="shared" si="11"/>
+        <v>80.428518811744894</v>
       </c>
       <c r="W62" s="3">
+        <f t="shared" si="12"/>
+        <v>2.3406080408499208</v>
+      </c>
+      <c r="X62" s="3">
+        <f t="shared" si="13"/>
+        <v>8.5159608171134806</v>
+      </c>
+      <c r="Y62" s="3">
+        <f t="shared" si="14"/>
+        <v>5.0978574056913986E-2</v>
+      </c>
+      <c r="Z62" s="3">
+        <f t="shared" si="15"/>
+        <v>2.4451207178656471E-2</v>
+      </c>
+      <c r="AA62" s="3">
         <f t="shared" si="9"/>
-        <v>2.4656821601966037</v>
-      </c>
-      <c r="X62" s="3">
+        <v>5.2882942652334304</v>
+      </c>
+      <c r="AB62" s="3">
         <f t="shared" si="10"/>
-        <v>8.9710247496481053</v>
-      </c>
-      <c r="Y62" s="3">
-        <f t="shared" si="11"/>
-        <v>5.3702695372588399E-2</v>
-      </c>
-      <c r="Z62" s="3">
-        <f t="shared" si="12"/>
-        <v>1.456282070599527E-2</v>
+        <v>3.3511882838227045</v>
       </c>
       <c r="AD62">
         <v>24.272366120000001</v>
@@ -43382,7 +43774,7 @@
         <v>2040</v>
       </c>
       <c r="B63">
-        <v>10120.275</v>
+        <v>10800</v>
       </c>
       <c r="C63">
         <v>314.29854999999998</v>
@@ -43394,7 +43786,7 @@
         <v>6.84544</v>
       </c>
       <c r="F63">
-        <v>1.856311209</v>
+        <v>3.2833258827952898</v>
       </c>
       <c r="G63">
         <v>710.11599999999999</v>
@@ -43404,7 +43796,7 @@
       </c>
       <c r="I63" s="3">
         <f t="shared" si="5"/>
-        <v>12746.920713208998</v>
+        <v>13428.072727882794</v>
       </c>
       <c r="J63" s="3">
         <f t="shared" si="6"/>
@@ -43413,7 +43805,7 @@
       <c r="K63" s="7"/>
       <c r="L63" s="3">
         <f t="shared" si="7"/>
-        <v>52.32840643171059</v>
+        <v>55.124658190670168</v>
       </c>
       <c r="M63" s="3">
         <v>46.427511940000002</v>
@@ -43435,24 +43827,32 @@
       </c>
       <c r="U63" s="7"/>
       <c r="V63" s="3">
-        <f t="shared" si="8"/>
-        <v>79.393880511964468</v>
+        <f t="shared" si="11"/>
+        <v>80.428518811744894</v>
       </c>
       <c r="W63" s="3">
+        <f t="shared" si="12"/>
+        <v>2.3406080408499208</v>
+      </c>
+      <c r="X63" s="3">
+        <f t="shared" si="13"/>
+        <v>8.5159608171134806</v>
+      </c>
+      <c r="Y63" s="3">
+        <f t="shared" si="14"/>
+        <v>5.0978574056913986E-2</v>
+      </c>
+      <c r="Z63" s="3">
+        <f t="shared" si="15"/>
+        <v>2.4451207178656471E-2</v>
+      </c>
+      <c r="AA63" s="3">
         <f t="shared" si="9"/>
-        <v>2.4656821601966037</v>
-      </c>
-      <c r="X63" s="3">
+        <v>5.2882942652334304</v>
+      </c>
+      <c r="AB63" s="3">
         <f t="shared" si="10"/>
-        <v>8.9710247496481053</v>
-      </c>
-      <c r="Y63" s="3">
-        <f t="shared" si="11"/>
-        <v>5.3702695372588399E-2</v>
-      </c>
-      <c r="Z63" s="3">
-        <f t="shared" si="12"/>
-        <v>1.456282070599527E-2</v>
+        <v>3.3511882838227045</v>
       </c>
       <c r="AD63">
         <v>24.359466650000002</v>
@@ -43481,7 +43881,7 @@
         <v>2041</v>
       </c>
       <c r="B64">
-        <v>10120.275</v>
+        <v>10800</v>
       </c>
       <c r="C64">
         <v>314.29854999999998</v>
@@ -43493,7 +43893,7 @@
         <v>6.84544</v>
       </c>
       <c r="F64">
-        <v>1.856311209</v>
+        <v>3.2833258827952898</v>
       </c>
       <c r="G64">
         <v>710.11599999999999</v>
@@ -43503,7 +43903,7 @@
       </c>
       <c r="I64" s="3">
         <f t="shared" si="5"/>
-        <v>12746.920713208998</v>
+        <v>13428.072727882794</v>
       </c>
       <c r="J64" s="3">
         <f t="shared" si="6"/>
@@ -43512,7 +43912,7 @@
       <c r="K64" s="7"/>
       <c r="L64" s="3">
         <f t="shared" si="7"/>
-        <v>52.149603704379203</v>
+        <v>54.936300854763807</v>
       </c>
       <c r="M64" s="3">
         <v>45.441578999999997</v>
@@ -43534,24 +43934,32 @@
       </c>
       <c r="U64" s="7"/>
       <c r="V64" s="3">
-        <f t="shared" si="8"/>
-        <v>79.393880511964468</v>
+        <f t="shared" si="11"/>
+        <v>80.428518811744894</v>
       </c>
       <c r="W64" s="3">
+        <f t="shared" si="12"/>
+        <v>2.3406080408499208</v>
+      </c>
+      <c r="X64" s="3">
+        <f t="shared" si="13"/>
+        <v>8.5159608171134806</v>
+      </c>
+      <c r="Y64" s="3">
+        <f t="shared" si="14"/>
+        <v>5.0978574056913986E-2</v>
+      </c>
+      <c r="Z64" s="3">
+        <f t="shared" si="15"/>
+        <v>2.4451207178656471E-2</v>
+      </c>
+      <c r="AA64" s="3">
         <f t="shared" si="9"/>
-        <v>2.4656821601966037</v>
-      </c>
-      <c r="X64" s="3">
+        <v>5.2882942652334304</v>
+      </c>
+      <c r="AB64" s="3">
         <f t="shared" si="10"/>
-        <v>8.9710247496481053</v>
-      </c>
-      <c r="Y64" s="3">
-        <f t="shared" si="11"/>
-        <v>5.3702695372588399E-2</v>
-      </c>
-      <c r="Z64" s="3">
-        <f t="shared" si="12"/>
-        <v>1.456282070599527E-2</v>
+        <v>3.3511882838227045</v>
       </c>
       <c r="AD64">
         <v>24.442986730000001</v>
@@ -43577,7 +43985,7 @@
         <v>2042</v>
       </c>
       <c r="B65">
-        <v>10120.275</v>
+        <v>10800</v>
       </c>
       <c r="C65">
         <v>314.29854999999998</v>
@@ -43589,7 +43997,7 @@
         <v>6.84544</v>
       </c>
       <c r="F65">
-        <v>1.856311209</v>
+        <v>3.2833258827952898</v>
       </c>
       <c r="G65">
         <v>710.11599999999999</v>
@@ -43599,7 +44007,7 @@
       </c>
       <c r="I65" s="3">
         <f t="shared" si="5"/>
-        <v>12746.920713208998</v>
+        <v>13428.072727882794</v>
       </c>
       <c r="J65" s="3">
         <f t="shared" si="6"/>
@@ -43608,7 +44016,7 @@
       <c r="K65" s="7"/>
       <c r="L65" s="3">
         <f t="shared" si="7"/>
-        <v>51.978984461294232</v>
+        <v>54.756564300621193</v>
       </c>
       <c r="M65" s="3">
         <v>44.476583300000001</v>
@@ -43630,24 +44038,32 @@
       </c>
       <c r="U65" s="7"/>
       <c r="V65" s="3">
-        <f t="shared" si="8"/>
-        <v>79.393880511964468</v>
+        <f t="shared" si="11"/>
+        <v>80.428518811744894</v>
       </c>
       <c r="W65" s="3">
+        <f t="shared" si="12"/>
+        <v>2.3406080408499208</v>
+      </c>
+      <c r="X65" s="3">
+        <f t="shared" si="13"/>
+        <v>8.5159608171134806</v>
+      </c>
+      <c r="Y65" s="3">
+        <f t="shared" si="14"/>
+        <v>5.0978574056913986E-2</v>
+      </c>
+      <c r="Z65" s="3">
+        <f t="shared" si="15"/>
+        <v>2.4451207178656471E-2</v>
+      </c>
+      <c r="AA65" s="3">
         <f t="shared" si="9"/>
-        <v>2.4656821601966037</v>
-      </c>
-      <c r="X65" s="3">
+        <v>5.2882942652334304</v>
+      </c>
+      <c r="AB65" s="3">
         <f t="shared" si="10"/>
-        <v>8.9710247496481053</v>
-      </c>
-      <c r="Y65" s="3">
-        <f t="shared" si="11"/>
-        <v>5.3702695372588399E-2</v>
-      </c>
-      <c r="Z65" s="3">
-        <f t="shared" si="12"/>
-        <v>1.456282070599527E-2</v>
+        <v>3.3511882838227045</v>
       </c>
       <c r="AD65">
         <v>24.523219999999998</v>
@@ -43673,7 +44089,7 @@
         <v>2043</v>
       </c>
       <c r="B66">
-        <v>10120.275</v>
+        <v>10800</v>
       </c>
       <c r="C66">
         <v>314.29854999999998</v>
@@ -43685,7 +44101,7 @@
         <v>6.84544</v>
       </c>
       <c r="F66">
-        <v>1.856311209</v>
+        <v>3.2833258827952898</v>
       </c>
       <c r="G66">
         <v>710.11599999999999</v>
@@ -43695,7 +44111,7 @@
       </c>
       <c r="I66" s="3">
         <f t="shared" si="5"/>
-        <v>12746.920713208998</v>
+        <v>13428.072727882794</v>
       </c>
       <c r="J66" s="3">
         <f t="shared" si="6"/>
@@ -43704,7 +44120,7 @@
       <c r="K66" s="7"/>
       <c r="L66" s="3">
         <f t="shared" si="7"/>
-        <v>51.815855758326691</v>
+        <v>54.584718555539922</v>
       </c>
       <c r="M66" s="3">
         <v>43.532080209999997</v>
@@ -43726,24 +44142,32 @@
       </c>
       <c r="U66" s="7"/>
       <c r="V66" s="3">
-        <f t="shared" si="8"/>
-        <v>79.393880511964468</v>
+        <f t="shared" si="11"/>
+        <v>80.428518811744894</v>
       </c>
       <c r="W66" s="3">
+        <f t="shared" si="12"/>
+        <v>2.3406080408499208</v>
+      </c>
+      <c r="X66" s="3">
+        <f t="shared" si="13"/>
+        <v>8.5159608171134806</v>
+      </c>
+      <c r="Y66" s="3">
+        <f t="shared" si="14"/>
+        <v>5.0978574056913986E-2</v>
+      </c>
+      <c r="Z66" s="3">
+        <f t="shared" si="15"/>
+        <v>2.4451207178656471E-2</v>
+      </c>
+      <c r="AA66" s="3">
         <f t="shared" si="9"/>
-        <v>2.4656821601966037</v>
-      </c>
-      <c r="X66" s="3">
+        <v>5.2882942652334304</v>
+      </c>
+      <c r="AB66" s="3">
         <f t="shared" si="10"/>
-        <v>8.9710247496481053</v>
-      </c>
-      <c r="Y66" s="3">
-        <f t="shared" si="11"/>
-        <v>5.3702695372588399E-2</v>
-      </c>
-      <c r="Z66" s="3">
-        <f t="shared" si="12"/>
-        <v>1.456282070599527E-2</v>
+        <v>3.3511882838227045</v>
       </c>
       <c r="AD66">
         <v>24.600424960000002</v>
@@ -43769,7 +44193,7 @@
         <v>2044</v>
       </c>
       <c r="B67">
-        <v>10120.275</v>
+        <v>10800</v>
       </c>
       <c r="C67">
         <v>314.29854999999998</v>
@@ -43781,7 +44205,7 @@
         <v>6.84544</v>
       </c>
       <c r="F67">
-        <v>1.856311209</v>
+        <v>3.2833258827952898</v>
       </c>
       <c r="G67">
         <v>710.11599999999999</v>
@@ -43791,7 +44215,7 @@
       </c>
       <c r="I67" s="3">
         <f t="shared" si="5"/>
-        <v>12746.920713208998</v>
+        <v>13428.072727882794</v>
       </c>
       <c r="J67" s="3">
         <f t="shared" si="6"/>
@@ -43800,7 +44224,7 @@
       <c r="K67" s="7"/>
       <c r="L67" s="3">
         <f t="shared" si="7"/>
-        <v>51.659608197521948</v>
+        <v>54.420121657414846</v>
       </c>
       <c r="M67" s="3">
         <v>42.60763455</v>
@@ -43822,24 +44246,32 @@
       </c>
       <c r="U67" s="7"/>
       <c r="V67" s="3">
-        <f t="shared" si="8"/>
-        <v>79.393880511964468</v>
+        <f t="shared" si="11"/>
+        <v>80.428518811744894</v>
       </c>
       <c r="W67" s="3">
+        <f t="shared" si="12"/>
+        <v>2.3406080408499208</v>
+      </c>
+      <c r="X67" s="3">
+        <f t="shared" si="13"/>
+        <v>8.5159608171134806</v>
+      </c>
+      <c r="Y67" s="3">
+        <f t="shared" si="14"/>
+        <v>5.0978574056913986E-2</v>
+      </c>
+      <c r="Z67" s="3">
+        <f t="shared" si="15"/>
+        <v>2.4451207178656471E-2</v>
+      </c>
+      <c r="AA67" s="3">
         <f t="shared" si="9"/>
-        <v>2.4656821601966037</v>
-      </c>
-      <c r="X67" s="3">
+        <v>5.2882942652334304</v>
+      </c>
+      <c r="AB67" s="3">
         <f t="shared" si="10"/>
-        <v>8.9710247496481053</v>
-      </c>
-      <c r="Y67" s="3">
-        <f t="shared" si="11"/>
-        <v>5.3702695372588399E-2</v>
-      </c>
-      <c r="Z67" s="3">
-        <f t="shared" si="12"/>
-        <v>1.456282070599527E-2</v>
+        <v>3.3511882838227045</v>
       </c>
       <c r="AD67">
         <v>24.674830409999998</v>
@@ -43865,7 +44297,7 @@
         <v>2045</v>
       </c>
       <c r="B68">
-        <v>10120.275</v>
+        <v>10800</v>
       </c>
       <c r="C68">
         <v>314.29854999999998</v>
@@ -43877,7 +44309,7 @@
         <v>6.84544</v>
       </c>
       <c r="F68">
-        <v>1.856311209</v>
+        <v>3.2833258827952898</v>
       </c>
       <c r="G68">
         <v>710.11599999999999</v>
@@ -43887,7 +44319,7 @@
       </c>
       <c r="I68" s="3">
         <f t="shared" si="5"/>
-        <v>12746.920713208998</v>
+        <v>13428.072727882794</v>
       </c>
       <c r="J68" s="3">
         <f t="shared" si="6"/>
@@ -43896,7 +44328,7 @@
       <c r="K68" s="7"/>
       <c r="L68" s="3">
         <f t="shared" si="7"/>
-        <v>51.509703013700729</v>
+        <v>54.262206051291081</v>
       </c>
       <c r="M68" s="3">
         <v>41.702820389999999</v>
@@ -43918,24 +44350,32 @@
       </c>
       <c r="U68" s="7"/>
       <c r="V68" s="3">
-        <f t="shared" si="8"/>
-        <v>79.393880511964468</v>
+        <f t="shared" si="11"/>
+        <v>80.428518811744894</v>
       </c>
       <c r="W68" s="3">
+        <f t="shared" si="12"/>
+        <v>2.3406080408499208</v>
+      </c>
+      <c r="X68" s="3">
+        <f t="shared" si="13"/>
+        <v>8.5159608171134806</v>
+      </c>
+      <c r="Y68" s="3">
+        <f t="shared" si="14"/>
+        <v>5.0978574056913986E-2</v>
+      </c>
+      <c r="Z68" s="3">
+        <f t="shared" si="15"/>
+        <v>2.4451207178656471E-2</v>
+      </c>
+      <c r="AA68" s="3">
         <f t="shared" si="9"/>
-        <v>2.4656821601966037</v>
-      </c>
-      <c r="X68" s="3">
+        <v>5.2882942652334304</v>
+      </c>
+      <c r="AB68" s="3">
         <f t="shared" si="10"/>
-        <v>8.9710247496481053</v>
-      </c>
-      <c r="Y68" s="3">
-        <f t="shared" si="11"/>
-        <v>5.3702695372588399E-2</v>
-      </c>
-      <c r="Z68" s="3">
-        <f t="shared" si="12"/>
-        <v>1.456282070599527E-2</v>
+        <v>3.3511882838227045</v>
       </c>
       <c r="AD68">
         <v>24.746639890000001</v>
@@ -43964,7 +44404,7 @@
         <v>2046</v>
       </c>
       <c r="B69">
-        <v>10120.275</v>
+        <v>10800</v>
       </c>
       <c r="C69">
         <v>314.29854999999998</v>
@@ -43976,7 +44416,7 @@
         <v>6.84544</v>
       </c>
       <c r="F69">
-        <v>1.856311209</v>
+        <v>3.2833258827952898</v>
       </c>
       <c r="G69">
         <v>710.11599999999999</v>
@@ -43986,7 +44426,7 @@
       </c>
       <c r="I69" s="3">
         <f t="shared" si="5"/>
-        <v>12746.920713208998</v>
+        <v>13428.072727882794</v>
       </c>
       <c r="J69" s="3">
         <f t="shared" si="6"/>
@@ -43995,7 +44435,7 @@
       <c r="K69" s="7"/>
       <c r="L69" s="3">
         <f t="shared" si="7"/>
-        <v>51.365661718044031</v>
+        <v>54.110467679537329</v>
       </c>
       <c r="M69" s="3">
         <v>40.817220829999997</v>
@@ -44017,24 +44457,32 @@
       </c>
       <c r="U69" s="7"/>
       <c r="V69" s="3">
-        <f t="shared" si="8"/>
-        <v>79.393880511964468</v>
+        <f t="shared" si="11"/>
+        <v>80.428518811744894</v>
       </c>
       <c r="W69" s="3">
+        <f t="shared" si="12"/>
+        <v>2.3406080408499208</v>
+      </c>
+      <c r="X69" s="3">
+        <f t="shared" si="13"/>
+        <v>8.5159608171134806</v>
+      </c>
+      <c r="Y69" s="3">
+        <f t="shared" si="14"/>
+        <v>5.0978574056913986E-2</v>
+      </c>
+      <c r="Z69" s="3">
+        <f t="shared" si="15"/>
+        <v>2.4451207178656471E-2</v>
+      </c>
+      <c r="AA69" s="3">
         <f t="shared" si="9"/>
-        <v>2.4656821601966037</v>
-      </c>
-      <c r="X69" s="3">
+        <v>5.2882942652334304</v>
+      </c>
+      <c r="AB69" s="3">
         <f t="shared" si="10"/>
-        <v>8.9710247496481053</v>
-      </c>
-      <c r="Y69" s="3">
-        <f t="shared" si="11"/>
-        <v>5.3702695372588399E-2</v>
-      </c>
-      <c r="Z69" s="3">
-        <f t="shared" si="12"/>
-        <v>1.456282070599527E-2</v>
+        <v>3.3511882838227045</v>
       </c>
       <c r="AD69">
         <v>24.816035240000001</v>
@@ -44060,7 +44508,7 @@
         <v>2047</v>
       </c>
       <c r="B70">
-        <v>10120.275</v>
+        <v>10800</v>
       </c>
       <c r="C70">
         <v>314.29854999999998</v>
@@ -44072,7 +44520,7 @@
         <v>6.84544</v>
       </c>
       <c r="F70">
-        <v>1.856311209</v>
+        <v>3.2833258827952898</v>
       </c>
       <c r="G70">
         <v>710.11599999999999</v>
@@ -44082,7 +44530,7 @@
       </c>
       <c r="I70" s="3">
         <f t="shared" si="5"/>
-        <v>12746.920713208998</v>
+        <v>13428.072727882794</v>
       </c>
       <c r="J70" s="3">
         <f t="shared" si="6"/>
@@ -44091,7 +44539,7 @@
       <c r="K70" s="7"/>
       <c r="L70" s="3">
         <f t="shared" si="7"/>
-        <v>51.227057425424789</v>
+        <v>53.964456845739697</v>
       </c>
       <c r="M70" s="3">
         <v>39.950427830000002</v>
@@ -44113,24 +44561,32 @@
       </c>
       <c r="U70" s="7"/>
       <c r="V70" s="3">
-        <f t="shared" si="8"/>
-        <v>79.393880511964468</v>
+        <f t="shared" si="11"/>
+        <v>80.428518811744894</v>
       </c>
       <c r="W70" s="3">
+        <f t="shared" si="12"/>
+        <v>2.3406080408499208</v>
+      </c>
+      <c r="X70" s="3">
+        <f t="shared" si="13"/>
+        <v>8.5159608171134806</v>
+      </c>
+      <c r="Y70" s="3">
+        <f t="shared" si="14"/>
+        <v>5.0978574056913986E-2</v>
+      </c>
+      <c r="Z70" s="3">
+        <f t="shared" si="15"/>
+        <v>2.4451207178656471E-2</v>
+      </c>
+      <c r="AA70" s="3">
         <f t="shared" si="9"/>
-        <v>2.4656821601966037</v>
-      </c>
-      <c r="X70" s="3">
+        <v>5.2882942652334304</v>
+      </c>
+      <c r="AB70" s="3">
         <f t="shared" si="10"/>
-        <v>8.9710247496481053</v>
-      </c>
-      <c r="Y70" s="3">
-        <f t="shared" si="11"/>
-        <v>5.3702695372588399E-2</v>
-      </c>
-      <c r="Z70" s="3">
-        <f t="shared" si="12"/>
-        <v>1.456282070599527E-2</v>
+        <v>3.3511882838227045</v>
       </c>
       <c r="AD70">
         <v>24.88317962</v>
@@ -44156,7 +44612,7 @@
         <v>2048</v>
       </c>
       <c r="B71">
-        <v>10120.275</v>
+        <v>10800</v>
       </c>
       <c r="C71">
         <v>314.29854999999998</v>
@@ -44168,7 +44624,7 @@
         <v>6.84544</v>
       </c>
       <c r="F71">
-        <v>1.856311209</v>
+        <v>3.2833258827952898</v>
       </c>
       <c r="G71">
         <v>710.11599999999999</v>
@@ -44178,7 +44634,7 @@
       </c>
       <c r="I71" s="3">
         <f t="shared" si="5"/>
-        <v>12746.920713208998</v>
+        <v>13428.072727882794</v>
       </c>
       <c r="J71" s="3">
         <f t="shared" si="6"/>
@@ -44187,7 +44643,7 @@
       <c r="K71" s="7"/>
       <c r="L71" s="3">
         <f t="shared" si="7"/>
-        <v>51.093507705558338</v>
+        <v>53.823770683842042</v>
       </c>
       <c r="M71" s="3">
         <v>39.102042009999998</v>
@@ -44209,24 +44665,32 @@
       </c>
       <c r="U71" s="7"/>
       <c r="V71" s="3">
-        <f t="shared" si="8"/>
-        <v>79.393880511964468</v>
+        <f t="shared" si="11"/>
+        <v>80.428518811744894</v>
       </c>
       <c r="W71" s="3">
+        <f t="shared" si="12"/>
+        <v>2.3406080408499208</v>
+      </c>
+      <c r="X71" s="3">
+        <f t="shared" si="13"/>
+        <v>8.5159608171134806</v>
+      </c>
+      <c r="Y71" s="3">
+        <f t="shared" si="14"/>
+        <v>5.0978574056913986E-2</v>
+      </c>
+      <c r="Z71" s="3">
+        <f t="shared" si="15"/>
+        <v>2.4451207178656471E-2</v>
+      </c>
+      <c r="AA71" s="3">
         <f t="shared" si="9"/>
-        <v>2.4656821601966037</v>
-      </c>
-      <c r="X71" s="3">
+        <v>5.2882942652334304</v>
+      </c>
+      <c r="AB71" s="3">
         <f t="shared" si="10"/>
-        <v>8.9710247496481053</v>
-      </c>
-      <c r="Y71" s="3">
-        <f t="shared" si="11"/>
-        <v>5.3702695372588399E-2</v>
-      </c>
-      <c r="Z71" s="3">
-        <f t="shared" si="12"/>
-        <v>1.456282070599527E-2</v>
+        <v>3.3511882838227045</v>
       </c>
       <c r="AD71">
         <v>24.94822001</v>
@@ -44252,7 +44716,7 @@
         <v>2049</v>
       </c>
       <c r="B72">
-        <v>10120.275</v>
+        <v>10800</v>
       </c>
       <c r="C72">
         <v>314.29854999999998</v>
@@ -44264,7 +44728,7 @@
         <v>6.84544</v>
       </c>
       <c r="F72">
-        <v>1.856311209</v>
+        <v>3.2833258827952898</v>
       </c>
       <c r="G72">
         <v>710.11599999999999</v>
@@ -44274,7 +44738,7 @@
       </c>
       <c r="I72" s="3">
         <f t="shared" si="5"/>
-        <v>12746.920713208998</v>
+        <v>13428.072727882794</v>
       </c>
       <c r="J72" s="3">
         <f t="shared" si="6"/>
@@ -44283,7 +44747,7 @@
       <c r="K72" s="7"/>
       <c r="L72" s="3">
         <f t="shared" si="7"/>
-        <v>50.964668696620926</v>
+        <v>53.688046957216272</v>
       </c>
       <c r="M72" s="3">
         <v>38.271672479999999</v>
@@ -44305,24 +44769,32 @@
       </c>
       <c r="U72" s="7"/>
       <c r="V72" s="3">
-        <f t="shared" si="8"/>
-        <v>79.393880511964468</v>
+        <f t="shared" si="11"/>
+        <v>80.428518811744894</v>
       </c>
       <c r="W72" s="3">
+        <f t="shared" si="12"/>
+        <v>2.3406080408499208</v>
+      </c>
+      <c r="X72" s="3">
+        <f t="shared" si="13"/>
+        <v>8.5159608171134806</v>
+      </c>
+      <c r="Y72" s="3">
+        <f t="shared" si="14"/>
+        <v>5.0978574056913986E-2</v>
+      </c>
+      <c r="Z72" s="3">
+        <f t="shared" si="15"/>
+        <v>2.4451207178656471E-2</v>
+      </c>
+      <c r="AA72" s="3">
         <f t="shared" si="9"/>
-        <v>2.4656821601966037</v>
-      </c>
-      <c r="X72" s="3">
+        <v>5.2882942652334304</v>
+      </c>
+      <c r="AB72" s="3">
         <f t="shared" si="10"/>
-        <v>8.9710247496481053</v>
-      </c>
-      <c r="Y72" s="3">
-        <f t="shared" si="11"/>
-        <v>5.3702695372588399E-2</v>
-      </c>
-      <c r="Z72" s="3">
-        <f t="shared" si="12"/>
-        <v>1.456282070599527E-2</v>
+        <v>3.3511882838227045</v>
       </c>
       <c r="AD72">
         <v>25.011289269999999</v>
@@ -44348,7 +44820,7 @@
         <v>2050</v>
       </c>
       <c r="B73">
-        <v>10120.275</v>
+        <v>10800</v>
       </c>
       <c r="C73">
         <v>314.29854999999998</v>
@@ -44360,7 +44832,7 @@
         <v>6.84544</v>
       </c>
       <c r="F73">
-        <v>1.856311209</v>
+        <v>3.2833258827952898</v>
       </c>
       <c r="G73">
         <v>710.11599999999999</v>
@@ -44370,7 +44842,7 @@
       </c>
       <c r="I73" s="3">
         <f t="shared" si="5"/>
-        <v>12746.920713208998</v>
+        <v>13428.072727882794</v>
       </c>
       <c r="J73" s="3">
         <f t="shared" si="6"/>
@@ -44379,7 +44851,7 @@
       <c r="K73" s="7"/>
       <c r="L73" s="3">
         <f t="shared" si="7"/>
-        <v>50.840230099698061</v>
+        <v>53.556958785631082</v>
       </c>
       <c r="M73" s="3">
         <v>37.458936649999998</v>
@@ -44403,24 +44875,32 @@
       </c>
       <c r="U73" s="7"/>
       <c r="V73" s="3">
-        <f t="shared" si="8"/>
-        <v>79.393880511964468</v>
+        <f t="shared" si="11"/>
+        <v>80.428518811744894</v>
       </c>
       <c r="W73" s="3">
+        <f t="shared" si="12"/>
+        <v>2.3406080408499208</v>
+      </c>
+      <c r="X73" s="3">
+        <f t="shared" si="13"/>
+        <v>8.5159608171134806</v>
+      </c>
+      <c r="Y73" s="3">
+        <f t="shared" si="14"/>
+        <v>5.0978574056913986E-2</v>
+      </c>
+      <c r="Z73" s="3">
+        <f t="shared" si="15"/>
+        <v>2.4451207178656471E-2</v>
+      </c>
+      <c r="AA73" s="3">
         <f t="shared" si="9"/>
-        <v>2.4656821601966037</v>
-      </c>
-      <c r="X73" s="3">
+        <v>5.2882942652334304</v>
+      </c>
+      <c r="AB73" s="3">
         <f t="shared" si="10"/>
-        <v>8.9710247496481053</v>
-      </c>
-      <c r="Y73" s="3">
-        <f t="shared" si="11"/>
-        <v>5.3702695372588399E-2</v>
-      </c>
-      <c r="Z73" s="3">
-        <f t="shared" si="12"/>
-        <v>1.456282070599527E-2</v>
+        <v>3.3511882838227045</v>
       </c>
       <c r="AD73">
         <v>25.072507909999999</v>
@@ -44461,6 +44941,91 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3082728B-DFD1-446B-B723-835D3EDCB1B8}">
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>2000</v>
+      </c>
+      <c r="B2" s="9">
+        <v>63.351635578919343</v>
+      </c>
+      <c r="C2" s="9">
+        <v>6.0599233268856629</v>
+      </c>
+      <c r="D2" s="9">
+        <v>19.274436295221182</v>
+      </c>
+      <c r="E2" s="9">
+        <v>4.2572299109033797E-2</v>
+      </c>
+      <c r="F2" s="9">
+        <v>0.35911327139593108</v>
+      </c>
+      <c r="G2" s="9">
+        <v>6.6994354624707197</v>
+      </c>
+      <c r="H2" s="9">
+        <v>4.2128837659981357</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2025</v>
+      </c>
+      <c r="B3" s="9">
+        <v>78.693850826255158</v>
+      </c>
+      <c r="C3" s="9">
+        <v>2.5548959209616982</v>
+      </c>
+      <c r="D3" s="9">
+        <v>9.129688688330905</v>
+      </c>
+      <c r="E3" s="9">
+        <v>6.2314654674512852E-2</v>
+      </c>
+      <c r="F3" s="9">
+        <v>2.4965100630913912E-2</v>
+      </c>
+      <c r="G3" s="9">
+        <v>5.8845562319040843</v>
+      </c>
+      <c r="H3" s="9">
+        <v>3.6497285772427279</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72633EE9-48B6-45B9-AA20-5B238FD67D43}">
   <dimension ref="A1:H57"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -45945,1499 +46510,6 @@
       </c>
       <c r="H57">
         <v>99</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2886825C-AE4A-4EAF-970C-700F7CC3D78A}">
-  <dimension ref="A1:H57"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2">
-        <v>1995</v>
-      </c>
-      <c r="B2">
-        <v>95</v>
-      </c>
-      <c r="C2">
-        <v>50</v>
-      </c>
-      <c r="D2">
-        <v>99</v>
-      </c>
-      <c r="E2">
-        <v>90</v>
-      </c>
-      <c r="F2">
-        <v>80</v>
-      </c>
-      <c r="G2">
-        <v>95.3</v>
-      </c>
-      <c r="H2">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3">
-        <v>1996</v>
-      </c>
-      <c r="B3">
-        <v>95</v>
-      </c>
-      <c r="C3">
-        <v>50</v>
-      </c>
-      <c r="D3">
-        <v>99</v>
-      </c>
-      <c r="E3">
-        <v>90</v>
-      </c>
-      <c r="F3">
-        <v>80</v>
-      </c>
-      <c r="G3">
-        <v>95.37</v>
-      </c>
-      <c r="H3">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4">
-        <v>1997</v>
-      </c>
-      <c r="B4">
-        <v>95</v>
-      </c>
-      <c r="C4">
-        <v>50</v>
-      </c>
-      <c r="D4">
-        <v>99</v>
-      </c>
-      <c r="E4">
-        <v>90</v>
-      </c>
-      <c r="F4">
-        <v>80</v>
-      </c>
-      <c r="G4">
-        <v>95.44</v>
-      </c>
-      <c r="H4">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5">
-        <v>1998</v>
-      </c>
-      <c r="B5">
-        <v>95</v>
-      </c>
-      <c r="C5">
-        <v>50</v>
-      </c>
-      <c r="D5">
-        <v>99</v>
-      </c>
-      <c r="E5">
-        <v>90</v>
-      </c>
-      <c r="F5">
-        <v>80</v>
-      </c>
-      <c r="G5">
-        <v>95.51</v>
-      </c>
-      <c r="H5">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6">
-        <v>1999</v>
-      </c>
-      <c r="B6">
-        <v>95</v>
-      </c>
-      <c r="C6">
-        <v>50</v>
-      </c>
-      <c r="D6">
-        <v>99</v>
-      </c>
-      <c r="E6">
-        <v>90</v>
-      </c>
-      <c r="F6">
-        <v>80</v>
-      </c>
-      <c r="G6">
-        <v>95.58</v>
-      </c>
-      <c r="H6">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A7">
-        <v>2000</v>
-      </c>
-      <c r="B7">
-        <v>95</v>
-      </c>
-      <c r="C7">
-        <v>50</v>
-      </c>
-      <c r="D7">
-        <v>99</v>
-      </c>
-      <c r="E7">
-        <v>90</v>
-      </c>
-      <c r="F7">
-        <v>80</v>
-      </c>
-      <c r="G7">
-        <v>95.65</v>
-      </c>
-      <c r="H7">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A8">
-        <v>2001</v>
-      </c>
-      <c r="B8">
-        <v>95</v>
-      </c>
-      <c r="C8">
-        <v>50</v>
-      </c>
-      <c r="D8">
-        <v>99</v>
-      </c>
-      <c r="E8">
-        <v>90</v>
-      </c>
-      <c r="F8">
-        <v>80</v>
-      </c>
-      <c r="G8">
-        <v>95.72</v>
-      </c>
-      <c r="H8">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A9">
-        <v>2002</v>
-      </c>
-      <c r="B9">
-        <v>95</v>
-      </c>
-      <c r="C9">
-        <v>50</v>
-      </c>
-      <c r="D9">
-        <v>99</v>
-      </c>
-      <c r="E9">
-        <v>90</v>
-      </c>
-      <c r="F9">
-        <v>80</v>
-      </c>
-      <c r="G9">
-        <v>95.79</v>
-      </c>
-      <c r="H9">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A10">
-        <v>2003</v>
-      </c>
-      <c r="B10">
-        <v>95</v>
-      </c>
-      <c r="C10">
-        <v>50</v>
-      </c>
-      <c r="D10">
-        <v>99</v>
-      </c>
-      <c r="E10">
-        <v>90</v>
-      </c>
-      <c r="F10">
-        <v>80</v>
-      </c>
-      <c r="G10">
-        <v>95.86</v>
-      </c>
-      <c r="H10">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A11">
-        <v>2004</v>
-      </c>
-      <c r="B11">
-        <v>95</v>
-      </c>
-      <c r="C11">
-        <v>49.365658340000003</v>
-      </c>
-      <c r="D11">
-        <v>99</v>
-      </c>
-      <c r="E11">
-        <v>90</v>
-      </c>
-      <c r="F11">
-        <v>80</v>
-      </c>
-      <c r="G11">
-        <v>95.93</v>
-      </c>
-      <c r="H11">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A12">
-        <v>2005</v>
-      </c>
-      <c r="B12">
-        <v>95</v>
-      </c>
-      <c r="C12">
-        <v>41.588057310000003</v>
-      </c>
-      <c r="D12">
-        <v>99</v>
-      </c>
-      <c r="E12">
-        <v>90</v>
-      </c>
-      <c r="F12">
-        <v>80</v>
-      </c>
-      <c r="G12">
-        <v>96</v>
-      </c>
-      <c r="H12">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A13">
-        <v>2006</v>
-      </c>
-      <c r="B13">
-        <v>95</v>
-      </c>
-      <c r="C13">
-        <v>33.638416139999997</v>
-      </c>
-      <c r="D13">
-        <v>99</v>
-      </c>
-      <c r="E13">
-        <v>90</v>
-      </c>
-      <c r="F13">
-        <v>80</v>
-      </c>
-      <c r="G13">
-        <v>96.5</v>
-      </c>
-      <c r="H13">
-        <v>93.7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A14">
-        <v>2007</v>
-      </c>
-      <c r="B14">
-        <v>95</v>
-      </c>
-      <c r="C14">
-        <v>32.313886099999998</v>
-      </c>
-      <c r="D14">
-        <v>99</v>
-      </c>
-      <c r="E14">
-        <v>90</v>
-      </c>
-      <c r="F14">
-        <v>80</v>
-      </c>
-      <c r="G14">
-        <v>97</v>
-      </c>
-      <c r="H14">
-        <v>94.283333330000005</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A15">
-        <v>2008</v>
-      </c>
-      <c r="B15">
-        <v>95</v>
-      </c>
-      <c r="C15">
-        <v>30.95939478</v>
-      </c>
-      <c r="D15">
-        <v>99</v>
-      </c>
-      <c r="E15">
-        <v>90</v>
-      </c>
-      <c r="F15">
-        <v>80</v>
-      </c>
-      <c r="G15">
-        <v>97.5</v>
-      </c>
-      <c r="H15">
-        <v>94.866666670000001</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A16">
-        <v>2009</v>
-      </c>
-      <c r="B16">
-        <v>95</v>
-      </c>
-      <c r="C16">
-        <v>31.313555950000001</v>
-      </c>
-      <c r="D16">
-        <v>99</v>
-      </c>
-      <c r="E16">
-        <v>90</v>
-      </c>
-      <c r="F16">
-        <v>80</v>
-      </c>
-      <c r="G16">
-        <v>98</v>
-      </c>
-      <c r="H16">
-        <v>95.45</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A17">
-        <v>2010</v>
-      </c>
-      <c r="B17">
-        <v>95</v>
-      </c>
-      <c r="C17">
-        <v>49.33536239</v>
-      </c>
-      <c r="D17">
-        <v>99</v>
-      </c>
-      <c r="E17">
-        <v>90</v>
-      </c>
-      <c r="F17">
-        <v>80</v>
-      </c>
-      <c r="G17">
-        <v>98.5</v>
-      </c>
-      <c r="H17">
-        <v>96.033333330000005</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A18">
-        <v>2011</v>
-      </c>
-      <c r="B18">
-        <v>95</v>
-      </c>
-      <c r="C18">
-        <v>49.661818310000001</v>
-      </c>
-      <c r="D18">
-        <v>99</v>
-      </c>
-      <c r="E18">
-        <v>90</v>
-      </c>
-      <c r="F18">
-        <v>80</v>
-      </c>
-      <c r="G18">
-        <v>99</v>
-      </c>
-      <c r="H18">
-        <v>96.5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A19">
-        <v>2012</v>
-      </c>
-      <c r="B19">
-        <v>95</v>
-      </c>
-      <c r="C19">
-        <v>48.63711241</v>
-      </c>
-      <c r="D19">
-        <v>99</v>
-      </c>
-      <c r="E19">
-        <v>90</v>
-      </c>
-      <c r="F19">
-        <v>80</v>
-      </c>
-      <c r="G19">
-        <v>99</v>
-      </c>
-      <c r="H19">
-        <v>96.5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A20">
-        <v>2013</v>
-      </c>
-      <c r="B20">
-        <v>95</v>
-      </c>
-      <c r="C20">
-        <v>49.920500959999998</v>
-      </c>
-      <c r="D20">
-        <v>99</v>
-      </c>
-      <c r="E20">
-        <v>90</v>
-      </c>
-      <c r="F20">
-        <v>80</v>
-      </c>
-      <c r="G20">
-        <v>99</v>
-      </c>
-      <c r="H20">
-        <v>96.5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A21">
-        <v>2014</v>
-      </c>
-      <c r="B21">
-        <v>95.2</v>
-      </c>
-      <c r="C21">
-        <v>50.133176429999999</v>
-      </c>
-      <c r="D21">
-        <v>99</v>
-      </c>
-      <c r="E21">
-        <v>90</v>
-      </c>
-      <c r="F21">
-        <v>80</v>
-      </c>
-      <c r="G21">
-        <v>99</v>
-      </c>
-      <c r="H21">
-        <v>96.5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A22">
-        <v>2015</v>
-      </c>
-      <c r="B22">
-        <v>95.5</v>
-      </c>
-      <c r="C22">
-        <v>50.540356459999998</v>
-      </c>
-      <c r="D22">
-        <v>99</v>
-      </c>
-      <c r="E22">
-        <v>90</v>
-      </c>
-      <c r="F22">
-        <v>80</v>
-      </c>
-      <c r="G22">
-        <v>99</v>
-      </c>
-      <c r="H22">
-        <v>96.5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A23">
-        <v>2016</v>
-      </c>
-      <c r="B23">
-        <v>95.7</v>
-      </c>
-      <c r="C23">
-        <v>53.417000399999999</v>
-      </c>
-      <c r="D23">
-        <v>99</v>
-      </c>
-      <c r="E23">
-        <v>90</v>
-      </c>
-      <c r="F23">
-        <v>80</v>
-      </c>
-      <c r="G23">
-        <v>99</v>
-      </c>
-      <c r="H23">
-        <v>96.5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A24">
-        <v>2017</v>
-      </c>
-      <c r="B24">
-        <v>95.9</v>
-      </c>
-      <c r="C24">
-        <v>59.32333715</v>
-      </c>
-      <c r="D24">
-        <v>99</v>
-      </c>
-      <c r="E24">
-        <v>90</v>
-      </c>
-      <c r="F24">
-        <v>80</v>
-      </c>
-      <c r="G24">
-        <v>99</v>
-      </c>
-      <c r="H24">
-        <v>96.5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A25">
-        <v>2018</v>
-      </c>
-      <c r="B25">
-        <v>96.2</v>
-      </c>
-      <c r="C25">
-        <v>63.600552669999999</v>
-      </c>
-      <c r="D25">
-        <v>99</v>
-      </c>
-      <c r="E25">
-        <v>90</v>
-      </c>
-      <c r="F25">
-        <v>80</v>
-      </c>
-      <c r="G25">
-        <v>99</v>
-      </c>
-      <c r="H25">
-        <v>96.5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A26">
-        <v>2019</v>
-      </c>
-      <c r="B26">
-        <v>96.4</v>
-      </c>
-      <c r="C26">
-        <v>65.063940110000004</v>
-      </c>
-      <c r="D26">
-        <v>99</v>
-      </c>
-      <c r="E26">
-        <v>90</v>
-      </c>
-      <c r="F26">
-        <v>80</v>
-      </c>
-      <c r="G26">
-        <v>99</v>
-      </c>
-      <c r="H26">
-        <v>96.5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A27">
-        <v>2020</v>
-      </c>
-      <c r="B27">
-        <v>96.6</v>
-      </c>
-      <c r="C27">
-        <v>66.726759759999993</v>
-      </c>
-      <c r="D27">
-        <v>99</v>
-      </c>
-      <c r="E27">
-        <v>90</v>
-      </c>
-      <c r="F27">
-        <v>80</v>
-      </c>
-      <c r="G27">
-        <v>99</v>
-      </c>
-      <c r="H27">
-        <v>96.5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A28">
-        <v>2021</v>
-      </c>
-      <c r="B28">
-        <v>96.9</v>
-      </c>
-      <c r="C28">
-        <v>66.180844960000002</v>
-      </c>
-      <c r="D28">
-        <v>99</v>
-      </c>
-      <c r="E28">
-        <v>90</v>
-      </c>
-      <c r="F28">
-        <v>80</v>
-      </c>
-      <c r="G28">
-        <v>99</v>
-      </c>
-      <c r="H28">
-        <v>96.5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A29">
-        <v>2022</v>
-      </c>
-      <c r="B29">
-        <v>97.1</v>
-      </c>
-      <c r="C29">
-        <v>65.587672920000003</v>
-      </c>
-      <c r="D29">
-        <v>99</v>
-      </c>
-      <c r="E29">
-        <v>90</v>
-      </c>
-      <c r="F29">
-        <v>80</v>
-      </c>
-      <c r="G29">
-        <v>99</v>
-      </c>
-      <c r="H29">
-        <v>96.5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A30">
-        <v>2023</v>
-      </c>
-      <c r="B30">
-        <v>97.4</v>
-      </c>
-      <c r="C30">
-        <v>66.98371616</v>
-      </c>
-      <c r="D30">
-        <v>99</v>
-      </c>
-      <c r="E30">
-        <v>90</v>
-      </c>
-      <c r="F30">
-        <v>80</v>
-      </c>
-      <c r="G30">
-        <v>99</v>
-      </c>
-      <c r="H30">
-        <v>96.5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A31">
-        <v>2024</v>
-      </c>
-      <c r="B31">
-        <v>97.6</v>
-      </c>
-      <c r="C31">
-        <v>68.784939679999994</v>
-      </c>
-      <c r="D31">
-        <v>99</v>
-      </c>
-      <c r="E31">
-        <v>90</v>
-      </c>
-      <c r="F31">
-        <v>80</v>
-      </c>
-      <c r="G31">
-        <v>99</v>
-      </c>
-      <c r="H31">
-        <v>96.5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A32">
-        <v>2025</v>
-      </c>
-      <c r="B32">
-        <v>97.8</v>
-      </c>
-      <c r="C32">
-        <v>69.379740209999994</v>
-      </c>
-      <c r="D32">
-        <v>99</v>
-      </c>
-      <c r="E32">
-        <v>90</v>
-      </c>
-      <c r="F32">
-        <v>80</v>
-      </c>
-      <c r="G32">
-        <v>99</v>
-      </c>
-      <c r="H32">
-        <v>96.5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A33">
-        <v>2026</v>
-      </c>
-      <c r="B33">
-        <v>98.1</v>
-      </c>
-      <c r="C33">
-        <v>69.848360650000004</v>
-      </c>
-      <c r="D33">
-        <v>99</v>
-      </c>
-      <c r="E33">
-        <v>90</v>
-      </c>
-      <c r="F33">
-        <v>80</v>
-      </c>
-      <c r="G33">
-        <v>99</v>
-      </c>
-      <c r="H33">
-        <v>96.5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A34">
-        <v>2027</v>
-      </c>
-      <c r="B34">
-        <v>98.3</v>
-      </c>
-      <c r="C34">
-        <v>70.190564620000004</v>
-      </c>
-      <c r="D34">
-        <v>99</v>
-      </c>
-      <c r="E34">
-        <v>90</v>
-      </c>
-      <c r="F34">
-        <v>80</v>
-      </c>
-      <c r="G34">
-        <v>99</v>
-      </c>
-      <c r="H34">
-        <v>96.5</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A35">
-        <v>2028</v>
-      </c>
-      <c r="B35">
-        <v>98.5</v>
-      </c>
-      <c r="C35">
-        <v>70.655697110000006</v>
-      </c>
-      <c r="D35">
-        <v>99</v>
-      </c>
-      <c r="E35">
-        <v>90</v>
-      </c>
-      <c r="F35">
-        <v>80</v>
-      </c>
-      <c r="G35">
-        <v>99</v>
-      </c>
-      <c r="H35">
-        <v>96.5</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A36">
-        <v>2029</v>
-      </c>
-      <c r="B36">
-        <v>98.8</v>
-      </c>
-      <c r="C36">
-        <v>71.125574380000003</v>
-      </c>
-      <c r="D36">
-        <v>99</v>
-      </c>
-      <c r="E36">
-        <v>90</v>
-      </c>
-      <c r="F36">
-        <v>80</v>
-      </c>
-      <c r="G36">
-        <v>99</v>
-      </c>
-      <c r="H36">
-        <v>96.5</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A37">
-        <v>2030</v>
-      </c>
-      <c r="B37">
-        <v>99</v>
-      </c>
-      <c r="C37">
-        <v>71.600236780000003</v>
-      </c>
-      <c r="D37">
-        <v>99</v>
-      </c>
-      <c r="E37">
-        <v>90</v>
-      </c>
-      <c r="F37">
-        <v>80</v>
-      </c>
-      <c r="G37">
-        <v>99</v>
-      </c>
-      <c r="H37">
-        <v>96.5</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A38">
-        <v>2031</v>
-      </c>
-      <c r="B38">
-        <v>99</v>
-      </c>
-      <c r="C38">
-        <v>71.600236780000003</v>
-      </c>
-      <c r="D38">
-        <v>99</v>
-      </c>
-      <c r="E38">
-        <v>90</v>
-      </c>
-      <c r="F38">
-        <v>80</v>
-      </c>
-      <c r="G38">
-        <v>99</v>
-      </c>
-      <c r="H38">
-        <v>96.5</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A39">
-        <v>2032</v>
-      </c>
-      <c r="B39">
-        <v>99</v>
-      </c>
-      <c r="C39">
-        <v>71.600236780000003</v>
-      </c>
-      <c r="D39">
-        <v>99</v>
-      </c>
-      <c r="E39">
-        <v>90</v>
-      </c>
-      <c r="F39">
-        <v>80</v>
-      </c>
-      <c r="G39">
-        <v>99</v>
-      </c>
-      <c r="H39">
-        <v>96.5</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A40">
-        <v>2033</v>
-      </c>
-      <c r="B40">
-        <v>99</v>
-      </c>
-      <c r="C40">
-        <v>71.600236780000003</v>
-      </c>
-      <c r="D40">
-        <v>99</v>
-      </c>
-      <c r="E40">
-        <v>90</v>
-      </c>
-      <c r="F40">
-        <v>80</v>
-      </c>
-      <c r="G40">
-        <v>99</v>
-      </c>
-      <c r="H40">
-        <v>96.5</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A41">
-        <v>2034</v>
-      </c>
-      <c r="B41">
-        <v>99</v>
-      </c>
-      <c r="C41">
-        <v>71.600236780000003</v>
-      </c>
-      <c r="D41">
-        <v>99</v>
-      </c>
-      <c r="E41">
-        <v>90</v>
-      </c>
-      <c r="F41">
-        <v>80</v>
-      </c>
-      <c r="G41">
-        <v>99</v>
-      </c>
-      <c r="H41">
-        <v>96.5</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A42">
-        <v>2035</v>
-      </c>
-      <c r="B42">
-        <v>99</v>
-      </c>
-      <c r="C42">
-        <v>71.600236780000003</v>
-      </c>
-      <c r="D42">
-        <v>99</v>
-      </c>
-      <c r="E42">
-        <v>90</v>
-      </c>
-      <c r="F42">
-        <v>80</v>
-      </c>
-      <c r="G42">
-        <v>99</v>
-      </c>
-      <c r="H42">
-        <v>96.5</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A43">
-        <v>2036</v>
-      </c>
-      <c r="B43">
-        <v>99</v>
-      </c>
-      <c r="C43">
-        <v>71.600236780000003</v>
-      </c>
-      <c r="D43">
-        <v>99</v>
-      </c>
-      <c r="E43">
-        <v>90</v>
-      </c>
-      <c r="F43">
-        <v>80</v>
-      </c>
-      <c r="G43">
-        <v>99</v>
-      </c>
-      <c r="H43">
-        <v>96.5</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A44">
-        <v>2037</v>
-      </c>
-      <c r="B44">
-        <v>99</v>
-      </c>
-      <c r="C44">
-        <v>71.600236780000003</v>
-      </c>
-      <c r="D44">
-        <v>99</v>
-      </c>
-      <c r="E44">
-        <v>90</v>
-      </c>
-      <c r="F44">
-        <v>80</v>
-      </c>
-      <c r="G44">
-        <v>99</v>
-      </c>
-      <c r="H44">
-        <v>96.5</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A45">
-        <v>2038</v>
-      </c>
-      <c r="B45">
-        <v>99</v>
-      </c>
-      <c r="C45">
-        <v>71.600236780000003</v>
-      </c>
-      <c r="D45">
-        <v>99</v>
-      </c>
-      <c r="E45">
-        <v>90</v>
-      </c>
-      <c r="F45">
-        <v>80</v>
-      </c>
-      <c r="G45">
-        <v>99</v>
-      </c>
-      <c r="H45">
-        <v>96.5</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A46">
-        <v>2039</v>
-      </c>
-      <c r="B46">
-        <v>99</v>
-      </c>
-      <c r="C46">
-        <v>71.600236780000003</v>
-      </c>
-      <c r="D46">
-        <v>99</v>
-      </c>
-      <c r="E46">
-        <v>90</v>
-      </c>
-      <c r="F46">
-        <v>80</v>
-      </c>
-      <c r="G46">
-        <v>99</v>
-      </c>
-      <c r="H46">
-        <v>96.5</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A47">
-        <v>2040</v>
-      </c>
-      <c r="B47">
-        <v>99</v>
-      </c>
-      <c r="C47">
-        <v>71.600236780000003</v>
-      </c>
-      <c r="D47">
-        <v>99</v>
-      </c>
-      <c r="E47">
-        <v>90</v>
-      </c>
-      <c r="F47">
-        <v>80</v>
-      </c>
-      <c r="G47">
-        <v>99</v>
-      </c>
-      <c r="H47">
-        <v>96.5</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A48">
-        <v>2041</v>
-      </c>
-      <c r="B48">
-        <v>99</v>
-      </c>
-      <c r="C48">
-        <v>71.600236780000003</v>
-      </c>
-      <c r="D48">
-        <v>99</v>
-      </c>
-      <c r="E48">
-        <v>90</v>
-      </c>
-      <c r="F48">
-        <v>80</v>
-      </c>
-      <c r="G48">
-        <v>99</v>
-      </c>
-      <c r="H48">
-        <v>96.5</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A49">
-        <v>2042</v>
-      </c>
-      <c r="B49">
-        <v>99</v>
-      </c>
-      <c r="C49">
-        <v>71.600236780000003</v>
-      </c>
-      <c r="D49">
-        <v>99</v>
-      </c>
-      <c r="E49">
-        <v>90</v>
-      </c>
-      <c r="F49">
-        <v>80</v>
-      </c>
-      <c r="G49">
-        <v>99</v>
-      </c>
-      <c r="H49">
-        <v>96.5</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A50">
-        <v>2043</v>
-      </c>
-      <c r="B50">
-        <v>99</v>
-      </c>
-      <c r="C50">
-        <v>71.600236780000003</v>
-      </c>
-      <c r="D50">
-        <v>99</v>
-      </c>
-      <c r="E50">
-        <v>90</v>
-      </c>
-      <c r="F50">
-        <v>80</v>
-      </c>
-      <c r="G50">
-        <v>99</v>
-      </c>
-      <c r="H50">
-        <v>96.5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A51">
-        <v>2044</v>
-      </c>
-      <c r="B51">
-        <v>99</v>
-      </c>
-      <c r="C51">
-        <v>71.600236780000003</v>
-      </c>
-      <c r="D51">
-        <v>99</v>
-      </c>
-      <c r="E51">
-        <v>90</v>
-      </c>
-      <c r="F51">
-        <v>80</v>
-      </c>
-      <c r="G51">
-        <v>99</v>
-      </c>
-      <c r="H51">
-        <v>96.5</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A52">
-        <v>2045</v>
-      </c>
-      <c r="B52">
-        <v>99</v>
-      </c>
-      <c r="C52">
-        <v>71.600236780000003</v>
-      </c>
-      <c r="D52">
-        <v>99</v>
-      </c>
-      <c r="E52">
-        <v>90</v>
-      </c>
-      <c r="F52">
-        <v>80</v>
-      </c>
-      <c r="G52">
-        <v>99</v>
-      </c>
-      <c r="H52">
-        <v>96.5</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A53">
-        <v>2046</v>
-      </c>
-      <c r="B53">
-        <v>99</v>
-      </c>
-      <c r="C53">
-        <v>71.600236780000003</v>
-      </c>
-      <c r="D53">
-        <v>99</v>
-      </c>
-      <c r="E53">
-        <v>90</v>
-      </c>
-      <c r="F53">
-        <v>80</v>
-      </c>
-      <c r="G53">
-        <v>99</v>
-      </c>
-      <c r="H53">
-        <v>96.5</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A54">
-        <v>2047</v>
-      </c>
-      <c r="B54">
-        <v>99</v>
-      </c>
-      <c r="C54">
-        <v>71.600236780000003</v>
-      </c>
-      <c r="D54">
-        <v>99</v>
-      </c>
-      <c r="E54">
-        <v>90</v>
-      </c>
-      <c r="F54">
-        <v>80</v>
-      </c>
-      <c r="G54">
-        <v>99</v>
-      </c>
-      <c r="H54">
-        <v>96.5</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A55">
-        <v>2048</v>
-      </c>
-      <c r="B55">
-        <v>99</v>
-      </c>
-      <c r="C55">
-        <v>71.600236780000003</v>
-      </c>
-      <c r="D55">
-        <v>99</v>
-      </c>
-      <c r="E55">
-        <v>90</v>
-      </c>
-      <c r="F55">
-        <v>80</v>
-      </c>
-      <c r="G55">
-        <v>99</v>
-      </c>
-      <c r="H55">
-        <v>96.5</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A56">
-        <v>2049</v>
-      </c>
-      <c r="B56">
-        <v>99</v>
-      </c>
-      <c r="C56">
-        <v>71.600236780000003</v>
-      </c>
-      <c r="D56">
-        <v>99</v>
-      </c>
-      <c r="E56">
-        <v>90</v>
-      </c>
-      <c r="F56">
-        <v>80</v>
-      </c>
-      <c r="G56">
-        <v>99</v>
-      </c>
-      <c r="H56">
-        <v>96.5</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A57">
-        <v>2050</v>
-      </c>
-      <c r="B57">
-        <v>99</v>
-      </c>
-      <c r="C57">
-        <v>71.600236780000003</v>
-      </c>
-      <c r="D57">
-        <v>99</v>
-      </c>
-      <c r="E57">
-        <v>90</v>
-      </c>
-      <c r="F57">
-        <v>80</v>
-      </c>
-      <c r="G57">
-        <v>99</v>
-      </c>
-      <c r="H57">
-        <v>96.5</v>
       </c>
     </row>
   </sheetData>
@@ -47447,6 +46519,1499 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2886825C-AE4A-4EAF-970C-700F7CC3D78A}">
+  <dimension ref="A1:H57"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1995</v>
+      </c>
+      <c r="B2">
+        <v>95</v>
+      </c>
+      <c r="C2">
+        <v>50</v>
+      </c>
+      <c r="D2">
+        <v>99</v>
+      </c>
+      <c r="E2">
+        <v>90</v>
+      </c>
+      <c r="F2">
+        <v>80</v>
+      </c>
+      <c r="G2">
+        <v>95.3</v>
+      </c>
+      <c r="H2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>1996</v>
+      </c>
+      <c r="B3">
+        <v>95</v>
+      </c>
+      <c r="C3">
+        <v>50</v>
+      </c>
+      <c r="D3">
+        <v>99</v>
+      </c>
+      <c r="E3">
+        <v>90</v>
+      </c>
+      <c r="F3">
+        <v>80</v>
+      </c>
+      <c r="G3">
+        <v>95.37</v>
+      </c>
+      <c r="H3">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>1997</v>
+      </c>
+      <c r="B4">
+        <v>95</v>
+      </c>
+      <c r="C4">
+        <v>50</v>
+      </c>
+      <c r="D4">
+        <v>99</v>
+      </c>
+      <c r="E4">
+        <v>90</v>
+      </c>
+      <c r="F4">
+        <v>80</v>
+      </c>
+      <c r="G4">
+        <v>95.44</v>
+      </c>
+      <c r="H4">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>1998</v>
+      </c>
+      <c r="B5">
+        <v>95</v>
+      </c>
+      <c r="C5">
+        <v>50</v>
+      </c>
+      <c r="D5">
+        <v>99</v>
+      </c>
+      <c r="E5">
+        <v>90</v>
+      </c>
+      <c r="F5">
+        <v>80</v>
+      </c>
+      <c r="G5">
+        <v>95.51</v>
+      </c>
+      <c r="H5">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>1999</v>
+      </c>
+      <c r="B6">
+        <v>95</v>
+      </c>
+      <c r="C6">
+        <v>50</v>
+      </c>
+      <c r="D6">
+        <v>99</v>
+      </c>
+      <c r="E6">
+        <v>90</v>
+      </c>
+      <c r="F6">
+        <v>80</v>
+      </c>
+      <c r="G6">
+        <v>95.58</v>
+      </c>
+      <c r="H6">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>2000</v>
+      </c>
+      <c r="B7">
+        <v>95</v>
+      </c>
+      <c r="C7">
+        <v>50</v>
+      </c>
+      <c r="D7">
+        <v>99</v>
+      </c>
+      <c r="E7">
+        <v>90</v>
+      </c>
+      <c r="F7">
+        <v>80</v>
+      </c>
+      <c r="G7">
+        <v>95.65</v>
+      </c>
+      <c r="H7">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>2001</v>
+      </c>
+      <c r="B8">
+        <v>95</v>
+      </c>
+      <c r="C8">
+        <v>50</v>
+      </c>
+      <c r="D8">
+        <v>99</v>
+      </c>
+      <c r="E8">
+        <v>90</v>
+      </c>
+      <c r="F8">
+        <v>80</v>
+      </c>
+      <c r="G8">
+        <v>95.72</v>
+      </c>
+      <c r="H8">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>2002</v>
+      </c>
+      <c r="B9">
+        <v>95</v>
+      </c>
+      <c r="C9">
+        <v>50</v>
+      </c>
+      <c r="D9">
+        <v>99</v>
+      </c>
+      <c r="E9">
+        <v>90</v>
+      </c>
+      <c r="F9">
+        <v>80</v>
+      </c>
+      <c r="G9">
+        <v>95.79</v>
+      </c>
+      <c r="H9">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>2003</v>
+      </c>
+      <c r="B10">
+        <v>95</v>
+      </c>
+      <c r="C10">
+        <v>50</v>
+      </c>
+      <c r="D10">
+        <v>99</v>
+      </c>
+      <c r="E10">
+        <v>90</v>
+      </c>
+      <c r="F10">
+        <v>80</v>
+      </c>
+      <c r="G10">
+        <v>95.86</v>
+      </c>
+      <c r="H10">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>2004</v>
+      </c>
+      <c r="B11">
+        <v>95</v>
+      </c>
+      <c r="C11">
+        <v>49.365658340000003</v>
+      </c>
+      <c r="D11">
+        <v>99</v>
+      </c>
+      <c r="E11">
+        <v>90</v>
+      </c>
+      <c r="F11">
+        <v>80</v>
+      </c>
+      <c r="G11">
+        <v>95.93</v>
+      </c>
+      <c r="H11">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>2005</v>
+      </c>
+      <c r="B12">
+        <v>95</v>
+      </c>
+      <c r="C12">
+        <v>41.588057310000003</v>
+      </c>
+      <c r="D12">
+        <v>99</v>
+      </c>
+      <c r="E12">
+        <v>90</v>
+      </c>
+      <c r="F12">
+        <v>80</v>
+      </c>
+      <c r="G12">
+        <v>96</v>
+      </c>
+      <c r="H12">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>2006</v>
+      </c>
+      <c r="B13">
+        <v>95</v>
+      </c>
+      <c r="C13">
+        <v>33.638416139999997</v>
+      </c>
+      <c r="D13">
+        <v>99</v>
+      </c>
+      <c r="E13">
+        <v>90</v>
+      </c>
+      <c r="F13">
+        <v>80</v>
+      </c>
+      <c r="G13">
+        <v>96.5</v>
+      </c>
+      <c r="H13">
+        <v>93.7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>2007</v>
+      </c>
+      <c r="B14">
+        <v>95</v>
+      </c>
+      <c r="C14">
+        <v>32.313886099999998</v>
+      </c>
+      <c r="D14">
+        <v>99</v>
+      </c>
+      <c r="E14">
+        <v>90</v>
+      </c>
+      <c r="F14">
+        <v>80</v>
+      </c>
+      <c r="G14">
+        <v>97</v>
+      </c>
+      <c r="H14">
+        <v>94.283333330000005</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>2008</v>
+      </c>
+      <c r="B15">
+        <v>95</v>
+      </c>
+      <c r="C15">
+        <v>30.95939478</v>
+      </c>
+      <c r="D15">
+        <v>99</v>
+      </c>
+      <c r="E15">
+        <v>90</v>
+      </c>
+      <c r="F15">
+        <v>80</v>
+      </c>
+      <c r="G15">
+        <v>97.5</v>
+      </c>
+      <c r="H15">
+        <v>94.866666670000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>2009</v>
+      </c>
+      <c r="B16">
+        <v>95</v>
+      </c>
+      <c r="C16">
+        <v>31.313555950000001</v>
+      </c>
+      <c r="D16">
+        <v>99</v>
+      </c>
+      <c r="E16">
+        <v>90</v>
+      </c>
+      <c r="F16">
+        <v>80</v>
+      </c>
+      <c r="G16">
+        <v>98</v>
+      </c>
+      <c r="H16">
+        <v>95.45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>2010</v>
+      </c>
+      <c r="B17">
+        <v>95</v>
+      </c>
+      <c r="C17">
+        <v>49.33536239</v>
+      </c>
+      <c r="D17">
+        <v>99</v>
+      </c>
+      <c r="E17">
+        <v>90</v>
+      </c>
+      <c r="F17">
+        <v>80</v>
+      </c>
+      <c r="G17">
+        <v>98.5</v>
+      </c>
+      <c r="H17">
+        <v>96.033333330000005</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>2011</v>
+      </c>
+      <c r="B18">
+        <v>95</v>
+      </c>
+      <c r="C18">
+        <v>49.661818310000001</v>
+      </c>
+      <c r="D18">
+        <v>99</v>
+      </c>
+      <c r="E18">
+        <v>90</v>
+      </c>
+      <c r="F18">
+        <v>80</v>
+      </c>
+      <c r="G18">
+        <v>99</v>
+      </c>
+      <c r="H18">
+        <v>96.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>2012</v>
+      </c>
+      <c r="B19">
+        <v>95</v>
+      </c>
+      <c r="C19">
+        <v>48.63711241</v>
+      </c>
+      <c r="D19">
+        <v>99</v>
+      </c>
+      <c r="E19">
+        <v>90</v>
+      </c>
+      <c r="F19">
+        <v>80</v>
+      </c>
+      <c r="G19">
+        <v>99</v>
+      </c>
+      <c r="H19">
+        <v>96.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>2013</v>
+      </c>
+      <c r="B20">
+        <v>95</v>
+      </c>
+      <c r="C20">
+        <v>49.920500959999998</v>
+      </c>
+      <c r="D20">
+        <v>99</v>
+      </c>
+      <c r="E20">
+        <v>90</v>
+      </c>
+      <c r="F20">
+        <v>80</v>
+      </c>
+      <c r="G20">
+        <v>99</v>
+      </c>
+      <c r="H20">
+        <v>96.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>2014</v>
+      </c>
+      <c r="B21">
+        <v>95.2</v>
+      </c>
+      <c r="C21">
+        <v>50.133176429999999</v>
+      </c>
+      <c r="D21">
+        <v>99</v>
+      </c>
+      <c r="E21">
+        <v>90</v>
+      </c>
+      <c r="F21">
+        <v>80</v>
+      </c>
+      <c r="G21">
+        <v>99</v>
+      </c>
+      <c r="H21">
+        <v>96.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>2015</v>
+      </c>
+      <c r="B22">
+        <v>95.5</v>
+      </c>
+      <c r="C22">
+        <v>50.540356459999998</v>
+      </c>
+      <c r="D22">
+        <v>99</v>
+      </c>
+      <c r="E22">
+        <v>90</v>
+      </c>
+      <c r="F22">
+        <v>80</v>
+      </c>
+      <c r="G22">
+        <v>99</v>
+      </c>
+      <c r="H22">
+        <v>96.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>2016</v>
+      </c>
+      <c r="B23">
+        <v>95.7</v>
+      </c>
+      <c r="C23">
+        <v>53.417000399999999</v>
+      </c>
+      <c r="D23">
+        <v>99</v>
+      </c>
+      <c r="E23">
+        <v>90</v>
+      </c>
+      <c r="F23">
+        <v>80</v>
+      </c>
+      <c r="G23">
+        <v>99</v>
+      </c>
+      <c r="H23">
+        <v>96.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>2017</v>
+      </c>
+      <c r="B24">
+        <v>95.9</v>
+      </c>
+      <c r="C24">
+        <v>59.32333715</v>
+      </c>
+      <c r="D24">
+        <v>99</v>
+      </c>
+      <c r="E24">
+        <v>90</v>
+      </c>
+      <c r="F24">
+        <v>80</v>
+      </c>
+      <c r="G24">
+        <v>99</v>
+      </c>
+      <c r="H24">
+        <v>96.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>2018</v>
+      </c>
+      <c r="B25">
+        <v>96.2</v>
+      </c>
+      <c r="C25">
+        <v>63.600552669999999</v>
+      </c>
+      <c r="D25">
+        <v>99</v>
+      </c>
+      <c r="E25">
+        <v>90</v>
+      </c>
+      <c r="F25">
+        <v>80</v>
+      </c>
+      <c r="G25">
+        <v>99</v>
+      </c>
+      <c r="H25">
+        <v>96.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>2019</v>
+      </c>
+      <c r="B26">
+        <v>96.4</v>
+      </c>
+      <c r="C26">
+        <v>65.063940110000004</v>
+      </c>
+      <c r="D26">
+        <v>99</v>
+      </c>
+      <c r="E26">
+        <v>90</v>
+      </c>
+      <c r="F26">
+        <v>80</v>
+      </c>
+      <c r="G26">
+        <v>99</v>
+      </c>
+      <c r="H26">
+        <v>96.5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>2020</v>
+      </c>
+      <c r="B27">
+        <v>96.6</v>
+      </c>
+      <c r="C27">
+        <v>66.726759759999993</v>
+      </c>
+      <c r="D27">
+        <v>99</v>
+      </c>
+      <c r="E27">
+        <v>90</v>
+      </c>
+      <c r="F27">
+        <v>80</v>
+      </c>
+      <c r="G27">
+        <v>99</v>
+      </c>
+      <c r="H27">
+        <v>96.5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>2021</v>
+      </c>
+      <c r="B28">
+        <v>96.9</v>
+      </c>
+      <c r="C28">
+        <v>66.180844960000002</v>
+      </c>
+      <c r="D28">
+        <v>99</v>
+      </c>
+      <c r="E28">
+        <v>90</v>
+      </c>
+      <c r="F28">
+        <v>80</v>
+      </c>
+      <c r="G28">
+        <v>99</v>
+      </c>
+      <c r="H28">
+        <v>96.5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>2022</v>
+      </c>
+      <c r="B29">
+        <v>97.1</v>
+      </c>
+      <c r="C29">
+        <v>65.587672920000003</v>
+      </c>
+      <c r="D29">
+        <v>99</v>
+      </c>
+      <c r="E29">
+        <v>90</v>
+      </c>
+      <c r="F29">
+        <v>80</v>
+      </c>
+      <c r="G29">
+        <v>99</v>
+      </c>
+      <c r="H29">
+        <v>96.5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>2023</v>
+      </c>
+      <c r="B30">
+        <v>97.4</v>
+      </c>
+      <c r="C30">
+        <v>66.98371616</v>
+      </c>
+      <c r="D30">
+        <v>99</v>
+      </c>
+      <c r="E30">
+        <v>90</v>
+      </c>
+      <c r="F30">
+        <v>80</v>
+      </c>
+      <c r="G30">
+        <v>99</v>
+      </c>
+      <c r="H30">
+        <v>96.5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>2024</v>
+      </c>
+      <c r="B31">
+        <v>97.6</v>
+      </c>
+      <c r="C31">
+        <v>68.784939679999994</v>
+      </c>
+      <c r="D31">
+        <v>99</v>
+      </c>
+      <c r="E31">
+        <v>90</v>
+      </c>
+      <c r="F31">
+        <v>80</v>
+      </c>
+      <c r="G31">
+        <v>99</v>
+      </c>
+      <c r="H31">
+        <v>96.5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>2025</v>
+      </c>
+      <c r="B32">
+        <v>97.8</v>
+      </c>
+      <c r="C32">
+        <v>69.379740209999994</v>
+      </c>
+      <c r="D32">
+        <v>99</v>
+      </c>
+      <c r="E32">
+        <v>90</v>
+      </c>
+      <c r="F32">
+        <v>80</v>
+      </c>
+      <c r="G32">
+        <v>99</v>
+      </c>
+      <c r="H32">
+        <v>96.5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>2026</v>
+      </c>
+      <c r="B33">
+        <v>98.1</v>
+      </c>
+      <c r="C33">
+        <v>69.848360650000004</v>
+      </c>
+      <c r="D33">
+        <v>99</v>
+      </c>
+      <c r="E33">
+        <v>90</v>
+      </c>
+      <c r="F33">
+        <v>80</v>
+      </c>
+      <c r="G33">
+        <v>99</v>
+      </c>
+      <c r="H33">
+        <v>96.5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>2027</v>
+      </c>
+      <c r="B34">
+        <v>98.3</v>
+      </c>
+      <c r="C34">
+        <v>70.190564620000004</v>
+      </c>
+      <c r="D34">
+        <v>99</v>
+      </c>
+      <c r="E34">
+        <v>90</v>
+      </c>
+      <c r="F34">
+        <v>80</v>
+      </c>
+      <c r="G34">
+        <v>99</v>
+      </c>
+      <c r="H34">
+        <v>96.5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>2028</v>
+      </c>
+      <c r="B35">
+        <v>98.5</v>
+      </c>
+      <c r="C35">
+        <v>70.655697110000006</v>
+      </c>
+      <c r="D35">
+        <v>99</v>
+      </c>
+      <c r="E35">
+        <v>90</v>
+      </c>
+      <c r="F35">
+        <v>80</v>
+      </c>
+      <c r="G35">
+        <v>99</v>
+      </c>
+      <c r="H35">
+        <v>96.5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>2029</v>
+      </c>
+      <c r="B36">
+        <v>98.8</v>
+      </c>
+      <c r="C36">
+        <v>71.125574380000003</v>
+      </c>
+      <c r="D36">
+        <v>99</v>
+      </c>
+      <c r="E36">
+        <v>90</v>
+      </c>
+      <c r="F36">
+        <v>80</v>
+      </c>
+      <c r="G36">
+        <v>99</v>
+      </c>
+      <c r="H36">
+        <v>96.5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>2030</v>
+      </c>
+      <c r="B37">
+        <v>99</v>
+      </c>
+      <c r="C37">
+        <v>71.600236780000003</v>
+      </c>
+      <c r="D37">
+        <v>99</v>
+      </c>
+      <c r="E37">
+        <v>90</v>
+      </c>
+      <c r="F37">
+        <v>80</v>
+      </c>
+      <c r="G37">
+        <v>99</v>
+      </c>
+      <c r="H37">
+        <v>96.5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>2031</v>
+      </c>
+      <c r="B38">
+        <v>99</v>
+      </c>
+      <c r="C38">
+        <v>71.600236780000003</v>
+      </c>
+      <c r="D38">
+        <v>99</v>
+      </c>
+      <c r="E38">
+        <v>90</v>
+      </c>
+      <c r="F38">
+        <v>80</v>
+      </c>
+      <c r="G38">
+        <v>99</v>
+      </c>
+      <c r="H38">
+        <v>96.5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>2032</v>
+      </c>
+      <c r="B39">
+        <v>99</v>
+      </c>
+      <c r="C39">
+        <v>71.600236780000003</v>
+      </c>
+      <c r="D39">
+        <v>99</v>
+      </c>
+      <c r="E39">
+        <v>90</v>
+      </c>
+      <c r="F39">
+        <v>80</v>
+      </c>
+      <c r="G39">
+        <v>99</v>
+      </c>
+      <c r="H39">
+        <v>96.5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>2033</v>
+      </c>
+      <c r="B40">
+        <v>99</v>
+      </c>
+      <c r="C40">
+        <v>71.600236780000003</v>
+      </c>
+      <c r="D40">
+        <v>99</v>
+      </c>
+      <c r="E40">
+        <v>90</v>
+      </c>
+      <c r="F40">
+        <v>80</v>
+      </c>
+      <c r="G40">
+        <v>99</v>
+      </c>
+      <c r="H40">
+        <v>96.5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A41">
+        <v>2034</v>
+      </c>
+      <c r="B41">
+        <v>99</v>
+      </c>
+      <c r="C41">
+        <v>71.600236780000003</v>
+      </c>
+      <c r="D41">
+        <v>99</v>
+      </c>
+      <c r="E41">
+        <v>90</v>
+      </c>
+      <c r="F41">
+        <v>80</v>
+      </c>
+      <c r="G41">
+        <v>99</v>
+      </c>
+      <c r="H41">
+        <v>96.5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <v>2035</v>
+      </c>
+      <c r="B42">
+        <v>99</v>
+      </c>
+      <c r="C42">
+        <v>71.600236780000003</v>
+      </c>
+      <c r="D42">
+        <v>99</v>
+      </c>
+      <c r="E42">
+        <v>90</v>
+      </c>
+      <c r="F42">
+        <v>80</v>
+      </c>
+      <c r="G42">
+        <v>99</v>
+      </c>
+      <c r="H42">
+        <v>96.5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A43">
+        <v>2036</v>
+      </c>
+      <c r="B43">
+        <v>99</v>
+      </c>
+      <c r="C43">
+        <v>71.600236780000003</v>
+      </c>
+      <c r="D43">
+        <v>99</v>
+      </c>
+      <c r="E43">
+        <v>90</v>
+      </c>
+      <c r="F43">
+        <v>80</v>
+      </c>
+      <c r="G43">
+        <v>99</v>
+      </c>
+      <c r="H43">
+        <v>96.5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A44">
+        <v>2037</v>
+      </c>
+      <c r="B44">
+        <v>99</v>
+      </c>
+      <c r="C44">
+        <v>71.600236780000003</v>
+      </c>
+      <c r="D44">
+        <v>99</v>
+      </c>
+      <c r="E44">
+        <v>90</v>
+      </c>
+      <c r="F44">
+        <v>80</v>
+      </c>
+      <c r="G44">
+        <v>99</v>
+      </c>
+      <c r="H44">
+        <v>96.5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A45">
+        <v>2038</v>
+      </c>
+      <c r="B45">
+        <v>99</v>
+      </c>
+      <c r="C45">
+        <v>71.600236780000003</v>
+      </c>
+      <c r="D45">
+        <v>99</v>
+      </c>
+      <c r="E45">
+        <v>90</v>
+      </c>
+      <c r="F45">
+        <v>80</v>
+      </c>
+      <c r="G45">
+        <v>99</v>
+      </c>
+      <c r="H45">
+        <v>96.5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A46">
+        <v>2039</v>
+      </c>
+      <c r="B46">
+        <v>99</v>
+      </c>
+      <c r="C46">
+        <v>71.600236780000003</v>
+      </c>
+      <c r="D46">
+        <v>99</v>
+      </c>
+      <c r="E46">
+        <v>90</v>
+      </c>
+      <c r="F46">
+        <v>80</v>
+      </c>
+      <c r="G46">
+        <v>99</v>
+      </c>
+      <c r="H46">
+        <v>96.5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A47">
+        <v>2040</v>
+      </c>
+      <c r="B47">
+        <v>99</v>
+      </c>
+      <c r="C47">
+        <v>71.600236780000003</v>
+      </c>
+      <c r="D47">
+        <v>99</v>
+      </c>
+      <c r="E47">
+        <v>90</v>
+      </c>
+      <c r="F47">
+        <v>80</v>
+      </c>
+      <c r="G47">
+        <v>99</v>
+      </c>
+      <c r="H47">
+        <v>96.5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A48">
+        <v>2041</v>
+      </c>
+      <c r="B48">
+        <v>99</v>
+      </c>
+      <c r="C48">
+        <v>71.600236780000003</v>
+      </c>
+      <c r="D48">
+        <v>99</v>
+      </c>
+      <c r="E48">
+        <v>90</v>
+      </c>
+      <c r="F48">
+        <v>80</v>
+      </c>
+      <c r="G48">
+        <v>99</v>
+      </c>
+      <c r="H48">
+        <v>96.5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A49">
+        <v>2042</v>
+      </c>
+      <c r="B49">
+        <v>99</v>
+      </c>
+      <c r="C49">
+        <v>71.600236780000003</v>
+      </c>
+      <c r="D49">
+        <v>99</v>
+      </c>
+      <c r="E49">
+        <v>90</v>
+      </c>
+      <c r="F49">
+        <v>80</v>
+      </c>
+      <c r="G49">
+        <v>99</v>
+      </c>
+      <c r="H49">
+        <v>96.5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A50">
+        <v>2043</v>
+      </c>
+      <c r="B50">
+        <v>99</v>
+      </c>
+      <c r="C50">
+        <v>71.600236780000003</v>
+      </c>
+      <c r="D50">
+        <v>99</v>
+      </c>
+      <c r="E50">
+        <v>90</v>
+      </c>
+      <c r="F50">
+        <v>80</v>
+      </c>
+      <c r="G50">
+        <v>99</v>
+      </c>
+      <c r="H50">
+        <v>96.5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A51">
+        <v>2044</v>
+      </c>
+      <c r="B51">
+        <v>99</v>
+      </c>
+      <c r="C51">
+        <v>71.600236780000003</v>
+      </c>
+      <c r="D51">
+        <v>99</v>
+      </c>
+      <c r="E51">
+        <v>90</v>
+      </c>
+      <c r="F51">
+        <v>80</v>
+      </c>
+      <c r="G51">
+        <v>99</v>
+      </c>
+      <c r="H51">
+        <v>96.5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A52">
+        <v>2045</v>
+      </c>
+      <c r="B52">
+        <v>99</v>
+      </c>
+      <c r="C52">
+        <v>71.600236780000003</v>
+      </c>
+      <c r="D52">
+        <v>99</v>
+      </c>
+      <c r="E52">
+        <v>90</v>
+      </c>
+      <c r="F52">
+        <v>80</v>
+      </c>
+      <c r="G52">
+        <v>99</v>
+      </c>
+      <c r="H52">
+        <v>96.5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A53">
+        <v>2046</v>
+      </c>
+      <c r="B53">
+        <v>99</v>
+      </c>
+      <c r="C53">
+        <v>71.600236780000003</v>
+      </c>
+      <c r="D53">
+        <v>99</v>
+      </c>
+      <c r="E53">
+        <v>90</v>
+      </c>
+      <c r="F53">
+        <v>80</v>
+      </c>
+      <c r="G53">
+        <v>99</v>
+      </c>
+      <c r="H53">
+        <v>96.5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A54">
+        <v>2047</v>
+      </c>
+      <c r="B54">
+        <v>99</v>
+      </c>
+      <c r="C54">
+        <v>71.600236780000003</v>
+      </c>
+      <c r="D54">
+        <v>99</v>
+      </c>
+      <c r="E54">
+        <v>90</v>
+      </c>
+      <c r="F54">
+        <v>80</v>
+      </c>
+      <c r="G54">
+        <v>99</v>
+      </c>
+      <c r="H54">
+        <v>96.5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A55">
+        <v>2048</v>
+      </c>
+      <c r="B55">
+        <v>99</v>
+      </c>
+      <c r="C55">
+        <v>71.600236780000003</v>
+      </c>
+      <c r="D55">
+        <v>99</v>
+      </c>
+      <c r="E55">
+        <v>90</v>
+      </c>
+      <c r="F55">
+        <v>80</v>
+      </c>
+      <c r="G55">
+        <v>99</v>
+      </c>
+      <c r="H55">
+        <v>96.5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A56">
+        <v>2049</v>
+      </c>
+      <c r="B56">
+        <v>99</v>
+      </c>
+      <c r="C56">
+        <v>71.600236780000003</v>
+      </c>
+      <c r="D56">
+        <v>99</v>
+      </c>
+      <c r="E56">
+        <v>90</v>
+      </c>
+      <c r="F56">
+        <v>80</v>
+      </c>
+      <c r="G56">
+        <v>99</v>
+      </c>
+      <c r="H56">
+        <v>96.5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A57">
+        <v>2050</v>
+      </c>
+      <c r="B57">
+        <v>99</v>
+      </c>
+      <c r="C57">
+        <v>71.600236780000003</v>
+      </c>
+      <c r="D57">
+        <v>99</v>
+      </c>
+      <c r="E57">
+        <v>90</v>
+      </c>
+      <c r="F57">
+        <v>80</v>
+      </c>
+      <c r="G57">
+        <v>99</v>
+      </c>
+      <c r="H57">
+        <v>96.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0188699D-EC8B-4A24-8D21-3FBF9C878E79}">
   <dimension ref="A1:AF44"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -47684,7 +48249,7 @@
       </c>
       <c r="B6">
         <f>'mass per m2'!B35/1000</f>
-        <v>8.08</v>
+        <v>8.0449999999999999</v>
       </c>
       <c r="C6">
         <f>'mass per m2'!$C$32/100</f>
@@ -47737,7 +48302,7 @@
       </c>
       <c r="B7">
         <f>'mass per m2'!B36/1000</f>
-        <v>8.16</v>
+        <v>8.09</v>
       </c>
       <c r="C7">
         <f>'mass per m2'!$C$32/100</f>
@@ -47790,7 +48355,7 @@
       </c>
       <c r="B8">
         <f>'mass per m2'!B37/1000</f>
-        <v>8.2927</v>
+        <v>8.18</v>
       </c>
       <c r="C8">
         <f>'mass per m2'!$C$32/100</f>
@@ -47843,7 +48408,7 @@
       </c>
       <c r="B9">
         <f>'mass per m2'!B38/1000</f>
-        <v>8.2256625000000003</v>
+        <v>8.09</v>
       </c>
       <c r="C9">
         <f>'mass per m2'!$C$32/100</f>
@@ -47896,7 +48461,7 @@
       </c>
       <c r="B10">
         <f>'mass per m2'!B39/1000</f>
-        <v>8.1588875000000005</v>
+        <v>8.1349999999999998</v>
       </c>
       <c r="C10">
         <f>'mass per m2'!$C$32/100</f>
@@ -47949,7 +48514,7 @@
       </c>
       <c r="B11">
         <f>'mass per m2'!B40/1000</f>
-        <v>8.2897499999999997</v>
+        <v>8.2083750000000002</v>
       </c>
       <c r="C11">
         <f>'mass per m2'!$C$32/100</f>
@@ -48002,7 +48567,7 @@
       </c>
       <c r="B12">
         <f>'mass per m2'!B41/1000</f>
-        <v>8.3501499999999993</v>
+        <v>8.2535499999999988</v>
       </c>
       <c r="C12">
         <f>'mass per m2'!$C$32/100</f>
@@ -48055,7 +48620,7 @@
       </c>
       <c r="B13">
         <f>'mass per m2'!B42/1000</f>
-        <v>8.6074999999999999</v>
+        <v>8.4499999999999993</v>
       </c>
       <c r="C13">
         <f>'mass per m2'!$C$32/100</f>
@@ -48108,7 +48673,7 @@
       </c>
       <c r="B14">
         <f>'mass per m2'!B43/1000</f>
-        <v>8.9755000000000003</v>
+        <v>8.7641000000000009</v>
       </c>
       <c r="C14">
         <f>'mass per m2'!$C$32/100</f>
@@ -48161,7 +48726,7 @@
       </c>
       <c r="B15">
         <f>'mass per m2'!B44/1000</f>
-        <v>9.0269999999999992</v>
+        <v>9.0766000000000009</v>
       </c>
       <c r="C15">
         <f>'mass per m2'!$C$32/100</f>
@@ -48214,7 +48779,7 @@
       </c>
       <c r="B16">
         <f>'mass per m2'!B45/1000</f>
-        <v>9.1065000000000005</v>
+        <v>9.4842124999999999</v>
       </c>
       <c r="C16">
         <f>'mass per m2'!$C$32/100</f>
@@ -48267,7 +48832,7 @@
       </c>
       <c r="B17">
         <f>'mass per m2'!B46/1000</f>
-        <v>9.1835499999999985</v>
+        <v>9.6543749999999999</v>
       </c>
       <c r="C17">
         <f>'mass per m2'!$C$32/100</f>
@@ -48320,7 +48885,7 @@
       </c>
       <c r="B18">
         <f>'mass per m2'!B47/1000</f>
-        <v>9.1088250000000013</v>
+        <v>10.055524999999999</v>
       </c>
       <c r="C18">
         <f>'mass per m2'!$C$32/100</f>
@@ -48373,7 +48938,7 @@
       </c>
       <c r="B19">
         <f>'mass per m2'!B48/1000</f>
-        <v>9.0341000000000005</v>
+        <v>10.349549999999999</v>
       </c>
       <c r="C19">
         <f>'mass per m2'!$C$32/100</f>
@@ -48426,7 +48991,7 @@
       </c>
       <c r="B20">
         <f>'mass per m2'!B49/1000</f>
-        <v>9.2052083329999999</v>
+        <v>10.5123125</v>
       </c>
       <c r="C20">
         <f>'mass per m2'!$C$32/100</f>
@@ -48479,7 +49044,7 @@
       </c>
       <c r="B21">
         <f>'mass per m2'!B50/1000</f>
-        <v>9.3738666669999997</v>
+        <v>10.676825000000001</v>
       </c>
       <c r="C21">
         <f>'mass per m2'!$C$32/100</f>
@@ -48532,7 +49097,7 @@
       </c>
       <c r="B22">
         <f>'mass per m2'!B51/1000</f>
-        <v>9.5400749999999999</v>
+        <v>10.7117312499999</v>
       </c>
       <c r="C22">
         <f>'mass per m2'!$C$32/100</f>
@@ -48585,7 +49150,7 @@
       </c>
       <c r="B23">
         <f>'mass per m2'!B52/1000</f>
-        <v>9.7358083330000014</v>
+        <v>10.747249999999999</v>
       </c>
       <c r="C23">
         <f>'mass per m2'!$C$32/100</f>
@@ -48638,7 +49203,7 @@
       </c>
       <c r="B24">
         <f>'mass per m2'!B53/1000</f>
-        <v>9.9292083330000001</v>
+        <v>10.7754888888888</v>
       </c>
       <c r="C24">
         <f>'mass per m2'!$C$32/100</f>
@@ -48691,7 +49256,7 @@
       </c>
       <c r="B25">
         <f>'mass per m2'!B54/1000</f>
-        <v>10.120274999999999</v>
+        <v>10.8041555555555</v>
       </c>
       <c r="C25">
         <f>'mass per m2'!$C$32/100</f>
@@ -48744,7 +49309,7 @@
       </c>
       <c r="B26">
         <f>'mass per m2'!B55/1000</f>
-        <v>10.120274999999999</v>
+        <v>10.83325</v>
       </c>
       <c r="C26">
         <f>'mass per m2'!$C$32/100</f>
@@ -48797,7 +49362,7 @@
       </c>
       <c r="B27">
         <f>'mass per m2'!B56/1000</f>
-        <v>10.120274999999999</v>
+        <v>10.8221666666666</v>
       </c>
       <c r="C27">
         <f>'mass per m2'!$C$32/100</f>
@@ -48850,7 +49415,7 @@
       </c>
       <c r="B28">
         <f>'mass per m2'!B57/1000</f>
-        <v>10.120274999999999</v>
+        <v>10.811083333333299</v>
       </c>
       <c r="C28">
         <f>'mass per m2'!$C$32/100</f>
@@ -48903,7 +49468,7 @@
       </c>
       <c r="B29">
         <f>'mass per m2'!B58/1000</f>
-        <v>10.120274999999999</v>
+        <v>10.8</v>
       </c>
       <c r="C29">
         <f>'mass per m2'!$C$32/100</f>
@@ -48956,7 +49521,7 @@
       </c>
       <c r="B30">
         <f>'mass per m2'!B59/1000</f>
-        <v>10.120274999999999</v>
+        <v>10.8</v>
       </c>
       <c r="C30">
         <f>'mass per m2'!$C$32/100</f>
@@ -49009,7 +49574,7 @@
       </c>
       <c r="B31">
         <f>'mass per m2'!B60/1000</f>
-        <v>10.120274999999999</v>
+        <v>10.8</v>
       </c>
       <c r="C31">
         <f>'mass per m2'!$C$32/100</f>
@@ -49062,7 +49627,7 @@
       </c>
       <c r="B32">
         <f>'mass per m2'!B61/1000</f>
-        <v>10.120274999999999</v>
+        <v>10.8</v>
       </c>
       <c r="C32">
         <f>'mass per m2'!$C$32/100</f>
@@ -49115,7 +49680,7 @@
       </c>
       <c r="B33">
         <f>'mass per m2'!B62/1000</f>
-        <v>10.120274999999999</v>
+        <v>10.8</v>
       </c>
       <c r="C33">
         <f>'mass per m2'!$C$32/100</f>
@@ -49168,7 +49733,7 @@
       </c>
       <c r="B34">
         <f>'mass per m2'!B63/1000</f>
-        <v>10.120274999999999</v>
+        <v>10.8</v>
       </c>
       <c r="C34">
         <f>'mass per m2'!$C$32/100</f>
@@ -49221,7 +49786,7 @@
       </c>
       <c r="B35">
         <f>'mass per m2'!B64/1000</f>
-        <v>10.120274999999999</v>
+        <v>10.8</v>
       </c>
       <c r="C35">
         <f>'mass per m2'!$C$32/100</f>
@@ -49274,7 +49839,7 @@
       </c>
       <c r="B36">
         <f>'mass per m2'!B65/1000</f>
-        <v>10.120274999999999</v>
+        <v>10.8</v>
       </c>
       <c r="C36">
         <f>'mass per m2'!$C$32/100</f>
@@ -49342,7 +49907,7 @@
       </c>
       <c r="B37">
         <f>'mass per m2'!B66/1000</f>
-        <v>10.120274999999999</v>
+        <v>10.8</v>
       </c>
       <c r="C37">
         <f>'mass per m2'!$C$32/100</f>
@@ -49413,7 +49978,7 @@
       </c>
       <c r="B38">
         <f>'mass per m2'!B67/1000</f>
-        <v>10.120274999999999</v>
+        <v>10.8</v>
       </c>
       <c r="C38">
         <f>'mass per m2'!$C$32/100</f>
@@ -49484,7 +50049,7 @@
       </c>
       <c r="B39">
         <f>'mass per m2'!B68/1000</f>
-        <v>10.120274999999999</v>
+        <v>10.8</v>
       </c>
       <c r="C39">
         <f>'mass per m2'!$C$32/100</f>
@@ -49555,7 +50120,7 @@
       </c>
       <c r="B40">
         <f>'mass per m2'!B69/1000</f>
-        <v>10.120274999999999</v>
+        <v>10.8</v>
       </c>
       <c r="C40">
         <f>'mass per m2'!$C$32/100</f>
@@ -49608,7 +50173,7 @@
       </c>
       <c r="B41">
         <f>'mass per m2'!B70/1000</f>
-        <v>10.120274999999999</v>
+        <v>10.8</v>
       </c>
       <c r="C41">
         <f>'mass per m2'!$C$32/100</f>
@@ -49661,7 +50226,7 @@
       </c>
       <c r="B42">
         <f>'mass per m2'!B71/1000</f>
-        <v>10.120274999999999</v>
+        <v>10.8</v>
       </c>
       <c r="C42">
         <f>'mass per m2'!$C$32/100</f>
@@ -49714,7 +50279,7 @@
       </c>
       <c r="B43">
         <f>'mass per m2'!B72/1000</f>
-        <v>10.120274999999999</v>
+        <v>10.8</v>
       </c>
       <c r="C43">
         <f>'mass per m2'!$C$32/100</f>
@@ -49767,7 +50332,7 @@
       </c>
       <c r="B44">
         <f>'mass per m2'!B73/1000</f>
-        <v>10.120274999999999</v>
+        <v>10.8</v>
       </c>
       <c r="C44">
         <f>'mass per m2'!$C$32/100</f>
@@ -49825,7 +50390,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E72CE93-524C-4FA7-9EC7-337A4A16DA07}">
   <dimension ref="A1:G58"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>

--- a/PV_ICE/baselines/SupportingMaterial/Manual Files/BaselineGraphs.xlsx
+++ b/PV_ICE/baselines/SupportingMaterial/Manual Files/BaselineGraphs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hmirletz\Documents\GitHub\PV_ICE\PV_ICE\baselines\SupportingMaterial\Manual Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9E66EDF-F298-4FCC-BF88-1F35DD76603C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DD06540-8CAA-4878-8F6C-5008E0CFB206}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{31D47E9D-A833-4D35-B79A-EFF0E4DE6D01}"/>
+    <workbookView xWindow="-28920" yWindow="45" windowWidth="29040" windowHeight="15720" xr2:uid="{31D47E9D-A833-4D35-B79A-EFF0E4DE6D01}"/>
   </bookViews>
   <sheets>
     <sheet name="mass per m2" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="56">
   <si>
     <t>Year</t>
   </si>
@@ -208,13 +208,16 @@
   <si>
     <t>%Backsheet</t>
   </si>
+  <si>
+    <t>Mass per Module g/m^2</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="167" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -277,10 +280,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -290,10 +293,10 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF1F77BE"/>
+      <color rgb="FFD62728"/>
       <color rgb="FF8C564B"/>
       <color rgb="FF9467BD"/>
-      <color rgb="FFD62728"/>
-      <color rgb="FF1F77BE"/>
       <color rgb="FF00BFBF"/>
       <color rgb="FFFF7F0E"/>
       <color rgb="FF19809E"/>
@@ -8212,130 +8215,130 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="42"/>
                 <c:pt idx="0">
-                  <c:v>2.0013003899999999</c:v>
+                  <c:v>2.2506500000000003</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.9871506589999999</c:v>
+                  <c:v>1.8851199999999999</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.9665931299999999</c:v>
+                  <c:v>1.9236300000000002</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.9629861980000001</c:v>
+                  <c:v>1.85331</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.619458128</c:v>
+                  <c:v>1.64114</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.592739726</c:v>
+                  <c:v>1.8393199999999998</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.495242424</c:v>
+                  <c:v>1.6882300000000001</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.4125263159999999</c:v>
+                  <c:v>1.6708900000000002</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.379820896</c:v>
+                  <c:v>1.6153299999999999</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.3616666669999999</c:v>
+                  <c:v>1.55301</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.3436470589999998</c:v>
+                  <c:v>1.57385</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.3436470589999998</c:v>
+                  <c:v>1.57996</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.2721764710000001</c:v>
+                  <c:v>1.57996</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.2507352940000001</c:v>
+                  <c:v>1.57996</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.2292941180000001</c:v>
+                  <c:v>1.57996</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.2150000000000001</c:v>
+                  <c:v>1.57996</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.2007058820000001</c:v>
+                  <c:v>1.57996</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.1911764709999999</c:v>
+                  <c:v>1.57996</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.1816470589999999</c:v>
+                  <c:v>1.57996</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.1721176470000001</c:v>
+                  <c:v>1.57996</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1.1625882349999999</c:v>
+                  <c:v>1.57996</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1.1530588239999999</c:v>
+                  <c:v>1.57996</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1.1435294120000001</c:v>
+                  <c:v>1.57996</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1.1435294120000001</c:v>
+                  <c:v>1.57996</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1.1435294120000001</c:v>
+                  <c:v>1.57996</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1.1435294120000001</c:v>
+                  <c:v>1.57996</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1.1435294120000001</c:v>
+                  <c:v>1.57996</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>1.1435294120000001</c:v>
+                  <c:v>1.57996</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>1.1435294120000001</c:v>
+                  <c:v>1.57996</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>1.1435294120000001</c:v>
+                  <c:v>1.57996</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>1.1435294120000001</c:v>
+                  <c:v>1.57996</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>1.1435294120000001</c:v>
+                  <c:v>1.57996</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>1.1435294120000001</c:v>
+                  <c:v>1.57996</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>1.1435294120000001</c:v>
+                  <c:v>1.57996</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>1.1435294120000001</c:v>
+                  <c:v>1.57996</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>1.1435294120000001</c:v>
+                  <c:v>1.57996</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>1.1435294120000001</c:v>
+                  <c:v>1.57996</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>1.1435294120000001</c:v>
+                  <c:v>1.57996</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>1.1435294120000001</c:v>
+                  <c:v>1.57996</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>1.1435294120000001</c:v>
+                  <c:v>1.57996</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>1.1435294120000001</c:v>
+                  <c:v>1.57996</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>1.1435294120000001</c:v>
+                  <c:v>1.57996</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10384,130 +10387,130 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="42"/>
                 <c:pt idx="0">
-                  <c:v>2.0013003899999999</c:v>
+                  <c:v>2.2506500000000003</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.9871506589999999</c:v>
+                  <c:v>1.8851199999999999</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.9665931299999999</c:v>
+                  <c:v>1.9236300000000002</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.9629861980000001</c:v>
+                  <c:v>1.85331</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.619458128</c:v>
+                  <c:v>1.64114</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.592739726</c:v>
+                  <c:v>1.8393199999999998</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.495242424</c:v>
+                  <c:v>1.6882300000000001</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.4125263159999999</c:v>
+                  <c:v>1.6708900000000002</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.379820896</c:v>
+                  <c:v>1.6153299999999999</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.3616666669999999</c:v>
+                  <c:v>1.55301</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.3436470589999998</c:v>
+                  <c:v>1.57385</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.3436470589999998</c:v>
+                  <c:v>1.57996</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.2721764710000001</c:v>
+                  <c:v>1.57996</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.2507352940000001</c:v>
+                  <c:v>1.57996</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.2292941180000001</c:v>
+                  <c:v>1.57996</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.2150000000000001</c:v>
+                  <c:v>1.57996</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.2007058820000001</c:v>
+                  <c:v>1.57996</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.1911764709999999</c:v>
+                  <c:v>1.57996</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.1816470589999999</c:v>
+                  <c:v>1.57996</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.1721176470000001</c:v>
+                  <c:v>1.57996</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1.1625882349999999</c:v>
+                  <c:v>1.57996</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1.1530588239999999</c:v>
+                  <c:v>1.57996</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1.1435294120000001</c:v>
+                  <c:v>1.57996</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1.1435294120000001</c:v>
+                  <c:v>1.57996</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1.1435294120000001</c:v>
+                  <c:v>1.57996</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1.1435294120000001</c:v>
+                  <c:v>1.57996</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1.1435294120000001</c:v>
+                  <c:v>1.57996</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>1.1435294120000001</c:v>
+                  <c:v>1.57996</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>1.1435294120000001</c:v>
+                  <c:v>1.57996</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>1.1435294120000001</c:v>
+                  <c:v>1.57996</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>1.1435294120000001</c:v>
+                  <c:v>1.57996</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>1.1435294120000001</c:v>
+                  <c:v>1.57996</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>1.1435294120000001</c:v>
+                  <c:v>1.57996</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>1.1435294120000001</c:v>
+                  <c:v>1.57996</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>1.1435294120000001</c:v>
+                  <c:v>1.57996</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>1.1435294120000001</c:v>
+                  <c:v>1.57996</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>1.1435294120000001</c:v>
+                  <c:v>1.57996</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>1.1435294120000001</c:v>
+                  <c:v>1.57996</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>1.1435294120000001</c:v>
+                  <c:v>1.57996</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>1.1435294120000001</c:v>
+                  <c:v>1.57996</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>1.1435294120000001</c:v>
+                  <c:v>1.57996</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>1.1435294120000001</c:v>
+                  <c:v>1.57996</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15894,139 +15897,139 @@
                   <c:v>2113.8328529999999</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2083.4794809999999</c:v>
+                  <c:v>2438.13</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2054.6821599999998</c:v>
+                  <c:v>2686.73</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2027.3242250000001</c:v>
+                  <c:v>1826.82</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2001.3003900000001</c:v>
+                  <c:v>2250.65</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1987.1506589999999</c:v>
+                  <c:v>1885.12</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1966.59313</c:v>
+                  <c:v>1923.63</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1962.9861980000001</c:v>
+                  <c:v>1853.31</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1619.458128</c:v>
+                  <c:v>1641.14</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1592.739726</c:v>
+                  <c:v>1839.32</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1495.242424</c:v>
+                  <c:v>1688.23</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1412.526316</c:v>
+                  <c:v>1670.89</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1379.8208959999999</c:v>
+                  <c:v>1615.33</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1361.666667</c:v>
+                  <c:v>1553.01</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1343.6470589999999</c:v>
+                  <c:v>1573.85</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1343.6470589999999</c:v>
+                  <c:v>1579.96</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1272.176471</c:v>
+                  <c:v>1579.96</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>1250.7352940000001</c:v>
+                  <c:v>1579.96</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>1229.294118</c:v>
+                  <c:v>1579.96</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>1215</c:v>
+                  <c:v>1579.96</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>1200.705882</c:v>
+                  <c:v>1579.96</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>1191.176471</c:v>
+                  <c:v>1579.96</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>1181.6470589999999</c:v>
+                  <c:v>1579.96</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>1172.117647</c:v>
+                  <c:v>1579.96</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>1162.5882349999999</c:v>
+                  <c:v>1579.96</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>1153.058824</c:v>
+                  <c:v>1579.96</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>1143.5294120000001</c:v>
+                  <c:v>1579.96</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>1143.5294120000001</c:v>
+                  <c:v>1579.96</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>1143.5294120000001</c:v>
+                  <c:v>1579.96</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>1143.5294120000001</c:v>
+                  <c:v>1579.96</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>1143.5294120000001</c:v>
+                  <c:v>1579.96</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>1143.5294120000001</c:v>
+                  <c:v>1579.96</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>1143.5294120000001</c:v>
+                  <c:v>1579.96</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>1143.5294120000001</c:v>
+                  <c:v>1579.96</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>1143.5294120000001</c:v>
+                  <c:v>1579.96</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>1143.5294120000001</c:v>
+                  <c:v>1579.96</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>1143.5294120000001</c:v>
+                  <c:v>1579.96</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>1143.5294120000001</c:v>
+                  <c:v>1579.96</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>1143.5294120000001</c:v>
+                  <c:v>1579.96</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>1143.5294120000001</c:v>
+                  <c:v>1579.96</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>1143.5294120000001</c:v>
+                  <c:v>1579.96</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>1143.5294120000001</c:v>
+                  <c:v>1579.96</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>1143.5294120000001</c:v>
+                  <c:v>1579.96</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>1143.5294120000001</c:v>
+                  <c:v>1579.96</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>1143.5294120000001</c:v>
+                  <c:v>1579.96</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>1143.5294120000001</c:v>
+                  <c:v>1579.96</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -21033,7 +21036,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent2"/>
+              <a:srgbClr val="1F77BE"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -21640,139 +21643,139 @@
                   <c:v>2113.8328529999999</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2083.4794809999999</c:v>
+                  <c:v>2438.13</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2054.6821599999998</c:v>
+                  <c:v>2686.73</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2027.3242250000001</c:v>
+                  <c:v>1826.82</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2001.3003900000001</c:v>
+                  <c:v>2250.65</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1987.1506589999999</c:v>
+                  <c:v>1885.12</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1966.59313</c:v>
+                  <c:v>1923.63</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1962.9861980000001</c:v>
+                  <c:v>1853.31</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1619.458128</c:v>
+                  <c:v>1641.14</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1592.739726</c:v>
+                  <c:v>1839.32</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1495.242424</c:v>
+                  <c:v>1688.23</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1412.526316</c:v>
+                  <c:v>1670.89</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1379.8208959999999</c:v>
+                  <c:v>1615.33</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1361.666667</c:v>
+                  <c:v>1553.01</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1343.6470589999999</c:v>
+                  <c:v>1573.85</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1343.6470589999999</c:v>
+                  <c:v>1579.96</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1272.176471</c:v>
+                  <c:v>1579.96</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>1250.7352940000001</c:v>
+                  <c:v>1579.96</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>1229.294118</c:v>
+                  <c:v>1579.96</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>1215</c:v>
+                  <c:v>1579.96</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>1200.705882</c:v>
+                  <c:v>1579.96</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>1191.176471</c:v>
+                  <c:v>1579.96</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>1181.6470589999999</c:v>
+                  <c:v>1579.96</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>1172.117647</c:v>
+                  <c:v>1579.96</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>1162.5882349999999</c:v>
+                  <c:v>1579.96</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>1153.058824</c:v>
+                  <c:v>1579.96</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>1143.5294120000001</c:v>
+                  <c:v>1579.96</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>1143.5294120000001</c:v>
+                  <c:v>1579.96</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>1143.5294120000001</c:v>
+                  <c:v>1579.96</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>1143.5294120000001</c:v>
+                  <c:v>1579.96</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>1143.5294120000001</c:v>
+                  <c:v>1579.96</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>1143.5294120000001</c:v>
+                  <c:v>1579.96</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>1143.5294120000001</c:v>
+                  <c:v>1579.96</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>1143.5294120000001</c:v>
+                  <c:v>1579.96</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>1143.5294120000001</c:v>
+                  <c:v>1579.96</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>1143.5294120000001</c:v>
+                  <c:v>1579.96</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>1143.5294120000001</c:v>
+                  <c:v>1579.96</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>1143.5294120000001</c:v>
+                  <c:v>1579.96</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>1143.5294120000001</c:v>
+                  <c:v>1579.96</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>1143.5294120000001</c:v>
+                  <c:v>1579.96</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>1143.5294120000001</c:v>
+                  <c:v>1579.96</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>1143.5294120000001</c:v>
+                  <c:v>1579.96</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>1143.5294120000001</c:v>
+                  <c:v>1579.96</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>1143.5294120000001</c:v>
+                  <c:v>1579.96</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>1143.5294120000001</c:v>
+                  <c:v>1579.96</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>1143.5294120000001</c:v>
+                  <c:v>1579.96</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -22182,7 +22185,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent5"/>
+              <a:srgbClr val="D62728"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -22546,6 +22549,775 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000004-DBE5-436A-91E1-726844B48FC9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'mass per m2'!$G$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Encapsulant</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="8C564B"/>
+            </a:solidFill>
+            <a:ln w="25400">
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:cat>
+            <c:numRef>
+              <c:f>'mass per m2'!$A$18:$A$73</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="56"/>
+                <c:pt idx="0">
+                  <c:v>1995</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1996</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1997</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1998</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2001</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2002</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2003</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2004</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2005</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2006</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2007</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2009</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2011</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2025</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2026</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>2027</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>2028</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>2029</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>2030</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>2031</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>2032</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>2033</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>2034</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>2035</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>2036</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>2037</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>2038</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>2039</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>2040</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>2041</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>2042</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>2043</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>2044</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>2045</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>2046</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>2047</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>2048</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>2049</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>2050</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'mass per m2'!$G$18:$G$73</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="56"/>
+                <c:pt idx="0">
+                  <c:v>846</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>846</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>846</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>846</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>846</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>846</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>846</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>846</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>846</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>846</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>846</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>846</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>846</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>846</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>846</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>846</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>846</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>846</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>846</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>848.09</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>850.28</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>852.81</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>847.99</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>848.95500000000004</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>851.31</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>849.44500000000005</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>849.14499999999998</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>839.24437499999999</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>829.23500000000001</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>801.36775</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>773.91700000000003</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>752.61400000000003</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>731.46833330000004</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>710.48</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>710.35866669999996</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>710.23733330000005</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>710.11599999999999</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>710.11599999999999</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>710.11599999999999</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>710.11599999999999</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>710.11599999999999</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>710.11599999999999</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>710.11599999999999</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>710.11599999999999</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>710.11599999999999</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>710.11599999999999</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>710.11599999999999</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>710.11599999999999</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>710.11599999999999</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>710.11599999999999</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>710.11599999999999</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>710.11599999999999</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>710.11599999999999</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>710.11599999999999</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>710.11599999999999</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>710.11599999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-F1C7-4714-AAFC-6A8CDD513AC5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'mass per m2'!$H$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Backsheets</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="95000"/>
+                <a:lumOff val="5000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln w="25400">
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:cat>
+            <c:numRef>
+              <c:f>'mass per m2'!$A$18:$A$73</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="56"/>
+                <c:pt idx="0">
+                  <c:v>1995</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1996</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1997</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1998</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2001</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2002</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2003</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2004</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2005</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2006</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2007</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2009</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2011</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2025</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2026</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>2027</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>2028</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>2029</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>2030</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>2031</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>2032</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>2033</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>2034</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>2035</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>2036</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>2037</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>2038</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>2039</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>2040</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>2041</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>2042</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>2043</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>2044</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>2045</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>2046</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>2047</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>2048</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>2049</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>2050</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'mass per m2'!$H$18:$H$73</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="56"/>
+                <c:pt idx="0">
+                  <c:v>532</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>532</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>532</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>532</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>532</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>532</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>532</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>532</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>532</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>532</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>532</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>532</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>532</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>532</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>532</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>532</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>532</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>532</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>532</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>532</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>532</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>532</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>532</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>532</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>532</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>532</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>520</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>510</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>490</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>480</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>470</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>460</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>450</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-F1C7-4714-AAFC-6A8CDD513AC5}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -22589,12 +23361,9 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:sysClr val="windowText" lastClr="000000"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -22649,12 +23418,9 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:sysClr val="windowText" lastClr="000000"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -22677,7 +23443,7 @@
       </c:spPr>
     </c:plotArea>
     <c:legend>
-      <c:legendPos val="b"/>
+      <c:legendPos val="r"/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -22691,12 +23457,9 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
+                <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
@@ -22738,7 +23501,11 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr/>
+        <a:defRPr sz="1600">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:defRPr>
       </a:pPr>
       <a:endParaRPr lang="en-US"/>
     </a:p>
@@ -23509,139 +24276,139 @@
                   <c:v>85.981485768230385</c:v>
                 </c:pt>
                 <c:pt idx="26" formatCode="0.00">
-                  <c:v>84.193545779284662</c:v>
+                  <c:v>86.689131917869148</c:v>
                 </c:pt>
                 <c:pt idx="27" formatCode="0.00">
-                  <c:v>83.096907447896299</c:v>
+                  <c:v>87.506543541945049</c:v>
                 </c:pt>
                 <c:pt idx="28" formatCode="0.00">
-                  <c:v>82.028770610005424</c:v>
+                  <c:v>80.641731390600967</c:v>
                 </c:pt>
                 <c:pt idx="29" formatCode="0.00">
-                  <c:v>81.147459980008009</c:v>
+                  <c:v>82.857937487369213</c:v>
                 </c:pt>
                 <c:pt idx="30" formatCode="0.00">
-                  <c:v>80.286218198459665</c:v>
+                  <c:v>79.592132082813407</c:v>
                 </c:pt>
                 <c:pt idx="31" formatCode="0.00">
-                  <c:v>78.009681965637796</c:v>
+                  <c:v>77.725157925902707</c:v>
                 </c:pt>
                 <c:pt idx="32" formatCode="0.00">
-                  <c:v>76.745457632786014</c:v>
+                  <c:v>76.033274528889905</c:v>
                 </c:pt>
                 <c:pt idx="33" formatCode="0.00">
-                  <c:v>71.986293263839585</c:v>
+                  <c:v>72.12180496383958</c:v>
                 </c:pt>
                 <c:pt idx="34" formatCode="0.00">
-                  <c:v>71.059923965287609</c:v>
+                  <c:v>72.57268638246552</c:v>
                 </c:pt>
                 <c:pt idx="35" formatCode="0.00">
-                  <c:v>67.041474332923386</c:v>
+                  <c:v>68.176695368217509</c:v>
                 </c:pt>
                 <c:pt idx="36" formatCode="0.00">
-                  <c:v>64.924893674336843</c:v>
+                  <c:v>66.401257582908272</c:v>
                 </c:pt>
                 <c:pt idx="37" formatCode="0.00">
-                  <c:v>64.399375382792428</c:v>
+                  <c:v>65.729935292396945</c:v>
                 </c:pt>
                 <c:pt idx="38" formatCode="0.00">
-                  <c:v>62.058672393083782</c:v>
+                  <c:v>63.098581811562049</c:v>
                 </c:pt>
                 <c:pt idx="39" formatCode="0.00">
-                  <c:v>60.372298122585782</c:v>
+                  <c:v>61.571271773627451</c:v>
                 </c:pt>
                 <c:pt idx="40" formatCode="0.00">
-                  <c:v>58.764820998651295</c:v>
+                  <c:v>59.931649333294459</c:v>
                 </c:pt>
                 <c:pt idx="41" formatCode="0.00">
-                  <c:v>58.010418686832558</c:v>
+                  <c:v>59.483429074533177</c:v>
                 </c:pt>
                 <c:pt idx="42" formatCode="0.00">
-                  <c:v>58.368388715061307</c:v>
+                  <c:v>59.909494924740606</c:v>
                 </c:pt>
                 <c:pt idx="43" formatCode="0.00">
-                  <c:v>57.802485787500444</c:v>
+                  <c:v>59.415995537936766</c:v>
                 </c:pt>
                 <c:pt idx="44" formatCode="0.00">
-                  <c:v>58.60119343906829</c:v>
+                  <c:v>60.257064030023031</c:v>
                 </c:pt>
                 <c:pt idx="45" formatCode="0.00">
-                  <c:v>58.966709209597525</c:v>
+                  <c:v>60.667130474000743</c:v>
                 </c:pt>
                 <c:pt idx="46" formatCode="0.00">
-                  <c:v>58.875608458111593</c:v>
+                  <c:v>60.600924657022787</c:v>
                 </c:pt>
                 <c:pt idx="47" formatCode="0.00">
-                  <c:v>58.859910652644167</c:v>
+                  <c:v>60.611557350656604</c:v>
                 </c:pt>
                 <c:pt idx="48" formatCode="0.00">
-                  <c:v>58.345323657063062</c:v>
+                  <c:v>60.124385704277479</c:v>
                 </c:pt>
                 <c:pt idx="49" formatCode="0.00">
-                  <c:v>58.016297896041003</c:v>
+                  <c:v>59.823616005950427</c:v>
                 </c:pt>
                 <c:pt idx="50" formatCode="0.00">
-                  <c:v>57.69452681207899</c:v>
+                  <c:v>59.530765639884748</c:v>
                 </c:pt>
                 <c:pt idx="51" formatCode="0.00">
-                  <c:v>57.421323369126519</c:v>
+                  <c:v>59.287016937826891</c:v>
                 </c:pt>
                 <c:pt idx="52" formatCode="0.00">
-                  <c:v>57.218260275592819</c:v>
+                  <c:v>59.073337928897217</c:v>
                 </c:pt>
                 <c:pt idx="53" formatCode="0.00">
-                  <c:v>56.868236204654721</c:v>
+                  <c:v>58.713484979585679</c:v>
                 </c:pt>
                 <c:pt idx="54" formatCode="0.00">
-                  <c:v>56.539703918164967</c:v>
+                  <c:v>58.375805538977438</c:v>
                 </c:pt>
                 <c:pt idx="55" formatCode="0.00">
-                  <c:v>56.229974831828194</c:v>
+                  <c:v>58.057525328194117</c:v>
                 </c:pt>
                 <c:pt idx="56" formatCode="0.00">
-                  <c:v>55.983039395046426</c:v>
+                  <c:v>57.802564154580516</c:v>
                 </c:pt>
                 <c:pt idx="57" formatCode="0.00">
-                  <c:v>55.750456624231717</c:v>
+                  <c:v>57.562422128057094</c:v>
                 </c:pt>
                 <c:pt idx="58" formatCode="0.00">
-                  <c:v>55.530699784183319</c:v>
+                  <c:v>57.335522892457007</c:v>
                 </c:pt>
                 <c:pt idx="59" formatCode="0.00">
-                  <c:v>55.322471082941924</c:v>
+                  <c:v>57.120526475820938</c:v>
                 </c:pt>
                 <c:pt idx="60" formatCode="0.00">
-                  <c:v>55.124658190670168</c:v>
+                  <c:v>56.916284396082183</c:v>
                 </c:pt>
                 <c:pt idx="61" formatCode="0.00">
-                  <c:v>54.936300854763807</c:v>
+                  <c:v>56.7218051911236</c:v>
                 </c:pt>
                 <c:pt idx="62" formatCode="0.00">
-                  <c:v>54.756564300621193</c:v>
+                  <c:v>56.536226955036064</c:v>
                 </c:pt>
                 <c:pt idx="63" formatCode="0.00">
-                  <c:v>54.584718555539922</c:v>
+                  <c:v>56.358795990013633</c:v>
                 </c:pt>
                 <c:pt idx="64" formatCode="0.00">
-                  <c:v>54.420121657414846</c:v>
+                  <c:v>56.188849469311485</c:v>
                 </c:pt>
                 <c:pt idx="65" formatCode="0.00">
-                  <c:v>54.262206051291081</c:v>
+                  <c:v>56.025801391668416</c:v>
                 </c:pt>
                 <c:pt idx="66" formatCode="0.00">
-                  <c:v>54.110467679537329</c:v>
+                  <c:v>55.869131316896024</c:v>
                 </c:pt>
                 <c:pt idx="67" formatCode="0.00">
-                  <c:v>53.964456845739697</c:v>
+                  <c:v>55.718374932836639</c:v>
                 </c:pt>
                 <c:pt idx="68" formatCode="0.00">
-                  <c:v>53.823770683842042</c:v>
+                  <c:v>55.573116279740525</c:v>
                 </c:pt>
                 <c:pt idx="69" formatCode="0.00">
-                  <c:v>53.688046957216272</c:v>
+                  <c:v>55.432981347797572</c:v>
                 </c:pt>
                 <c:pt idx="70" formatCode="0.00">
-                  <c:v>53.556958785631082</c:v>
+                  <c:v>55.297632632725303</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -38087,16 +38854,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>31</xdr:col>
-      <xdr:colOff>146467</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>51138</xdr:rowOff>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>64576</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>140188</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>38</xdr:col>
       <xdr:colOff>341547</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>82888</xdr:rowOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>86911</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -38831,13 +39598,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="B1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
+      <c r="B1" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
       <c r="I1" s="2" t="s">
         <v>25</v>
       </c>
@@ -38855,23 +39622,23 @@
       <c r="S1" s="2"/>
       <c r="T1" s="2"/>
       <c r="U1" s="5"/>
-      <c r="V1" s="8" t="s">
+      <c r="V1" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="W1" s="8"/>
-      <c r="X1" s="8"/>
-      <c r="Y1" s="8"/>
-      <c r="Z1" s="8"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
+      <c r="Y1" s="9"/>
+      <c r="Z1" s="9"/>
       <c r="AA1" s="2"/>
       <c r="AB1" s="2"/>
       <c r="AC1" s="2"/>
-      <c r="AD1" s="8" t="s">
+      <c r="AD1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="AE1" s="8"/>
-      <c r="AF1" s="8"/>
-      <c r="AG1" s="8"/>
-      <c r="AH1" s="8"/>
+      <c r="AE1" s="9"/>
+      <c r="AF1" s="9"/>
+      <c r="AG1" s="9"/>
+      <c r="AH1" s="9"/>
       <c r="AI1" s="1" t="s">
         <v>18</v>
       </c>
@@ -39183,7 +39950,7 @@
         <v>6.3082624904031128</v>
       </c>
       <c r="AB18" s="3">
-        <f t="shared" ref="AA18:AB18" si="4">H18/$I18*100</f>
+        <f t="shared" ref="AB18" si="4">H18/$I18*100</f>
         <v>3.9668979254071584</v>
       </c>
       <c r="AD18">
@@ -39268,7 +40035,7 @@
         <v>4.036899881435034E-2</v>
       </c>
       <c r="Z19" s="3">
-        <f t="shared" ref="Z18:Z49" si="8">F19/$I19*100</f>
+        <f t="shared" ref="Z19:Z49" si="8">F19/$I19*100</f>
         <v>0.6350565289672454</v>
       </c>
       <c r="AA19" s="3">
@@ -40165,7 +40932,7 @@
         <v>465.8</v>
       </c>
       <c r="D29">
-        <v>2083.4794809999999</v>
+        <v>2438.13</v>
       </c>
       <c r="E29">
         <v>5.3760000000000003</v>
@@ -40181,7 +40948,7 @@
       </c>
       <c r="I29" s="3">
         <f t="shared" si="5"/>
-        <v>11964.838338142858</v>
+        <v>12319.488857142858</v>
       </c>
       <c r="J29" s="3">
         <f t="shared" si="6"/>
@@ -40190,7 +40957,7 @@
       <c r="K29" s="7"/>
       <c r="L29" s="3">
         <f t="shared" si="7"/>
-        <v>84.193545779284662</v>
+        <v>86.689131917869148</v>
       </c>
       <c r="M29" s="3">
         <v>96.321512409999997</v>
@@ -40211,31 +40978,31 @@
       <c r="U29" s="7"/>
       <c r="V29" s="3">
         <f t="shared" si="0"/>
-        <v>66.862583295393975</v>
+        <v>64.937759129199492</v>
       </c>
       <c r="W29" s="3">
         <f t="shared" si="1"/>
-        <v>3.8930739123743141</v>
+        <v>3.7810010252976403</v>
       </c>
       <c r="X29" s="3">
         <f t="shared" si="2"/>
-        <v>17.413352542825837</v>
+        <v>19.790837333209392</v>
       </c>
       <c r="Y29" s="3">
         <f t="shared" si="3"/>
-        <v>4.4931655974504749E-2</v>
+        <v>4.3638174134822058E-2</v>
       </c>
       <c r="Z29" s="3">
         <f t="shared" si="8"/>
-        <v>0.26897862079975599</v>
+        <v>0.26123532815403649</v>
       </c>
       <c r="AA29" s="3">
         <f t="shared" si="9"/>
-        <v>7.0707181834879131</v>
+        <v>6.8671680279128458</v>
       </c>
       <c r="AB29" s="3">
         <f t="shared" si="10"/>
-        <v>4.4463617891436993</v>
+        <v>4.3183609820917654</v>
       </c>
       <c r="AD29">
         <v>14.211111109999999</v>
@@ -40264,7 +41031,7 @@
         <v>442.51</v>
       </c>
       <c r="D30">
-        <v>2054.6821599999998</v>
+        <v>2686.73</v>
       </c>
       <c r="E30">
         <v>5.3760000000000003</v>
@@ -40280,7 +41047,7 @@
       </c>
       <c r="I30" s="3">
         <f t="shared" si="5"/>
-        <v>11910.556731428573</v>
+        <v>12542.604571428572</v>
       </c>
       <c r="J30" s="3">
         <f t="shared" si="6"/>
@@ -40289,7 +41056,7 @@
       <c r="K30" s="7"/>
       <c r="L30" s="3">
         <f t="shared" si="7"/>
-        <v>83.096907447896299</v>
+        <v>87.506543541945049</v>
       </c>
       <c r="M30" s="3">
         <v>94.276032310000005</v>
@@ -40312,31 +41079,31 @@
       <c r="U30" s="7"/>
       <c r="V30" s="3">
         <f t="shared" si="0"/>
-        <v>67.167305277093163</v>
+        <v>63.782605554061725</v>
       </c>
       <c r="W30" s="3">
         <f t="shared" si="1"/>
-        <v>3.7152755322708129</v>
+        <v>3.5280550979659822</v>
       </c>
       <c r="X30" s="3">
         <f t="shared" si="2"/>
-        <v>17.25093298601465</v>
+        <v>21.420829977533032</v>
       </c>
       <c r="Y30" s="3">
         <f t="shared" si="3"/>
-        <v>4.5136429146206615E-2</v>
+        <v>4.2861910932329481E-2</v>
       </c>
       <c r="Z30" s="3">
         <f t="shared" si="8"/>
-        <v>0.25178144149584619</v>
+        <v>0.23909365281979686</v>
       </c>
       <c r="AA30" s="3">
         <f t="shared" si="9"/>
-        <v>7.1029425330526035</v>
+        <v>6.7450105373420275</v>
       </c>
       <c r="AB30" s="3">
         <f t="shared" si="10"/>
-        <v>4.4666258009266961</v>
+        <v>4.2415432693451045</v>
       </c>
       <c r="AD30">
         <v>14.33333333</v>
@@ -40365,7 +41132,7 @@
         <v>419.22</v>
       </c>
       <c r="D31">
-        <v>2027.3242250000001</v>
+        <v>1826.82</v>
       </c>
       <c r="E31">
         <v>5.3760000000000003</v>
@@ -40381,7 +41148,7 @@
       </c>
       <c r="I31" s="3">
         <f t="shared" si="5"/>
-        <v>11857.714510714286</v>
+        <v>11657.210285714285</v>
       </c>
       <c r="J31" s="3">
         <f t="shared" si="6"/>
@@ -40390,7 +41157,7 @@
       <c r="K31" s="7"/>
       <c r="L31" s="3">
         <f t="shared" si="7"/>
-        <v>82.028770610005424</v>
+        <v>80.641731390600967</v>
       </c>
       <c r="M31" s="3">
         <v>92.273989950000001</v>
@@ -40413,31 +41180,31 @@
       <c r="U31" s="7"/>
       <c r="V31" s="3">
         <f t="shared" si="0"/>
-        <v>67.466626834129229</v>
+        <v>68.627054019981642</v>
       </c>
       <c r="W31" s="3">
         <f t="shared" si="1"/>
-        <v>3.5354199126754575</v>
+        <v>3.5962291982820886</v>
       </c>
       <c r="X31" s="3">
         <f t="shared" si="2"/>
-        <v>17.097090869983155</v>
+        <v>15.67115935309786</v>
       </c>
       <c r="Y31" s="3">
         <f t="shared" si="3"/>
-        <v>4.5337573232534845E-2</v>
+        <v>4.6117380301427674E-2</v>
       </c>
       <c r="Z31" s="3">
         <f t="shared" si="8"/>
-        <v>0.23439833780086028</v>
+        <v>0.2384299933951361</v>
       </c>
       <c r="AA31" s="3">
         <f t="shared" si="9"/>
-        <v>7.1345957877091664</v>
+        <v>7.2573109626130599</v>
       </c>
       <c r="AB31" s="3">
         <f t="shared" si="10"/>
-        <v>4.486530684469594</v>
+        <v>4.5636990923287799</v>
       </c>
       <c r="AD31">
         <v>14.455555560000001</v>
@@ -40466,7 +41233,7 @@
         <v>419.22</v>
       </c>
       <c r="D32">
-        <v>2001.3003900000001</v>
+        <v>2250.65</v>
       </c>
       <c r="E32">
         <v>5.3760000000000003</v>
@@ -40482,7 +41249,7 @@
       </c>
       <c r="I32" s="3">
         <f t="shared" si="5"/>
-        <v>11829.49639</v>
+        <v>12078.846</v>
       </c>
       <c r="J32" s="3">
         <f t="shared" si="6"/>
@@ -40491,7 +41258,7 @@
       <c r="K32" s="7"/>
       <c r="L32" s="3">
         <f t="shared" si="7"/>
-        <v>81.147459980008009</v>
+        <v>82.857937487369213</v>
       </c>
       <c r="M32" s="3">
         <v>90.314462890000001</v>
@@ -40514,31 +41281,31 @@
       <c r="U32" s="7"/>
       <c r="V32" s="3">
         <f t="shared" si="0"/>
-        <v>67.627561954055423</v>
+        <v>66.231492644247638</v>
       </c>
       <c r="W32" s="3">
         <f t="shared" si="1"/>
-        <v>3.5438533152973899</v>
+        <v>3.470695793290187</v>
       </c>
       <c r="X32" s="3">
         <f t="shared" si="2"/>
-        <v>16.917883264175035</v>
+        <v>18.632988614971996</v>
       </c>
       <c r="Y32" s="3">
         <f t="shared" si="3"/>
-        <v>4.5445721633125248E-2</v>
+        <v>4.4507563056934416E-2</v>
       </c>
       <c r="Z32" s="3">
         <f t="shared" si="8"/>
-        <v>0.21640819825297736</v>
+        <v>0.21194077646159246</v>
       </c>
       <c r="AA32" s="3">
         <f t="shared" si="9"/>
-        <v>7.151614676641362</v>
+        <v>7.0039803471291879</v>
       </c>
       <c r="AB32" s="3">
         <f t="shared" si="10"/>
-        <v>4.4972328699446855</v>
+        <v>4.4043942608424684</v>
       </c>
       <c r="AD32">
         <v>14.57777778</v>
@@ -40570,7 +41337,7 @@
         <v>419.22</v>
       </c>
       <c r="D33">
-        <v>1987.1506589999999</v>
+        <v>1885.12</v>
       </c>
       <c r="E33">
         <v>5.3760000000000003</v>
@@ -40586,7 +41353,7 @@
       </c>
       <c r="I33" s="3">
         <f t="shared" si="5"/>
-        <v>11802.07407517357</v>
+        <v>11700.04341617357</v>
       </c>
       <c r="J33" s="3">
         <f t="shared" si="6"/>
@@ -40595,7 +41362,7 @@
       <c r="K33" s="7"/>
       <c r="L33" s="3">
         <f t="shared" si="7"/>
-        <v>80.286218198459665</v>
+        <v>79.592132082813407</v>
       </c>
       <c r="M33" s="3">
         <v>88.396548280000005</v>
@@ -40620,31 +41387,31 @@
       <c r="U33" s="7"/>
       <c r="V33" s="3">
         <f t="shared" si="0"/>
-        <v>67.784695715717618</v>
+        <v>68.3758146481849</v>
       </c>
       <c r="W33" s="3">
         <f t="shared" si="1"/>
-        <v>3.5520875172428932</v>
+        <v>3.5830636271015091</v>
       </c>
       <c r="X33" s="3">
         <f t="shared" si="2"/>
-        <v>16.837300345200347</v>
+        <v>16.112076963698289</v>
       </c>
       <c r="Y33" s="3">
         <f t="shared" si="3"/>
-        <v>4.5551315520962248E-2</v>
+        <v>4.5948547443580248E-2</v>
       </c>
       <c r="Z33" s="3">
         <f t="shared" si="8"/>
-        <v>0.10445126928580732</v>
+        <v>0.10536214042188238</v>
       </c>
       <c r="AA33" s="3">
         <f t="shared" si="9"/>
-        <v>7.168231571937139</v>
+        <v>7.2307423990455515</v>
       </c>
       <c r="AB33" s="3">
         <f t="shared" si="10"/>
-        <v>4.5076822650952222</v>
+        <v>4.5469916741042953</v>
       </c>
       <c r="AD33">
         <v>14.7</v>
@@ -40679,7 +41446,7 @@
         <v>419.22</v>
       </c>
       <c r="D34">
-        <v>1966.59313</v>
+        <v>1923.63</v>
       </c>
       <c r="E34">
         <v>5.3760000000000003</v>
@@ -40695,7 +41462,7 @@
       </c>
       <c r="I34" s="3">
         <f t="shared" si="5"/>
-        <v>11779.461976811308</v>
+        <v>11736.498846811308</v>
       </c>
       <c r="J34" s="3">
         <f t="shared" si="6"/>
@@ -40704,7 +41471,7 @@
       <c r="K34" s="7"/>
       <c r="L34" s="3">
         <f t="shared" si="7"/>
-        <v>78.009681965637796</v>
+        <v>77.725157925902707</v>
       </c>
       <c r="M34" s="3">
         <v>86.519362419999993</v>
@@ -40727,31 +41494,31 @@
       <c r="U34" s="7"/>
       <c r="V34" s="3">
         <f t="shared" si="0"/>
-        <v>67.914816616824751</v>
+        <v>68.163428501281899</v>
       </c>
       <c r="W34" s="3">
         <f t="shared" si="1"/>
-        <v>3.5589061777631597</v>
+        <v>3.5719340620384248</v>
       </c>
       <c r="X34" s="3">
         <f t="shared" si="2"/>
-        <v>16.695101472982177</v>
+        <v>16.390151995990113</v>
       </c>
       <c r="Y34" s="3">
         <f t="shared" si="3"/>
-        <v>4.5638756766506243E-2</v>
+        <v>4.5805823952861438E-2</v>
       </c>
       <c r="Z34" s="3">
         <f t="shared" si="8"/>
-        <v>8.7209813415342022E-2</v>
+        <v>8.7529057390904386E-2</v>
       </c>
       <c r="AA34" s="3">
         <f t="shared" si="9"/>
-        <v>7.1819918572292183</v>
+        <v>7.2082825640105614</v>
       </c>
       <c r="AB34" s="3">
         <f t="shared" si="10"/>
-        <v>4.5163353050188464</v>
+        <v>4.5328679953352466</v>
       </c>
       <c r="AD34">
         <v>15.1</v>
@@ -40783,7 +41550,7 @@
         <v>419.22</v>
       </c>
       <c r="D35">
-        <v>1962.9861980000001</v>
+        <v>1853.31</v>
       </c>
       <c r="E35">
         <v>5.3760000000000003</v>
@@ -40799,7 +41566,7 @@
       </c>
       <c r="I35" s="3">
         <f t="shared" si="5"/>
-        <v>11818.800475449047</v>
+        <v>11709.124277449046</v>
       </c>
       <c r="J35" s="3">
         <f t="shared" si="6"/>
@@ -40808,7 +41575,7 @@
       <c r="K35" s="7"/>
       <c r="L35" s="3">
         <f t="shared" si="7"/>
-        <v>76.745457632786014</v>
+        <v>76.033274528889905</v>
       </c>
       <c r="M35" s="3">
         <v>84.682040420000007</v>
@@ -40835,31 +41602,31 @@
       <c r="U35" s="7"/>
       <c r="V35" s="3">
         <f t="shared" si="0"/>
-        <v>68.069513625445438</v>
+        <v>68.707102336372898</v>
       </c>
       <c r="W35" s="3">
         <f t="shared" si="1"/>
-        <v>3.5470604725990356</v>
+        <v>3.5802848280241455</v>
       </c>
       <c r="X35" s="3">
         <f t="shared" si="2"/>
-        <v>16.609013766478849</v>
+        <v>15.827912968430486</v>
       </c>
       <c r="Y35" s="3">
         <f t="shared" si="3"/>
-        <v>4.5486849627146643E-2</v>
+        <v>4.5912912636462494E-2</v>
       </c>
       <c r="Z35" s="3">
         <f t="shared" si="8"/>
-        <v>6.953563067688924E-2</v>
+        <v>7.0186952109428935E-2</v>
       </c>
       <c r="AA35" s="3">
         <f t="shared" si="9"/>
-        <v>7.1580868274862457</v>
+        <v>7.2251346894433164</v>
       </c>
       <c r="AB35" s="3">
         <f t="shared" si="10"/>
-        <v>4.501302827686386</v>
+        <v>4.5434653129832672</v>
       </c>
       <c r="AD35">
         <v>15.4</v>
@@ -40891,7 +41658,7 @@
         <v>419.22</v>
       </c>
       <c r="D36">
-        <v>1619.458128</v>
+        <v>1641.14</v>
       </c>
       <c r="E36">
         <v>5.3760000000000003</v>
@@ -40907,7 +41674,7 @@
       </c>
       <c r="I36" s="3">
         <f t="shared" si="5"/>
-        <v>11517.806922214333</v>
+        <v>11539.488794214332</v>
       </c>
       <c r="J36" s="3">
         <f t="shared" si="6"/>
@@ -40916,7 +41683,7 @@
       <c r="K36" s="7"/>
       <c r="L36" s="3">
         <f t="shared" si="7"/>
-        <v>71.986293263839585</v>
+        <v>72.12180496383958</v>
       </c>
       <c r="M36" s="3">
         <v>82.883735720000004</v>
@@ -40941,31 +41708,31 @@
       <c r="U36" s="7"/>
       <c r="V36" s="3">
         <f t="shared" si="0"/>
-        <v>70.239065949237784</v>
+        <v>70.107091780843561</v>
       </c>
       <c r="W36" s="3">
         <f t="shared" si="1"/>
-        <v>3.6397554050975853</v>
+        <v>3.6329165656817355</v>
       </c>
       <c r="X36" s="3">
         <f t="shared" si="2"/>
-        <v>14.060472961016213</v>
+        <v>14.221947169989321</v>
       </c>
       <c r="Y36" s="3">
         <f t="shared" si="3"/>
-        <v>4.6675552353906344E-2</v>
+        <v>4.6587852337925222E-2</v>
       </c>
       <c r="Z36" s="3">
         <f t="shared" si="8"/>
-        <v>4.9946958246341898E-2</v>
+        <v>4.9853111493266537E-2</v>
       </c>
       <c r="AA36" s="3">
         <f t="shared" si="9"/>
-        <v>7.3451483056928515</v>
+        <v>7.3313472987136779</v>
       </c>
       <c r="AB36" s="3">
         <f t="shared" si="10"/>
-        <v>4.6189348683553151</v>
+        <v>4.6102562209405162</v>
       </c>
       <c r="AD36">
         <v>16</v>
@@ -40997,7 +41764,7 @@
         <v>419.22</v>
       </c>
       <c r="D37">
-        <v>1592.739726</v>
+        <v>1839.32</v>
       </c>
       <c r="E37">
         <v>5.3760000000000003</v>
@@ -41013,7 +41780,7 @@
       </c>
       <c r="I37" s="3">
         <f t="shared" si="5"/>
-        <v>11582.76760634188</v>
+        <v>11829.34788034188</v>
       </c>
       <c r="J37" s="3">
         <f t="shared" si="6"/>
@@ -41022,7 +41789,7 @@
       <c r="K37" s="7"/>
       <c r="L37" s="3">
         <f t="shared" si="7"/>
-        <v>71.059923965287609</v>
+        <v>72.57268638246552</v>
       </c>
       <c r="M37" s="3">
         <v>81.123619750000003</v>
@@ -41047,31 +41814,31 @@
       <c r="U37" s="7"/>
       <c r="V37" s="3">
         <f t="shared" si="0"/>
-        <v>70.622154203639781</v>
+        <v>69.150050220381118</v>
       </c>
       <c r="W37" s="3">
         <f t="shared" si="1"/>
-        <v>3.6193422353606204</v>
+        <v>3.5438978060376742</v>
       </c>
       <c r="X37" s="3">
         <f t="shared" si="2"/>
-        <v>13.750942608292785</v>
+        <v>15.548786108967164</v>
       </c>
       <c r="Y37" s="3">
         <f t="shared" si="3"/>
-        <v>4.6413777628211188E-2</v>
+        <v>4.544629217417713E-2</v>
       </c>
       <c r="Z37" s="3">
         <f t="shared" si="8"/>
-        <v>4.6119205041768384E-2</v>
+        <v>4.5157859891478261E-2</v>
       </c>
       <c r="AA37" s="3">
         <f t="shared" si="9"/>
-        <v>7.3219978922450943</v>
+        <v>7.1693723828121056</v>
       </c>
       <c r="AB37" s="3">
         <f t="shared" si="10"/>
-        <v>4.5930300777917319</v>
+        <v>4.4972893297362786</v>
       </c>
       <c r="AD37">
         <v>16.3</v>
@@ -41103,7 +41870,7 @@
         <v>419.22</v>
       </c>
       <c r="D38">
-        <v>1495.242424</v>
+        <v>1688.23</v>
       </c>
       <c r="E38">
         <v>5.7881600000000004</v>
@@ -41119,7 +41886,7 @@
       </c>
       <c r="I38" s="3">
         <f t="shared" si="5"/>
-        <v>11397.050636596976</v>
+        <v>11590.038212596975</v>
       </c>
       <c r="J38" s="3">
         <f t="shared" si="6"/>
@@ -41128,7 +41895,7 @@
       <c r="K38" s="7"/>
       <c r="L38" s="3">
         <f t="shared" si="7"/>
-        <v>67.041474332923386</v>
+        <v>68.176695368217509</v>
       </c>
       <c r="M38" s="3">
         <v>79.40088154</v>
@@ -41155,31 +41922,31 @@
       <c r="U38" s="7"/>
       <c r="V38" s="3">
         <f t="shared" si="0"/>
-        <v>70.983276796386846</v>
+        <v>69.801322925813508</v>
       </c>
       <c r="W38" s="3">
         <f t="shared" si="1"/>
-        <v>3.6783200616293317</v>
+        <v>3.6170717672385098</v>
       </c>
       <c r="X38" s="3">
         <f t="shared" si="2"/>
-        <v>13.119555854201781</v>
+        <v>14.566215995432158</v>
       </c>
       <c r="Y38" s="3">
         <f t="shared" si="3"/>
-        <v>5.0786472610849759E-2</v>
+        <v>4.9940818950096021E-2</v>
       </c>
       <c r="Z38" s="3">
         <f t="shared" si="8"/>
-        <v>3.9659844823900024E-2</v>
+        <v>3.899946241819046E-2</v>
       </c>
       <c r="AA38" s="3">
         <f t="shared" si="9"/>
-        <v>7.4605266494971332</v>
+        <v>7.3363002295872342</v>
       </c>
       <c r="AB38" s="3">
         <f t="shared" si="10"/>
-        <v>4.667874320850161</v>
+        <v>4.5901488005602964</v>
       </c>
       <c r="AD38">
         <v>17</v>
@@ -41214,7 +41981,7 @@
         <v>419.219999999999</v>
       </c>
       <c r="D39">
-        <v>1412.526316</v>
+        <v>1670.89</v>
       </c>
       <c r="E39">
         <v>6.2003199999999996</v>
@@ -41230,7 +41997,7 @@
       </c>
       <c r="I39" s="3">
         <f t="shared" si="5"/>
-        <v>11361.856393008948</v>
+        <v>11620.220077008948</v>
       </c>
       <c r="J39" s="3">
         <f t="shared" si="6"/>
@@ -41239,7 +42006,7 @@
       <c r="K39" s="7"/>
       <c r="L39" s="3">
         <f t="shared" si="7"/>
-        <v>64.924893674336843</v>
+        <v>66.401257582908272</v>
       </c>
       <c r="M39" s="3">
         <v>77.714727339999996</v>
@@ -41264,31 +42031,31 @@
       <c r="U39" s="7"/>
       <c r="V39" s="3">
         <f t="shared" si="0"/>
-        <v>71.599215115987022</v>
+        <v>70.007279948986607</v>
       </c>
       <c r="W39" s="3">
         <f t="shared" si="1"/>
-        <v>3.6897139472555636</v>
+        <v>3.6076769391781305</v>
       </c>
       <c r="X39" s="3">
         <f t="shared" si="2"/>
-        <v>12.432178925172298</v>
+        <v>14.379159679651165</v>
       </c>
       <c r="Y39" s="3">
         <f t="shared" si="3"/>
-        <v>5.4571363917388642E-2</v>
+        <v>5.3358025570166022E-2</v>
       </c>
       <c r="Z39" s="3">
         <f t="shared" si="8"/>
-        <v>3.608351370707015E-2</v>
+        <v>3.5281233761316942E-2</v>
       </c>
       <c r="AA39" s="3">
         <f t="shared" si="9"/>
-        <v>7.5059037053552409</v>
+        <v>7.3390176291696694</v>
       </c>
       <c r="AB39" s="3">
         <f t="shared" si="10"/>
-        <v>4.6823334286054203</v>
+        <v>4.578226543682959</v>
       </c>
       <c r="AD39">
         <v>17.5</v>
@@ -41320,7 +42087,7 @@
         <v>419.219999999999</v>
       </c>
       <c r="D40">
-        <v>1379.8208959999999</v>
+        <v>1615.33</v>
       </c>
       <c r="E40">
         <v>7.2038399999999996</v>
@@ -41336,7 +42103,7 @@
       </c>
       <c r="I40" s="3">
         <f t="shared" si="5"/>
-        <v>11398.689442754259</v>
+        <v>11634.19854675426</v>
       </c>
       <c r="J40" s="3">
         <f t="shared" si="6"/>
@@ -41345,7 +42112,7 @@
       <c r="K40" s="7"/>
       <c r="L40" s="3">
         <f t="shared" si="7"/>
-        <v>64.399375382792428</v>
+        <v>65.729935292396945</v>
       </c>
       <c r="M40" s="3">
         <v>76.064380240000006</v>
@@ -41370,31 +42137,31 @@
       <c r="U40" s="7"/>
       <c r="V40" s="3">
         <f t="shared" si="0"/>
-        <v>72.011568007213071</v>
+        <v>70.55385007409896</v>
       </c>
       <c r="W40" s="3">
         <f t="shared" si="1"/>
-        <v>3.6777912242050093</v>
+        <v>3.603342321478209</v>
       </c>
       <c r="X40" s="3">
         <f t="shared" si="2"/>
-        <v>12.10508368466081</v>
+        <v>13.884325538269666</v>
       </c>
       <c r="Y40" s="3">
         <f t="shared" si="3"/>
-        <v>6.3198844359947229E-2</v>
+        <v>6.1919520893940268E-2</v>
       </c>
       <c r="Z40" s="3">
         <f t="shared" si="8"/>
-        <v>3.5791015929947399E-2</v>
+        <v>3.5066504477006516E-2</v>
       </c>
       <c r="AA40" s="3">
         <f t="shared" si="9"/>
-        <v>7.439364009860248</v>
+        <v>7.2887702284965261</v>
       </c>
       <c r="AB40" s="3">
         <f t="shared" si="10"/>
-        <v>4.6672032137709785</v>
+        <v>4.572725812285702</v>
       </c>
       <c r="AD40">
         <v>17.7</v>
@@ -41426,7 +42193,7 @@
         <v>410.8550082557</v>
       </c>
       <c r="D41">
-        <v>1361.666667</v>
+        <v>1553.01</v>
       </c>
       <c r="E41">
         <v>7.45472</v>
@@ -41442,7 +42209,7 @@
       </c>
       <c r="I41" s="3">
         <f t="shared" si="5"/>
-        <v>11418.795720327416</v>
+        <v>11610.139053327417</v>
       </c>
       <c r="J41" s="3">
         <f t="shared" si="6"/>
@@ -41451,7 +42218,7 @@
       <c r="K41" s="7"/>
       <c r="L41" s="3">
         <f t="shared" si="7"/>
-        <v>62.058672393083782</v>
+        <v>63.098581811562049</v>
       </c>
       <c r="M41" s="3">
         <v>74.449079859999998</v>
@@ -41476,31 +42243,31 @@
       <c r="U41" s="7"/>
       <c r="V41" s="3">
         <f t="shared" si="0"/>
-        <v>72.28038929978635</v>
+        <v>71.08915717624042</v>
       </c>
       <c r="W41" s="3">
         <f t="shared" si="1"/>
-        <v>3.5980590100609957</v>
+        <v>3.5387604435103701</v>
       </c>
       <c r="X41" s="3">
         <f t="shared" si="2"/>
-        <v>11.924783491625124</v>
+        <v>13.376325579450436</v>
       </c>
       <c r="Y41" s="3">
         <f t="shared" si="3"/>
-        <v>6.5284642816836796E-2</v>
+        <v>6.420870556122675E-2</v>
       </c>
       <c r="Z41" s="3">
         <f t="shared" si="8"/>
-        <v>3.7782662702678015E-2</v>
+        <v>3.7159977601497141E-2</v>
       </c>
       <c r="AA41" s="3">
         <f t="shared" si="9"/>
-        <v>7.4347157160252406</v>
+        <v>7.3121863235280822</v>
       </c>
       <c r="AB41" s="3">
         <f t="shared" si="10"/>
-        <v>4.6589851769827941</v>
+        <v>4.5822017941079789</v>
       </c>
       <c r="AD41">
         <v>18.399999999999999</v>
@@ -41532,7 +42299,7 @@
         <v>402.14066674430001</v>
       </c>
       <c r="D42">
-        <v>1343.6470589999999</v>
+        <v>1573.85</v>
       </c>
       <c r="E42">
         <v>8.26112</v>
@@ -41548,7 +42315,7 @@
       </c>
       <c r="I42" s="3">
         <f t="shared" si="5"/>
-        <v>11591.48123953647</v>
+        <v>11821.684180536471</v>
       </c>
       <c r="J42" s="3">
         <f t="shared" si="6"/>
@@ -41557,7 +42324,7 @@
       <c r="K42" s="7"/>
       <c r="L42" s="3">
         <f t="shared" si="7"/>
-        <v>60.372298122585782</v>
+        <v>61.571271773627451</v>
       </c>
       <c r="M42" s="3">
         <v>72.868081930000002</v>
@@ -41582,31 +42349,31 @@
       <c r="U42" s="7"/>
       <c r="V42" s="3">
         <f t="shared" si="0"/>
-        <v>72.898362386841129</v>
+        <v>71.478816985419897</v>
       </c>
       <c r="W42" s="3">
         <f t="shared" si="1"/>
-        <v>3.4692776396227094</v>
+        <v>3.4017206059894147</v>
       </c>
       <c r="X42" s="3">
         <f t="shared" si="2"/>
-        <v>11.591676949940272</v>
+        <v>13.313246877219301</v>
       </c>
       <c r="Y42" s="3">
         <f t="shared" si="3"/>
-        <v>7.1268889879429712E-2</v>
+        <v>6.9881075097584858E-2</v>
       </c>
       <c r="Z42" s="3">
         <f t="shared" si="8"/>
-        <v>3.5563994859528145E-2</v>
+        <v>3.4871459338755947E-2</v>
       </c>
       <c r="AA42" s="3">
         <f t="shared" si="9"/>
-        <v>7.3442727672830443</v>
+        <v>7.2012581879121669</v>
       </c>
       <c r="AB42" s="3">
         <f t="shared" si="10"/>
-        <v>4.5895773715739034</v>
+        <v>4.5002048090228852</v>
       </c>
       <c r="AD42">
         <v>19.2</v>
@@ -41638,7 +42405,7 @@
         <v>400.587999999999</v>
       </c>
       <c r="D43">
-        <v>1343.6470589999999</v>
+        <v>1579.96</v>
       </c>
       <c r="E43">
         <v>8.2252799999999997</v>
@@ -41654,7 +42421,7 @@
       </c>
       <c r="I43" s="3">
         <f t="shared" si="5"/>
-        <v>11901.397373741956</v>
+        <v>12137.710314741957</v>
       </c>
       <c r="J43" s="3">
         <f t="shared" si="6"/>
@@ -41663,7 +42430,7 @@
       <c r="K43" s="7"/>
       <c r="L43" s="3">
         <f t="shared" si="7"/>
-        <v>58.764820998651295</v>
+        <v>59.931649333294459</v>
       </c>
       <c r="M43" s="3">
         <v>71.320658019999996</v>
@@ -41692,31 +42459,31 @@
       <c r="U43" s="7"/>
       <c r="V43" s="3">
         <f t="shared" si="0"/>
-        <v>73.639251969993268</v>
+        <v>72.205545961625802</v>
       </c>
       <c r="W43" s="3">
         <f t="shared" si="1"/>
-        <v>3.3658904700032619</v>
+        <v>3.3003588783418367</v>
       </c>
       <c r="X43" s="3">
         <f t="shared" si="2"/>
-        <v>11.289826033071439</v>
+        <v>13.016952613221017</v>
       </c>
       <c r="Y43" s="3">
         <f t="shared" si="3"/>
-        <v>6.9111884442640562E-2</v>
+        <v>6.7766323192026745E-2</v>
       </c>
       <c r="Z43" s="3">
         <f t="shared" si="8"/>
-        <v>2.8501146843804604E-2</v>
+        <v>2.7946248954673732E-2</v>
       </c>
       <c r="AA43" s="3">
         <f t="shared" si="9"/>
-        <v>7.1373551636392714</v>
+        <v>6.9983957268143033</v>
       </c>
       <c r="AB43" s="3">
         <f t="shared" si="10"/>
-        <v>4.4700633320063003</v>
+        <v>4.383034247850313</v>
       </c>
       <c r="AD43">
         <v>20.252588490000001</v>
@@ -41751,7 +42518,7 @@
         <v>388.94299999999998</v>
       </c>
       <c r="D44">
-        <v>1272.176471</v>
+        <v>1579.96</v>
       </c>
       <c r="E44">
         <v>8.2700800000000001</v>
@@ -41767,7 +42534,7 @@
       </c>
       <c r="I44" s="3">
         <f t="shared" si="5"/>
-        <v>12121.198554527598</v>
+        <v>12428.982083527599</v>
       </c>
       <c r="J44" s="3">
         <f t="shared" si="6"/>
@@ -41776,7 +42543,7 @@
       <c r="K44" s="7"/>
       <c r="L44" s="3">
         <f t="shared" si="7"/>
-        <v>58.010418686832558</v>
+        <v>59.483429074533177</v>
       </c>
       <c r="M44" s="3">
         <v>69.806095139999996</v>
@@ -41803,31 +42570,31 @@
       <c r="U44" s="7"/>
       <c r="V44" s="3">
         <f t="shared" si="0"/>
-        <v>74.882033811826659</v>
+        <v>73.027702019374672</v>
       </c>
       <c r="W44" s="3">
         <f t="shared" si="1"/>
-        <v>3.2087833414354816</v>
+        <v>3.1293230401826277</v>
       </c>
       <c r="X44" s="3">
         <f t="shared" si="2"/>
-        <v>10.49546763281761</v>
+        <v>12.711901822547123</v>
       </c>
       <c r="Y44" s="3">
         <f t="shared" si="3"/>
-        <v>6.8228236364554065E-2</v>
+        <v>6.653867504532425E-2</v>
       </c>
       <c r="Z44" s="3">
         <f t="shared" si="8"/>
-        <v>5.0028085096680219E-2</v>
+        <v>4.8789220926091739E-2</v>
       </c>
       <c r="AA44" s="3">
         <f t="shared" si="9"/>
-        <v>7.0054540908648111</v>
+        <v>6.8319754127362557</v>
       </c>
       <c r="AB44" s="3">
         <f t="shared" si="10"/>
-        <v>4.2900048015941934</v>
+        <v>4.1837698091878925</v>
       </c>
       <c r="AD44">
         <v>20.894864800000001</v>
@@ -41859,7 +42626,7 @@
         <v>372.64</v>
       </c>
       <c r="D45">
-        <v>1250.7352940000001</v>
+        <v>1579.96</v>
       </c>
       <c r="E45">
         <v>8.3148800000000005</v>
@@ -41875,7 +42642,7 @@
       </c>
       <c r="I45" s="3">
         <f t="shared" si="5"/>
-        <v>12469.170193278707</v>
+        <v>12798.394899278708</v>
       </c>
       <c r="J45" s="3">
         <f t="shared" si="6"/>
@@ -41884,7 +42651,7 @@
       <c r="K45" s="7"/>
       <c r="L45" s="3">
         <f t="shared" si="7"/>
-        <v>58.368388715061307</v>
+        <v>59.909494924740606</v>
       </c>
       <c r="M45" s="3">
         <v>68.323695470000004</v>
@@ -41911,31 +42678,31 @@
       <c r="U45" s="7"/>
       <c r="V45" s="3">
         <f t="shared" si="0"/>
-        <v>76.061296405371877</v>
+        <v>74.104702774365165</v>
       </c>
       <c r="W45" s="3">
         <f t="shared" si="1"/>
-        <v>2.9884907674198335</v>
+        <v>2.9116151121497369</v>
       </c>
       <c r="X45" s="3">
         <f t="shared" si="2"/>
-        <v>10.030621722319481</v>
+        <v>12.344985542593653</v>
       </c>
       <c r="Y45" s="3">
         <f t="shared" si="3"/>
-        <v>6.6683507171006406E-2</v>
+        <v>6.4968146907770516E-2</v>
       </c>
       <c r="Z45" s="3">
         <f t="shared" si="8"/>
-        <v>3.2264731464459497E-2</v>
+        <v>3.1434756548530444E-2</v>
       </c>
       <c r="AA45" s="3">
         <f t="shared" si="9"/>
-        <v>6.7305551371203549</v>
+        <v>6.5574189701499055</v>
       </c>
       <c r="AB45" s="3">
         <f t="shared" si="10"/>
-        <v>4.0900877291329838</v>
+        <v>3.9848746972852243</v>
       </c>
       <c r="AD45">
         <v>21.362882320000001</v>
@@ -41967,7 +42734,7 @@
         <v>337.70499999999998</v>
       </c>
       <c r="D46">
-        <v>1229.294118</v>
+        <v>1579.96</v>
       </c>
       <c r="E46">
         <v>8.3865599999999993</v>
@@ -41983,7 +42750,7 @@
       </c>
       <c r="I46" s="3">
         <f t="shared" si="5"/>
-        <v>12562.279003882797</v>
+        <v>12912.944885882798</v>
       </c>
       <c r="J46" s="3">
         <f t="shared" si="6"/>
@@ -41992,7 +42759,7 @@
       <c r="K46" s="7"/>
       <c r="L46" s="3">
         <f t="shared" si="7"/>
-        <v>57.802485787500444</v>
+        <v>59.415995537936766</v>
       </c>
       <c r="M46" s="3">
         <v>66.87277598</v>
@@ -42019,31 +42786,31 @@
       <c r="U46" s="7"/>
       <c r="V46" s="3">
         <f t="shared" si="0"/>
-        <v>76.852098230074247</v>
+        <v>74.765091040965714</v>
       </c>
       <c r="W46" s="3">
         <f t="shared" si="1"/>
-        <v>2.6882462958800772</v>
+        <v>2.6152438733723646</v>
       </c>
       <c r="X46" s="3">
         <f t="shared" si="2"/>
-        <v>9.785597960529655</v>
+        <v>12.235473890446993</v>
       </c>
       <c r="Y46" s="3">
         <f t="shared" si="3"/>
-        <v>6.6759860988661768E-2</v>
+        <v>6.4946920118653079E-2</v>
       </c>
       <c r="Z46" s="3">
         <f t="shared" si="8"/>
-        <v>2.6136387209521991E-2</v>
+        <v>2.542662353019734E-2</v>
       </c>
       <c r="AA46" s="3">
         <f t="shared" si="9"/>
-        <v>6.6009917447598241</v>
+        <v>6.4217342157680015</v>
       </c>
       <c r="AB46" s="3">
         <f t="shared" si="10"/>
-        <v>3.9801695205579981</v>
+        <v>3.8720834357980558</v>
       </c>
       <c r="AD46">
         <v>21.733112049999999</v>
@@ -42075,7 +42842,7 @@
         <v>342.2853667</v>
       </c>
       <c r="D47">
-        <v>1215</v>
+        <v>1579.96</v>
       </c>
       <c r="E47">
         <v>8.45824</v>
@@ -42091,7 +42858,7 @@
       </c>
       <c r="I47" s="3">
         <f t="shared" si="5"/>
-        <v>12915.919682582795</v>
+        <v>13280.879682582794</v>
       </c>
       <c r="J47" s="3">
         <f t="shared" si="6"/>
@@ -42100,7 +42867,7 @@
       <c r="K47" s="7"/>
       <c r="L47" s="3">
         <f t="shared" si="7"/>
-        <v>58.60119343906829</v>
+        <v>60.257064030023031</v>
       </c>
       <c r="M47" s="3">
         <v>65.452668169999995</v>
@@ -42127,31 +42894,31 @@
       <c r="U47" s="7"/>
       <c r="V47" s="3">
         <f t="shared" si="0"/>
-        <v>77.853728167417628</v>
+        <v>75.71429935614367</v>
       </c>
       <c r="W47" s="3">
         <f t="shared" si="1"/>
-        <v>2.6501044843254498</v>
+        <v>2.5772793284837152</v>
       </c>
       <c r="X47" s="3">
         <f t="shared" si="2"/>
-        <v>9.4069956291106074</v>
+        <v>11.896501118612182</v>
       </c>
       <c r="Y47" s="3">
         <f t="shared" si="3"/>
-        <v>6.5486935563760076E-2</v>
+        <v>6.3687347541387315E-2</v>
       </c>
       <c r="Z47" s="3">
         <f t="shared" si="8"/>
-        <v>2.5420767266173674E-2</v>
+        <v>2.4722201851592757E-2</v>
       </c>
       <c r="AA47" s="3">
         <f t="shared" si="9"/>
-        <v>6.2044962317367913</v>
+        <v>6.0339960089462563</v>
       </c>
       <c r="AB47" s="3">
         <f t="shared" si="10"/>
-        <v>3.7937677845795861</v>
+        <v>3.6895146384212061</v>
       </c>
       <c r="AD47">
         <v>22.040369699999999</v>
@@ -42183,7 +42950,7 @@
         <v>336.01129950000001</v>
       </c>
       <c r="D48">
-        <v>1200.705882</v>
+        <v>1579.96</v>
       </c>
       <c r="E48">
         <v>8.1954133329999994</v>
@@ -42199,7 +42966,7 @@
       </c>
       <c r="I48" s="3">
         <f t="shared" si="5"/>
-        <v>13151.662920715795</v>
+        <v>13530.917038715796</v>
       </c>
       <c r="J48" s="3">
         <f t="shared" si="6"/>
@@ -42208,7 +42975,7 @@
       <c r="K48" s="7"/>
       <c r="L48" s="3">
         <f t="shared" si="7"/>
-        <v>58.966709209597525</v>
+        <v>60.667130474000743</v>
       </c>
       <c r="M48" s="3">
         <v>64.062717710000001</v>
@@ -42237,31 +43004,31 @@
       <c r="U48" s="7"/>
       <c r="V48" s="3">
         <f t="shared" si="0"/>
-        <v>78.693850826255158</v>
+        <v>76.488163887096476</v>
       </c>
       <c r="W48" s="3">
         <f t="shared" si="1"/>
-        <v>2.5548959209616982</v>
+        <v>2.4832854901007542</v>
       </c>
       <c r="X48" s="3">
         <f t="shared" si="2"/>
-        <v>9.129688688330905</v>
+        <v>11.676666078723901</v>
       </c>
       <c r="Y48" s="3">
         <f t="shared" si="3"/>
-        <v>6.2314654674512852E-2</v>
+        <v>6.0568055435936789E-2</v>
       </c>
       <c r="Z48" s="3">
         <f t="shared" si="8"/>
-        <v>2.4965100630913912E-2</v>
+        <v>2.4265361123719568E-2</v>
       </c>
       <c r="AA48" s="3">
         <f t="shared" si="9"/>
-        <v>5.8845562319040843</v>
+        <v>5.7196197255929055</v>
       </c>
       <c r="AB48" s="3">
         <f t="shared" si="10"/>
-        <v>3.6497285772427279</v>
+        <v>3.5474314019262971</v>
       </c>
       <c r="AD48">
         <v>22.303538889999999</v>
@@ -42296,7 +43063,7 @@
         <v>329.73723219999999</v>
       </c>
       <c r="D49">
-        <v>1191.176471</v>
+        <v>1579.96</v>
       </c>
       <c r="E49">
         <v>7.9325866669999998</v>
@@ -42312,7 +43079,7 @@
       </c>
       <c r="I49" s="3">
         <f t="shared" si="5"/>
-        <v>13267.056115749796</v>
+        <v>13655.839644749796</v>
       </c>
       <c r="J49" s="3">
         <f t="shared" si="6"/>
@@ -42321,7 +43088,7 @@
       <c r="K49" s="7"/>
       <c r="L49" s="3">
         <f t="shared" si="7"/>
-        <v>58.875608458111593</v>
+        <v>60.600924657022787</v>
       </c>
       <c r="M49" s="3">
         <v>62.70228419</v>
@@ -42348,31 +43115,31 @@
       <c r="U49" s="7"/>
       <c r="V49" s="3">
         <f t="shared" si="0"/>
-        <v>79.236210416872041</v>
+        <v>76.980345211080632</v>
       </c>
       <c r="W49" s="3">
         <f t="shared" si="1"/>
-        <v>2.4853835645464497</v>
+        <v>2.4146243715359725</v>
       </c>
       <c r="X49" s="3">
         <f t="shared" si="2"/>
-        <v>8.9784535514695829</v>
+        <v>11.569848805360282</v>
       </c>
       <c r="Y49" s="3">
         <f t="shared" si="3"/>
-        <v>5.9791611626508034E-2</v>
+        <v>5.8089336674730277E-2</v>
       </c>
       <c r="Z49" s="3">
         <f t="shared" si="8"/>
-        <v>2.4747961071013611E-2</v>
+        <v>2.4043383403799828E-2</v>
       </c>
       <c r="AA49" s="3">
         <f t="shared" si="9"/>
-        <v>5.6728033215035927</v>
+        <v>5.5112978738685943</v>
       </c>
       <c r="AB49" s="3">
         <f t="shared" si="10"/>
-        <v>3.5426095729108003</v>
+        <v>3.4417510180759843</v>
       </c>
       <c r="AD49">
         <v>22.534045020000001</v>
@@ -42404,7 +43171,7 @@
         <v>323.463165</v>
       </c>
       <c r="D50">
-        <v>1181.6470589999999</v>
+        <v>1579.96</v>
       </c>
       <c r="E50">
         <v>7.6697600000000001</v>
@@ -42420,7 +43187,7 @@
       </c>
       <c r="I50" s="3">
         <f t="shared" si="5"/>
-        <v>13384.356643182797</v>
+        <v>13782.669584182797</v>
       </c>
       <c r="J50" s="3">
         <f t="shared" si="6"/>
@@ -42429,7 +43196,7 @@
       <c r="K50" s="7"/>
       <c r="L50" s="3">
         <f t="shared" si="7"/>
-        <v>58.859910652644167</v>
+        <v>60.611557350656604</v>
       </c>
       <c r="M50" s="3">
         <v>61.370740789999999</v>
@@ -42456,31 +43223,31 @@
       <c r="U50" s="7"/>
       <c r="V50" s="3">
         <f t="shared" ref="V50:V73" si="11">B50/$I50*100</f>
-        <v>79.770924256102717</v>
+        <v>77.465580487055192</v>
       </c>
       <c r="W50" s="3">
         <f t="shared" ref="W50:W73" si="12">C50/$I50*100</f>
-        <v>2.4167255373066672</v>
+        <v>2.3468832581694574</v>
       </c>
       <c r="X50" s="3">
         <f t="shared" ref="X50:X73" si="13">D50/$I50*100</f>
-        <v>8.8285682345580749</v>
+        <v>11.463381533960492</v>
       </c>
       <c r="Y50" s="3">
         <f t="shared" ref="Y50:Y73" si="14">E50/$I50*100</f>
-        <v>5.7303912354326907E-2</v>
+        <v>5.5647855106400683E-2</v>
       </c>
       <c r="Z50" s="3">
         <f t="shared" ref="Z50:Z73" si="15">F50/$I50*100</f>
-        <v>2.4531069892460039E-2</v>
+        <v>2.3822133025399414E-2</v>
       </c>
       <c r="AA50" s="3">
         <f t="shared" si="9"/>
-        <v>5.4650989419993303</v>
+        <v>5.3071600449556184</v>
       </c>
       <c r="AB50" s="3">
         <f t="shared" si="10"/>
-        <v>3.4368480477864201</v>
+        <v>3.3375246877274272</v>
       </c>
       <c r="AD50">
         <v>22.739342440000001</v>
@@ -42512,7 +43279,7 @@
         <v>320.40829330000003</v>
       </c>
       <c r="D51">
-        <v>1172.117647</v>
+        <v>1579.96</v>
       </c>
       <c r="E51">
         <v>7.3949866670000004</v>
@@ -42528,7 +43295,7 @@
       </c>
       <c r="I51" s="3">
         <f t="shared" si="5"/>
-        <v>13375.415502849695</v>
+        <v>13783.257855849695</v>
       </c>
       <c r="J51" s="3">
         <f t="shared" si="6"/>
@@ -42537,7 +43304,7 @@
       <c r="K51" s="7"/>
       <c r="L51" s="3">
         <f t="shared" si="7"/>
-        <v>58.345323657063062</v>
+        <v>60.124385704277479</v>
       </c>
       <c r="M51" s="3">
         <v>60.067473990000003</v>
@@ -42564,31 +43331,31 @@
       <c r="U51" s="7"/>
       <c r="V51" s="3">
         <f t="shared" si="11"/>
-        <v>80.085222382196022</v>
+        <v>77.715525328097812</v>
       </c>
       <c r="W51" s="3">
         <f t="shared" si="12"/>
-        <v>2.3955016068976365</v>
+        <v>2.3246194524614285</v>
       </c>
       <c r="X51" s="3">
         <f t="shared" si="13"/>
-        <v>8.7632241910561568</v>
+        <v>11.462892274988935</v>
       </c>
       <c r="Y51" s="3">
         <f t="shared" si="14"/>
-        <v>5.5287902386467642E-2</v>
+        <v>5.3651950390389926E-2</v>
       </c>
       <c r="Z51" s="3">
         <f t="shared" si="15"/>
-        <v>2.4547468316746958E-2</v>
+        <v>2.3821116292922193E-2</v>
       </c>
       <c r="AA51" s="3">
         <f t="shared" si="9"/>
-        <v>5.3118349844805106</v>
+        <v>5.1546594239943655</v>
       </c>
       <c r="AB51" s="3">
         <f t="shared" si="10"/>
-        <v>3.3643814646664647</v>
+        <v>3.264830453774159</v>
       </c>
       <c r="AD51">
         <v>22.924571610000001</v>
@@ -42620,7 +43387,7 @@
         <v>317.35342170000001</v>
       </c>
       <c r="D52">
-        <v>1162.5882349999999</v>
+        <v>1579.96</v>
       </c>
       <c r="E52">
         <v>7.1202133329999997</v>
@@ -42636,7 +43403,7 @@
       </c>
       <c r="I52" s="3">
         <f t="shared" si="5"/>
-        <v>13397.953862615796</v>
+        <v>13815.325627615797</v>
       </c>
       <c r="J52" s="3">
         <f t="shared" si="6"/>
@@ -42645,7 +43412,7 @@
       <c r="K52" s="7"/>
       <c r="L52" s="3">
         <f t="shared" si="7"/>
-        <v>58.016297896041003</v>
+        <v>59.823616005950427</v>
       </c>
       <c r="M52" s="3">
         <v>58.791883319999997</v>
@@ -42672,31 +43439,31 @@
       <c r="U52" s="7"/>
       <c r="V52" s="3">
         <f t="shared" si="11"/>
-        <v>80.215606877016995</v>
+        <v>77.792230814430141</v>
       </c>
       <c r="W52" s="3">
         <f t="shared" si="12"/>
-        <v>2.36867080566316</v>
+        <v>2.2971114127461059</v>
       </c>
       <c r="X52" s="3">
         <f t="shared" si="13"/>
-        <v>8.6773566092353906</v>
+        <v>11.436284909866901</v>
       </c>
       <c r="Y52" s="3">
         <f t="shared" si="14"/>
-        <v>5.3144035320702776E-2</v>
+        <v>5.1538512554255178E-2</v>
       </c>
       <c r="Z52" s="3">
         <f t="shared" si="15"/>
-        <v>2.4506173975988442E-2</v>
+        <v>2.3765823342101818E-2</v>
       </c>
       <c r="AA52" s="3">
         <f t="shared" si="9"/>
-        <v>5.3019936774234475</v>
+        <v>5.1418163121689027</v>
       </c>
       <c r="AB52" s="3">
         <f t="shared" si="10"/>
-        <v>3.3587218213643162</v>
+        <v>3.2572522148915826</v>
       </c>
       <c r="AD52">
         <v>23.093431240000001</v>
@@ -42728,7 +43495,7 @@
         <v>314.29854999999998</v>
       </c>
       <c r="D53">
-        <v>1153.058824</v>
+        <v>1579.96</v>
       </c>
       <c r="E53">
         <v>6.84544</v>
@@ -42744,7 +43511,7 @@
       </c>
       <c r="I53" s="3">
         <f t="shared" si="5"/>
-        <v>13413.212362071594</v>
+        <v>13840.113538071595</v>
       </c>
       <c r="J53" s="3">
         <f t="shared" si="6"/>
@@ -42753,7 +43520,7 @@
       <c r="K53" s="7"/>
       <c r="L53" s="3">
         <f t="shared" si="7"/>
-        <v>57.69452681207899</v>
+        <v>59.530765639884748</v>
       </c>
       <c r="M53" s="3">
         <v>57.54338104</v>
@@ -42782,31 +43549,31 @@
       <c r="U53" s="7"/>
       <c r="V53" s="3">
         <f t="shared" si="11"/>
-        <v>80.334886215315152</v>
+        <v>77.856939968356613</v>
       </c>
       <c r="W53" s="3">
         <f t="shared" si="12"/>
-        <v>2.3432011774356072</v>
+        <v>2.2709246505487313</v>
       </c>
       <c r="X53" s="3">
         <f t="shared" si="13"/>
-        <v>8.5964405309834131</v>
+        <v>11.415802302877227</v>
       </c>
       <c r="Y53" s="3">
         <f t="shared" si="14"/>
-        <v>5.1035052716803191E-2</v>
+        <v>4.9460865918256089E-2</v>
       </c>
       <c r="Z53" s="3">
         <f t="shared" si="15"/>
-        <v>2.4478296430164019E-2</v>
+        <v>2.3723258293824448E-2</v>
       </c>
       <c r="AA53" s="3">
         <f t="shared" si="9"/>
-        <v>5.2950576948168742</v>
+        <v>5.1317305406943978</v>
       </c>
       <c r="AB53" s="3">
         <f t="shared" si="10"/>
-        <v>3.3549010323020045</v>
+        <v>3.2514184133109394</v>
       </c>
       <c r="AD53">
         <v>23.248673839999999</v>
@@ -42841,7 +43608,7 @@
         <v>314.29854999999998</v>
       </c>
       <c r="D54">
-        <v>1143.5294120000001</v>
+        <v>1579.96</v>
       </c>
       <c r="E54">
         <v>6.84544</v>
@@ -42857,7 +43624,7 @@
       </c>
       <c r="I54" s="3">
         <f t="shared" si="5"/>
-        <v>13432.228283438295</v>
+        <v>13868.658871438296</v>
       </c>
       <c r="J54" s="3">
         <f t="shared" si="6"/>
@@ -42866,7 +43633,7 @@
       <c r="K54" s="7"/>
       <c r="L54" s="3">
         <f t="shared" si="7"/>
-        <v>57.421323369126519</v>
+        <v>59.287016937826891</v>
       </c>
       <c r="M54" s="3">
         <v>56.321391920000003</v>
@@ -42889,31 +43656,31 @@
       <c r="U54" s="7"/>
       <c r="V54" s="3">
         <f t="shared" si="11"/>
-        <v>80.434573680353822</v>
+        <v>77.903391061164797</v>
       </c>
       <c r="W54" s="3">
         <f t="shared" si="12"/>
-        <v>2.3398839222195522</v>
+        <v>2.2662504926650096</v>
       </c>
       <c r="X54" s="3">
         <f t="shared" si="13"/>
-        <v>8.5133262171396531</v>
+        <v>11.392305590945327</v>
       </c>
       <c r="Y54" s="3">
         <f t="shared" si="14"/>
-        <v>5.0962802712639338E-2</v>
+        <v>4.9359062498089051E-2</v>
       </c>
       <c r="Z54" s="3">
         <f t="shared" si="15"/>
-        <v>2.4443642659375989E-2</v>
+        <v>2.3674429613068863E-2</v>
       </c>
       <c r="AA54" s="3">
         <f t="shared" si="9"/>
-        <v>5.2866582149706369</v>
+        <v>5.1202932207269365</v>
       </c>
       <c r="AB54" s="3">
         <f t="shared" si="10"/>
-        <v>3.3501515199443284</v>
+        <v>3.2447261423867677</v>
       </c>
       <c r="AD54">
         <v>23.392404590000002</v>
@@ -42945,7 +43712,7 @@
         <v>314.29854999999998</v>
       </c>
       <c r="D55">
-        <v>1143.5294120000001</v>
+        <v>1579.96</v>
       </c>
       <c r="E55">
         <v>6.84544</v>
@@ -42961,7 +43728,7 @@
       </c>
       <c r="I55" s="3">
         <f t="shared" si="5"/>
-        <v>13461.322727882794</v>
+        <v>13897.753315882794</v>
       </c>
       <c r="J55" s="3">
         <f t="shared" si="6"/>
@@ -42970,7 +43737,7 @@
       <c r="K55" s="7"/>
       <c r="L55" s="3">
         <f t="shared" si="7"/>
-        <v>57.218260275592819</v>
+        <v>59.073337928897217</v>
       </c>
       <c r="M55" s="3">
         <v>55.125352909999997</v>
@@ -42993,31 +43760,31 @@
       <c r="U55" s="7"/>
       <c r="V55" s="3">
         <f t="shared" si="11"/>
-        <v>80.476861145010687</v>
+        <v>77.949649513633389</v>
       </c>
       <c r="W55" s="3">
         <f t="shared" si="12"/>
-        <v>2.334826646336805</v>
+        <v>2.2615061791376712</v>
       </c>
       <c r="X55" s="3">
         <f t="shared" si="13"/>
-        <v>8.4949260567936413</v>
+        <v>11.368456210791795</v>
       </c>
       <c r="Y55" s="3">
         <f t="shared" si="14"/>
-        <v>5.0852654961022953E-2</v>
+        <v>4.9255731084079712E-2</v>
       </c>
       <c r="Z55" s="3">
         <f t="shared" si="15"/>
-        <v>2.4390811729032021E-2</v>
+        <v>2.362486805002504E-2</v>
       </c>
       <c r="AA55" s="3">
         <f t="shared" si="9"/>
-        <v>5.2752319690628759</v>
+        <v>5.1095740718642402</v>
       </c>
       <c r="AB55" s="3">
         <f t="shared" si="10"/>
-        <v>3.3429107161059521</v>
+        <v>3.237933425438813</v>
       </c>
       <c r="AD55">
         <v>23.526270570000001</v>
@@ -43049,7 +43816,7 @@
         <v>314.29854999999998</v>
       </c>
       <c r="D56">
-        <v>1143.5294120000001</v>
+        <v>1579.96</v>
       </c>
       <c r="E56">
         <v>6.84544</v>
@@ -43065,7 +43832,7 @@
       </c>
       <c r="I56" s="3">
         <f t="shared" si="5"/>
-        <v>13450.239394549395</v>
+        <v>13886.669982549396</v>
       </c>
       <c r="J56" s="3">
         <f t="shared" si="6"/>
@@ -43074,7 +43841,7 @@
       <c r="K56" s="7"/>
       <c r="L56" s="3">
         <f t="shared" si="7"/>
-        <v>56.868236204654721</v>
+        <v>58.713484979585679</v>
       </c>
       <c r="M56" s="3">
         <v>53.95471294</v>
@@ -43097,31 +43864,31 @@
       <c r="U56" s="7"/>
       <c r="V56" s="3">
         <f t="shared" si="11"/>
-        <v>80.460773590782324</v>
+        <v>77.932050522308188</v>
       </c>
       <c r="W56" s="3">
         <f t="shared" si="12"/>
-        <v>2.3367506018321653</v>
+        <v>2.2633111494329556</v>
       </c>
       <c r="X56" s="3">
         <f t="shared" si="13"/>
-        <v>8.5019260881215732</v>
+        <v>11.377529688438248</v>
       </c>
       <c r="Y56" s="3">
         <f t="shared" si="14"/>
-        <v>5.0894558819332698E-2</v>
+        <v>4.92950434380761E-2</v>
       </c>
       <c r="Z56" s="3">
         <f t="shared" si="15"/>
-        <v>2.4410910367333925E-2</v>
+        <v>2.3643723707132538E-2</v>
       </c>
       <c r="AA56" s="3">
         <f t="shared" si="9"/>
-        <v>5.279578892014138</v>
+        <v>5.1136521634946543</v>
       </c>
       <c r="AB56" s="3">
         <f t="shared" si="10"/>
-        <v>3.3456653580631359</v>
+        <v>3.2405177091807458</v>
       </c>
       <c r="AD56">
         <v>23.651585300000001</v>
@@ -43153,7 +43920,7 @@
         <v>314.29854999999998</v>
       </c>
       <c r="D57">
-        <v>1143.5294120000001</v>
+        <v>1579.96</v>
       </c>
       <c r="E57">
         <v>6.84544</v>
@@ -43169,7 +43936,7 @@
       </c>
       <c r="I57" s="3">
         <f t="shared" si="5"/>
-        <v>13439.156061216094</v>
+        <v>13875.586649216093</v>
       </c>
       <c r="J57" s="3">
         <f t="shared" si="6"/>
@@ -43178,7 +43945,7 @@
       <c r="K57" s="7"/>
       <c r="L57" s="3">
         <f t="shared" si="7"/>
-        <v>56.539703918164967</v>
+        <v>58.375805538977438</v>
       </c>
       <c r="M57" s="3">
         <v>52.808932630000001</v>
@@ -43201,31 +43968,31 @@
       <c r="U57" s="7"/>
       <c r="V57" s="3">
         <f t="shared" si="11"/>
-        <v>80.444659501595353</v>
+        <v>77.914423416065631</v>
       </c>
       <c r="W57" s="3">
         <f t="shared" si="12"/>
-        <v>2.3386777307172624</v>
+        <v>2.2651190032225155</v>
       </c>
       <c r="X57" s="3">
         <f t="shared" si="13"/>
-        <v>8.5089376653650035</v>
+        <v>11.386617661237844</v>
       </c>
       <c r="Y57" s="3">
         <f t="shared" si="14"/>
-        <v>5.0936531794248417E-2</v>
+        <v>4.9334418594739103E-2</v>
       </c>
       <c r="Z57" s="3">
         <f t="shared" si="15"/>
-        <v>2.4431042156513101E-2</v>
+        <v>2.3662609486718764E-2</v>
       </c>
       <c r="AA57" s="3">
         <f t="shared" si="9"/>
-        <v>5.2839329848197512</v>
+        <v>5.1177367699989702</v>
       </c>
       <c r="AB57" s="3">
         <f t="shared" si="10"/>
-        <v>3.3484245435518813</v>
+        <v>3.2431061213935983</v>
       </c>
       <c r="AD57">
         <v>23.769413579999998</v>
@@ -43257,7 +44024,7 @@
         <v>314.29854999999998</v>
       </c>
       <c r="D58">
-        <v>1143.5294120000001</v>
+        <v>1579.96</v>
       </c>
       <c r="E58">
         <v>6.84544</v>
@@ -43273,7 +44040,7 @@
       </c>
       <c r="I58" s="3">
         <f t="shared" si="5"/>
-        <v>13428.072727882794</v>
+        <v>13864.503315882794</v>
       </c>
       <c r="J58" s="3">
         <f t="shared" si="6"/>
@@ -43282,7 +44049,7 @@
       <c r="K58" s="7"/>
       <c r="L58" s="3">
         <f t="shared" si="7"/>
-        <v>56.229974831828194</v>
+        <v>58.057525328194117</v>
       </c>
       <c r="M58" s="3">
         <v>51.687484079999997</v>
@@ -43305,31 +44072,31 @@
       <c r="U58" s="7"/>
       <c r="V58" s="3">
         <f t="shared" si="11"/>
-        <v>80.428518811744894</v>
+        <v>77.89676812748003</v>
       </c>
       <c r="W58" s="3">
         <f t="shared" si="12"/>
-        <v>2.3406080408499208</v>
+        <v>2.2669297474215915</v>
       </c>
       <c r="X58" s="3">
         <f t="shared" si="13"/>
-        <v>8.5159608171134806</v>
+        <v>11.395720163953088</v>
       </c>
       <c r="Y58" s="3">
         <f t="shared" si="14"/>
-        <v>5.0978574056913986E-2</v>
+        <v>4.9373856704683049E-2</v>
       </c>
       <c r="Z58" s="3">
         <f t="shared" si="15"/>
-        <v>2.4451207178656471E-2</v>
+        <v>2.3681525461023922E-2</v>
       </c>
       <c r="AA58" s="3">
         <f t="shared" si="9"/>
-        <v>5.2882942652334304</v>
+        <v>5.1218279070012596</v>
       </c>
       <c r="AB58" s="3">
         <f t="shared" si="10"/>
-        <v>3.3511882838227045</v>
+        <v>3.2456986719783343</v>
       </c>
       <c r="AD58">
         <v>23.880630870000001</v>
@@ -43364,7 +44131,7 @@
         <v>314.29854999999998</v>
       </c>
       <c r="D59">
-        <v>1143.5294120000001</v>
+        <v>1579.96</v>
       </c>
       <c r="E59">
         <v>6.84544</v>
@@ -43380,7 +44147,7 @@
       </c>
       <c r="I59" s="3">
         <f t="shared" si="5"/>
-        <v>13428.072727882794</v>
+        <v>13864.503315882794</v>
       </c>
       <c r="J59" s="3">
         <f t="shared" si="6"/>
@@ -43389,7 +44156,7 @@
       <c r="K59" s="7"/>
       <c r="L59" s="3">
         <f t="shared" si="7"/>
-        <v>55.983039395046426</v>
+        <v>57.802564154580516</v>
       </c>
       <c r="M59" s="3">
         <v>50.589850570000003</v>
@@ -43412,31 +44179,31 @@
       <c r="U59" s="7"/>
       <c r="V59" s="3">
         <f t="shared" si="11"/>
-        <v>80.428518811744894</v>
+        <v>77.89676812748003</v>
       </c>
       <c r="W59" s="3">
         <f t="shared" si="12"/>
-        <v>2.3406080408499208</v>
+        <v>2.2669297474215915</v>
       </c>
       <c r="X59" s="3">
         <f t="shared" si="13"/>
-        <v>8.5159608171134806</v>
+        <v>11.395720163953088</v>
       </c>
       <c r="Y59" s="3">
         <f t="shared" si="14"/>
-        <v>5.0978574056913986E-2</v>
+        <v>4.9373856704683049E-2</v>
       </c>
       <c r="Z59" s="3">
         <f t="shared" si="15"/>
-        <v>2.4451207178656471E-2</v>
+        <v>2.3681525461023922E-2</v>
       </c>
       <c r="AA59" s="3">
         <f t="shared" si="9"/>
-        <v>5.2882942652334304</v>
+        <v>5.1218279070012596</v>
       </c>
       <c r="AB59" s="3">
         <f t="shared" si="10"/>
-        <v>3.3511882838227045</v>
+        <v>3.2456986719783343</v>
       </c>
       <c r="AD59">
         <v>23.985965879999998</v>
@@ -43468,7 +44235,7 @@
         <v>314.29854999999998</v>
       </c>
       <c r="D60">
-        <v>1143.5294120000001</v>
+        <v>1579.96</v>
       </c>
       <c r="E60">
         <v>6.84544</v>
@@ -43484,7 +44251,7 @@
       </c>
       <c r="I60" s="3">
         <f t="shared" si="5"/>
-        <v>13428.072727882794</v>
+        <v>13864.503315882794</v>
       </c>
       <c r="J60" s="3">
         <f t="shared" si="6"/>
@@ -43493,7 +44260,7 @@
       <c r="K60" s="7"/>
       <c r="L60" s="3">
         <f t="shared" si="7"/>
-        <v>55.750456624231717</v>
+        <v>57.562422128057094</v>
       </c>
       <c r="M60" s="3">
         <v>49.515526360000003</v>
@@ -43516,31 +44283,31 @@
       <c r="U60" s="7"/>
       <c r="V60" s="3">
         <f t="shared" si="11"/>
-        <v>80.428518811744894</v>
+        <v>77.89676812748003</v>
       </c>
       <c r="W60" s="3">
         <f t="shared" si="12"/>
-        <v>2.3406080408499208</v>
+        <v>2.2669297474215915</v>
       </c>
       <c r="X60" s="3">
         <f t="shared" si="13"/>
-        <v>8.5159608171134806</v>
+        <v>11.395720163953088</v>
       </c>
       <c r="Y60" s="3">
         <f t="shared" si="14"/>
-        <v>5.0978574056913986E-2</v>
+        <v>4.9373856704683049E-2</v>
       </c>
       <c r="Z60" s="3">
         <f t="shared" si="15"/>
-        <v>2.4451207178656471E-2</v>
+        <v>2.3681525461023922E-2</v>
       </c>
       <c r="AA60" s="3">
         <f t="shared" si="9"/>
-        <v>5.2882942652334304</v>
+        <v>5.1218279070012596</v>
       </c>
       <c r="AB60" s="3">
         <f t="shared" si="10"/>
-        <v>3.3511882838227045</v>
+        <v>3.2456986719783343</v>
       </c>
       <c r="AD60">
         <v>24.08603183</v>
@@ -43572,7 +44339,7 @@
         <v>314.29854999999998</v>
       </c>
       <c r="D61">
-        <v>1143.5294120000001</v>
+        <v>1579.96</v>
       </c>
       <c r="E61">
         <v>6.84544</v>
@@ -43588,7 +44355,7 @@
       </c>
       <c r="I61" s="3">
         <f t="shared" si="5"/>
-        <v>13428.072727882794</v>
+        <v>13864.503315882794</v>
       </c>
       <c r="J61" s="3">
         <f t="shared" si="6"/>
@@ -43597,7 +44364,7 @@
       <c r="K61" s="7"/>
       <c r="L61" s="3">
         <f t="shared" si="7"/>
-        <v>55.530699784183319</v>
+        <v>57.335522892457007</v>
       </c>
       <c r="M61" s="3">
         <v>48.464016460000003</v>
@@ -43620,31 +44387,31 @@
       <c r="U61" s="7"/>
       <c r="V61" s="3">
         <f t="shared" si="11"/>
-        <v>80.428518811744894</v>
+        <v>77.89676812748003</v>
       </c>
       <c r="W61" s="3">
         <f t="shared" si="12"/>
-        <v>2.3406080408499208</v>
+        <v>2.2669297474215915</v>
       </c>
       <c r="X61" s="3">
         <f t="shared" si="13"/>
-        <v>8.5159608171134806</v>
+        <v>11.395720163953088</v>
       </c>
       <c r="Y61" s="3">
         <f t="shared" si="14"/>
-        <v>5.0978574056913986E-2</v>
+        <v>4.9373856704683049E-2</v>
       </c>
       <c r="Z61" s="3">
         <f t="shared" si="15"/>
-        <v>2.4451207178656471E-2</v>
+        <v>2.3681525461023922E-2</v>
       </c>
       <c r="AA61" s="3">
         <f t="shared" si="9"/>
-        <v>5.2882942652334304</v>
+        <v>5.1218279070012596</v>
       </c>
       <c r="AB61" s="3">
         <f t="shared" si="10"/>
-        <v>3.3511882838227045</v>
+        <v>3.2456986719783343</v>
       </c>
       <c r="AD61">
         <v>24.181349740000002</v>
@@ -43676,7 +44443,7 @@
         <v>314.29854999999998</v>
       </c>
       <c r="D62">
-        <v>1143.5294120000001</v>
+        <v>1579.96</v>
       </c>
       <c r="E62">
         <v>6.84544</v>
@@ -43692,7 +44459,7 @@
       </c>
       <c r="I62" s="3">
         <f t="shared" si="5"/>
-        <v>13428.072727882794</v>
+        <v>13864.503315882794</v>
       </c>
       <c r="J62" s="3">
         <f t="shared" si="6"/>
@@ -43701,7 +44468,7 @@
       <c r="K62" s="7"/>
       <c r="L62" s="3">
         <f t="shared" si="7"/>
-        <v>55.322471082941924</v>
+        <v>57.120526475820938</v>
       </c>
       <c r="M62" s="3">
         <v>47.43483638</v>
@@ -43724,31 +44491,31 @@
       <c r="U62" s="7"/>
       <c r="V62" s="3">
         <f t="shared" si="11"/>
-        <v>80.428518811744894</v>
+        <v>77.89676812748003</v>
       </c>
       <c r="W62" s="3">
         <f t="shared" si="12"/>
-        <v>2.3406080408499208</v>
+        <v>2.2669297474215915</v>
       </c>
       <c r="X62" s="3">
         <f t="shared" si="13"/>
-        <v>8.5159608171134806</v>
+        <v>11.395720163953088</v>
       </c>
       <c r="Y62" s="3">
         <f t="shared" si="14"/>
-        <v>5.0978574056913986E-2</v>
+        <v>4.9373856704683049E-2</v>
       </c>
       <c r="Z62" s="3">
         <f t="shared" si="15"/>
-        <v>2.4451207178656471E-2</v>
+        <v>2.3681525461023922E-2</v>
       </c>
       <c r="AA62" s="3">
         <f t="shared" si="9"/>
-        <v>5.2882942652334304</v>
+        <v>5.1218279070012596</v>
       </c>
       <c r="AB62" s="3">
         <f t="shared" si="10"/>
-        <v>3.3511882838227045</v>
+        <v>3.2456986719783343</v>
       </c>
       <c r="AD62">
         <v>24.272366120000001</v>
@@ -43780,7 +44547,7 @@
         <v>314.29854999999998</v>
       </c>
       <c r="D63">
-        <v>1143.5294120000001</v>
+        <v>1579.96</v>
       </c>
       <c r="E63">
         <v>6.84544</v>
@@ -43796,7 +44563,7 @@
       </c>
       <c r="I63" s="3">
         <f t="shared" si="5"/>
-        <v>13428.072727882794</v>
+        <v>13864.503315882794</v>
       </c>
       <c r="J63" s="3">
         <f t="shared" si="6"/>
@@ -43805,7 +44572,7 @@
       <c r="K63" s="7"/>
       <c r="L63" s="3">
         <f t="shared" si="7"/>
-        <v>55.124658190670168</v>
+        <v>56.916284396082183</v>
       </c>
       <c r="M63" s="3">
         <v>46.427511940000002</v>
@@ -43828,31 +44595,31 @@
       <c r="U63" s="7"/>
       <c r="V63" s="3">
         <f t="shared" si="11"/>
-        <v>80.428518811744894</v>
+        <v>77.89676812748003</v>
       </c>
       <c r="W63" s="3">
         <f t="shared" si="12"/>
-        <v>2.3406080408499208</v>
+        <v>2.2669297474215915</v>
       </c>
       <c r="X63" s="3">
         <f t="shared" si="13"/>
-        <v>8.5159608171134806</v>
+        <v>11.395720163953088</v>
       </c>
       <c r="Y63" s="3">
         <f t="shared" si="14"/>
-        <v>5.0978574056913986E-2</v>
+        <v>4.9373856704683049E-2</v>
       </c>
       <c r="Z63" s="3">
         <f t="shared" si="15"/>
-        <v>2.4451207178656471E-2</v>
+        <v>2.3681525461023922E-2</v>
       </c>
       <c r="AA63" s="3">
         <f t="shared" si="9"/>
-        <v>5.2882942652334304</v>
+        <v>5.1218279070012596</v>
       </c>
       <c r="AB63" s="3">
         <f t="shared" si="10"/>
-        <v>3.3511882838227045</v>
+        <v>3.2456986719783343</v>
       </c>
       <c r="AD63">
         <v>24.359466650000002</v>
@@ -43887,7 +44654,7 @@
         <v>314.29854999999998</v>
       </c>
       <c r="D64">
-        <v>1143.5294120000001</v>
+        <v>1579.96</v>
       </c>
       <c r="E64">
         <v>6.84544</v>
@@ -43903,7 +44670,7 @@
       </c>
       <c r="I64" s="3">
         <f t="shared" si="5"/>
-        <v>13428.072727882794</v>
+        <v>13864.503315882794</v>
       </c>
       <c r="J64" s="3">
         <f t="shared" si="6"/>
@@ -43912,7 +44679,7 @@
       <c r="K64" s="7"/>
       <c r="L64" s="3">
         <f t="shared" si="7"/>
-        <v>54.936300854763807</v>
+        <v>56.7218051911236</v>
       </c>
       <c r="M64" s="3">
         <v>45.441578999999997</v>
@@ -43935,31 +44702,31 @@
       <c r="U64" s="7"/>
       <c r="V64" s="3">
         <f t="shared" si="11"/>
-        <v>80.428518811744894</v>
+        <v>77.89676812748003</v>
       </c>
       <c r="W64" s="3">
         <f t="shared" si="12"/>
-        <v>2.3406080408499208</v>
+        <v>2.2669297474215915</v>
       </c>
       <c r="X64" s="3">
         <f t="shared" si="13"/>
-        <v>8.5159608171134806</v>
+        <v>11.395720163953088</v>
       </c>
       <c r="Y64" s="3">
         <f t="shared" si="14"/>
-        <v>5.0978574056913986E-2</v>
+        <v>4.9373856704683049E-2</v>
       </c>
       <c r="Z64" s="3">
         <f t="shared" si="15"/>
-        <v>2.4451207178656471E-2</v>
+        <v>2.3681525461023922E-2</v>
       </c>
       <c r="AA64" s="3">
         <f t="shared" si="9"/>
-        <v>5.2882942652334304</v>
+        <v>5.1218279070012596</v>
       </c>
       <c r="AB64" s="3">
         <f t="shared" si="10"/>
-        <v>3.3511882838227045</v>
+        <v>3.2456986719783343</v>
       </c>
       <c r="AD64">
         <v>24.442986730000001</v>
@@ -43991,7 +44758,7 @@
         <v>314.29854999999998</v>
       </c>
       <c r="D65">
-        <v>1143.5294120000001</v>
+        <v>1579.96</v>
       </c>
       <c r="E65">
         <v>6.84544</v>
@@ -44007,7 +44774,7 @@
       </c>
       <c r="I65" s="3">
         <f t="shared" si="5"/>
-        <v>13428.072727882794</v>
+        <v>13864.503315882794</v>
       </c>
       <c r="J65" s="3">
         <f t="shared" si="6"/>
@@ -44016,7 +44783,7 @@
       <c r="K65" s="7"/>
       <c r="L65" s="3">
         <f t="shared" si="7"/>
-        <v>54.756564300621193</v>
+        <v>56.536226955036064</v>
       </c>
       <c r="M65" s="3">
         <v>44.476583300000001</v>
@@ -44039,31 +44806,31 @@
       <c r="U65" s="7"/>
       <c r="V65" s="3">
         <f t="shared" si="11"/>
-        <v>80.428518811744894</v>
+        <v>77.89676812748003</v>
       </c>
       <c r="W65" s="3">
         <f t="shared" si="12"/>
-        <v>2.3406080408499208</v>
+        <v>2.2669297474215915</v>
       </c>
       <c r="X65" s="3">
         <f t="shared" si="13"/>
-        <v>8.5159608171134806</v>
+        <v>11.395720163953088</v>
       </c>
       <c r="Y65" s="3">
         <f t="shared" si="14"/>
-        <v>5.0978574056913986E-2</v>
+        <v>4.9373856704683049E-2</v>
       </c>
       <c r="Z65" s="3">
         <f t="shared" si="15"/>
-        <v>2.4451207178656471E-2</v>
+        <v>2.3681525461023922E-2</v>
       </c>
       <c r="AA65" s="3">
         <f t="shared" si="9"/>
-        <v>5.2882942652334304</v>
+        <v>5.1218279070012596</v>
       </c>
       <c r="AB65" s="3">
         <f t="shared" si="10"/>
-        <v>3.3511882838227045</v>
+        <v>3.2456986719783343</v>
       </c>
       <c r="AD65">
         <v>24.523219999999998</v>
@@ -44095,7 +44862,7 @@
         <v>314.29854999999998</v>
       </c>
       <c r="D66">
-        <v>1143.5294120000001</v>
+        <v>1579.96</v>
       </c>
       <c r="E66">
         <v>6.84544</v>
@@ -44111,7 +44878,7 @@
       </c>
       <c r="I66" s="3">
         <f t="shared" si="5"/>
-        <v>13428.072727882794</v>
+        <v>13864.503315882794</v>
       </c>
       <c r="J66" s="3">
         <f t="shared" si="6"/>
@@ -44120,7 +44887,7 @@
       <c r="K66" s="7"/>
       <c r="L66" s="3">
         <f t="shared" si="7"/>
-        <v>54.584718555539922</v>
+        <v>56.358795990013633</v>
       </c>
       <c r="M66" s="3">
         <v>43.532080209999997</v>
@@ -44143,31 +44910,31 @@
       <c r="U66" s="7"/>
       <c r="V66" s="3">
         <f t="shared" si="11"/>
-        <v>80.428518811744894</v>
+        <v>77.89676812748003</v>
       </c>
       <c r="W66" s="3">
         <f t="shared" si="12"/>
-        <v>2.3406080408499208</v>
+        <v>2.2669297474215915</v>
       </c>
       <c r="X66" s="3">
         <f t="shared" si="13"/>
-        <v>8.5159608171134806</v>
+        <v>11.395720163953088</v>
       </c>
       <c r="Y66" s="3">
         <f t="shared" si="14"/>
-        <v>5.0978574056913986E-2</v>
+        <v>4.9373856704683049E-2</v>
       </c>
       <c r="Z66" s="3">
         <f t="shared" si="15"/>
-        <v>2.4451207178656471E-2</v>
+        <v>2.3681525461023922E-2</v>
       </c>
       <c r="AA66" s="3">
         <f t="shared" si="9"/>
-        <v>5.2882942652334304</v>
+        <v>5.1218279070012596</v>
       </c>
       <c r="AB66" s="3">
         <f t="shared" si="10"/>
-        <v>3.3511882838227045</v>
+        <v>3.2456986719783343</v>
       </c>
       <c r="AD66">
         <v>24.600424960000002</v>
@@ -44199,7 +44966,7 @@
         <v>314.29854999999998</v>
       </c>
       <c r="D67">
-        <v>1143.5294120000001</v>
+        <v>1579.96</v>
       </c>
       <c r="E67">
         <v>6.84544</v>
@@ -44215,7 +44982,7 @@
       </c>
       <c r="I67" s="3">
         <f t="shared" si="5"/>
-        <v>13428.072727882794</v>
+        <v>13864.503315882794</v>
       </c>
       <c r="J67" s="3">
         <f t="shared" si="6"/>
@@ -44224,7 +44991,7 @@
       <c r="K67" s="7"/>
       <c r="L67" s="3">
         <f t="shared" si="7"/>
-        <v>54.420121657414846</v>
+        <v>56.188849469311485</v>
       </c>
       <c r="M67" s="3">
         <v>42.60763455</v>
@@ -44247,31 +45014,31 @@
       <c r="U67" s="7"/>
       <c r="V67" s="3">
         <f t="shared" si="11"/>
-        <v>80.428518811744894</v>
+        <v>77.89676812748003</v>
       </c>
       <c r="W67" s="3">
         <f t="shared" si="12"/>
-        <v>2.3406080408499208</v>
+        <v>2.2669297474215915</v>
       </c>
       <c r="X67" s="3">
         <f t="shared" si="13"/>
-        <v>8.5159608171134806</v>
+        <v>11.395720163953088</v>
       </c>
       <c r="Y67" s="3">
         <f t="shared" si="14"/>
-        <v>5.0978574056913986E-2</v>
+        <v>4.9373856704683049E-2</v>
       </c>
       <c r="Z67" s="3">
         <f t="shared" si="15"/>
-        <v>2.4451207178656471E-2</v>
+        <v>2.3681525461023922E-2</v>
       </c>
       <c r="AA67" s="3">
         <f t="shared" si="9"/>
-        <v>5.2882942652334304</v>
+        <v>5.1218279070012596</v>
       </c>
       <c r="AB67" s="3">
         <f t="shared" si="10"/>
-        <v>3.3511882838227045</v>
+        <v>3.2456986719783343</v>
       </c>
       <c r="AD67">
         <v>24.674830409999998</v>
@@ -44303,7 +45070,7 @@
         <v>314.29854999999998</v>
       </c>
       <c r="D68">
-        <v>1143.5294120000001</v>
+        <v>1579.96</v>
       </c>
       <c r="E68">
         <v>6.84544</v>
@@ -44319,7 +45086,7 @@
       </c>
       <c r="I68" s="3">
         <f t="shared" si="5"/>
-        <v>13428.072727882794</v>
+        <v>13864.503315882794</v>
       </c>
       <c r="J68" s="3">
         <f t="shared" si="6"/>
@@ -44328,7 +45095,7 @@
       <c r="K68" s="7"/>
       <c r="L68" s="3">
         <f t="shared" si="7"/>
-        <v>54.262206051291081</v>
+        <v>56.025801391668416</v>
       </c>
       <c r="M68" s="3">
         <v>41.702820389999999</v>
@@ -44351,31 +45118,31 @@
       <c r="U68" s="7"/>
       <c r="V68" s="3">
         <f t="shared" si="11"/>
-        <v>80.428518811744894</v>
+        <v>77.89676812748003</v>
       </c>
       <c r="W68" s="3">
         <f t="shared" si="12"/>
-        <v>2.3406080408499208</v>
+        <v>2.2669297474215915</v>
       </c>
       <c r="X68" s="3">
         <f t="shared" si="13"/>
-        <v>8.5159608171134806</v>
+        <v>11.395720163953088</v>
       </c>
       <c r="Y68" s="3">
         <f t="shared" si="14"/>
-        <v>5.0978574056913986E-2</v>
+        <v>4.9373856704683049E-2</v>
       </c>
       <c r="Z68" s="3">
         <f t="shared" si="15"/>
-        <v>2.4451207178656471E-2</v>
+        <v>2.3681525461023922E-2</v>
       </c>
       <c r="AA68" s="3">
         <f t="shared" si="9"/>
-        <v>5.2882942652334304</v>
+        <v>5.1218279070012596</v>
       </c>
       <c r="AB68" s="3">
         <f t="shared" si="10"/>
-        <v>3.3511882838227045</v>
+        <v>3.2456986719783343</v>
       </c>
       <c r="AD68">
         <v>24.746639890000001</v>
@@ -44410,7 +45177,7 @@
         <v>314.29854999999998</v>
       </c>
       <c r="D69">
-        <v>1143.5294120000001</v>
+        <v>1579.96</v>
       </c>
       <c r="E69">
         <v>6.84544</v>
@@ -44426,7 +45193,7 @@
       </c>
       <c r="I69" s="3">
         <f t="shared" si="5"/>
-        <v>13428.072727882794</v>
+        <v>13864.503315882794</v>
       </c>
       <c r="J69" s="3">
         <f t="shared" si="6"/>
@@ -44435,7 +45202,7 @@
       <c r="K69" s="7"/>
       <c r="L69" s="3">
         <f t="shared" si="7"/>
-        <v>54.110467679537329</v>
+        <v>55.869131316896024</v>
       </c>
       <c r="M69" s="3">
         <v>40.817220829999997</v>
@@ -44458,31 +45225,31 @@
       <c r="U69" s="7"/>
       <c r="V69" s="3">
         <f t="shared" si="11"/>
-        <v>80.428518811744894</v>
+        <v>77.89676812748003</v>
       </c>
       <c r="W69" s="3">
         <f t="shared" si="12"/>
-        <v>2.3406080408499208</v>
+        <v>2.2669297474215915</v>
       </c>
       <c r="X69" s="3">
         <f t="shared" si="13"/>
-        <v>8.5159608171134806</v>
+        <v>11.395720163953088</v>
       </c>
       <c r="Y69" s="3">
         <f t="shared" si="14"/>
-        <v>5.0978574056913986E-2</v>
+        <v>4.9373856704683049E-2</v>
       </c>
       <c r="Z69" s="3">
         <f t="shared" si="15"/>
-        <v>2.4451207178656471E-2</v>
+        <v>2.3681525461023922E-2</v>
       </c>
       <c r="AA69" s="3">
         <f t="shared" si="9"/>
-        <v>5.2882942652334304</v>
+        <v>5.1218279070012596</v>
       </c>
       <c r="AB69" s="3">
         <f t="shared" si="10"/>
-        <v>3.3511882838227045</v>
+        <v>3.2456986719783343</v>
       </c>
       <c r="AD69">
         <v>24.816035240000001</v>
@@ -44514,7 +45281,7 @@
         <v>314.29854999999998</v>
       </c>
       <c r="D70">
-        <v>1143.5294120000001</v>
+        <v>1579.96</v>
       </c>
       <c r="E70">
         <v>6.84544</v>
@@ -44530,7 +45297,7 @@
       </c>
       <c r="I70" s="3">
         <f t="shared" si="5"/>
-        <v>13428.072727882794</v>
+        <v>13864.503315882794</v>
       </c>
       <c r="J70" s="3">
         <f t="shared" si="6"/>
@@ -44539,7 +45306,7 @@
       <c r="K70" s="7"/>
       <c r="L70" s="3">
         <f t="shared" si="7"/>
-        <v>53.964456845739697</v>
+        <v>55.718374932836639</v>
       </c>
       <c r="M70" s="3">
         <v>39.950427830000002</v>
@@ -44562,31 +45329,31 @@
       <c r="U70" s="7"/>
       <c r="V70" s="3">
         <f t="shared" si="11"/>
-        <v>80.428518811744894</v>
+        <v>77.89676812748003</v>
       </c>
       <c r="W70" s="3">
         <f t="shared" si="12"/>
-        <v>2.3406080408499208</v>
+        <v>2.2669297474215915</v>
       </c>
       <c r="X70" s="3">
         <f t="shared" si="13"/>
-        <v>8.5159608171134806</v>
+        <v>11.395720163953088</v>
       </c>
       <c r="Y70" s="3">
         <f t="shared" si="14"/>
-        <v>5.0978574056913986E-2</v>
+        <v>4.9373856704683049E-2</v>
       </c>
       <c r="Z70" s="3">
         <f t="shared" si="15"/>
-        <v>2.4451207178656471E-2</v>
+        <v>2.3681525461023922E-2</v>
       </c>
       <c r="AA70" s="3">
         <f t="shared" si="9"/>
-        <v>5.2882942652334304</v>
+        <v>5.1218279070012596</v>
       </c>
       <c r="AB70" s="3">
         <f t="shared" si="10"/>
-        <v>3.3511882838227045</v>
+        <v>3.2456986719783343</v>
       </c>
       <c r="AD70">
         <v>24.88317962</v>
@@ -44618,7 +45385,7 @@
         <v>314.29854999999998</v>
       </c>
       <c r="D71">
-        <v>1143.5294120000001</v>
+        <v>1579.96</v>
       </c>
       <c r="E71">
         <v>6.84544</v>
@@ -44634,7 +45401,7 @@
       </c>
       <c r="I71" s="3">
         <f t="shared" si="5"/>
-        <v>13428.072727882794</v>
+        <v>13864.503315882794</v>
       </c>
       <c r="J71" s="3">
         <f t="shared" si="6"/>
@@ -44643,7 +45410,7 @@
       <c r="K71" s="7"/>
       <c r="L71" s="3">
         <f t="shared" si="7"/>
-        <v>53.823770683842042</v>
+        <v>55.573116279740525</v>
       </c>
       <c r="M71" s="3">
         <v>39.102042009999998</v>
@@ -44666,31 +45433,31 @@
       <c r="U71" s="7"/>
       <c r="V71" s="3">
         <f t="shared" si="11"/>
-        <v>80.428518811744894</v>
+        <v>77.89676812748003</v>
       </c>
       <c r="W71" s="3">
         <f t="shared" si="12"/>
-        <v>2.3406080408499208</v>
+        <v>2.2669297474215915</v>
       </c>
       <c r="X71" s="3">
         <f t="shared" si="13"/>
-        <v>8.5159608171134806</v>
+        <v>11.395720163953088</v>
       </c>
       <c r="Y71" s="3">
         <f t="shared" si="14"/>
-        <v>5.0978574056913986E-2</v>
+        <v>4.9373856704683049E-2</v>
       </c>
       <c r="Z71" s="3">
         <f t="shared" si="15"/>
-        <v>2.4451207178656471E-2</v>
+        <v>2.3681525461023922E-2</v>
       </c>
       <c r="AA71" s="3">
         <f t="shared" si="9"/>
-        <v>5.2882942652334304</v>
+        <v>5.1218279070012596</v>
       </c>
       <c r="AB71" s="3">
         <f t="shared" si="10"/>
-        <v>3.3511882838227045</v>
+        <v>3.2456986719783343</v>
       </c>
       <c r="AD71">
         <v>24.94822001</v>
@@ -44722,7 +45489,7 @@
         <v>314.29854999999998</v>
       </c>
       <c r="D72">
-        <v>1143.5294120000001</v>
+        <v>1579.96</v>
       </c>
       <c r="E72">
         <v>6.84544</v>
@@ -44738,7 +45505,7 @@
       </c>
       <c r="I72" s="3">
         <f t="shared" si="5"/>
-        <v>13428.072727882794</v>
+        <v>13864.503315882794</v>
       </c>
       <c r="J72" s="3">
         <f t="shared" si="6"/>
@@ -44747,7 +45514,7 @@
       <c r="K72" s="7"/>
       <c r="L72" s="3">
         <f t="shared" si="7"/>
-        <v>53.688046957216272</v>
+        <v>55.432981347797572</v>
       </c>
       <c r="M72" s="3">
         <v>38.271672479999999</v>
@@ -44770,31 +45537,31 @@
       <c r="U72" s="7"/>
       <c r="V72" s="3">
         <f t="shared" si="11"/>
-        <v>80.428518811744894</v>
+        <v>77.89676812748003</v>
       </c>
       <c r="W72" s="3">
         <f t="shared" si="12"/>
-        <v>2.3406080408499208</v>
+        <v>2.2669297474215915</v>
       </c>
       <c r="X72" s="3">
         <f t="shared" si="13"/>
-        <v>8.5159608171134806</v>
+        <v>11.395720163953088</v>
       </c>
       <c r="Y72" s="3">
         <f t="shared" si="14"/>
-        <v>5.0978574056913986E-2</v>
+        <v>4.9373856704683049E-2</v>
       </c>
       <c r="Z72" s="3">
         <f t="shared" si="15"/>
-        <v>2.4451207178656471E-2</v>
+        <v>2.3681525461023922E-2</v>
       </c>
       <c r="AA72" s="3">
         <f t="shared" si="9"/>
-        <v>5.2882942652334304</v>
+        <v>5.1218279070012596</v>
       </c>
       <c r="AB72" s="3">
         <f t="shared" si="10"/>
-        <v>3.3511882838227045</v>
+        <v>3.2456986719783343</v>
       </c>
       <c r="AD72">
         <v>25.011289269999999</v>
@@ -44826,7 +45593,7 @@
         <v>314.29854999999998</v>
       </c>
       <c r="D73">
-        <v>1143.5294120000001</v>
+        <v>1579.96</v>
       </c>
       <c r="E73">
         <v>6.84544</v>
@@ -44842,7 +45609,7 @@
       </c>
       <c r="I73" s="3">
         <f t="shared" si="5"/>
-        <v>13428.072727882794</v>
+        <v>13864.503315882794</v>
       </c>
       <c r="J73" s="3">
         <f t="shared" si="6"/>
@@ -44851,7 +45618,7 @@
       <c r="K73" s="7"/>
       <c r="L73" s="3">
         <f t="shared" si="7"/>
-        <v>53.556958785631082</v>
+        <v>55.297632632725303</v>
       </c>
       <c r="M73" s="3">
         <v>37.458936649999998</v>
@@ -44876,31 +45643,31 @@
       <c r="U73" s="7"/>
       <c r="V73" s="3">
         <f t="shared" si="11"/>
-        <v>80.428518811744894</v>
+        <v>77.89676812748003</v>
       </c>
       <c r="W73" s="3">
         <f t="shared" si="12"/>
-        <v>2.3406080408499208</v>
+        <v>2.2669297474215915</v>
       </c>
       <c r="X73" s="3">
         <f t="shared" si="13"/>
-        <v>8.5159608171134806</v>
+        <v>11.395720163953088</v>
       </c>
       <c r="Y73" s="3">
         <f t="shared" si="14"/>
-        <v>5.0978574056913986E-2</v>
+        <v>4.9373856704683049E-2</v>
       </c>
       <c r="Z73" s="3">
         <f t="shared" si="15"/>
-        <v>2.4451207178656471E-2</v>
+        <v>2.3681525461023922E-2</v>
       </c>
       <c r="AA73" s="3">
         <f t="shared" si="9"/>
-        <v>5.2882942652334304</v>
+        <v>5.1218279070012596</v>
       </c>
       <c r="AB73" s="3">
         <f t="shared" si="10"/>
-        <v>3.3511882838227045</v>
+        <v>3.2456986719783343</v>
       </c>
       <c r="AD73">
         <v>25.072507909999999</v>
@@ -44972,25 +45739,25 @@
       <c r="A2">
         <v>2000</v>
       </c>
-      <c r="B2" s="9">
+      <c r="B2" s="8">
         <v>63.351635578919343</v>
       </c>
-      <c r="C2" s="9">
+      <c r="C2" s="8">
         <v>6.0599233268856629</v>
       </c>
-      <c r="D2" s="9">
+      <c r="D2" s="8">
         <v>19.274436295221182</v>
       </c>
-      <c r="E2" s="9">
+      <c r="E2" s="8">
         <v>4.2572299109033797E-2</v>
       </c>
-      <c r="F2" s="9">
+      <c r="F2" s="8">
         <v>0.35911327139593108</v>
       </c>
-      <c r="G2" s="9">
+      <c r="G2" s="8">
         <v>6.6994354624707197</v>
       </c>
-      <c r="H2" s="9">
+      <c r="H2" s="8">
         <v>4.2128837659981357</v>
       </c>
     </row>
@@ -44998,25 +45765,25 @@
       <c r="A3">
         <v>2025</v>
       </c>
-      <c r="B3" s="9">
+      <c r="B3" s="8">
         <v>78.693850826255158</v>
       </c>
-      <c r="C3" s="9">
+      <c r="C3" s="8">
         <v>2.5548959209616982</v>
       </c>
-      <c r="D3" s="9">
+      <c r="D3" s="8">
         <v>9.129688688330905</v>
       </c>
-      <c r="E3" s="9">
+      <c r="E3" s="8">
         <v>6.2314654674512852E-2</v>
       </c>
-      <c r="F3" s="9">
+      <c r="F3" s="8">
         <v>2.4965100630913912E-2</v>
       </c>
-      <c r="G3" s="9">
+      <c r="G3" s="8">
         <v>5.8845562319040843</v>
       </c>
-      <c r="H3" s="9">
+      <c r="H3" s="8">
         <v>3.6497285772427279</v>
       </c>
     </row>
@@ -48020,19 +48787,19 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8" t="s">
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
@@ -48098,7 +48865,7 @@
       </c>
       <c r="D3">
         <f>'mass per m2'!D32/1000</f>
-        <v>2.0013003899999999</v>
+        <v>2.2506500000000003</v>
       </c>
       <c r="E3">
         <v>5.3760000000000003</v>
@@ -48151,7 +48918,7 @@
       </c>
       <c r="D4">
         <f>'mass per m2'!D33/1000</f>
-        <v>1.9871506589999999</v>
+        <v>1.8851199999999999</v>
       </c>
       <c r="E4">
         <v>5.3760000000000003</v>
@@ -48204,7 +48971,7 @@
       </c>
       <c r="D5">
         <f>'mass per m2'!D34/1000</f>
-        <v>1.9665931299999999</v>
+        <v>1.9236300000000002</v>
       </c>
       <c r="E5">
         <v>5.3760000000000003</v>
@@ -48257,7 +49024,7 @@
       </c>
       <c r="D6">
         <f>'mass per m2'!D35/1000</f>
-        <v>1.9629861980000001</v>
+        <v>1.85331</v>
       </c>
       <c r="E6">
         <v>5.3760000000000003</v>
@@ -48310,7 +49077,7 @@
       </c>
       <c r="D7">
         <f>'mass per m2'!D36/1000</f>
-        <v>1.619458128</v>
+        <v>1.64114</v>
       </c>
       <c r="E7">
         <v>5.3760000000000003</v>
@@ -48363,7 +49130,7 @@
       </c>
       <c r="D8">
         <f>'mass per m2'!D37/1000</f>
-        <v>1.592739726</v>
+        <v>1.8393199999999998</v>
       </c>
       <c r="E8">
         <v>5.3760000000000003</v>
@@ -48416,7 +49183,7 @@
       </c>
       <c r="D9">
         <f>'mass per m2'!D38/1000</f>
-        <v>1.495242424</v>
+        <v>1.6882300000000001</v>
       </c>
       <c r="E9">
         <v>5.7881600000000004</v>
@@ -48469,7 +49236,7 @@
       </c>
       <c r="D10">
         <f>'mass per m2'!D39/1000</f>
-        <v>1.4125263159999999</v>
+        <v>1.6708900000000002</v>
       </c>
       <c r="E10">
         <v>6.2003199999999996</v>
@@ -48522,7 +49289,7 @@
       </c>
       <c r="D11">
         <f>'mass per m2'!D40/1000</f>
-        <v>1.379820896</v>
+        <v>1.6153299999999999</v>
       </c>
       <c r="E11">
         <v>7.2038399999999996</v>
@@ -48575,7 +49342,7 @@
       </c>
       <c r="D12">
         <f>'mass per m2'!D41/1000</f>
-        <v>1.3616666669999999</v>
+        <v>1.55301</v>
       </c>
       <c r="E12">
         <v>7.45472</v>
@@ -48628,7 +49395,7 @@
       </c>
       <c r="D13">
         <f>'mass per m2'!D42/1000</f>
-        <v>1.3436470589999998</v>
+        <v>1.57385</v>
       </c>
       <c r="E13">
         <v>8.26112</v>
@@ -48681,7 +49448,7 @@
       </c>
       <c r="D14">
         <f>'mass per m2'!D43/1000</f>
-        <v>1.3436470589999998</v>
+        <v>1.57996</v>
       </c>
       <c r="E14">
         <v>8.2252799999999997</v>
@@ -48734,7 +49501,7 @@
       </c>
       <c r="D15">
         <f>'mass per m2'!D44/1000</f>
-        <v>1.2721764710000001</v>
+        <v>1.57996</v>
       </c>
       <c r="E15">
         <v>8.2700800000000001</v>
@@ -48787,7 +49554,7 @@
       </c>
       <c r="D16">
         <f>'mass per m2'!D45/1000</f>
-        <v>1.2507352940000001</v>
+        <v>1.57996</v>
       </c>
       <c r="E16">
         <v>8.3148800000000005</v>
@@ -48840,7 +49607,7 @@
       </c>
       <c r="D17">
         <f>'mass per m2'!D46/1000</f>
-        <v>1.2292941180000001</v>
+        <v>1.57996</v>
       </c>
       <c r="E17">
         <v>8.3865599999999993</v>
@@ -48893,7 +49660,7 @@
       </c>
       <c r="D18">
         <f>'mass per m2'!D47/1000</f>
-        <v>1.2150000000000001</v>
+        <v>1.57996</v>
       </c>
       <c r="E18">
         <v>8.45824</v>
@@ -48946,7 +49713,7 @@
       </c>
       <c r="D19">
         <f>'mass per m2'!D48/1000</f>
-        <v>1.2007058820000001</v>
+        <v>1.57996</v>
       </c>
       <c r="E19">
         <v>8.1954133329999994</v>
@@ -48999,7 +49766,7 @@
       </c>
       <c r="D20">
         <f>'mass per m2'!D49/1000</f>
-        <v>1.1911764709999999</v>
+        <v>1.57996</v>
       </c>
       <c r="E20">
         <v>7.9325866669999998</v>
@@ -49052,7 +49819,7 @@
       </c>
       <c r="D21">
         <f>'mass per m2'!D50/1000</f>
-        <v>1.1816470589999999</v>
+        <v>1.57996</v>
       </c>
       <c r="E21">
         <v>7.6697600000000001</v>
@@ -49105,7 +49872,7 @@
       </c>
       <c r="D22">
         <f>'mass per m2'!D51/1000</f>
-        <v>1.1721176470000001</v>
+        <v>1.57996</v>
       </c>
       <c r="E22">
         <v>7.3949866670000004</v>
@@ -49158,7 +49925,7 @@
       </c>
       <c r="D23">
         <f>'mass per m2'!D52/1000</f>
-        <v>1.1625882349999999</v>
+        <v>1.57996</v>
       </c>
       <c r="E23">
         <v>7.1202133329999997</v>
@@ -49211,7 +49978,7 @@
       </c>
       <c r="D24">
         <f>'mass per m2'!D53/1000</f>
-        <v>1.1530588239999999</v>
+        <v>1.57996</v>
       </c>
       <c r="E24">
         <v>6.84544</v>
@@ -49264,7 +50031,7 @@
       </c>
       <c r="D25">
         <f>'mass per m2'!D54/1000</f>
-        <v>1.1435294120000001</v>
+        <v>1.57996</v>
       </c>
       <c r="E25">
         <v>6.84544</v>
@@ -49317,7 +50084,7 @@
       </c>
       <c r="D26">
         <f>'mass per m2'!D55/1000</f>
-        <v>1.1435294120000001</v>
+        <v>1.57996</v>
       </c>
       <c r="E26">
         <v>6.84544</v>
@@ -49370,7 +50137,7 @@
       </c>
       <c r="D27">
         <f>'mass per m2'!D56/1000</f>
-        <v>1.1435294120000001</v>
+        <v>1.57996</v>
       </c>
       <c r="E27">
         <v>6.84544</v>
@@ -49423,7 +50190,7 @@
       </c>
       <c r="D28">
         <f>'mass per m2'!D57/1000</f>
-        <v>1.1435294120000001</v>
+        <v>1.57996</v>
       </c>
       <c r="E28">
         <v>6.84544</v>
@@ -49476,7 +50243,7 @@
       </c>
       <c r="D29">
         <f>'mass per m2'!D58/1000</f>
-        <v>1.1435294120000001</v>
+        <v>1.57996</v>
       </c>
       <c r="E29">
         <v>6.84544</v>
@@ -49529,7 +50296,7 @@
       </c>
       <c r="D30">
         <f>'mass per m2'!D59/1000</f>
-        <v>1.1435294120000001</v>
+        <v>1.57996</v>
       </c>
       <c r="E30">
         <v>6.84544</v>
@@ -49582,7 +50349,7 @@
       </c>
       <c r="D31">
         <f>'mass per m2'!D60/1000</f>
-        <v>1.1435294120000001</v>
+        <v>1.57996</v>
       </c>
       <c r="E31">
         <v>6.84544</v>
@@ -49635,7 +50402,7 @@
       </c>
       <c r="D32">
         <f>'mass per m2'!D61/1000</f>
-        <v>1.1435294120000001</v>
+        <v>1.57996</v>
       </c>
       <c r="E32">
         <v>6.84544</v>
@@ -49688,7 +50455,7 @@
       </c>
       <c r="D33">
         <f>'mass per m2'!D62/1000</f>
-        <v>1.1435294120000001</v>
+        <v>1.57996</v>
       </c>
       <c r="E33">
         <v>6.84544</v>
@@ -49741,7 +50508,7 @@
       </c>
       <c r="D34">
         <f>'mass per m2'!D63/1000</f>
-        <v>1.1435294120000001</v>
+        <v>1.57996</v>
       </c>
       <c r="E34">
         <v>6.84544</v>
@@ -49794,7 +50561,7 @@
       </c>
       <c r="D35">
         <f>'mass per m2'!D64/1000</f>
-        <v>1.1435294120000001</v>
+        <v>1.57996</v>
       </c>
       <c r="E35">
         <v>6.84544</v>
@@ -49847,7 +50614,7 @@
       </c>
       <c r="D36">
         <f>'mass per m2'!D65/1000</f>
-        <v>1.1435294120000001</v>
+        <v>1.57996</v>
       </c>
       <c r="E36">
         <v>6.84544</v>
@@ -49915,7 +50682,7 @@
       </c>
       <c r="D37">
         <f>'mass per m2'!D66/1000</f>
-        <v>1.1435294120000001</v>
+        <v>1.57996</v>
       </c>
       <c r="E37">
         <v>6.84544</v>
@@ -49986,7 +50753,7 @@
       </c>
       <c r="D38">
         <f>'mass per m2'!D67/1000</f>
-        <v>1.1435294120000001</v>
+        <v>1.57996</v>
       </c>
       <c r="E38">
         <v>6.84544</v>
@@ -50057,7 +50824,7 @@
       </c>
       <c r="D39">
         <f>'mass per m2'!D68/1000</f>
-        <v>1.1435294120000001</v>
+        <v>1.57996</v>
       </c>
       <c r="E39">
         <v>6.84544</v>
@@ -50128,7 +50895,7 @@
       </c>
       <c r="D40">
         <f>'mass per m2'!D69/1000</f>
-        <v>1.1435294120000001</v>
+        <v>1.57996</v>
       </c>
       <c r="E40">
         <v>6.84544</v>
@@ -50181,7 +50948,7 @@
       </c>
       <c r="D41">
         <f>'mass per m2'!D70/1000</f>
-        <v>1.1435294120000001</v>
+        <v>1.57996</v>
       </c>
       <c r="E41">
         <v>6.84544</v>
@@ -50234,7 +51001,7 @@
       </c>
       <c r="D42">
         <f>'mass per m2'!D71/1000</f>
-        <v>1.1435294120000001</v>
+        <v>1.57996</v>
       </c>
       <c r="E42">
         <v>6.84544</v>
@@ -50287,7 +51054,7 @@
       </c>
       <c r="D43">
         <f>'mass per m2'!D72/1000</f>
-        <v>1.1435294120000001</v>
+        <v>1.57996</v>
       </c>
       <c r="E43">
         <v>6.84544</v>
@@ -50340,7 +51107,7 @@
       </c>
       <c r="D44">
         <f>'mass per m2'!D73/1000</f>
-        <v>1.1435294120000001</v>
+        <v>1.57996</v>
       </c>
       <c r="E44">
         <v>6.84544</v>
